--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -781,19 +781,19 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="Q2" t="n">
         <v>1.57</v>
       </c>
       <c r="R2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
         <v>2.4</v>
@@ -802,7 +802,7 @@
         <v>1.65</v>
       </c>
       <c r="U2" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
@@ -820,7 +820,7 @@
         <v>46</v>
       </c>
       <c r="AA2" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
         <v>12.5</v>
@@ -856,13 +856,13 @@
         <v>27</v>
       </c>
       <c r="AM2" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN2" t="n">
         <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
@@ -871,10 +871,10 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -910,17 +910,17 @@
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BF2" t="n">
         <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.5</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>1.34</v>
       </c>
       <c r="H5" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I5" t="n">
         <v>19</v>
@@ -1369,7 +1369,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
         <v>1.96</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1542,10 +1542,10 @@
         <v>2.98</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
         <v>3.9</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1927,7 +1927,7 @@
         <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
         <v>3.35</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.3</v>
+        <v>1.95</v>
       </c>
       <c r="G15" t="n">
         <v>2.54</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5094,7 +5094,7 @@
         <v>8.4</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD24" t="n">
         <v>16</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K25" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5252,7 +5252,7 @@
         <v>1.79</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -6025,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="Q29" t="n">
         <v>1.86</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -760,16 +760,16 @@
         <v>1.65</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>1000</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>1.29</v>
       </c>
       <c r="I2" t="n">
         <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>1.23</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
@@ -778,149 +778,149 @@
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>1.25</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>1.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>1.15</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.01</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AS2" t="n">
-        <v>12.5</v>
+        <v>80</v>
       </c>
       <c r="AT2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="AX2" t="n">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="AY2" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="BA2" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>44</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="n">
         <v>630</v>
@@ -960,10 +960,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>760</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="K3" t="n">
         <v>690</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.18</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>1.01</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1.34</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>15.5</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>6.4</v>
+        <v>1000</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.46</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>2.98</v>
+        <v>3.2</v>
       </c>
       <c r="H6" t="n">
-        <v>2.98</v>
+        <v>1.09</v>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>1000</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>1.04</v>
       </c>
       <c r="I8" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J8" t="n">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>85</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>1.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -2115,23 +2115,23 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>1.22</v>
       </c>
       <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="K9" t="n">
         <v>5.4</v>
       </c>
-      <c r="H9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="I9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.5</v>
-      </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.49</v>
+        <v>1.04</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -2309,19 +2309,19 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="G10" t="n">
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.04</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>1.21</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>2.24</v>
+        <v>1.21</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>1000</v>
       </c>
       <c r="J11" t="n">
-        <v>2.54</v>
+        <v>1.01</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.83</v>
+        <v>1.04</v>
       </c>
       <c r="G12" t="n">
-        <v>2.34</v>
+        <v>1000</v>
       </c>
       <c r="H12" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K12" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>110</v>
       </c>
       <c r="H13" t="n">
-        <v>3.25</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>110</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,22 +2915,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>1.16</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="W13" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>1.42</v>
       </c>
       <c r="G14" t="n">
-        <v>2.84</v>
+        <v>1000</v>
       </c>
       <c r="H14" t="n">
-        <v>2.82</v>
+        <v>1.42</v>
       </c>
       <c r="I14" t="n">
-        <v>3.25</v>
+        <v>1000</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>1.03</v>
       </c>
       <c r="K14" t="n">
         <v>3.6</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.61</v>
+        <v>1.24</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H15" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
-        <v>2.66</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
-        <v>7.4</v>
+        <v>4.7</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.26</v>
+        <v>6.2</v>
       </c>
       <c r="G19" t="n">
         <v>1000</v>
       </c>
       <c r="H19" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="I19" t="n">
         <v>1.79</v>
       </c>
       <c r="J19" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="K19" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="G21" t="n">
         <v>4.3</v>
       </c>
       <c r="H21" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="I21" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>2.78</v>
+        <v>1.3</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -4831,22 +4831,22 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="G23" t="n">
-        <v>2.58</v>
+        <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>2.78</v>
+        <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K23" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.54</v>
+        <v>1.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -5028,10 +5028,10 @@
         <v>2.3</v>
       </c>
       <c r="G24" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H24" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I24" t="n">
         <v>3.75</v>
@@ -5052,7 +5052,7 @@
         <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P24" t="n">
         <v>1.71</v>
@@ -5070,13 +5070,13 @@
         <v>2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="V24" t="n">
         <v>1.36</v>
       </c>
       <c r="W24" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X24" t="n">
         <v>11</v>
@@ -5088,7 +5088,7 @@
         <v>25</v>
       </c>
       <c r="AA24" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AB24" t="n">
         <v>8.4</v>
@@ -5103,16 +5103,16 @@
         <v>55</v>
       </c>
       <c r="AF24" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH24" t="n">
         <v>21</v>
       </c>
       <c r="AI24" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ24" t="n">
         <v>32</v>
@@ -5121,7 +5121,7 @@
         <v>28</v>
       </c>
       <c r="AL24" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AM24" t="n">
         <v>160</v>
@@ -5130,25 +5130,25 @@
         <v>25</v>
       </c>
       <c r="AO24" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AP24" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR24" t="n">
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="AT24" t="n">
         <v>7.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
         <v>14</v>
@@ -5178,17 +5178,17 @@
         <v>28</v>
       </c>
       <c r="BE24" t="n">
-        <v>44</v>
+        <v>13.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG24" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="G25" t="n">
-        <v>2.24</v>
+        <v>1000</v>
       </c>
       <c r="H25" t="n">
         <v>4.2</v>
       </c>
       <c r="I25" t="n">
-        <v>4.3</v>
+        <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="K25" t="n">
         <v>3.5</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="G26" t="n">
         <v>2.12</v>
       </c>
       <c r="H26" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="I26" t="n">
         <v>7.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K26" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q26" t="n">
         <v>2.04</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -5801,19 +5801,19 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.43</v>
+        <v>1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>1.72</v>
+        <v>1000</v>
       </c>
       <c r="H28" t="n">
-        <v>2.38</v>
+        <v>1.04</v>
       </c>
       <c r="I28" t="n">
         <v>1000</v>
       </c>
       <c r="J28" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="K28" t="n">
         <v>1000</v>
@@ -5834,7 +5834,7 @@
         <v>1.05</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="G29" t="n">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="H29" t="n">
-        <v>2.74</v>
+        <v>7.6</v>
       </c>
       <c r="I29" t="n">
         <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>2.66</v>
+        <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 03:58:44</t>
+          <t>2026-03-07 06:29:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH30"/>
+  <dimension ref="A1:BH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1000</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
-        <v>1.29</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
         <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>1.23</v>
+        <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
       </c>
       <c r="M2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>1.25</v>
+        <v>5.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>1.25</v>
+        <v>2.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.15</v>
+        <v>1.56</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
       <c r="T2" t="n">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U2" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V2" t="n">
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM2" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AV2" t="n">
         <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>42</v>
+        <v>4.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>4.8</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>44</v>
+        <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.04</v>
+        <v>10.5</v>
       </c>
       <c r="G3" t="n">
         <v>630</v>
@@ -960,10 +960,10 @@
         <v>1.04</v>
       </c>
       <c r="I3" t="n">
-        <v>760</v>
+        <v>1.41</v>
       </c>
       <c r="J3" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="K3" t="n">
         <v>690</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.18</v>
+        <v>2.02</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -1342,16 +1342,16 @@
         <v>1.33</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
         <v>1000</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.05</v>
+        <v>1.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.04</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>1.09</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>1.07</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.04</v>
+        <v>2.2</v>
       </c>
       <c r="G8" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H8" t="n">
-        <v>1.04</v>
+        <v>2.64</v>
       </c>
       <c r="I8" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="K8" t="n">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.04</v>
+        <v>1.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.22</v>
+        <v>3.25</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.22</v>
+        <v>1.97</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>2.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>2.7</v>
       </c>
       <c r="K9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.04</v>
+        <v>1.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I10" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.01</v>
+        <v>1.69</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.21</v>
+        <v>2.6</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="H11" t="n">
-        <v>1.21</v>
+        <v>1.81</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="J11" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>5.9</v>
+        <v>15.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.25</v>
+        <v>1.64</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.04</v>
+        <v>1.96</v>
       </c>
       <c r="G12" t="n">
-        <v>1000</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>1.04</v>
+        <v>3.7</v>
       </c>
       <c r="I12" t="n">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="J12" t="n">
-        <v>1.01</v>
+        <v>2.72</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>3.3</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>110</v>
+        <v>5.7</v>
       </c>
       <c r="L13" t="n">
         <v>1.01</v>
@@ -2915,22 +2915,22 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="O13" t="n">
         <v>1.36</v>
       </c>
       <c r="P13" t="n">
-        <v>1.16</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.36</v>
+        <v>1.96</v>
       </c>
       <c r="R13" t="n">
-        <v>1.16</v>
+        <v>1.24</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>3.3</v>
       </c>
       <c r="T13" t="n">
         <v>1.01</v>
@@ -2939,10 +2939,10 @@
         <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="X13" t="n">
         <v>1000</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.42</v>
+        <v>2.28</v>
       </c>
       <c r="G14" t="n">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="H14" t="n">
-        <v>1.42</v>
+        <v>2.58</v>
       </c>
       <c r="I14" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.6</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G15" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>2.84</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.74</v>
+        <v>2.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -3464,12 +3464,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -3503,7 +3503,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q16" t="n">
         <v>1.01</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -3852,12 +3852,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,31 +4046,31 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
         <v>1.01</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="G23" t="n">
         <v>1000</v>
       </c>
       <c r="H23" t="n">
-        <v>1.04</v>
+        <v>1.53</v>
       </c>
       <c r="I23" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="J23" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="K23" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,191 +5011,191 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Q24" t="n">
         <v>1.01</v>
       </c>
-      <c r="M24" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.32</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="G25" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>1.58</v>
       </c>
       <c r="I25" t="n">
         <v>1000</v>
       </c>
       <c r="J25" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>1000</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,191 +5399,191 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I26" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W26" t="n">
         <v>1.74</v>
       </c>
-      <c r="G26" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="H26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K26" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N27" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S27" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AT27" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>8.4</v>
-      </c>
       <c r="AU27" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AV27" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX27" t="n">
         <v>9.800000000000001</v>
       </c>
-      <c r="AW27" t="n">
-        <v>25</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>16.5</v>
-      </c>
       <c r="AY27" t="n">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="BB27" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="BC27" t="n">
-        <v>36</v>
+        <v>19.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="BE27" t="n">
-        <v>100</v>
+        <v>13.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,36 +5787,36 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.04</v>
+        <v>2.12</v>
       </c>
       <c r="G28" t="n">
-        <v>1000</v>
+        <v>2.24</v>
       </c>
       <c r="H28" t="n">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J28" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1000</v>
+        <v>3.45</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -5831,10 +5831,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.05</v>
+        <v>1.78</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.32</v>
+        <v>1.77</v>
       </c>
       <c r="G29" t="n">
-        <v>1.49</v>
+        <v>1.96</v>
       </c>
       <c r="H29" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J29" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K29" t="n">
-        <v>9.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>
@@ -6175,17 +6175,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -6216,19 +6216,19 @@
         <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="P30" t="n">
         <v>1.24</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R30" t="n">
         <v>1.08</v>
       </c>
       <c r="S30" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="T30" t="n">
         <v>1.01</v>
@@ -6297,19 +6297,19 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR30" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU30" t="n">
         <v>6.2</v>
@@ -6318,31 +6318,31 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX30" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
         <v>42</v>
       </c>
       <c r="BB30" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BC30" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BD30" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BE30" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="BF30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,589 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 06:29:39</t>
+          <t>2026-03-07 09:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Univ de Concepcion</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="H31" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I31" t="n">
+        <v>11</v>
+      </c>
+      <c r="J31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>2026-03-07 09:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH32" t="inlineStr">
+        <is>
+          <t>2026-03-07 09:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>26</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-07 09:00:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH33"/>
+  <dimension ref="A1:BH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>10:30:00</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Eyupspor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ludogorets</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>10.5</v>
+        <v>3.6</v>
       </c>
       <c r="G3" t="n">
-        <v>630</v>
+        <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I3" t="n">
-        <v>1.41</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
-        <v>5.2</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>690</v>
+        <v>1000</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>2.02</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,191 +1131,191 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ASA Targu Mures</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Ludogorets</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.04</v>
+        <v>4.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1000</v>
+        <v>630</v>
       </c>
       <c r="H4" t="n">
-        <v>1.04</v>
+        <v>1.21</v>
       </c>
       <c r="I4" t="n">
-        <v>1000</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="K4" t="n">
-        <v>85</v>
+        <v>690</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="P4" t="n">
-        <v>1.24</v>
+        <v>2.02</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>ASA Targu Mures</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I5" t="n">
         <v>1000</v>
       </c>
       <c r="J5" t="n">
-        <v>3.15</v>
+        <v>1.01</v>
       </c>
       <c r="K5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.34</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="n">
         <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>2.84</v>
+        <v>3.15</v>
       </c>
       <c r="K6" t="n">
-        <v>3.9</v>
+        <v>1000</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.07</v>
+        <v>1.72</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.36</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NK Radomlje</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NK Bravo</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>1.07</v>
       </c>
       <c r="Q7" t="n">
         <v>1.01</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,36 +1907,36 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>NK Radomlje</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>NK Bravo</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Novi Pazar</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="G9" t="n">
-        <v>5.4</v>
+        <v>3.1</v>
       </c>
       <c r="H9" t="n">
-        <v>1.97</v>
+        <v>2.64</v>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.48</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.93</v>
+        <v>2.94</v>
       </c>
       <c r="G10" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="H10" t="n">
-        <v>3.05</v>
+        <v>2.1</v>
       </c>
       <c r="I10" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>3.45</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>2.36</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>3.65</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="I11" t="n">
-        <v>3.45</v>
+        <v>4.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.64</v>
+        <v>1.04</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>3.65</v>
       </c>
       <c r="H12" t="n">
-        <v>3.7</v>
+        <v>1.81</v>
       </c>
       <c r="I12" t="n">
-        <v>5.7</v>
+        <v>3.45</v>
       </c>
       <c r="J12" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>15</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.9</v>
+        <v>1.09</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3</v>
+        <v>1.04</v>
       </c>
       <c r="I13" t="n">
-        <v>5.1</v>
+        <v>1000</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="K13" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.62</v>
+        <v>1.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="R13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AS13" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AV13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AZ13" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BE13" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.28</v>
+        <v>1.26</v>
       </c>
       <c r="G14" t="n">
-        <v>3.1</v>
+        <v>2.58</v>
       </c>
       <c r="H14" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.6</v>
+        <v>110</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.06</v>
+        <v>1.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.5</v>
+        <v>1000</v>
       </c>
       <c r="H15" t="n">
-        <v>2.84</v>
+        <v>1.42</v>
       </c>
       <c r="I15" t="n">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J15" t="n">
-        <v>3.85</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>950</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,7 +3697,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q17" t="n">
         <v>1.01</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,31 +3852,31 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
         <v>1.01</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
@@ -4046,12 +4046,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q19" t="n">
         <v>1.01</v>
@@ -4218,14 +4218,14 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,31 +4240,31 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q22" t="n">
         <v>1.01</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4822,31 +4822,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.48</v>
+        <v>1.07</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,31 +5016,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.07</v>
+        <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.52</v>
+        <v>1.07</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5404,186 +5404,186 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.3</v>
+        <v>1.44</v>
       </c>
       <c r="G26" t="n">
-        <v>2.34</v>
+        <v>2.8</v>
       </c>
       <c r="H26" t="n">
-        <v>3.65</v>
+        <v>2.98</v>
       </c>
       <c r="I26" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.08</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL26" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS26" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV26" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW26" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX26" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA26" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC26" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BD26" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE26" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BF26" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG26" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,39 +5593,39 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="J27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K27" t="n">
         <v>3.4</v>
       </c>
-      <c r="K27" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
         <v>1.1</v>
@@ -5634,127 +5634,127 @@
         <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P27" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R27" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
         <v>4.4</v>
       </c>
       <c r="T27" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X27" t="n">
         <v>11</v>
       </c>
       <c r="Y27" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="Z27" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="AA27" t="n">
-        <v>150</v>
+        <v>80</v>
       </c>
       <c r="AB27" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AE27" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI27" t="n">
         <v>80</v>
       </c>
-      <c r="AF27" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>85</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="AK27" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AL27" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM27" t="n">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="AN27" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="AO27" t="n">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="AP27" t="n">
         <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS27" t="n">
-        <v>13.5</v>
+        <v>60</v>
       </c>
       <c r="AT27" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU27" t="n">
         <v>6.8</v>
       </c>
-      <c r="AU27" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV27" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AW27" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA27" t="n">
         <v>32</v>
       </c>
-      <c r="AX27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>60</v>
-      </c>
       <c r="BB27" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BD27" t="n">
         <v>28</v>
@@ -5763,21 +5763,21 @@
         <v>13.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BG27" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="G28" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I28" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="J28" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N28" t="n">
         <v>3.2</v>
       </c>
-      <c r="K28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P28" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="G29" t="n">
-        <v>1.96</v>
+        <v>2.22</v>
       </c>
       <c r="H29" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I29" t="n">
-        <v>6.6</v>
+        <v>4.3</v>
       </c>
       <c r="J29" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>3.45</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="R30" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P31" t="n">
-        <v>1.86</v>
+        <v>1.24</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.96</v>
+        <v>1.48</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,36 +6563,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="G32" t="n">
         <v>1.56</v>
       </c>
       <c r="H32" t="n">
-        <v>2.88</v>
+        <v>7.6</v>
       </c>
       <c r="I32" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="J32" t="n">
-        <v>2.92</v>
+        <v>4.1</v>
       </c>
       <c r="K32" t="n">
-        <v>1000</v>
+        <v>5.1</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.71</v>
+        <v>1.94</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,201 +6740,395 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 09:00:35</t>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH33" t="inlineStr">
+        <is>
+          <t>2026-03-07 11:31:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Deportivo Recoleta</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N33" t="n">
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N34" t="n">
         <v>1.25</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>1.45</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P34" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>1.45</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>1.08</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>1.45</v>
       </c>
-      <c r="T33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>26</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>40</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>30</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>2026-03-07 09:00:35</t>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-07 11:31:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH34"/>
+  <dimension ref="A1:BH38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,7 +811,7 @@
         <v>2.38</v>
       </c>
       <c r="X2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>29</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="F3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
         <v>3.6</v>
       </c>
-      <c r="G3" t="n">
-        <v>5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="I3" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1000</v>
-      </c>
       <c r="L3" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="O3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.2</v>
       </c>
       <c r="Q3" t="n">
         <v>1.43</v>
@@ -999,10 +999,10 @@
         <v>1.01</v>
       </c>
       <c r="V3" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -1151,13 +1151,13 @@
         <v>630</v>
       </c>
       <c r="H4" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="I4" t="n">
         <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>690</v>
@@ -1166,7 +1166,7 @@
         <v>1.01</v>
       </c>
       <c r="M4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N4" t="n">
         <v>2.02</v>
@@ -1256,7 +1256,7 @@
         <v>18</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AR4" t="n">
         <v>5.8</v>
@@ -1271,7 +1271,7 @@
         <v>12</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW4" t="n">
         <v>12</v>
@@ -1280,10 +1280,10 @@
         <v>100</v>
       </c>
       <c r="AY4" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AZ4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA4" t="n">
         <v>42</v>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Romanian Liga II</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>10:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASA Targu Mures</t>
+          <t>Rukh Vynnyky</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Metalist 1925</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.04</v>
+        <v>4.4</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.02</v>
       </c>
       <c r="J5" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>85</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.24</v>
+        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bulgarian A League</t>
+          <t>Romanian Liga II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PFC Levski Sofia</t>
+          <t>ASA Targu Mures</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.04</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1000</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="I6" t="n">
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>3.15</v>
+        <v>1.02</v>
       </c>
       <c r="K6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Greek Super League</t>
+          <t>Bulgarian A League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1718,186 +1718,186 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>PFC Levski Sofia</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kifisia</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.9</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1</v>
+        <v>1.34</v>
       </c>
       <c r="H7" t="n">
-        <v>1.33</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>2.84</v>
+        <v>5.2</v>
       </c>
       <c r="K7" t="n">
-        <v>3.95</v>
+        <v>5.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.07</v>
+        <v>1.72</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Slovenian Premier League</t>
+          <t>Greek Super League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:30:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NK Radomlje</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NK Bravo</t>
+          <t>Kifisia</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q8" t="n">
         <v>2.38</v>
       </c>
-      <c r="Q8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Ukrainian Premier League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Veres Rivne</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>LNZ-Lebedyn</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.2</v>
+        <v>3.75</v>
       </c>
       <c r="G9" t="n">
-        <v>3.1</v>
+        <v>9.4</v>
       </c>
       <c r="H9" t="n">
-        <v>2.64</v>
+        <v>1.63</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>2.84</v>
+        <v>2.44</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.8</v>
+        <v>2.28</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Slovenian Premier League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,191 +2295,191 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:30:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>NK Radomlje</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>FK Novi Pazar</t>
+          <t>NK Bravo</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G10" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="H10" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="I10" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="J10" t="n">
-        <v>2.7</v>
+        <v>3.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3.45</v>
+        <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P10" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.36</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AY10" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BA10" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC10" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BD10" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE10" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.95</v>
+        <v>3.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>4.2</v>
       </c>
       <c r="H11" t="n">
-        <v>1.67</v>
+        <v>2.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.8</v>
+        <v>2.22</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AC Horsens</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.6</v>
+        <v>1.82</v>
       </c>
       <c r="G12" t="n">
-        <v>3.65</v>
+        <v>1.99</v>
       </c>
       <c r="H12" t="n">
-        <v>1.81</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K12" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.64</v>
+        <v>1.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,191 +2877,191 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.09</v>
+        <v>2.26</v>
       </c>
       <c r="G13" t="n">
-        <v>1000</v>
+        <v>2.72</v>
       </c>
       <c r="H13" t="n">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="I13" t="n">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="K13" t="n">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P13" t="n">
-        <v>1.21</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,191 +3071,191 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.26</v>
+        <v>1.95</v>
       </c>
       <c r="G14" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
-        <v>2.42</v>
+        <v>1.67</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="L14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.98</v>
+        <v>1.69</v>
       </c>
       <c r="R14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.42</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="H15" t="n">
-        <v>1.42</v>
+        <v>1.99</v>
       </c>
       <c r="I15" t="n">
-        <v>1000</v>
+        <v>2.64</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>2.74</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="G16" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H16" t="n">
-        <v>2.92</v>
+        <v>3.9</v>
       </c>
       <c r="I16" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="J16" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="K16" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.74</v>
+        <v>1.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,191 +3653,191 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V17" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G18" t="n">
-        <v>1.71</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>2.46</v>
+        <v>2.58</v>
       </c>
       <c r="I18" t="n">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>950</v>
+        <v>3.6</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,36 +4041,36 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -4085,10 +4085,10 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -4240,12 +4240,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q20" t="n">
         <v>1.01</v>
@@ -4412,14 +4412,14 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.6</v>
+        <v>1.04</v>
       </c>
       <c r="G21" t="n">
-        <v>4.3</v>
+        <v>1.71</v>
       </c>
       <c r="H21" t="n">
-        <v>1.91</v>
+        <v>2.46</v>
       </c>
       <c r="I21" t="n">
-        <v>2.44</v>
+        <v>1000</v>
       </c>
       <c r="J21" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="K21" t="n">
-        <v>5.1</v>
+        <v>950</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -4628,12 +4628,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4667,7 +4667,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q22" t="n">
         <v>1.01</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
         <v>1000</v>
       </c>
       <c r="H24" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="I24" t="n">
         <v>1.79</v>
@@ -5040,7 +5040,7 @@
         <v>2.34</v>
       </c>
       <c r="K24" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5058,7 +5058,7 @@
         <v>1.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q25" t="n">
         <v>1.01</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,7 +5443,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Q26" t="n">
         <v>1.01</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,191 +5593,191 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="G27" t="n">
-        <v>2.34</v>
+        <v>4.3</v>
       </c>
       <c r="H27" t="n">
-        <v>3.65</v>
+        <v>1.93</v>
       </c>
       <c r="I27" t="n">
-        <v>3.75</v>
+        <v>2.44</v>
       </c>
       <c r="J27" t="n">
-        <v>3.3</v>
+        <v>2.88</v>
       </c>
       <c r="K27" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="R27" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR27" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AW27" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AX27" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AY27" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA27" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="BC27" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BD27" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE27" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BF27" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG27" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5787,66 +5787,66 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.74</v>
+        <v>1.24</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="R28" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -5855,123 +5855,123 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR28" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV28" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AW28" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA28" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BB28" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC28" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD28" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="BE28" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BF28" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BG28" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G29" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="H29" t="n">
-        <v>4.2</v>
+        <v>2.98</v>
       </c>
       <c r="I29" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="J29" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="K29" t="n">
-        <v>3.45</v>
+        <v>5.2</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.1</v>
+        <v>2.34</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,14 +6158,14 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6175,191 +6175,191 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="G30" t="n">
-        <v>2.02</v>
+        <v>2.34</v>
       </c>
       <c r="H30" t="n">
-        <v>5</v>
+        <v>3.65</v>
       </c>
       <c r="I30" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P30" t="n">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG30" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,191 +6369,191 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N31" t="n">
-        <v>1.25</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P31" t="n">
-        <v>1.24</v>
+        <v>1.74</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.48</v>
+        <v>2.3</v>
       </c>
       <c r="R31" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA31" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB31" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI31" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AO31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="AS31" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="AT31" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV31" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,36 +6563,36 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.49</v>
+        <v>2.1</v>
       </c>
       <c r="G32" t="n">
-        <v>1.56</v>
+        <v>2.22</v>
       </c>
       <c r="H32" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="I32" t="n">
-        <v>11</v>
+        <v>4.3</v>
       </c>
       <c r="J32" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -6607,10 +6607,10 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.94</v>
+        <v>2.22</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -6757,36 +6757,36 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="G33" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="H33" t="n">
-        <v>2.88</v>
+        <v>4.9</v>
       </c>
       <c r="I33" t="n">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J33" t="n">
-        <v>2.92</v>
+        <v>3.35</v>
       </c>
       <c r="K33" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.86</v>
+        <v>1.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 11:31:26</t>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>
@@ -6951,17 +6951,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>20:30:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Deportivo Recoleta</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Club Sportivo Ameliano</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -6992,143 +6992,919 @@
         <v>1.25</v>
       </c>
       <c r="O34" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P34" t="n">
         <v>1.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R34" t="n">
         <v>1.08</v>
       </c>
       <c r="S34" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:02:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>18:30:00</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Cerro Largo FC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J35" t="n">
+        <v>3</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:02:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Univ de Concepcion</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="G36" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H36" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I36" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH36" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:02:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H37" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="K37" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:02:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:30:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="O38" t="n">
         <v>1.45</v>
       </c>
-      <c r="T34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>2026-03-07 11:31:26</t>
+      <c r="P38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-07 14:02:13</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH38"/>
+  <dimension ref="A1:BH39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>1.64</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
@@ -775,7 +775,7 @@
         <v>4.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -913,14 +913,14 @@
         <v>4.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BG2" t="n">
         <v>4.7</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
+        <v>15</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N4" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>4.5</v>
       </c>
-      <c r="G4" t="n">
-        <v>630</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="K4" t="n">
-        <v>690</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AR4" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>7.4</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>32</v>
+        <v>8.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>12</v>
+        <v>1.4</v>
       </c>
       <c r="AV4" t="n">
-        <v>9.4</v>
+        <v>5.6</v>
       </c>
       <c r="AW4" t="n">
-        <v>12</v>
+        <v>1.53</v>
       </c>
       <c r="AX4" t="n">
-        <v>100</v>
+        <v>1.07</v>
       </c>
       <c r="AY4" t="n">
-        <v>44</v>
+        <v>1.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>30</v>
+        <v>8.6</v>
       </c>
       <c r="BA4" t="n">
-        <v>42</v>
+        <v>1.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>100</v>
+        <v>1.08</v>
       </c>
       <c r="BC4" t="n">
-        <v>100</v>
+        <v>1.08</v>
       </c>
       <c r="BD4" t="n">
-        <v>100</v>
+        <v>1.08</v>
       </c>
       <c r="BE4" t="n">
-        <v>100</v>
+        <v>1.08</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="G5" t="n">
         <v>7.2</v>
@@ -1360,70 +1360,70 @@
         <v>1.49</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.49</v>
+        <v>2.52</v>
       </c>
       <c r="O5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P5" t="n">
         <v>1.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.49</v>
       </c>
       <c r="Q5" t="n">
         <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
         <v>1.98</v>
       </c>
       <c r="W5" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>12.5</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>20</v>
-      </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="AG5" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="AH5" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.02</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.89</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.26</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>2.16</v>
+        <v>5.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.99</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW5" t="n">
-        <v>2.28</v>
+        <v>3.55</v>
       </c>
       <c r="AX5" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AY5" t="n">
-        <v>2.26</v>
+        <v>6.2</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2.3</v>
+        <v>3.55</v>
       </c>
       <c r="BA5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="BD5" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="BE5" t="n">
-        <v>2.42</v>
+        <v>1.45</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.42</v>
+        <v>1.54</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.42</v>
+        <v>6.2</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -1545,7 +1545,7 @@
         <v>1000</v>
       </c>
       <c r="J6" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K6" t="n">
         <v>110</v>
@@ -1641,52 +1641,52 @@
         <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB6" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.34</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="I7" t="n">
         <v>22</v>
@@ -1745,34 +1745,34 @@
         <v>5.7</v>
       </c>
       <c r="L7" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>1.72</v>
+        <v>3.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.82</v>
+        <v>1.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V7" t="n">
         <v>1.06</v>
@@ -1781,55 +1781,55 @@
         <v>3.85</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>540</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,59 +1838,59 @@
         <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23</v>
+        <v>5.7</v>
       </c>
       <c r="AR7" t="n">
-        <v>70</v>
+        <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="AT7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>5.9</v>
       </c>
-      <c r="AU7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>100</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>28</v>
-      </c>
       <c r="BA7" t="n">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="BE7" t="n">
-        <v>100</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -1921,7 +1921,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
         <v>2.72</v>
@@ -1942,13 +1942,13 @@
         <v>1.51</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N8" t="n">
-        <v>1.59</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P8" t="n">
         <v>1.59</v>
@@ -1957,134 +1957,134 @@
         <v>2.38</v>
       </c>
       <c r="R8" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W8" t="n">
         <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Y8" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AA8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>11.5</v>
+        <v>8.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>15.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
-        <v>17.5</v>
+        <v>13</v>
       </c>
       <c r="AH8" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ8" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AK8" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AP8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE8" t="n">
         <v>2.12</v>
       </c>
-      <c r="AQ8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>2.58</v>
-      </c>
       <c r="BF8" t="n">
-        <v>2.58</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="G9" t="n">
-        <v>9.4</v>
+        <v>7.4</v>
       </c>
       <c r="H9" t="n">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="I9" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J9" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="K9" t="n">
-        <v>8.199999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2139,22 +2139,22 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="O9" t="n">
-        <v>1.51</v>
+        <v>1.01</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="R9" t="n">
         <v>1.08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
         <v>1.01</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="W9" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2223,52 +2223,52 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
         <v>1.01</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -2417,52 +2417,52 @@
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AS10" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AU10" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV10" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX10" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AY10" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BA10" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BB10" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BC10" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD10" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE10" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF10" t="n">
         <v>1.01</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.6</v>
+        <v>1.95</v>
       </c>
       <c r="G11" t="n">
-        <v>4.2</v>
+        <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="I11" t="n">
-        <v>2.22</v>
+        <v>4.7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>1.84</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.82</v>
+        <v>2.36</v>
       </c>
       <c r="G12" t="n">
-        <v>1.99</v>
+        <v>2.7</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>2.92</v>
       </c>
       <c r="I12" t="n">
-        <v>5.1</v>
+        <v>3.4</v>
       </c>
       <c r="J12" t="n">
-        <v>3.3</v>
+        <v>2.98</v>
       </c>
       <c r="K12" t="n">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P12" t="n">
-        <v>1.05</v>
+        <v>1.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AX12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BE12" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BG12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -2882,186 +2882,186 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mladost Lucani</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>FK Novi Pazar</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="J13" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
-        <v>6.2</v>
+        <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M13" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>1.31</v>
+        <v>1.46</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.93</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="S13" t="n">
-        <v>3.35</v>
+        <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="W13" t="n">
-        <v>1.58</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="Y13" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC13" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG13" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH13" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI13" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK13" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL13" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AM13" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN13" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AP13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AR13" t="n">
         <v>11.5</v>
       </c>
-      <c r="AQ13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>1.05</v>
-      </c>
       <c r="AS13" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.05</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.05</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.05</v>
+        <v>3.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.05</v>
+        <v>14.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.05</v>
+        <v>18.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.05</v>
+        <v>4.1</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.05</v>
+        <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.05</v>
+        <v>3.85</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="G14" t="n">
-        <v>2.56</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
-        <v>1.67</v>
+        <v>4.8</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K14" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P14" t="n">
-        <v>1.84</v>
+        <v>1.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.69</v>
+        <v>1.32</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,186 +3270,186 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mladost Lucani</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Novi Pazar</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="H15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>38</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>50</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AW15" t="n">
         <v>1.99</v>
       </c>
-      <c r="I15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0</v>
-      </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BG15" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,186 +3464,186 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wisla Plock</t>
+          <t>AC Horsens</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.85</v>
+        <v>1.97</v>
       </c>
       <c r="G16" t="n">
-        <v>2.34</v>
+        <v>3.65</v>
       </c>
       <c r="H16" t="n">
-        <v>3.9</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>5.7</v>
+        <v>3.15</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>110</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P16" t="n">
-        <v>1.21</v>
+        <v>1.65</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Portuguese Segunda Liga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3658,31 +3658,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Benfica B</t>
+          <t>Wisla Plock</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Feirense</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.42</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>2.42</v>
+        <v>3.9</v>
       </c>
       <c r="I17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>110</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,22 +3691,22 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="O17" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="P17" t="n">
-        <v>1.66</v>
+        <v>1.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.98</v>
+        <v>1.4</v>
       </c>
       <c r="R17" t="n">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,10 +3715,10 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="W17" t="n">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3775,52 +3775,52 @@
         <v>1000</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>90</v>
       </c>
       <c r="BF17" t="n">
         <v>1.01</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Romanian Liga I</t>
+          <t>Portuguese Segunda Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3852,186 +3852,186 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Benfica B</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dinamo Bucharest</t>
+          <t>Feirense</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
-        <v>2.58</v>
+        <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ18" t="n">
         <v>3.6</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>2</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0</v>
-      </c>
-      <c r="T18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dutch Eerste Divisie</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,191 +4041,191 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:00:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Jong AZ Alkmaar</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Dinamo Bucharest</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.08</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="K19" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.74</v>
+        <v>1.69</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.46</v>
+        <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BG19" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Dutch Eerste Divisie</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,191 +4235,191 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:30:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Jong AZ Alkmaar</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.24</v>
+        <v>2.74</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,31 +4434,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.04</v>
+        <v>6.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1.71</v>
+        <v>1000</v>
       </c>
       <c r="H21" t="n">
-        <v>2.46</v>
+        <v>1.46</v>
       </c>
       <c r="I21" t="n">
-        <v>1000</v>
+        <v>1.79</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="K21" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,31 +4628,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5016,31 +5016,31 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.48</v>
+        <v>1.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -5210,12 +5210,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5598,31 +5598,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -5792,12 +5792,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -5831,7 +5831,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>1.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q28" t="n">
         <v>1.01</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5981,36 +5981,36 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>16:45:00</t>
+          <t>16:30:00</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>2.12</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>2.8</v>
+        <v>1.71</v>
       </c>
       <c r="H29" t="n">
-        <v>2.98</v>
+        <v>2.46</v>
       </c>
       <c r="I29" t="n">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="J29" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="K29" t="n">
-        <v>5.2</v>
+        <v>950</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
@@ -6025,10 +6025,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
@@ -6201,10 +6201,10 @@
         <v>3.75</v>
       </c>
       <c r="J30" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.4</v>
       </c>
       <c r="L30" t="n">
         <v>1.01</v>
@@ -6234,7 +6234,7 @@
         <v>1.99</v>
       </c>
       <c r="U30" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V30" t="n">
         <v>1.36</v>
@@ -6352,14 +6352,14 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6369,66 +6369,66 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:45:00</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Oviedo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="G31" t="n">
-        <v>1.97</v>
+        <v>2.62</v>
       </c>
       <c r="H31" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="I31" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="J31" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.74</v>
+        <v>1.54</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.3</v>
+        <v>2.48</v>
       </c>
       <c r="R31" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6437,123 +6437,123 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>85</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -6563,66 +6563,66 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>17:15:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tondela</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Rio Ave</t>
+          <t>Oviedo</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="G32" t="n">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="H32" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="I32" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6631,123 +6631,123 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG32" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -6757,54 +6757,54 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:15:00</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Llaneros FC</t>
+          <t>Tondela</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Jaguares de Cordoba</t>
+          <t>Rio Ave</t>
         </is>
       </c>
       <c r="F33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I33" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
         <v>1.8</v>
       </c>
-      <c r="G33" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="H33" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="I33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K33" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Q33" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,14 +6934,14 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Paraguayan Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -6951,191 +6951,191 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>18:30:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sportivo Trinidense</t>
+          <t>Llaneros FC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Nacional (Par)</t>
+          <t>Jaguares de Cordoba</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>1.24</v>
+        <v>1.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.48</v>
+        <v>2.04</v>
       </c>
       <c r="R34" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Uruguayan Primera Division</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7150,186 +7150,186 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cerro Largo FC</t>
+          <t>Sportivo Trinidense</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Torque</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.65</v>
+        <v>1.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.26</v>
+        <v>1.48</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Uruguayan Primera Division</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7339,36 +7339,36 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>18:30:00</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Universidad de Chile</t>
+          <t>Cerro Largo FC</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Univ de Concepcion</t>
+          <t>Torque</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.49</v>
+        <v>3.75</v>
       </c>
       <c r="G36" t="n">
-        <v>1.56</v>
+        <v>4.3</v>
       </c>
       <c r="H36" t="n">
-        <v>7.6</v>
+        <v>2.18</v>
       </c>
       <c r="I36" t="n">
-        <v>10.5</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="K36" t="n">
-        <v>5.1</v>
+        <v>3.45</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -7383,10 +7383,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>1.84</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.96</v>
+        <v>2.26</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -7516,14 +7516,14 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7533,36 +7533,36 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>20:20:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Millonarios</t>
+          <t>Universidad de Chile</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Univ de Concepcion</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.04</v>
+        <v>1.49</v>
       </c>
       <c r="G37" t="n">
         <v>1.56</v>
       </c>
       <c r="H37" t="n">
-        <v>2.88</v>
+        <v>7.8</v>
       </c>
       <c r="I37" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="J37" t="n">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="K37" t="n">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -7577,10 +7577,10 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="R37" t="n">
         <v>0</v>
@@ -7710,201 +7710,395 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-07 14:02:13</t>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>20:20:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Cucuta Deportivo</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G38" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="H38" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="I38" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="J38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K38" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH38" t="inlineStr">
+        <is>
+          <t>2026-03-07 16:28:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>Paraguayan Primera Division</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>20:30:00</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D39" t="inlineStr">
         <is>
           <t>Deportivo Recoleta</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>Club Sportivo Ameliano</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N38" t="n">
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N39" t="n">
         <v>1.25</v>
       </c>
-      <c r="O38" t="n">
+      <c r="O39" t="n">
         <v>1.45</v>
       </c>
-      <c r="P38" t="n">
+      <c r="P39" t="n">
         <v>1.24</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="Q39" t="n">
         <v>1.45</v>
       </c>
-      <c r="R38" t="n">
+      <c r="R39" t="n">
         <v>1.08</v>
       </c>
-      <c r="S38" t="n">
+      <c r="S39" t="n">
         <v>1.45</v>
       </c>
-      <c r="T38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BE38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BF38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>2026-03-07 14:02:13</t>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH39" t="inlineStr">
+        <is>
+          <t>2026-03-07 16:28:30</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
         <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="I3" t="n">
         <v>2.4</v>
@@ -966,37 +966,37 @@
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.49</v>
       </c>
       <c r="M3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>1.22</v>
+        <v>2.98</v>
       </c>
       <c r="O3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.43</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
         <v>1.71</v>
@@ -1005,37 +1005,37 @@
         <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE3" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF3" t="n">
         <v>1000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
@@ -1044,77 +1044,77 @@
         <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN3" t="n">
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" t="n">
         <v>1.21</v>
@@ -1157,7 +1157,7 @@
         <v>1.26</v>
       </c>
       <c r="J4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>8.800000000000001</v>
@@ -1190,7 +1190,7 @@
         <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="V4" t="n">
         <v>4.8</v>
@@ -1253,37 +1253,37 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA4" t="n">
         <v>1.35</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="H5" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
       </c>
       <c r="J5" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>1.49</v>
@@ -1372,7 +1372,7 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1399,10 +1399,10 @@
         <v>6.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AB5" t="n">
         <v>14.5</v>
@@ -1417,7 +1417,7 @@
         <v>29</v>
       </c>
       <c r="AF5" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
         <v>26</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6</v>
       </c>
-      <c r="AT5" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AX5" t="n">
+      <c r="BA5" t="n">
         <v>2.36</v>
       </c>
-      <c r="AY5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA5" t="n">
+      <c r="BB5" t="n">
         <v>2.4</v>
       </c>
-      <c r="BB5" t="n">
-        <v>1.45</v>
-      </c>
       <c r="BC5" t="n">
-        <v>1.54</v>
+        <v>2.38</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.54</v>
+        <v>1.78</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.45</v>
+        <v>1.79</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.54</v>
+        <v>1.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
         <v>5.7</v>
@@ -1757,7 +1757,7 @@
         <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
         <v>1.97</v>
@@ -1775,10 +1775,10 @@
         <v>1.52</v>
       </c>
       <c r="V7" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="X7" t="n">
         <v>15</v>
@@ -1787,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="Z7" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>65</v>
       </c>
       <c r="AE7" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
         <v>7.8</v>
@@ -1814,7 +1814,7 @@
         <v>55</v>
       </c>
       <c r="AI7" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="AJ7" t="n">
         <v>9.800000000000001</v>
@@ -1826,7 +1826,7 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="AN7" t="n">
         <v>8.199999999999999</v>
@@ -1844,7 +1844,7 @@
         <v>6.4</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT7" t="n">
         <v>5.7</v>
@@ -1865,13 +1865,13 @@
         <v>10</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA7" t="n">
         <v>6.6</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -2115,34 +2115,34 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="G9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="H9" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="J9" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
         <v>1.54</v>
@@ -2151,31 +2151,31 @@
         <v>2.38</v>
       </c>
       <c r="R9" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="W9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -2739,10 +2739,10 @@
         <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U12" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
@@ -2784,7 +2784,7 @@
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ12" t="n">
         <v>44</v>
@@ -2796,13 +2796,13 @@
         <v>50</v>
       </c>
       <c r="AM12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN12" t="n">
         <v>27</v>
       </c>
       <c r="AO12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP12" t="n">
         <v>12</v>
@@ -2826,7 +2826,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AX12" t="n">
         <v>14</v>
@@ -2841,16 +2841,16 @@
         <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BE12" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF12" t="n">
         <v>16</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J13" t="n">
         <v>3.1</v>
@@ -2924,7 +2924,7 @@
         <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
@@ -2936,13 +2936,13 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3002,7 +3002,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AR13" t="n">
         <v>11.5</v>
@@ -3014,7 +3014,7 @@
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV13" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="G14" t="n">
         <v>1.98</v>
@@ -3097,10 +3097,10 @@
         <v>5.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L14" t="n">
         <v>1.41</v>
@@ -3109,146 +3109,146 @@
         <v>1.08</v>
       </c>
       <c r="N14" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="O14" t="n">
         <v>1.33</v>
       </c>
-      <c r="O14" t="n">
-        <v>1.32</v>
-      </c>
       <c r="P14" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1</v>
+        <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V14" t="n">
         <v>1.24</v>
       </c>
       <c r="W14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X14" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z14" t="n">
         <v>1000</v>
       </c>
       <c r="AA14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB14" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE14" t="n">
         <v>1000</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
         <v>1000</v>
       </c>
       <c r="AJ14" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AK14" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL14" t="n">
         <v>1000</v>
       </c>
       <c r="AM14" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN14" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO14" t="n">
         <v>1000</v>
       </c>
       <c r="AP14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AS14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC14" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD14" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BG14" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H15" t="n">
         <v>2.04</v>
@@ -3291,10 +3291,10 @@
         <v>2.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L15" t="n">
         <v>1.37</v>
@@ -3303,28 +3303,28 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>2.04</v>
+        <v>4</v>
       </c>
       <c r="O15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
         <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V15" t="n">
         <v>1.84</v>
@@ -3333,116 +3333,116 @@
         <v>1.32</v>
       </c>
       <c r="X15" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y15" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>27</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO15" t="n">
         <v>15</v>
       </c>
-      <c r="Z15" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>44</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>23</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>100</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP15" t="n">
-        <v>2.14</v>
+        <v>5.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.87</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.93</v>
+        <v>11.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.02</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.95</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.82</v>
+        <v>7.6</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.88</v>
+        <v>9.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.99</v>
+        <v>17.5</v>
       </c>
       <c r="AX15" t="n">
-        <v>2.04</v>
+        <v>21</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.95</v>
+        <v>13</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.97</v>
+        <v>5.6</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.04</v>
+        <v>6.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>2.08</v>
+        <v>7.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.06</v>
+        <v>7</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.14</v>
+        <v>7.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.12</v>
+        <v>6.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.12</v>
+        <v>10</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H16" t="n">
         <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
@@ -3521,10 +3521,10 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W16" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3593,7 +3593,7 @@
         <v>27</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
@@ -3602,10 +3602,10 @@
         <v>9.4</v>
       </c>
       <c r="AW16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY16" t="n">
         <v>9.800000000000001</v>
@@ -3614,16 +3614,16 @@
         <v>16</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BB16" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BC16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD16" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O17" t="n">
         <v>1.4</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
         <v>1.74</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -4076,31 +4076,31 @@
         <v>1.01</v>
       </c>
       <c r="M19" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>2.56</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="Q19" t="n">
         <v>2.16</v>
       </c>
       <c r="R19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
         <v>4.1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U19" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="V19" t="n">
         <v>1.45</v>
@@ -4154,7 +4154,7 @@
         <v>55</v>
       </c>
       <c r="AM19" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN19" t="n">
         <v>34</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
@@ -4261,22 +4261,22 @@
         <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K20" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>2.74</v>
+        <v>6.2</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="P20" t="n">
         <v>2.74</v>
@@ -4285,134 +4285,134 @@
         <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>1.41</v>
+        <v>2.04</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="V20" t="n">
         <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="X20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="Y20" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AG20" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AM20" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT20" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AU20" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV20" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -4446,31 +4446,31 @@
         <v>6.2</v>
       </c>
       <c r="G21" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.46</v>
+        <v>1.13</v>
       </c>
       <c r="I21" t="n">
         <v>1.79</v>
       </c>
       <c r="J21" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="K21" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P21" t="n">
         <v>1.48</v>
@@ -4479,134 +4479,134 @@
         <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -4637,170 +4637,170 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="G22" t="n">
         <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="I22" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="J22" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="K22" t="n">
-        <v>4.9</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P22" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P23" t="n">
-        <v>1.07</v>
+        <v>1.52</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -5025,170 +5025,170 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="P24" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -5219,170 +5219,170 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P25" t="n">
-        <v>1.24</v>
+        <v>1.59</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P26" t="n">
-        <v>1.07</v>
+        <v>1.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -5607,170 +5607,170 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="P27" t="n">
-        <v>1.24</v>
+        <v>1.47</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -5801,170 +5801,170 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="P28" t="n">
-        <v>1.07</v>
+        <v>1.73</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -5995,170 +5995,170 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="G29" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="H29" t="n">
-        <v>2.46</v>
+        <v>6.2</v>
       </c>
       <c r="I29" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="J29" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
       <c r="K29" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>1.25</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BG29" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -6201,22 +6201,22 @@
         <v>3.75</v>
       </c>
       <c r="J30" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K30" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L30" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
         <v>3.15</v>
       </c>
       <c r="O30" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P30" t="n">
         <v>1.72</v>
@@ -6225,7 +6225,7 @@
         <v>2.26</v>
       </c>
       <c r="R30" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S30" t="n">
         <v>4.4</v>
@@ -6249,10 +6249,10 @@
         <v>12</v>
       </c>
       <c r="Z30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AA30" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AB30" t="n">
         <v>8.4</v>
@@ -6261,13 +6261,13 @@
         <v>7.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG30" t="n">
         <v>11.5</v>
@@ -6276,16 +6276,16 @@
         <v>21</v>
       </c>
       <c r="AI30" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ30" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK30" t="n">
         <v>28</v>
       </c>
       <c r="AL30" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM30" t="n">
         <v>160</v>
@@ -6294,22 +6294,22 @@
         <v>25</v>
       </c>
       <c r="AO30" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AP30" t="n">
         <v>10</v>
       </c>
       <c r="AQ30" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS30" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AT30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU30" t="n">
         <v>6.8</v>
@@ -6318,28 +6318,28 @@
         <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="AX30" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AY30" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BA30" t="n">
         <v>32</v>
       </c>
       <c r="BB30" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="BC30" t="n">
-        <v>18.5</v>
+        <v>24</v>
       </c>
       <c r="BD30" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="BE30" t="n">
         <v>42</v>
@@ -6348,11 +6348,11 @@
         <v>21</v>
       </c>
       <c r="BG30" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -6383,170 +6383,170 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="G31" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="H31" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="I31" t="n">
-        <v>3.35</v>
+        <v>3.15</v>
       </c>
       <c r="J31" t="n">
         <v>3.1</v>
       </c>
       <c r="K31" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P31" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q31" t="n">
         <v>2.48</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="BG31" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6595,7 @@
         <v>3.55</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
         <v>1.1</v>
@@ -6607,40 +6607,40 @@
         <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="R32" t="n">
         <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U32" t="n">
         <v>1.9</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="X32" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y32" t="n">
         <v>14.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB32" t="n">
         <v>7.6</v>
@@ -6649,10 +6649,10 @@
         <v>7.8</v>
       </c>
       <c r="AD32" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF32" t="n">
         <v>10.5</v>
@@ -6667,80 +6667,80 @@
         <v>85</v>
       </c>
       <c r="AJ32" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AK32" t="n">
         <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM32" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="AN32" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP32" t="n">
         <v>10</v>
       </c>
       <c r="AQ32" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AS32" t="n">
         <v>40</v>
       </c>
       <c r="AT32" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU32" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW32" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AX32" t="n">
         <v>9.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ32" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB32" t="n">
         <v>19.5</v>
       </c>
-      <c r="BA32" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>19</v>
-      </c>
       <c r="BC32" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BD32" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="BE32" t="n">
         <v>44</v>
       </c>
       <c r="BF32" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BG32" t="n">
         <v>38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -6774,10 +6774,10 @@
         <v>2.1</v>
       </c>
       <c r="G33" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H33" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
         <v>4.3</v>
@@ -6786,19 +6786,19 @@
         <v>3.3</v>
       </c>
       <c r="K33" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P33" t="n">
         <v>1.8</v>
@@ -6807,134 +6807,134 @@
         <v>2.22</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BG33" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -6965,7 +6965,7 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G34" t="n">
         <v>1.98</v>
@@ -6974,161 +6974,161 @@
         <v>4.9</v>
       </c>
       <c r="I34" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BG34" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,22 +7183,22 @@
         <v>1.01</v>
       </c>
       <c r="N35" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="O35" t="n">
         <v>1.01</v>
       </c>
       <c r="P35" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.48</v>
+        <v>2.26</v>
       </c>
       <c r="R35" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="S35" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7207,10 +7207,10 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="W35" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -7353,34 +7353,34 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="G36" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="H36" t="n">
         <v>2.18</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.32</v>
       </c>
       <c r="J36" t="n">
-        <v>3</v>
+        <v>2.42</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P36" t="n">
         <v>1.65</v>
@@ -7389,134 +7389,134 @@
         <v>2.26</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,34 +7959,34 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.25</v>
+        <v>1.46</v>
       </c>
       <c r="O39" t="n">
         <v>1.45</v>
       </c>
       <c r="P39" t="n">
-        <v>1.24</v>
+        <v>1.46</v>
       </c>
       <c r="Q39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="S39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V39" t="n">
         <v>1.45</v>
       </c>
-      <c r="R39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S39" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="T39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.01</v>
-      </c>
       <c r="W39" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-07 16:28:30</t>
+          <t>2026-03-07 18:52:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -796,10 +796,10 @@
         <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="U2" t="n">
         <v>2.34</v>
@@ -871,7 +871,7 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>38</v>
+        <v>4.7</v>
       </c>
       <c r="AS2" t="n">
         <v>5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -957,10 +957,10 @@
         <v>4.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="I3" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
@@ -999,7 +999,7 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="W3" t="n">
         <v>1.31</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
         <v>27</v>
@@ -1160,7 +1160,7 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.01</v>
@@ -1190,7 +1190,7 @@
         <v>2.3</v>
       </c>
       <c r="U4" t="n">
-        <v>1.47</v>
+        <v>1.54</v>
       </c>
       <c r="V4" t="n">
         <v>4.8</v>
@@ -1277,7 +1277,7 @@
         <v>1.54</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="AY4" t="n">
         <v>1.51</v>
@@ -1289,26 +1289,26 @@
         <v>1.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.08</v>
+        <v>1.27</v>
       </c>
       <c r="BG4" t="n">
         <v>3.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
         <v>3.65</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.1</v>
@@ -1372,7 +1372,7 @@
         <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
         <v>1.38</v>
       </c>
       <c r="R6" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
         <v>1.38</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
         <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="I7" t="n">
         <v>21</v>
@@ -1742,7 +1742,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="G9" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="I9" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
@@ -2139,22 +2139,22 @@
         <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>2.64</v>
+        <v>1.41</v>
       </c>
       <c r="O9" t="n">
-        <v>1.52</v>
+        <v>1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>1.54</v>
+        <v>1.41</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S9" t="n">
-        <v>4.8</v>
+        <v>2.3</v>
       </c>
       <c r="T9" t="n">
         <v>2.12</v>
@@ -2163,10 +2163,10 @@
         <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="W9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>10.5</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU9" t="n">
         <v>3.6</v>
       </c>
-      <c r="AQ9" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AV9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AW9" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="AX9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY9" t="n">
         <v>4.9</v>
       </c>
-      <c r="AY9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AZ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BG9" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA9" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -2327,10 +2327,10 @@
         <v>6.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N10" t="n">
         <v>2.38</v>
@@ -2348,7 +2348,7 @@
         <v>1.37</v>
       </c>
       <c r="S10" t="n">
-        <v>2.46</v>
+        <v>2.6</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
         <v>1.69</v>
       </c>
       <c r="R11" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="S11" t="n">
         <v>1.69</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -2739,10 +2739,10 @@
         <v>3.35</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V12" t="n">
         <v>1.41</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="J13" t="n">
         <v>3.1</v>
@@ -2909,7 +2909,7 @@
         <v>3.45</v>
       </c>
       <c r="L13" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.1</v>
@@ -2936,13 +2936,13 @@
         <v>2</v>
       </c>
       <c r="U13" t="n">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6</v>
+        <v>1.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3002,7 +3002,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>6.8</v>
+        <v>5.9</v>
       </c>
       <c r="AR13" t="n">
         <v>11.5</v>
@@ -3014,7 +3014,7 @@
         <v>10</v>
       </c>
       <c r="AU13" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
         <v>10</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3085,7 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="G14" t="n">
         <v>1.98</v>
@@ -3100,10 +3100,10 @@
         <v>3.45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3112,22 +3112,22 @@
         <v>3.45</v>
       </c>
       <c r="O14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>1.31</v>
       </c>
       <c r="S14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T14" t="n">
-        <v>1.74</v>
+        <v>1.84</v>
       </c>
       <c r="U14" t="n">
         <v>2</v>
@@ -3223,7 +3223,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
         <v>2.04</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J15" t="n">
         <v>3.6</v>
@@ -3297,7 +3297,7 @@
         <v>3.9</v>
       </c>
       <c r="L15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
@@ -3315,13 +3315,13 @@
         <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
-        <v>2.74</v>
+        <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U15" t="n">
         <v>2.2</v>
@@ -3399,7 +3399,7 @@
         <v>6.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>13</v>
+        <v>5.5</v>
       </c>
       <c r="AU15" t="n">
         <v>7.6</v>
@@ -3408,10 +3408,10 @@
         <v>9.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AX15" t="n">
-        <v>21</v>
+        <v>6.4</v>
       </c>
       <c r="AY15" t="n">
         <v>13</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         <v>1.65</v>
       </c>
       <c r="O16" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="P16" t="n">
         <v>1.65</v>
@@ -3509,7 +3509,7 @@
         <v>1.95</v>
       </c>
       <c r="R16" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S16" t="n">
         <v>3.25</v>
@@ -3581,25 +3581,25 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU16" t="n">
         <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW16" t="n">
         <v>23</v>
@@ -3611,10 +3611,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BB16" t="n">
         <v>30</v>
@@ -3623,7 +3623,7 @@
         <v>25</v>
       </c>
       <c r="BD16" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="BE16" t="n">
         <v>50</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -3667,13 +3667,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>1.7</v>
       </c>
       <c r="G17" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I17" t="n">
         <v>5.3</v>
@@ -3682,155 +3682,155 @@
         <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>1.23</v>
+        <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P17" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="R17" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="V17" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM17" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>9.4</v>
+        <v>3.25</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.800000000000001</v>
+        <v>3.4</v>
       </c>
       <c r="AR17" t="n">
-        <v>22</v>
+        <v>3.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>60</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>6.6</v>
+        <v>2.96</v>
       </c>
       <c r="AV17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF17" t="n">
         <v>14.5</v>
       </c>
-      <c r="AW17" t="n">
-        <v>42</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>19</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>36</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>90</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -3870,7 +3870,7 @@
         <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
@@ -3909,7 +3909,7 @@
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W18" t="n">
         <v>1.74</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -4267,7 +4267,7 @@
         <v>4.7</v>
       </c>
       <c r="L20" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -4300,7 +4300,7 @@
         <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X20" t="n">
         <v>36</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="G21" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="H21" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="I21" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="J21" t="n">
-        <v>2.68</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
@@ -4467,22 +4467,22 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.48</v>
+        <v>2.64</v>
       </c>
       <c r="O21" t="n">
         <v>1.43</v>
       </c>
       <c r="P21" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4491,10 +4491,10 @@
         <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X21" t="n">
         <v>1000</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>4.3</v>
       </c>
       <c r="H22" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="I22" t="n">
         <v>2.2</v>
@@ -4661,7 +4661,7 @@
         <v>1.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="O22" t="n">
         <v>1.46</v>
@@ -4670,13 +4670,13 @@
         <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T22" t="n">
         <v>1.85</v>
@@ -4691,10 +4691,10 @@
         <v>1.3</v>
       </c>
       <c r="X22" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Z22" t="n">
         <v>14.5</v>
@@ -4706,7 +4706,7 @@
         <v>15.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>13.5</v>
@@ -4715,7 +4715,7 @@
         <v>34</v>
       </c>
       <c r="AF22" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG22" t="n">
         <v>23</v>
@@ -4727,22 +4727,22 @@
         <v>65</v>
       </c>
       <c r="AJ22" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK22" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL22" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN22" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO22" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AP22" t="n">
         <v>3.15</v>
@@ -4754,7 +4754,7 @@
         <v>3.3</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AT22" t="n">
         <v>3.35</v>
@@ -4766,13 +4766,13 @@
         <v>3.25</v>
       </c>
       <c r="AW22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AX22" t="n">
         <v>3.85</v>
       </c>
-      <c r="AX22" t="n">
-        <v>3.9</v>
-      </c>
       <c r="AY22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AZ22" t="n">
         <v>3.7</v>
@@ -4781,10 +4781,10 @@
         <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BD22" t="n">
         <v>4.1</v>
@@ -4793,14 +4793,14 @@
         <v>4.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -4831,170 +4831,170 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="G23" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="H23" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="J23" t="n">
-        <v>2.92</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N23" t="n">
+        <v>3</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="P23" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="X23" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB23" t="n">
         <v>8.6</v>
       </c>
-      <c r="L23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC23" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL23" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM23" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV23" t="n">
         <v>15</v>
       </c>
       <c r="AW23" t="n">
-        <v>44</v>
+        <v>4.8</v>
       </c>
       <c r="AX23" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AY23" t="n">
         <v>9</v>
       </c>
-      <c r="AY23" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ23" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>50</v>
+        <v>4.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD23" t="n">
-        <v>36</v>
+        <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>50</v>
+        <v>4.9</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BG23" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5061,7 @@
         <v>2.12</v>
       </c>
       <c r="R24" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S24" t="n">
         <v>2.12</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
         <v>1.96</v>
       </c>
       <c r="R25" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S25" t="n">
         <v>1.96</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -5413,170 +5413,170 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.04</v>
+        <v>1.47</v>
       </c>
       <c r="G26" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>12</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.54</v>
       </c>
-      <c r="H26" t="n">
+      <c r="V26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="X26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF26" t="n">
         <v>8</v>
       </c>
-      <c r="I26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="K26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="S26" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>50</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG26" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -5643,7 +5643,7 @@
         <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="S27" t="n">
         <v>2.16</v>
@@ -5652,7 +5652,7 @@
         <v>1.01</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V27" t="n">
         <v>1.8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N28" t="n">
         <v>1.73</v>
@@ -5837,7 +5837,7 @@
         <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.08</v>
+        <v>1.2</v>
       </c>
       <c r="S28" t="n">
         <v>1.8</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.51</v>
       </c>
       <c r="G29" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="H29" t="n">
         <v>6.2</v>
@@ -6019,13 +6019,13 @@
         <v>1.01</v>
       </c>
       <c r="N29" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="O29" t="n">
         <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q29" t="n">
         <v>1.59</v>
@@ -6046,119 +6046,119 @@
         <v>1.13</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="X29" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Y29" t="n">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="Z29" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AA29" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AB29" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>130</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC29" t="n">
         <v>13.5</v>
       </c>
-      <c r="AC29" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>38</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>21</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.9</v>
-      </c>
       <c r="BD29" t="n">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF29" t="n">
-        <v>2.08</v>
+        <v>5.6</v>
       </c>
       <c r="BG29" t="n">
-        <v>2.08</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -6192,7 +6192,7 @@
         <v>2.3</v>
       </c>
       <c r="G30" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H30" t="n">
         <v>3.65</v>
@@ -6210,10 +6210,10 @@
         <v>1.49</v>
       </c>
       <c r="M30" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O30" t="n">
         <v>1.42</v>
@@ -6222,7 +6222,7 @@
         <v>1.72</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="R30" t="n">
         <v>1.27</v>
@@ -6240,7 +6240,7 @@
         <v>1.36</v>
       </c>
       <c r="W30" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X30" t="n">
         <v>11</v>
@@ -6312,7 +6312,7 @@
         <v>8</v>
       </c>
       <c r="AU30" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV30" t="n">
         <v>14</v>
@@ -6348,11 +6348,11 @@
         <v>21</v>
       </c>
       <c r="BG30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>2.96</v>
       </c>
       <c r="I31" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
         <v>3.1</v>
@@ -6431,7 +6431,7 @@
         <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="W31" t="n">
         <v>1.55</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -6577,10 +6577,10 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G32" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
         <v>4.9</v>
@@ -6592,16 +6592,16 @@
         <v>3.5</v>
       </c>
       <c r="K32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M32" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>1.42</v>
@@ -6610,13 +6610,13 @@
         <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
         <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6628,7 +6628,7 @@
         <v>1.25</v>
       </c>
       <c r="W32" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="X32" t="n">
         <v>11</v>
@@ -6640,7 +6640,7 @@
         <v>36</v>
       </c>
       <c r="AA32" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AB32" t="n">
         <v>7.6</v>
@@ -6664,7 +6664,7 @@
         <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AJ32" t="n">
         <v>21</v>
@@ -6691,7 +6691,7 @@
         <v>13</v>
       </c>
       <c r="AR32" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AS32" t="n">
         <v>40</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G33" t="n">
         <v>2.24</v>
@@ -6789,16 +6789,16 @@
         <v>3.5</v>
       </c>
       <c r="L33" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="M33" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N33" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="P33" t="n">
         <v>1.8</v>
@@ -6807,16 +6807,16 @@
         <v>2.22</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="T33" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U33" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V33" t="n">
         <v>1.3</v>
@@ -6825,116 +6825,116 @@
         <v>1.8</v>
       </c>
       <c r="X33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>85</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV33" t="n">
         <v>14.5</v>
       </c>
-      <c r="Y33" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB33" t="n">
+      <c r="AW33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD33" t="n">
         <v>10</v>
       </c>
-      <c r="AC33" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>32</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>19</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>48</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>36</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>3</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.65</v>
-      </c>
       <c r="BE33" t="n">
-        <v>3.95</v>
+        <v>12</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.95</v>
+        <v>15</v>
       </c>
       <c r="BG33" t="n">
-        <v>3.95</v>
+        <v>11</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -6989,22 +6989,22 @@
         <v>1.01</v>
       </c>
       <c r="N34" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="O34" t="n">
         <v>1.4</v>
       </c>
       <c r="P34" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R34" t="n">
         <v>1.2</v>
       </c>
       <c r="S34" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T34" t="n">
         <v>1.01</v>
@@ -7097,7 +7097,7 @@
         <v>2.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>2.06</v>
+        <v>8.4</v>
       </c>
       <c r="AY34" t="n">
         <v>2.08</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>3.15</v>
       </c>
       <c r="G35" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="H35" t="n">
         <v>1.67</v>
@@ -7171,7 +7171,7 @@
         <v>2.86</v>
       </c>
       <c r="J35" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="K35" t="n">
         <v>1000</v>
@@ -7186,7 +7186,7 @@
         <v>1.46</v>
       </c>
       <c r="O35" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="P35" t="n">
         <v>1.46</v>
@@ -7195,7 +7195,7 @@
         <v>2.26</v>
       </c>
       <c r="R35" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="S35" t="n">
         <v>4.2</v>
@@ -7210,7 +7210,7 @@
         <v>1.53</v>
       </c>
       <c r="W35" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X35" t="n">
         <v>1000</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H36" t="n">
         <v>2.18</v>
       </c>
       <c r="I36" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="J36" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="K36" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L36" t="n">
         <v>1.01</v>
@@ -7380,19 +7380,19 @@
         <v>1.65</v>
       </c>
       <c r="O36" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P36" t="n">
         <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R36" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="T36" t="n">
         <v>1.01</v>
@@ -7401,122 +7401,122 @@
         <v>1.01</v>
       </c>
       <c r="V36" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="X36" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB36" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AD36" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF36" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG36" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AH36" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI36" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ36" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AK36" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL36" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AM36" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN36" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO36" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AP36" t="n">
-        <v>9.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AR36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AS36" t="n">
-        <v>23</v>
+        <v>4.3</v>
       </c>
       <c r="AT36" t="n">
-        <v>8.800000000000001</v>
+        <v>4.9</v>
       </c>
       <c r="AU36" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BG36" t="n">
         <v>6</v>
       </c>
-      <c r="AV36" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>38</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>50</v>
-      </c>
-      <c r="BF36" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BG36" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -7547,7 +7547,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="G37" t="n">
         <v>1.56</v>
@@ -7562,19 +7562,19 @@
         <v>4.2</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P37" t="n">
         <v>1.86</v>
@@ -7583,134 +7583,134 @@
         <v>1.96</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BG37" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -7759,16 +7759,16 @@
         <v>5.8</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P38" t="n">
         <v>1.84</v>
@@ -7777,134 +7777,134 @@
         <v>1.71</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="G39" t="n">
-        <v>4</v>
+        <v>1000</v>
       </c>
       <c r="H39" t="n">
-        <v>2.28</v>
+        <v>1.87</v>
       </c>
       <c r="I39" t="n">
         <v>3.25</v>
       </c>
       <c r="J39" t="n">
-        <v>2.74</v>
+        <v>2</v>
       </c>
       <c r="K39" t="n">
-        <v>5.3</v>
+        <v>7.8</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7971,7 +7971,7 @@
         <v>2.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="S39" t="n">
         <v>4.1</v>
@@ -7983,10 +7983,10 @@
         <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W39" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-07 18:52:57</t>
+          <t>2026-03-07 21:15:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -871,7 +871,7 @@
         <v>21</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.7</v>
+        <v>38</v>
       </c>
       <c r="AS2" t="n">
         <v>5</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>3.7</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H3" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="J3" t="n">
         <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L3" t="n">
         <v>1.49</v>
@@ -975,7 +975,7 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
@@ -984,7 +984,7 @@
         <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -999,10 +999,10 @@
         <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X3" t="n">
         <v>11.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="G4" t="n">
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I4" t="n">
         <v>1.26</v>
@@ -1160,10 +1160,10 @@
         <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M4" t="n">
         <v>1.04</v>
@@ -1172,13 +1172,13 @@
         <v>3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
@@ -1187,7 +1187,7 @@
         <v>2.46</v>
       </c>
       <c r="T4" t="n">
-        <v>2.3</v>
+        <v>2.52</v>
       </c>
       <c r="U4" t="n">
         <v>1.54</v>
@@ -1253,43 +1253,43 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AX4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BB4" t="n">
         <v>1.27</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.28</v>
       </c>
       <c r="BC4" t="n">
         <v>1.27</v>
@@ -1301,14 +1301,14 @@
         <v>1.27</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="BG4" t="n">
         <v>3.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -1342,10 +1342,10 @@
         <v>4.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
@@ -1363,22 +1363,22 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="O5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
         <v>2.06</v>
@@ -1393,10 +1393,10 @@
         <v>1.2</v>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.4</v>
+        <v>970</v>
       </c>
       <c r="Z5" t="n">
         <v>12</v>
@@ -1405,13 +1405,13 @@
         <v>28</v>
       </c>
       <c r="AB5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>29</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="AX5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>6.2</v>
       </c>
-      <c r="AY5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>6</v>
-      </c>
       <c r="BA5" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="BG5" t="n">
         <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -1769,7 +1769,7 @@
         <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="U7" t="n">
         <v>1.52</v>
@@ -1820,7 +1820,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AK7" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AL7" t="n">
         <v>65</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
         <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -1975,10 +1975,10 @@
         <v>1.58</v>
       </c>
       <c r="X8" t="n">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="Y8" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="Z8" t="n">
         <v>23</v>
@@ -1987,22 +1987,22 @@
         <v>80</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.4</v>
+        <v>970</v>
       </c>
       <c r="AD8" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AE8" t="n">
         <v>50</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>970</v>
       </c>
       <c r="AG8" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AH8" t="n">
         <v>22</v>
@@ -2038,7 +2038,7 @@
         <v>7</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2050,7 +2050,7 @@
         <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX8" t="n">
         <v>6.2</v>
@@ -2062,7 +2062,7 @@
         <v>7</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.74</v>
+        <v>2.18</v>
       </c>
       <c r="BB8" t="n">
         <v>4.2</v>
@@ -2074,17 +2074,17 @@
         <v>4.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BF8" t="n">
         <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -2115,46 +2115,46 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="G9" t="n">
         <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
-        <v>2.06</v>
+        <v>1.93</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
       </c>
       <c r="M9" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N9" t="n">
-        <v>1.41</v>
+        <v>2.64</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1</v>
+        <v>1.52</v>
       </c>
       <c r="P9" t="n">
-        <v>1.41</v>
+        <v>1.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.3</v>
+        <v>2.58</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S9" t="n">
-        <v>2.3</v>
+        <v>4.8</v>
       </c>
       <c r="T9" t="n">
         <v>2.12</v>
@@ -2163,10 +2163,10 @@
         <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="W9" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="X9" t="n">
         <v>10.5</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -2309,170 +2309,170 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4</v>
+        <v>3.45</v>
       </c>
       <c r="H10" t="n">
-        <v>2.02</v>
+        <v>2.22</v>
       </c>
       <c r="I10" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.29</v>
       </c>
       <c r="M10" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>2.38</v>
+        <v>4.2</v>
       </c>
       <c r="O10" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P10" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.59</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y10" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC10" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF10" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP10" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AY10" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC10" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD10" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG10" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
         <v>2.56</v>
       </c>
       <c r="H11" t="n">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="I11" t="n">
         <v>4.7</v>
@@ -2518,7 +2518,7 @@
         <v>3.2</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="H13" t="n">
         <v>2.18</v>
       </c>
       <c r="I13" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="K13" t="n">
         <v>3.45</v>
@@ -2924,7 +2924,7 @@
         <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.34</v>
+        <v>2.14</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
@@ -2933,7 +2933,7 @@
         <v>4</v>
       </c>
       <c r="T13" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="U13" t="n">
         <v>1.86</v>
@@ -2942,7 +2942,7 @@
         <v>1.72</v>
       </c>
       <c r="W13" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -3005,25 +3005,25 @@
         <v>5.9</v>
       </c>
       <c r="AR13" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="AS13" t="n">
         <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
         <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="AY13" t="n">
         <v>14.5</v>
@@ -3050,11 +3050,11 @@
         <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>3.8</v>
       </c>
       <c r="L14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M14" t="n">
         <v>1.08</v>
@@ -3223,7 +3223,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA14" t="n">
         <v>7</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="G15" t="n">
         <v>4.1</v>
@@ -3315,7 +3315,7 @@
         <v>1.81</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3339,7 +3339,7 @@
         <v>11</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA15" t="n">
         <v>27</v>
@@ -3360,10 +3360,10 @@
         <v>30</v>
       </c>
       <c r="AG15" t="n">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AI15" t="n">
         <v>36</v>
@@ -3414,7 +3414,7 @@
         <v>6.4</v>
       </c>
       <c r="AY15" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>5.6</v>
@@ -3429,7 +3429,7 @@
         <v>7</v>
       </c>
       <c r="BD15" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="BE15" t="n">
         <v>7.6</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.28</v>
+        <v>2.82</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
       </c>
       <c r="K16" t="n">
-        <v>110</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,34 +3497,34 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>1.65</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U16" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V16" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
         <v>1000</v>
@@ -3581,52 +3581,52 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS16" t="n">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AV16" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW16" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="AY16" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BA16" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BB16" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC16" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BD16" t="n">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE16" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF16" t="n">
         <v>1.01</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.7</v>
+        <v>1.99</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H17" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="I17" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="J17" t="n">
         <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3694,19 +3694,19 @@
         <v>3.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
       </c>
       <c r="S17" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="T17" t="n">
         <v>1.79</v>
@@ -3718,7 +3718,7 @@
         <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -3784,7 +3784,7 @@
         <v>3.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
@@ -3802,7 +3802,7 @@
         <v>3.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ17" t="n">
         <v>3.7</v>
@@ -3814,7 +3814,7 @@
         <v>3.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -3864,13 +3864,13 @@
         <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="H18" t="n">
         <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX19" t="n">
         <v>14</v>
@@ -4196,13 +4196,13 @@
         <v>17</v>
       </c>
       <c r="BA19" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB19" t="n">
         <v>7.4</v>
       </c>
       <c r="BC19" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD19" t="n">
         <v>7.6</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.65</v>
@@ -4297,7 +4297,7 @@
         <v>2.54</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
         <v>1.74</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -4443,170 +4443,170 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="G21" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="H21" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="I21" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.01</v>
       </c>
       <c r="M21" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="P21" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T21" t="n">
         <v>2.18</v>
       </c>
-      <c r="R21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="S21" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U21" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="V21" t="n">
         <v>2.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="X21" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y21" t="n">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="Z21" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AA21" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC21" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE21" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF21" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AG21" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AH21" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AI21" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
         <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>1000</v>
+        <v>240</v>
       </c>
       <c r="AL21" t="n">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AM21" t="n">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AN21" t="n">
         <v>1000</v>
       </c>
       <c r="AO21" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP21" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AT21" t="n">
-        <v>13.5</v>
+        <v>4.2</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.199999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="AW21" t="n">
-        <v>17.5</v>
+        <v>4.3</v>
       </c>
       <c r="AX21" t="n">
-        <v>40</v>
+        <v>4.9</v>
       </c>
       <c r="AY21" t="n">
-        <v>24</v>
+        <v>4.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>26</v>
+        <v>4.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>44</v>
+        <v>4.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="BC21" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="BD21" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="BE21" t="n">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
         <v>1.1</v>
@@ -4670,7 +4670,7 @@
         <v>1.62</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
@@ -4697,13 +4697,13 @@
         <v>9</v>
       </c>
       <c r="Z22" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA22" t="n">
         <v>34</v>
       </c>
       <c r="AB22" t="n">
-        <v>15.5</v>
+        <v>970</v>
       </c>
       <c r="AC22" t="n">
         <v>9.199999999999999</v>
@@ -4745,7 +4745,7 @@
         <v>28</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AQ22" t="n">
         <v>2.9</v>
@@ -4784,7 +4784,7 @@
         <v>4.1</v>
       </c>
       <c r="BC22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD22" t="n">
         <v>4.1</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -4846,10 +4846,10 @@
         <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L23" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4861,10 +4861,10 @@
         <v>1.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="R23" t="n">
         <v>1.26</v>
@@ -4873,13 +4873,13 @@
         <v>3.75</v>
       </c>
       <c r="T23" t="n">
-        <v>1.69</v>
+        <v>1.85</v>
       </c>
       <c r="U23" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="V23" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W23" t="n">
         <v>1.95</v>
@@ -4939,19 +4939,19 @@
         <v>120</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.800000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ23" t="n">
         <v>11</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AU23" t="n">
         <v>6.8</v>
@@ -4972,7 +4972,7 @@
         <v>4.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB23" t="n">
         <v>19</v>
@@ -4984,7 +4984,7 @@
         <v>4.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF23" t="n">
         <v>13.5</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -5133,52 +5133,52 @@
         <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR24" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AS24" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT24" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV24" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW24" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AX24" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY24" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ24" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA24" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB24" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC24" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD24" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BE24" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF24" t="n">
         <v>1.01</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>5</v>
       </c>
       <c r="I25" t="n">
-        <v>150</v>
+        <v>17</v>
       </c>
       <c r="J25" t="n">
         <v>3.3</v>
@@ -5267,7 +5267,7 @@
         <v>1.01</v>
       </c>
       <c r="V25" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
         <v>2.14</v>
@@ -5327,52 +5327,52 @@
         <v>1000</v>
       </c>
       <c r="AP25" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ25" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR25" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="AS25" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT25" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AU25" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV25" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW25" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AX25" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY25" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ25" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA25" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BB25" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BC25" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD25" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE25" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="G26" t="n">
         <v>1.66</v>
       </c>
       <c r="H26" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
         <v>12</v>
@@ -5446,13 +5446,13 @@
         <v>1.71</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="T26" t="n">
         <v>2.08</v>
@@ -5464,13 +5464,13 @@
         <v>1.09</v>
       </c>
       <c r="W26" t="n">
-        <v>2.74</v>
+        <v>2.5</v>
       </c>
       <c r="X26" t="n">
         <v>14.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z26" t="n">
         <v>100</v>
@@ -5479,10 +5479,10 @@
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC26" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AD26" t="n">
         <v>44</v>
@@ -5491,22 +5491,22 @@
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AG26" t="n">
         <v>12.5</v>
       </c>
       <c r="AH26" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AI26" t="n">
         <v>220</v>
       </c>
       <c r="AJ26" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK26" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="AL26" t="n">
         <v>75</v>
@@ -5515,68 +5515,68 @@
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
       <c r="AR26" t="n">
-        <v>5.8</v>
+        <v>4.2</v>
       </c>
       <c r="AS26" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.45</v>
+        <v>5.5</v>
       </c>
       <c r="AU26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW26" t="n">
         <v>4.3</v>
       </c>
-      <c r="AV26" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AX26" t="n">
-        <v>3.85</v>
+        <v>3</v>
       </c>
       <c r="AY26" t="n">
-        <v>4.7</v>
+        <v>3.25</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.94</v>
+        <v>4</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.47</v>
+        <v>4.3</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>5.4</v>
+        <v>3.75</v>
       </c>
       <c r="BD26" t="n">
-        <v>1.87</v>
+        <v>4.1</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.48</v>
+        <v>4.3</v>
       </c>
       <c r="BF26" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>1.48</v>
+        <v>4.4</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -5610,7 +5610,7 @@
         <v>3.85</v>
       </c>
       <c r="G27" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="H27" t="n">
         <v>1.75</v>
@@ -5634,7 +5634,7 @@
         <v>1.47</v>
       </c>
       <c r="O27" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P27" t="n">
         <v>1.47</v>
@@ -5649,7 +5649,7 @@
         <v>2.16</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="U27" t="n">
         <v>1.65</v>
@@ -5715,52 +5715,52 @@
         <v>1000</v>
       </c>
       <c r="AP27" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR27" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS27" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT27" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU27" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV27" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW27" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AX27" t="n">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AY27" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA27" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB27" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BC27" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BD27" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BE27" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF27" t="n">
         <v>1.01</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
         <v>1.8</v>
       </c>
       <c r="R28" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S28" t="n">
         <v>1.8</v>
@@ -5909,52 +5909,52 @@
         <v>1000</v>
       </c>
       <c r="AP28" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ28" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AR28" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AS28" t="n">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="AT28" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AW28" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AX28" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AY28" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ28" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA28" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB28" t="n">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC28" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD28" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE28" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -5995,16 +5995,16 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G29" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="H29" t="n">
         <v>6.2</v>
       </c>
       <c r="I29" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="J29" t="n">
         <v>4.3</v>
@@ -6016,37 +6016,37 @@
         <v>1.32</v>
       </c>
       <c r="M29" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O29" t="n">
         <v>1.24</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
         <v>1.59</v>
       </c>
       <c r="R29" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="S29" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="T29" t="n">
-        <v>1.57</v>
+        <v>1.83</v>
       </c>
       <c r="U29" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V29" t="n">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="W29" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="X29" t="n">
         <v>21</v>
@@ -6058,7 +6058,7 @@
         <v>60</v>
       </c>
       <c r="AA29" t="n">
-        <v>230</v>
+        <v>180</v>
       </c>
       <c r="AB29" t="n">
         <v>9.800000000000001</v>
@@ -6100,7 +6100,7 @@
         <v>7.8</v>
       </c>
       <c r="AO29" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AP29" t="n">
         <v>17</v>
@@ -6109,10 +6109,10 @@
         <v>20</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT29" t="n">
         <v>8.199999999999999</v>
@@ -6124,7 +6124,7 @@
         <v>21</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX29" t="n">
         <v>8.4</v>
@@ -6136,7 +6136,7 @@
         <v>18</v>
       </c>
       <c r="BA29" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB29" t="n">
         <v>12</v>
@@ -6145,20 +6145,20 @@
         <v>13.5</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BG29" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -6195,7 +6195,7 @@
         <v>2.32</v>
       </c>
       <c r="H30" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I30" t="n">
         <v>3.75</v>
@@ -6330,7 +6330,7 @@
         <v>18.5</v>
       </c>
       <c r="BA30" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB30" t="n">
         <v>27</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
         <v>3.45</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="M31" t="n">
         <v>1.11</v>
@@ -6440,7 +6440,7 @@
         <v>11.5</v>
       </c>
       <c r="Y31" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z31" t="n">
         <v>21</v>
@@ -6455,7 +6455,7 @@
         <v>8</v>
       </c>
       <c r="AD31" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE31" t="n">
         <v>50</v>
@@ -6500,7 +6500,7 @@
         <v>14.5</v>
       </c>
       <c r="AS31" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT31" t="n">
         <v>6.2</v>
@@ -6512,7 +6512,7 @@
         <v>10</v>
       </c>
       <c r="AW31" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX31" t="n">
         <v>11.5</v>
@@ -6524,29 +6524,29 @@
         <v>17</v>
       </c>
       <c r="BA31" t="n">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BB31" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BC31" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD31" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE31" t="n">
-        <v>120</v>
+        <v>1.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BG31" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -6589,7 +6589,7 @@
         <v>5</v>
       </c>
       <c r="J32" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K32" t="n">
         <v>3.6</v>
@@ -6664,7 +6664,7 @@
         <v>23</v>
       </c>
       <c r="AI32" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ32" t="n">
         <v>21</v>
@@ -6673,7 +6673,7 @@
         <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM32" t="n">
         <v>150</v>
@@ -6736,11 +6736,11 @@
         <v>15.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -6774,10 +6774,10 @@
         <v>2.12</v>
       </c>
       <c r="G33" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I33" t="n">
         <v>4.3</v>
@@ -6822,7 +6822,7 @@
         <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="X33" t="n">
         <v>12.5</v>
@@ -6885,7 +6885,7 @@
         <v>12</v>
       </c>
       <c r="AR33" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AS33" t="n">
         <v>11.5</v>
@@ -6900,7 +6900,7 @@
         <v>14.5</v>
       </c>
       <c r="AW33" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="AX33" t="n">
         <v>11.5</v>
@@ -6915,7 +6915,7 @@
         <v>11</v>
       </c>
       <c r="BB33" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC33" t="n">
         <v>21</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>1.8</v>
       </c>
       <c r="G34" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H34" t="n">
         <v>4.9</v>
@@ -6986,149 +6986,149 @@
         <v>1.01</v>
       </c>
       <c r="M34" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P34" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R34" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="T34" t="n">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="U34" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V34" t="n">
         <v>1.17</v>
       </c>
       <c r="W34" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X34" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="Y34" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>50</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>190</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>110</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>120</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>60</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN34" t="n">
         <v>21</v>
       </c>
-      <c r="Z34" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>34</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>30</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>1000</v>
-      </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AP34" t="n">
-        <v>2.08</v>
+        <v>9.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>2.14</v>
+        <v>12.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT34" t="n">
-        <v>1.94</v>
+        <v>6.2</v>
       </c>
       <c r="AU34" t="n">
-        <v>1.99</v>
+        <v>7</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.22</v>
+        <v>18</v>
       </c>
       <c r="AW34" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY34" t="n">
-        <v>2.08</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ34" t="n">
-        <v>2.24</v>
+        <v>19.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="BB34" t="n">
-        <v>2.22</v>
+        <v>17.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.24</v>
+        <v>19.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>2.32</v>
+        <v>4.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF34" t="n">
-        <v>2.4</v>
+        <v>12.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>2.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7165,7 @@
         <v>4.5</v>
       </c>
       <c r="H35" t="n">
-        <v>1.67</v>
+        <v>1.99</v>
       </c>
       <c r="I35" t="n">
         <v>2.86</v>
@@ -7174,7 +7174,7 @@
         <v>2.34</v>
       </c>
       <c r="K35" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -7353,25 +7353,25 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G36" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H36" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I36" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="K36" t="n">
         <v>3.35</v>
       </c>
       <c r="L36" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M36" t="n">
         <v>1.01</v>
@@ -7461,13 +7461,13 @@
         <v>28</v>
       </c>
       <c r="AP36" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>4</v>
       </c>
       <c r="AR36" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AS36" t="n">
         <v>4.3</v>
@@ -7500,23 +7500,23 @@
         <v>7.2</v>
       </c>
       <c r="BC36" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="BD36" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="BE36" t="n">
         <v>1.97</v>
       </c>
       <c r="BF36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BG36" t="n">
         <v>6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>1.48</v>
       </c>
       <c r="G37" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H37" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="I37" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="J37" t="n">
         <v>4.2</v>
@@ -7565,152 +7565,152 @@
         <v>5.1</v>
       </c>
       <c r="L37" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M37" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.86</v>
+        <v>3.65</v>
       </c>
       <c r="O37" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P37" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="Q37" t="n">
         <v>1.96</v>
       </c>
       <c r="R37" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S37" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="V37" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="W37" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="X37" t="n">
-        <v>20</v>
+        <v>15.5</v>
       </c>
       <c r="Y37" t="n">
+        <v>28</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>85</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>320</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>38</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>170</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH37" t="n">
         <v>32</v>
       </c>
-      <c r="Z37" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>42</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF37" t="n">
+      <c r="AI37" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>46</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>250</v>
+      </c>
+      <c r="AP37" t="n">
         <v>12</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AQ37" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC37" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH37" t="n">
-        <v>36</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>19</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>60</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.16</v>
-      </c>
       <c r="BD37" t="n">
-        <v>2.28</v>
+        <v>4.4</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.36</v>
+        <v>7.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.36</v>
+        <v>4.8</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -7753,40 +7753,40 @@
         <v>11.5</v>
       </c>
       <c r="J38" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K38" t="n">
         <v>5.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M38" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N38" t="n">
+        <v>4</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P38" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q38" t="n">
         <v>1.84</v>
       </c>
-      <c r="O38" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.71</v>
-      </c>
       <c r="R38" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="S38" t="n">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="T38" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="U38" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V38" t="n">
         <v>1.09</v>
@@ -7795,7 +7795,7 @@
         <v>2.96</v>
       </c>
       <c r="X38" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y38" t="n">
         <v>1000</v>
@@ -7807,82 +7807,82 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC38" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AF38" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AG38" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH38" t="n">
         <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ38" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AK38" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL38" t="n">
         <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN38" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>14</v>
+        <v>4.1</v>
       </c>
       <c r="AQ38" t="n">
-        <v>19</v>
+        <v>4.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>44</v>
+        <v>4.9</v>
       </c>
       <c r="AS38" t="n">
-        <v>100</v>
+        <v>5.2</v>
       </c>
       <c r="AT38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV38" t="n">
-        <v>25</v>
+        <v>4.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>90</v>
+        <v>5.1</v>
       </c>
       <c r="AX38" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AY38" t="n">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="AZ38" t="n">
-        <v>20</v>
+        <v>4.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>85</v>
+        <v>5.1</v>
       </c>
       <c r="BB38" t="n">
         <v>9.800000000000001</v>
@@ -7891,20 +7891,20 @@
         <v>12.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>30</v>
+        <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>100</v>
+        <v>5.1</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>
@@ -7938,19 +7938,19 @@
         <v>2.96</v>
       </c>
       <c r="G39" t="n">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="H39" t="n">
-        <v>1.87</v>
+        <v>2.16</v>
       </c>
       <c r="I39" t="n">
         <v>3.25</v>
       </c>
       <c r="J39" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="K39" t="n">
-        <v>7.8</v>
+        <v>5</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7986,7 +7986,7 @@
         <v>1.44</v>
       </c>
       <c r="W39" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-07 21:15:56</t>
+          <t>2026-03-07 23:37:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH39"/>
+  <dimension ref="A1:BH42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="G2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
       </c>
       <c r="K2" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.19</v>
       </c>
       <c r="P2" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="R2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="S2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W2" t="n">
         <v>2.42</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="W2" t="n">
-        <v>2.38</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
       </c>
       <c r="Y2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
@@ -838,7 +838,7 @@
         <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -874,7 +874,7 @@
         <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -898,7 +898,7 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -910,17 +910,17 @@
         <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G3" t="n">
         <v>4.2</v>
@@ -960,10 +960,10 @@
         <v>2.16</v>
       </c>
       <c r="I3" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K3" t="n">
         <v>3.45</v>
@@ -975,31 +975,31 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V3" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
@@ -1089,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>17.5</v>
+        <v>6</v>
       </c>
       <c r="BA3" t="n">
         <v>7.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -1151,40 +1151,40 @@
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I4" t="n">
         <v>1.26</v>
       </c>
       <c r="J4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="K4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
       </c>
       <c r="M4" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
       </c>
       <c r="S4" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="T4" t="n">
         <v>2.52</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.27</v>
+        <v>1.72</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="AT4" t="n">
-        <v>9.4</v>
+        <v>1.24</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.25</v>
+        <v>2.06</v>
       </c>
       <c r="AV4" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.6</v>
+        <v>2.36</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="BF4" t="n">
         <v>1.16</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="G5" t="n">
         <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
@@ -1354,13 +1354,13 @@
         <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
         <v>2.54</v>
@@ -1402,7 +1402,7 @@
         <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB5" t="n">
         <v>970</v>
@@ -1450,10 +1450,10 @@
         <v>4.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS5" t="n">
         <v>6</v>
@@ -1465,7 +1465,7 @@
         <v>4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW5" t="n">
         <v>3.55</v>
@@ -1489,20 +1489,20 @@
         <v>2.42</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="BG5" t="n">
         <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -1733,13 +1733,13 @@
         <v>1.36</v>
       </c>
       <c r="H7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="I7" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K7" t="n">
         <v>5.6</v>
@@ -1760,7 +1760,7 @@
         <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="R7" t="n">
         <v>1.33</v>
@@ -1772,7 +1772,7 @@
         <v>2.6</v>
       </c>
       <c r="U7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="V7" t="n">
         <v>1.05</v>
@@ -1787,7 +1787,7 @@
         <v>38</v>
       </c>
       <c r="Z7" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AA7" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>65</v>
       </c>
       <c r="AE7" t="n">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="AF7" t="n">
         <v>7.8</v>
@@ -1814,7 +1814,7 @@
         <v>55</v>
       </c>
       <c r="AI7" t="n">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="AJ7" t="n">
         <v>9.800000000000001</v>
@@ -1826,10 +1826,10 @@
         <v>65</v>
       </c>
       <c r="AM7" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AN7" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AO7" t="n">
         <v>1000</v>
@@ -1838,25 +1838,25 @@
         <v>12.5</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS7" t="n">
         <v>6.8</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX7" t="n">
         <v>5.8</v>
@@ -1868,29 +1868,29 @@
         <v>6</v>
       </c>
       <c r="BA7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BC7" t="n">
         <v>15</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF7" t="n">
         <v>6</v>
       </c>
       <c r="BG7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -1924,10 +1924,10 @@
         <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="H8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
         <v>3.65</v>
@@ -1936,10 +1936,10 @@
         <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
         <v>1.1</v>
@@ -1948,13 +1948,13 @@
         <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
         <v>1.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R8" t="n">
         <v>1.22</v>
@@ -1972,7 +1972,7 @@
         <v>1.38</v>
       </c>
       <c r="W8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X8" t="n">
         <v>970</v>
@@ -2008,7 +2008,7 @@
         <v>22</v>
       </c>
       <c r="AI8" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ8" t="n">
         <v>42</v>
@@ -2029,16 +2029,16 @@
         <v>65</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR8" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
@@ -2047,44 +2047,44 @@
         <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>2.18</v>
+        <v>3.3</v>
       </c>
       <c r="BB8" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>3.15</v>
       </c>
       <c r="BD8" t="n">
-        <v>4.3</v>
+        <v>3.25</v>
       </c>
       <c r="BE8" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="BF8" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="G9" t="n">
         <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="I9" t="n">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="J9" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
@@ -2163,10 +2163,10 @@
         <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="X9" t="n">
         <v>10.5</v>
@@ -2223,13 +2223,13 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="AQ9" t="n">
         <v>3.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AS9" t="n">
         <v>4.7</v>
@@ -2238,7 +2238,7 @@
         <v>4.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV9" t="n">
         <v>4</v>
@@ -2247,16 +2247,16 @@
         <v>4.9</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AY9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>4.9</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>5</v>
-      </c>
       <c r="BA9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BB9" t="n">
         <v>5.7</v>
@@ -2265,20 +2265,20 @@
         <v>5.6</v>
       </c>
       <c r="BD9" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE9" t="n">
         <v>5.7</v>
       </c>
-      <c r="BE9" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BF9" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BG9" t="n">
         <v>4.7</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -2309,91 +2309,91 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="G10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="T10" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="U10" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="W10" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="Y10" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA10" t="n">
         <v>38</v>
       </c>
       <c r="AB10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AD10" t="n">
         <v>14</v>
       </c>
       <c r="AE10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF10" t="n">
         <v>29</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>30</v>
       </c>
       <c r="AG10" t="n">
         <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI10" t="n">
         <v>40</v>
@@ -2402,37 +2402,37 @@
         <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AL10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM10" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN10" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO10" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR10" t="n">
         <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="AT10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
@@ -2441,45 +2441,45 @@
         <v>20</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BB10" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE10" t="n">
         <v>4</v>
       </c>
-      <c r="BC10" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BG10" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,186 +2494,186 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LKS Lodz</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.95</v>
+        <v>3.65</v>
       </c>
       <c r="G11" t="n">
-        <v>2.56</v>
+        <v>4.1</v>
       </c>
       <c r="H11" t="n">
-        <v>2.84</v>
+        <v>2.04</v>
       </c>
       <c r="I11" t="n">
-        <v>4.7</v>
+        <v>2.18</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="K11" t="n">
-        <v>13.5</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
+        <v>4</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="V11" t="n">
         <v>1.84</v>
       </c>
-      <c r="O11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="W11" t="n">
-        <v>1.64</v>
+        <v>1.32</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="n">
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Serbian Super League</t>
+          <t>Turkish Super League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,179 +2688,179 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>FK Radnicki 1923</t>
+          <t>Genclerbirligi</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.36</v>
+        <v>1.86</v>
       </c>
       <c r="G12" t="n">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="H12" t="n">
-        <v>2.92</v>
+        <v>4.9</v>
       </c>
       <c r="I12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J12" t="n">
         <v>3.4</v>
       </c>
-      <c r="J12" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K12" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2</v>
+      </c>
+      <c r="R12" t="n">
         <v>1.31</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S12" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="V12" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="W12" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="X12" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="Z12" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AA12" t="n">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="AB12" t="n">
-        <v>13</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>16.5</v>
+        <v>19.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
         <v>21</v>
       </c>
       <c r="AI12" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AL12" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="AN12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BC12" t="n">
         <v>18</v>
       </c>
-      <c r="AS12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV12" t="n">
+      <c r="BD12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF12" t="n">
         <v>11.5</v>
       </c>
-      <c r="AW12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>16</v>
-      </c>
       <c r="BG12" t="n">
-        <v>3.9</v>
+        <v>7</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="G13" t="n">
         <v>4.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="I13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="J13" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="K13" t="n">
         <v>3.45</v>
@@ -2924,7 +2924,7 @@
         <v>1.62</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="R13" t="n">
         <v>1.23</v>
@@ -2936,13 +2936,13 @@
         <v>1.82</v>
       </c>
       <c r="U13" t="n">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="V13" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -2999,37 +2999,37 @@
         <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>8.800000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>5.9</v>
+        <v>2.98</v>
       </c>
       <c r="AR13" t="n">
-        <v>9.6</v>
+        <v>3.4</v>
       </c>
       <c r="AS13" t="n">
         <v>3.9</v>
       </c>
       <c r="AT13" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="AU13" t="n">
-        <v>5.6</v>
+        <v>2.92</v>
       </c>
       <c r="AV13" t="n">
-        <v>8.4</v>
+        <v>3.3</v>
       </c>
       <c r="AW13" t="n">
-        <v>21</v>
+        <v>3.9</v>
       </c>
       <c r="AX13" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="AY13" t="n">
-        <v>14.5</v>
+        <v>3.6</v>
       </c>
       <c r="AZ13" t="n">
-        <v>18.5</v>
+        <v>3.75</v>
       </c>
       <c r="BA13" t="n">
         <v>4.1</v>
@@ -3050,18 +3050,18 @@
         <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>19.5</v>
+        <v>3.85</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Serbian Super League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,186 +3076,186 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Genclerbirligi</t>
+          <t>FK Radnicki 1923</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>4.8</v>
+        <v>2.88</v>
       </c>
       <c r="I14" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="J14" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="M14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="T14" t="n">
-        <v>1.84</v>
+        <v>1.59</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="V14" t="n">
-        <v>1.24</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="X14" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD14" t="n">
         <v>16.5</v>
       </c>
-      <c r="Z14" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>130</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AE14" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF14" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="AG14" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AH14" t="n">
         <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="AK14" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM14" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="AO14" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>3.35</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.4</v>
+        <v>3.75</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.2</v>
+        <v>4</v>
       </c>
       <c r="AT14" t="n">
-        <v>7.4</v>
+        <v>3.25</v>
       </c>
       <c r="AU14" t="n">
-        <v>7.2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
-        <v>15.5</v>
+        <v>3.45</v>
       </c>
       <c r="AW14" t="n">
-        <v>7</v>
+        <v>3.95</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>3.55</v>
       </c>
       <c r="AY14" t="n">
-        <v>9.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AZ14" t="n">
-        <v>16.5</v>
+        <v>3.6</v>
       </c>
       <c r="BA14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>19</v>
+        <v>3.95</v>
       </c>
       <c r="BC14" t="n">
-        <v>18</v>
+        <v>3.85</v>
       </c>
       <c r="BD14" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>11.5</v>
+        <v>3.75</v>
       </c>
       <c r="BG14" t="n">
-        <v>7</v>
+        <v>3.9</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Turkish Super League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,49 +3270,49 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>LKS Lodz</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.65</v>
+        <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>4.1</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
-        <v>2.04</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
-        <v>2.18</v>
+        <v>3.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K15" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N15" t="n">
         <v>3.9</v>
       </c>
-      <c r="L15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="M15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N15" t="n">
-        <v>4</v>
-      </c>
       <c r="O15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="R15" t="n">
         <v>1.39</v>
@@ -3321,128 +3321,128 @@
         <v>3.1</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U15" t="n">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.32</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y15" t="n">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="Z15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AD15" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE15" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AF15" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL15" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM15" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN15" t="n">
         <v>1000</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG15" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -3482,7 +3482,7 @@
         <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
@@ -3497,13 +3497,13 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="Q16" t="n">
         <v>2.08</v>
@@ -3512,7 +3512,7 @@
         <v>1.25</v>
       </c>
       <c r="S16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T16" t="n">
         <v>1.68</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G17" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
         <v>4.1</v>
@@ -3700,7 +3700,7 @@
         <v>1.7</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
@@ -3718,7 +3718,7 @@
         <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -3739,10 +3739,10 @@
         <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AE17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AF17" t="n">
         <v>14.5</v>
@@ -3769,7 +3769,7 @@
         <v>170</v>
       </c>
       <c r="AN17" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO17" t="n">
         <v>110</v>
@@ -3784,13 +3784,13 @@
         <v>3.9</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.96</v>
+        <v>6.6</v>
       </c>
       <c r="AV17" t="n">
         <v>3.6</v>
@@ -3802,7 +3802,7 @@
         <v>3.3</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AZ17" t="n">
         <v>3.7</v>
@@ -3814,7 +3814,7 @@
         <v>3.8</v>
       </c>
       <c r="BC17" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="H18" t="n">
         <v>3.7</v>
       </c>
       <c r="I18" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J18" t="n">
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L18" t="n">
         <v>1.38</v>
@@ -3909,10 +3909,10 @@
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X18" t="n">
         <v>1000</v>
@@ -3969,16 +3969,16 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AQ18" t="n">
         <v>9.6</v>
       </c>
       <c r="AR18" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AS18" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT18" t="n">
         <v>3</v>
@@ -3987,10 +3987,10 @@
         <v>2.92</v>
       </c>
       <c r="AV18" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AW18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AX18" t="n">
         <v>9.6</v>
@@ -4011,7 +4011,7 @@
         <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BE18" t="n">
         <v>4.1</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -4252,22 +4252,22 @@
         <v>2.08</v>
       </c>
       <c r="G20" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J20" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
@@ -4285,7 +4285,7 @@
         <v>1.41</v>
       </c>
       <c r="R20" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S20" t="n">
         <v>2.04</v>
@@ -4297,10 +4297,10 @@
         <v>2.54</v>
       </c>
       <c r="V20" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="W20" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X20" t="n">
         <v>36</v>
@@ -4309,22 +4309,22 @@
         <v>25</v>
       </c>
       <c r="Z20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA20" t="n">
         <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AC20" t="n">
         <v>12.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AF20" t="n">
         <v>22</v>
@@ -4336,25 +4336,25 @@
         <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AJ20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK20" t="n">
         <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM20" t="n">
         <v>60</v>
       </c>
       <c r="AN20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>4.4</v>
@@ -4366,7 +4366,7 @@
         <v>4.4</v>
       </c>
       <c r="AS20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AT20" t="n">
         <v>4</v>
@@ -4387,39 +4387,39 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>12</v>
+        <v>3.9</v>
       </c>
       <c r="BA20" t="n">
         <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BC20" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD20" t="n">
         <v>4.3</v>
       </c>
       <c r="BE20" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4434,186 +4434,186 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Almeria</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Ahly Cairo</t>
+          <t>Leonesa</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>7.8</v>
+        <v>1.51</v>
       </c>
       <c r="G21" t="n">
-        <v>11</v>
+        <v>1.61</v>
       </c>
       <c r="H21" t="n">
-        <v>1.53</v>
+        <v>6.2</v>
       </c>
       <c r="I21" t="n">
-        <v>1.66</v>
+        <v>7.4</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="K21" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="O21" t="n">
-        <v>1.47</v>
+        <v>1.24</v>
       </c>
       <c r="P21" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="T21" t="n">
-        <v>2.18</v>
+        <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>2.5</v>
+        <v>1.16</v>
       </c>
       <c r="W21" t="n">
-        <v>1.1</v>
+        <v>2.62</v>
       </c>
       <c r="X21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.8</v>
+        <v>26</v>
       </c>
       <c r="Z21" t="n">
-        <v>8.199999999999999</v>
+        <v>60</v>
       </c>
       <c r="AA21" t="n">
-        <v>18.5</v>
+        <v>180</v>
       </c>
       <c r="AB21" t="n">
-        <v>23</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>11</v>
       </c>
       <c r="AD21" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AE21" t="n">
-        <v>27</v>
+        <v>110</v>
       </c>
       <c r="AF21" t="n">
-        <v>90</v>
+        <v>10.5</v>
       </c>
       <c r="AG21" t="n">
-        <v>38</v>
+        <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AK21" t="n">
-        <v>240</v>
+        <v>17</v>
       </c>
       <c r="AL21" t="n">
-        <v>230</v>
+        <v>34</v>
       </c>
       <c r="AM21" t="n">
-        <v>360</v>
+        <v>140</v>
       </c>
       <c r="AN21" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AO21" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP21" t="n">
         <v>17</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AQ21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AS21" t="n">
         <v>8.6</v>
       </c>
-      <c r="AQ21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>4</v>
-      </c>
       <c r="AT21" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.7</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
-        <v>4.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX21" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="AY21" t="n">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB21" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="BC21" t="n">
-        <v>5</v>
+        <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="BF21" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG21" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Italian Serie C</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4628,179 +4628,179 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Pyramids</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="G22" t="n">
-        <v>4.3</v>
+        <v>2.74</v>
       </c>
       <c r="H22" t="n">
-        <v>2.04</v>
+        <v>3.1</v>
       </c>
       <c r="I22" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="L22" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="M22" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.88</v>
+        <v>1.73</v>
       </c>
       <c r="O22" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>1.8</v>
       </c>
       <c r="R22" t="n">
         <v>1.23</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>1.81</v>
       </c>
       <c r="T22" t="n">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="U22" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.83</v>
+        <v>1.34</v>
       </c>
       <c r="W22" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="X22" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y22" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AA22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE22" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI22" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AL22" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM22" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.2</v>
+        <v>1.01</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2.9</v>
+        <v>1.01</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="AS22" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX22" t="n">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BA22" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -4822,179 +4822,179 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>S.S.D. Casarano Calcio</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.86</v>
+        <v>3.85</v>
       </c>
       <c r="G23" t="n">
-        <v>2.06</v>
+        <v>6.6</v>
       </c>
       <c r="H23" t="n">
-        <v>4.5</v>
+        <v>1.75</v>
       </c>
       <c r="I23" t="n">
-        <v>5.4</v>
+        <v>2.24</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="K23" t="n">
-        <v>4.1</v>
+        <v>5.9</v>
       </c>
       <c r="L23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.41</v>
       </c>
-      <c r="M23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3</v>
-      </c>
-      <c r="O23" t="n">
-        <v>1.39</v>
-      </c>
       <c r="P23" t="n">
-        <v>1.69</v>
+        <v>1.47</v>
       </c>
       <c r="Q23" t="n">
         <v>2.16</v>
       </c>
       <c r="R23" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S23" t="n">
-        <v>3.75</v>
+        <v>2.16</v>
       </c>
       <c r="T23" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="U23" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="V23" t="n">
-        <v>1.21</v>
+        <v>1.8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="X23" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="Z23" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB23" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC23" t="n">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AE23" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG23" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI23" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ23" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.9</v>
+        <v>1.01</v>
       </c>
       <c r="AU23" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV23" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="AX23" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY23" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BA23" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BB23" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC23" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE23" t="n">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BF23" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
-        <v>4.9</v>
+        <v>1.01</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -5016,186 +5016,186 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Catania</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Casertana</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="G24" t="n">
-        <v>2.2</v>
+        <v>1.66</v>
       </c>
       <c r="H24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
+        <v>12</v>
+      </c>
+      <c r="J24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P24" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>2</v>
+      </c>
+      <c r="R24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>27</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>40</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>220</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV24" t="n">
         <v>4</v>
       </c>
-      <c r="I24" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N24" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="P24" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="R24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AW24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD24" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG24" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Italian Serie C</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5210,179 +5210,179 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Pyramids</t>
         </is>
       </c>
       <c r="F25" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L25" t="n">
         <v>1.5</v>
       </c>
-      <c r="G25" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H25" t="n">
-        <v>5</v>
-      </c>
-      <c r="I25" t="n">
-        <v>17</v>
-      </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N25" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S25" t="n">
+        <v>4</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>120</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>29</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AR25" t="n">
         <v>3.3</v>
       </c>
-      <c r="K25" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="L25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S25" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W25" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AS25" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AT25" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU25" t="n">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ25" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG25" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -5404,179 +5404,179 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Catania</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Casertana</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F26" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="G26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="K26" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="L26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N26" t="n">
         <v>1.48</v>
       </c>
-      <c r="G26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="H26" t="n">
-        <v>7</v>
-      </c>
-      <c r="I26" t="n">
-        <v>12</v>
-      </c>
-      <c r="J26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="L26" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O26" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="P26" t="n">
-        <v>1.71</v>
+        <v>1.47</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S26" t="n">
-        <v>3.65</v>
+        <v>2.12</v>
       </c>
       <c r="T26" t="n">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U26" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="W26" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="X26" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y26" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z26" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AA26" t="n">
         <v>1000</v>
       </c>
       <c r="AB26" t="n">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="AC26" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD26" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AE26" t="n">
         <v>1000</v>
       </c>
       <c r="AF26" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH26" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AI26" t="n">
-        <v>220</v>
+        <v>1000</v>
       </c>
       <c r="AJ26" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK26" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL26" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM26" t="n">
         <v>1000</v>
       </c>
       <c r="AN26" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AO26" t="n">
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26" t="n">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="AT26" t="n">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AV26" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="AX26" t="n">
-        <v>3</v>
+        <v>1.01</v>
       </c>
       <c r="AY26" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BB26" t="n">
-        <v>3.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC26" t="n">
-        <v>3.75</v>
+        <v>1.01</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -5598,179 +5598,179 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>S.S.D. Casarano Calcio</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>3.85</v>
+        <v>1.84</v>
       </c>
       <c r="G27" t="n">
-        <v>6.6</v>
+        <v>2.04</v>
       </c>
       <c r="H27" t="n">
-        <v>1.75</v>
+        <v>4.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.24</v>
+        <v>5.6</v>
       </c>
       <c r="J27" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K27" t="n">
-        <v>5.9</v>
+        <v>4.2</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M27" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N27" t="n">
-        <v>1.47</v>
+        <v>3</v>
       </c>
       <c r="O27" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P27" t="n">
-        <v>1.47</v>
+        <v>1.69</v>
       </c>
       <c r="Q27" t="n">
         <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.16</v>
+        <v>3.8</v>
       </c>
       <c r="T27" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="U27" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>1.8</v>
+        <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>1.17</v>
+        <v>1.98</v>
       </c>
       <c r="X27" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="Y27" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z27" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AA27" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB27" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC27" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF27" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AK27" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL27" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM27" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AN27" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AT27" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG27" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -5792,55 +5792,55 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.08</v>
+        <v>1.5</v>
       </c>
       <c r="G28" t="n">
-        <v>2.94</v>
+        <v>1.88</v>
       </c>
       <c r="H28" t="n">
-        <v>2.74</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>4.4</v>
+        <v>17</v>
       </c>
       <c r="J28" t="n">
-        <v>2.88</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="O28" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.73</v>
+        <v>1.59</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="S28" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="T28" t="n">
         <v>1.01</v>
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.29</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.51</v>
+        <v>2.14</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,14 +5964,14 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5986,186 +5986,186 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Leonesa</t>
+          <t>Al Ahly Cairo</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.52</v>
+        <v>7.8</v>
       </c>
       <c r="G29" t="n">
-        <v>1.61</v>
+        <v>11</v>
       </c>
       <c r="H29" t="n">
-        <v>6.2</v>
+        <v>1.54</v>
       </c>
       <c r="I29" t="n">
-        <v>7.4</v>
+        <v>1.66</v>
       </c>
       <c r="J29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S29" t="n">
         <v>4.3</v>
       </c>
-      <c r="K29" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.78</v>
-      </c>
       <c r="T29" t="n">
-        <v>1.83</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="V29" t="n">
-        <v>1.15</v>
+        <v>2.5</v>
       </c>
       <c r="W29" t="n">
-        <v>2.62</v>
+        <v>1.11</v>
       </c>
       <c r="X29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AB29" t="n">
         <v>21</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>26</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>60</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>180</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AC29" t="n">
         <v>11</v>
       </c>
       <c r="AD29" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE29" t="n">
         <v>27</v>
       </c>
-      <c r="AE29" t="n">
-        <v>110</v>
-      </c>
       <c r="AF29" t="n">
-        <v>10.5</v>
+        <v>90</v>
       </c>
       <c r="AG29" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="AH29" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="AI29" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AK29" t="n">
+        <v>240</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>230</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>360</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO29" t="n">
         <v>17</v>
       </c>
-      <c r="AL29" t="n">
-        <v>34</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN29" t="n">
+      <c r="AP29" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AU29" t="n">
         <v>7.8</v>
       </c>
-      <c r="AO29" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>17</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AV29" t="n">
-        <v>21</v>
+        <v>3.75</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.4</v>
+        <v>5</v>
       </c>
       <c r="AY29" t="n">
-        <v>8.6</v>
+        <v>4.6</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>4.6</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.199999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="BB29" t="n">
-        <v>12</v>
+        <v>5.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>13.5</v>
+        <v>5.1</v>
       </c>
       <c r="BD29" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>8.4</v>
+        <v>5.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6180,186 +6180,186 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lazio</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sassuolo</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.3</v>
+        <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="H30" t="n">
-        <v>3.7</v>
+        <v>2.84</v>
       </c>
       <c r="I30" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="L30" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="O30" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="R30" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="V30" t="n">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="W30" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="X30" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="Z30" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH30" t="n">
         <v>24</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AI30" t="n">
         <v>75</v>
       </c>
-      <c r="AB30" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE30" t="n">
+      <c r="AJ30" t="n">
         <v>50</v>
       </c>
-      <c r="AF30" t="n">
-        <v>13</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>30</v>
-      </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AL30" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>180</v>
+      </c>
+      <c r="AN30" t="n">
         <v>48</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>25</v>
       </c>
       <c r="AO30" t="n">
         <v>60</v>
       </c>
       <c r="AP30" t="n">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ30" t="n">
-        <v>11</v>
+        <v>7.4</v>
       </c>
       <c r="AR30" t="n">
-        <v>22</v>
+        <v>15.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="AT30" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AU30" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV30" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AW30" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AX30" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AY30" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BA30" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>7.4</v>
       </c>
       <c r="BC30" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BD30" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BE30" t="n">
-        <v>42</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF30" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BG30" t="n">
-        <v>50</v>
+        <v>7.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -6374,179 +6374,179 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Lazio</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Sassuolo</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.54</v>
+        <v>2.3</v>
       </c>
       <c r="G31" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="H31" t="n">
-        <v>2.96</v>
+        <v>3.7</v>
       </c>
       <c r="I31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J31" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N31" t="n">
         <v>3.2</v>
       </c>
-      <c r="J31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L31" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N31" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O31" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="P31" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="R31" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T31" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="U31" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="V31" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="W31" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="X31" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y31" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Z31" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AA31" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AB31" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AE31" t="n">
         <v>50</v>
       </c>
       <c r="AF31" t="n">
-        <v>16.5</v>
+        <v>13</v>
       </c>
       <c r="AG31" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
         <v>70</v>
       </c>
       <c r="AJ31" t="n">
+        <v>30</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>28</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>60</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW31" t="n">
         <v>44</v>
       </c>
-      <c r="AK31" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN31" t="n">
+      <c r="AX31" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>55</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>27</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD31" t="n">
         <v>42</v>
       </c>
-      <c r="AO31" t="n">
-        <v>65</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>17</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BE31" t="n">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BG31" t="n">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -6595,13 +6595,13 @@
         <v>3.6</v>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>1.42</v>
@@ -6610,13 +6610,13 @@
         <v>1.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R32" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6706,7 +6706,7 @@
         <v>18</v>
       </c>
       <c r="AW32" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AX32" t="n">
         <v>9.6</v>
@@ -6736,11 +6736,11 @@
         <v>15.5</v>
       </c>
       <c r="BG32" t="n">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G33" t="n">
         <v>2.22</v>
@@ -6885,7 +6885,7 @@
         <v>12</v>
       </c>
       <c r="AR33" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS33" t="n">
         <v>11.5</v>
@@ -6915,7 +6915,7 @@
         <v>11</v>
       </c>
       <c r="BB33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC33" t="n">
         <v>21</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -6965,25 +6965,25 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="G34" t="n">
         <v>1.95</v>
       </c>
       <c r="H34" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I34" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J34" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
         <v>1.09</v>
@@ -6992,28 +6992,28 @@
         <v>3</v>
       </c>
       <c r="O34" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P34" t="n">
         <v>1.67</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="T34" t="n">
         <v>1.87</v>
       </c>
       <c r="U34" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="V34" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W34" t="n">
         <v>2.06</v>
@@ -7046,7 +7046,7 @@
         <v>12.5</v>
       </c>
       <c r="AG34" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH34" t="n">
         <v>29</v>
@@ -7055,7 +7055,7 @@
         <v>120</v>
       </c>
       <c r="AJ34" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK34" t="n">
         <v>28</v>
@@ -7082,7 +7082,7 @@
         <v>4.1</v>
       </c>
       <c r="AS34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT34" t="n">
         <v>6.2</v>
@@ -7115,20 +7115,20 @@
         <v>19.5</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF34" t="n">
         <v>12.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -7362,10 +7362,10 @@
         <v>2.22</v>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J36" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="K36" t="n">
         <v>3.35</v>
@@ -7374,13 +7374,13 @@
         <v>1.4</v>
       </c>
       <c r="M36" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>1.65</v>
+        <v>2.92</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>1.43</v>
       </c>
       <c r="P36" t="n">
         <v>1.65</v>
@@ -7395,10 +7395,10 @@
         <v>4.3</v>
       </c>
       <c r="T36" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U36" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V36" t="n">
         <v>1.7</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -7547,10 +7547,10 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="G37" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="H37" t="n">
         <v>7.4</v>
@@ -7559,10 +7559,10 @@
         <v>8.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K37" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L37" t="n">
         <v>1.33</v>
@@ -7589,7 +7589,7 @@
         <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U37" t="n">
         <v>1.65</v>
@@ -7598,7 +7598,7 @@
         <v>1.13</v>
       </c>
       <c r="W37" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="X37" t="n">
         <v>15.5</v>
@@ -7610,7 +7610,7 @@
         <v>85</v>
       </c>
       <c r="AA37" t="n">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="AB37" t="n">
         <v>8.800000000000001</v>
@@ -7619,7 +7619,7 @@
         <v>10.5</v>
       </c>
       <c r="AD37" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE37" t="n">
         <v>170</v>
@@ -7643,16 +7643,16 @@
         <v>21</v>
       </c>
       <c r="AL37" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM37" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN37" t="n">
         <v>11</v>
       </c>
       <c r="AO37" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP37" t="n">
         <v>12</v>
@@ -7661,10 +7661,10 @@
         <v>18</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AS37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AT37" t="n">
         <v>6.4</v>
@@ -7673,10 +7673,10 @@
         <v>8.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX37" t="n">
         <v>7.2</v>
@@ -7685,10 +7685,10 @@
         <v>9</v>
       </c>
       <c r="AZ37" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BB37" t="n">
         <v>11.5</v>
@@ -7697,20 +7697,20 @@
         <v>14.5</v>
       </c>
       <c r="BD37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BF37" t="n">
         <v>7.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -7741,22 +7741,22 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G38" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="H38" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="J38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="K38" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="L38" t="n">
         <v>1.32</v>
@@ -7765,7 +7765,7 @@
         <v>1.06</v>
       </c>
       <c r="N38" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="O38" t="n">
         <v>1.28</v>
@@ -7783,16 +7783,16 @@
         <v>3.05</v>
       </c>
       <c r="T38" t="n">
-        <v>2.04</v>
+        <v>1.97</v>
       </c>
       <c r="U38" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="V38" t="n">
         <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="X38" t="n">
         <v>19.5</v>
@@ -7807,19 +7807,19 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC38" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AF38" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG38" t="n">
         <v>12</v>
@@ -7828,10 +7828,10 @@
         <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AJ38" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK38" t="n">
         <v>19</v>
@@ -7840,10 +7840,10 @@
         <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="AN38" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
@@ -7858,34 +7858,34 @@
         <v>4.9</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AT38" t="n">
         <v>6.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AV38" t="n">
         <v>4.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AX38" t="n">
         <v>7</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="AZ38" t="n">
         <v>4.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BB38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BC38" t="n">
         <v>12.5</v>
@@ -7894,17 +7894,17 @@
         <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BG38" t="n">
         <v>5.1</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>
@@ -7950,13 +7950,13 @@
         <v>2.24</v>
       </c>
       <c r="K39" t="n">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
       </c>
       <c r="M39" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N39" t="n">
         <v>1.46</v>
@@ -8098,7 +8098,589 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-07 23:37:57</t>
+          <t>2026-03-08 01:59:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Ecuadorian Serie A</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Orense Sporting Club</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Manta FC</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="R40" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S40" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W40" t="n">
+        <v>2</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH40" t="inlineStr">
+        <is>
+          <t>2026-03-08 01:59:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Liverpool Montevideo</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="G41" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L41" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S41" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BH41" t="inlineStr">
+        <is>
+          <t>2026-03-08 01:59:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Colombian Primera A</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2026-03-09</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>22:30:00</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>America de Cali S.A</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="G42" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H42" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L42" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="R42" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S42" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W42" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>220</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH42" t="inlineStr">
+        <is>
+          <t>2026-03-08 01:59:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,22 +757,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L2" t="n">
         <v>1.3</v>
@@ -784,22 +784,22 @@
         <v>5.7</v>
       </c>
       <c r="O2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R2" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T2" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U2" t="n">
         <v>2.36</v>
@@ -808,7 +808,7 @@
         <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X2" t="n">
         <v>29</v>
@@ -838,7 +838,7 @@
         <v>14.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH2" t="n">
         <v>21</v>
@@ -874,7 +874,7 @@
         <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
         <v>10.5</v>
@@ -886,7 +886,7 @@
         <v>16.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -898,29 +898,29 @@
         <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC2" t="n">
         <v>14</v>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BF2" t="n">
         <v>6.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="G3" t="n">
         <v>4.2</v>
@@ -975,16 +975,16 @@
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>1.43</v>
       </c>
       <c r="P3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R3" t="n">
         <v>1.24</v>
@@ -993,13 +993,13 @@
         <v>4.4</v>
       </c>
       <c r="T3" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U3" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V3" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="W3" t="n">
         <v>1.33</v>
@@ -1089,7 +1089,7 @@
         <v>14</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6</v>
+        <v>17.5</v>
       </c>
       <c r="BA3" t="n">
         <v>7.2</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
         <v>27</v>
       </c>
       <c r="H4" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="J4" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K4" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="L4" t="n">
         <v>1.27</v>
@@ -1169,16 +1169,16 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.24</v>
       </c>
       <c r="P4" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="R4" t="n">
         <v>1.48</v>
@@ -1193,7 +1193,7 @@
         <v>1.54</v>
       </c>
       <c r="V4" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W4" t="n">
         <v>1.04</v>
@@ -1253,40 +1253,40 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT4" t="n">
         <v>1.24</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="AV4" t="n">
         <v>3.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="AZ4" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.800000000000001</v>
+        <v>1.25</v>
       </c>
       <c r="BB4" t="n">
         <v>1.16</v>
@@ -1304,11 +1304,11 @@
         <v>1.16</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G5" t="n">
         <v>6.2</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I5" t="n">
         <v>2.02</v>
@@ -1354,7 +1354,7 @@
         <v>3.15</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L5" t="n">
         <v>1.48</v>
@@ -1495,14 +1495,14 @@
         <v>1.71</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BG5" t="n">
         <v>6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1739,10 +1739,10 @@
         <v>19.5</v>
       </c>
       <c r="J7" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -1769,10 +1769,10 @@
         <v>3.55</v>
       </c>
       <c r="T7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="U7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="V7" t="n">
         <v>1.05</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -1921,10 +1921,10 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="H8" t="n">
         <v>3.3</v>
@@ -1939,10 +1939,10 @@
         <v>3.35</v>
       </c>
       <c r="L8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M8" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N8" t="n">
         <v>2.76</v>
@@ -1963,10 +1963,10 @@
         <v>4.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="U8" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V8" t="n">
         <v>1.38</v>
@@ -2011,7 +2011,7 @@
         <v>85</v>
       </c>
       <c r="AJ8" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AK8" t="n">
         <v>36</v>
@@ -2032,34 +2032,34 @@
         <v>5.2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AR8" t="n">
         <v>7.4</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AT8" t="n">
         <v>7.2</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>6.4</v>
       </c>
       <c r="AW8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AX8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA8" t="n">
         <v>3.3</v>
@@ -2071,20 +2071,20 @@
         <v>3.15</v>
       </c>
       <c r="BD8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.91</v>
+        <v>2.34</v>
       </c>
       <c r="BF8" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="G9" t="n">
         <v>6.6</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="I9" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L9" t="n">
         <v>1.49</v>
@@ -2163,7 +2163,7 @@
         <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="W9" t="n">
         <v>1.17</v>
@@ -2229,7 +2229,7 @@
         <v>3.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AS9" t="n">
         <v>4.7</v>
@@ -2238,7 +2238,7 @@
         <v>4.3</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AV9" t="n">
         <v>4</v>
@@ -2253,7 +2253,7 @@
         <v>4.8</v>
       </c>
       <c r="AZ9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BA9" t="n">
         <v>5.4</v>
@@ -2265,10 +2265,10 @@
         <v>5.6</v>
       </c>
       <c r="BD9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BF9" t="n">
         <v>5.7</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -2309,34 +2309,34 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G10" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H10" t="n">
         <v>2.24</v>
       </c>
       <c r="I10" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="J10" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O10" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.18</v>
@@ -2345,28 +2345,28 @@
         <v>1.7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S10" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="T10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U10" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="V10" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W10" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="X10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y10" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
@@ -2387,13 +2387,13 @@
         <v>28</v>
       </c>
       <c r="AF10" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG10" t="n">
         <v>17</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI10" t="n">
         <v>40</v>
@@ -2402,77 +2402,77 @@
         <v>65</v>
       </c>
       <c r="AK10" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AM10" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AN10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>16.5</v>
+        <v>13.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR10" t="n">
         <v>12</v>
       </c>
       <c r="AS10" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="AT10" t="n">
         <v>11</v>
       </c>
       <c r="AU10" t="n">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV10" t="n">
         <v>10</v>
       </c>
       <c r="AW10" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AX10" t="n">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AY10" t="n">
         <v>12</v>
       </c>
       <c r="AZ10" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BD10" t="n">
         <v>3.8</v>
       </c>
-      <c r="BB10" t="n">
+      <c r="BE10" t="n">
         <v>3.95</v>
       </c>
-      <c r="BC10" t="n">
-        <v>23</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>4</v>
-      </c>
       <c r="BF10" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -2515,10 +2515,10 @@
         <v>2.18</v>
       </c>
       <c r="J11" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L11" t="n">
         <v>1.36</v>
@@ -2533,7 +2533,7 @@
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
         <v>1.81</v>
@@ -2542,13 +2542,13 @@
         <v>1.39</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U11" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V11" t="n">
         <v>1.84</v>
@@ -2635,10 +2635,10 @@
         <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>5.6</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="n">
         <v>4.9</v>
@@ -2709,46 +2709,46 @@
         <v>5.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P12" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S12" t="n">
         <v>3.65</v>
       </c>
       <c r="T12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="U12" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W12" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X12" t="n">
         <v>15.5</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -2891,10 +2891,10 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H13" t="n">
         <v>2.16</v>
@@ -2903,7 +2903,7 @@
         <v>2.44</v>
       </c>
       <c r="J13" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="K13" t="n">
         <v>3.45</v>
@@ -2912,7 +2912,7 @@
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N13" t="n">
         <v>2.84</v>
@@ -2942,7 +2942,7 @@
         <v>1.69</v>
       </c>
       <c r="W13" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="X13" t="n">
         <v>12</v>
@@ -2999,37 +2999,37 @@
         <v>34</v>
       </c>
       <c r="AP13" t="n">
-        <v>3.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ13" t="n">
-        <v>2.98</v>
+        <v>5.8</v>
       </c>
       <c r="AR13" t="n">
-        <v>3.4</v>
+        <v>9.6</v>
       </c>
       <c r="AS13" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT13" t="n">
-        <v>3.3</v>
+        <v>8.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.92</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.3</v>
+        <v>8.4</v>
       </c>
       <c r="AW13" t="n">
-        <v>3.9</v>
+        <v>21</v>
       </c>
       <c r="AX13" t="n">
-        <v>3.85</v>
+        <v>20</v>
       </c>
       <c r="AY13" t="n">
-        <v>3.6</v>
+        <v>12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>3.75</v>
+        <v>15.5</v>
       </c>
       <c r="BA13" t="n">
         <v>4.1</v>
@@ -3050,11 +3050,11 @@
         <v>4.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.85</v>
+        <v>19.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
         <v>2.38</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>2.88</v>
@@ -3109,7 +3109,7 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O14" t="n">
         <v>1.31</v>
@@ -3121,7 +3121,7 @@
         <v>1.93</v>
       </c>
       <c r="R14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S14" t="n">
         <v>3.35</v>
@@ -3145,7 +3145,7 @@
         <v>15</v>
       </c>
       <c r="Z14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AA14" t="n">
         <v>65</v>
@@ -3193,43 +3193,43 @@
         <v>40</v>
       </c>
       <c r="AP14" t="n">
-        <v>3.45</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
-        <v>3.35</v>
+        <v>10.5</v>
       </c>
       <c r="AR14" t="n">
-        <v>3.75</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW14" t="n">
         <v>4</v>
       </c>
-      <c r="AT14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AX14" t="n">
-        <v>3.55</v>
+        <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>3.35</v>
+        <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>3.6</v>
+        <v>14.5</v>
       </c>
       <c r="BA14" t="n">
         <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BC14" t="n">
         <v>3.85</v>
@@ -3241,14 +3241,14 @@
         <v>4.2</v>
       </c>
       <c r="BF14" t="n">
-        <v>3.75</v>
+        <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H15" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="J15" t="n">
         <v>3.5</v>
@@ -3303,19 +3303,19 @@
         <v>1.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O15" t="n">
         <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>3.1</v>
@@ -3327,10 +3327,10 @@
         <v>1.01</v>
       </c>
       <c r="V15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="W15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -3476,13 +3476,13 @@
         <v>2.82</v>
       </c>
       <c r="G16" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
         <v>2.5</v>
       </c>
       <c r="I16" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J16" t="n">
         <v>3.2</v>
@@ -3491,46 +3491,46 @@
         <v>3.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M16" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O16" t="n">
         <v>1.37</v>
       </c>
       <c r="P16" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q16" t="n">
         <v>2.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="T16" t="n">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="U16" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="V16" t="n">
         <v>1.53</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y16" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV16" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BD16" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG16" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="G17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H17" t="n">
         <v>4.1</v>
@@ -3682,7 +3682,7 @@
         <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3697,10 +3697,10 @@
         <v>1.41</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="R17" t="n">
         <v>1.25</v>
@@ -3718,7 +3718,7 @@
         <v>1.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="X17" t="n">
         <v>13.5</v>
@@ -3739,10 +3739,10 @@
         <v>9.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE17" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AF17" t="n">
         <v>14.5</v>
@@ -3775,16 +3775,16 @@
         <v>110</v>
       </c>
       <c r="AP17" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AQ17" t="n">
-        <v>3.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR17" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT17" t="n">
         <v>6.6</v>
@@ -3793,28 +3793,28 @@
         <v>6.6</v>
       </c>
       <c r="AV17" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AW17" t="n">
         <v>4.1</v>
       </c>
       <c r="AX17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AY17" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AZ17" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA17" t="n">
         <v>4.1</v>
       </c>
       <c r="BB17" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC17" t="n">
         <v>3.8</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.75</v>
       </c>
       <c r="BD17" t="n">
         <v>4</v>
@@ -3826,11 +3826,11 @@
         <v>14.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>2.04</v>
       </c>
       <c r="G18" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H18" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="I18" t="n">
         <v>4.7</v>
@@ -3876,7 +3876,7 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L18" t="n">
         <v>1.38</v>
@@ -3885,13 +3885,13 @@
         <v>1.08</v>
       </c>
       <c r="N18" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
         <v>1.37</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q18" t="n">
         <v>1.94</v>
@@ -3909,7 +3909,7 @@
         <v>1.81</v>
       </c>
       <c r="V18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
         <v>1.75</v>
@@ -3942,7 +3942,7 @@
         <v>1000</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH18" t="n">
         <v>1000</v>
@@ -3969,10 +3969,10 @@
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR18" t="n">
         <v>3.8</v>
@@ -3981,7 +3981,7 @@
         <v>4.1</v>
       </c>
       <c r="AT18" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AU18" t="n">
         <v>2.92</v>
@@ -3999,7 +3999,7 @@
         <v>3.2</v>
       </c>
       <c r="AZ18" t="n">
-        <v>3.6</v>
+        <v>14</v>
       </c>
       <c r="BA18" t="n">
         <v>4</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -4058,16 +4058,16 @@
         <v>2.5</v>
       </c>
       <c r="G19" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H19" t="n">
         <v>2.84</v>
-      </c>
-      <c r="H19" t="n">
-        <v>2.82</v>
       </c>
       <c r="I19" t="n">
         <v>3.25</v>
       </c>
       <c r="J19" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K19" t="n">
         <v>3.6</v>
@@ -4079,7 +4079,7 @@
         <v>1.09</v>
       </c>
       <c r="N19" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>1.4</v>
@@ -4103,10 +4103,10 @@
         <v>1.95</v>
       </c>
       <c r="V19" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W19" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X19" t="n">
         <v>12</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -4249,58 +4249,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="G20" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H20" t="n">
         <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K20" t="n">
         <v>4.8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="M20" t="n">
         <v>1.01</v>
       </c>
       <c r="N20" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="O20" t="n">
         <v>1.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="R20" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="S20" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="U20" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="W20" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X20" t="n">
         <v>36</v>
@@ -4315,19 +4315,19 @@
         <v>60</v>
       </c>
       <c r="AB20" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AC20" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG20" t="n">
         <v>14</v>
@@ -4336,10 +4336,10 @@
         <v>17</v>
       </c>
       <c r="AI20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ20" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK20" t="n">
         <v>23</v>
@@ -4348,13 +4348,13 @@
         <v>29</v>
       </c>
       <c r="AM20" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AN20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AO20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP20" t="n">
         <v>4.4</v>
@@ -4387,13 +4387,13 @@
         <v>10</v>
       </c>
       <c r="AZ20" t="n">
-        <v>3.9</v>
+        <v>12</v>
       </c>
       <c r="BA20" t="n">
         <v>4.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC20" t="n">
         <v>4.1</v>
@@ -4405,14 +4405,14 @@
         <v>4.6</v>
       </c>
       <c r="BF20" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG20" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="G21" t="n">
         <v>1.61</v>
@@ -4455,7 +4455,7 @@
         <v>7.4</v>
       </c>
       <c r="J21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K21" t="n">
         <v>5.1</v>
@@ -4476,10 +4476,10 @@
         <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="R21" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S21" t="n">
         <v>2.78</v>
@@ -4488,7 +4488,7 @@
         <v>1.83</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
         <v>1.16</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -4637,19 +4637,19 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G22" t="n">
         <v>2.74</v>
       </c>
       <c r="H22" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K22" t="n">
         <v>4.2</v>
@@ -4661,22 +4661,22 @@
         <v>1.07</v>
       </c>
       <c r="N22" t="n">
-        <v>1.73</v>
+        <v>3.25</v>
       </c>
       <c r="O22" t="n">
         <v>1.28</v>
       </c>
       <c r="P22" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R22" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>1.81</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
         <v>1.01</v>
@@ -4685,16 +4685,16 @@
         <v>1.01</v>
       </c>
       <c r="V22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="W22" t="n">
         <v>1.57</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC22" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4718,7 +4718,7 @@
         <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AV22" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ22" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD22" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG22" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -4852,13 +4852,13 @@
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N23" t="n">
-        <v>1.47</v>
+        <v>2.48</v>
       </c>
       <c r="O23" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="P23" t="n">
         <v>1.47</v>
@@ -4876,7 +4876,7 @@
         <v>1.91</v>
       </c>
       <c r="U23" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V23" t="n">
         <v>1.8</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G24" t="n">
         <v>1.66</v>
@@ -5037,10 +5037,10 @@
         <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K24" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L24" t="n">
         <v>1.38</v>
@@ -5055,7 +5055,7 @@
         <v>1.4</v>
       </c>
       <c r="P24" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q24" t="n">
         <v>2</v>
@@ -5109,10 +5109,10 @@
         <v>12.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AI24" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ24" t="n">
         <v>16.5</v>
@@ -5136,10 +5136,10 @@
         <v>3.4</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AR24" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AS24" t="n">
         <v>4.4</v>
@@ -5154,19 +5154,19 @@
         <v>4</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX24" t="n">
         <v>3</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AZ24" t="n">
         <v>4</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB24" t="n">
         <v>3.5</v>
@@ -5178,7 +5178,7 @@
         <v>4.1</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
         <v>8.199999999999999</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -5252,13 +5252,13 @@
         <v>1.62</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
         <v>1.22</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="T25" t="n">
         <v>1.85</v>
@@ -5297,7 +5297,7 @@
         <v>34</v>
       </c>
       <c r="AF25" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AG25" t="n">
         <v>23</v>
@@ -5327,62 +5327,62 @@
         <v>29</v>
       </c>
       <c r="AP25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AR25" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AV25" t="n">
         <v>3.3</v>
       </c>
-      <c r="AS25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AW25" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AX25" t="n">
         <v>3.9</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BA25" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC25" t="n">
         <v>4.1</v>
       </c>
       <c r="BD25" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE25" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF25" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF25" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BG25" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G27" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="H27" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="I27" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J27" t="n">
         <v>3.05</v>
@@ -5643,34 +5643,34 @@
         <v>2.16</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="T27" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="V27" t="n">
         <v>1.22</v>
       </c>
       <c r="W27" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y27" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA27" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB27" t="n">
         <v>8.6</v>
@@ -5679,25 +5679,25 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
         <v>90</v>
       </c>
       <c r="AF27" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG27" t="n">
         <v>12.5</v>
       </c>
-      <c r="AG27" t="n">
-        <v>12</v>
-      </c>
       <c r="AH27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI27" t="n">
         <v>100</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK27" t="n">
         <v>27</v>
@@ -5709,10 +5709,10 @@
         <v>170</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP27" t="n">
         <v>9.800000000000001</v>
@@ -5721,10 +5721,10 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT27" t="n">
         <v>5.9</v>
@@ -5733,22 +5733,22 @@
         <v>6.8</v>
       </c>
       <c r="AV27" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX27" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AY27" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AZ27" t="n">
-        <v>18.5</v>
+        <v>4.2</v>
       </c>
       <c r="BA27" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB27" t="n">
         <v>17</v>
@@ -5757,20 +5757,20 @@
         <v>19.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BE27" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BF27" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G28" t="n">
         <v>1.88</v>
@@ -5810,13 +5810,13 @@
         <v>5</v>
       </c>
       <c r="I28" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J28" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K28" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5825,13 +5825,13 @@
         <v>1.01</v>
       </c>
       <c r="N28" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="O28" t="n">
         <v>1.35</v>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="Q28" t="n">
         <v>1.96</v>
@@ -5849,10 +5849,10 @@
         <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W28" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X28" t="n">
         <v>1000</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
         <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.8</v>
       </c>
       <c r="T29" t="n">
         <v>2.18</v>
@@ -6154,11 +6154,11 @@
         <v>5.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -6192,10 +6192,10 @@
         <v>2.74</v>
       </c>
       <c r="G30" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="H30" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="I30" t="n">
         <v>3.1</v>
@@ -6213,19 +6213,19 @@
         <v>1.12</v>
       </c>
       <c r="N30" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O30" t="n">
         <v>1.5</v>
       </c>
       <c r="P30" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -6234,19 +6234,19 @@
         <v>2.04</v>
       </c>
       <c r="U30" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V30" t="n">
         <v>1.47</v>
       </c>
       <c r="W30" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="X30" t="n">
         <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Z30" t="n">
         <v>18.5</v>
@@ -6255,16 +6255,16 @@
         <v>60</v>
       </c>
       <c r="AB30" t="n">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC30" t="n">
         <v>7.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF30" t="n">
         <v>17.5</v>
@@ -6276,25 +6276,25 @@
         <v>24</v>
       </c>
       <c r="AI30" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ30" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK30" t="n">
         <v>40</v>
       </c>
       <c r="AL30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM30" t="n">
         <v>180</v>
       </c>
       <c r="AN30" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AO30" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AP30" t="n">
         <v>8.199999999999999</v>
@@ -6306,7 +6306,7 @@
         <v>15.5</v>
       </c>
       <c r="AS30" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT30" t="n">
         <v>7.6</v>
@@ -6327,7 +6327,7 @@
         <v>11.5</v>
       </c>
       <c r="AZ30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA30" t="n">
         <v>50</v>
@@ -6342,7 +6342,7 @@
         <v>50</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BF30" t="n">
         <v>30</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -6482,7 +6482,7 @@
         <v>48</v>
       </c>
       <c r="AM31" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN31" t="n">
         <v>25</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -6601,22 +6601,22 @@
         <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
         <v>1.42</v>
       </c>
       <c r="P32" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
         <v>2.06</v>
@@ -6679,7 +6679,7 @@
         <v>150</v>
       </c>
       <c r="AN32" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO32" t="n">
         <v>110</v>
@@ -6718,7 +6718,7 @@
         <v>20</v>
       </c>
       <c r="BA32" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BB32" t="n">
         <v>19.5</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G33" t="n">
         <v>2.22</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -6971,19 +6971,19 @@
         <v>1.95</v>
       </c>
       <c r="H34" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I34" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K34" t="n">
         <v>4.2</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="M34" t="n">
         <v>1.09</v>
@@ -6995,22 +6995,22 @@
         <v>1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="R34" t="n">
         <v>1.24</v>
       </c>
       <c r="S34" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U34" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="V34" t="n">
         <v>1.19</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -7174,7 +7174,7 @@
         <v>2.34</v>
       </c>
       <c r="K35" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -7371,16 +7371,16 @@
         <v>3.35</v>
       </c>
       <c r="L36" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="M36" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N36" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P36" t="n">
         <v>1.65</v>
@@ -7506,7 +7506,7 @@
         <v>2.4</v>
       </c>
       <c r="BE36" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="BF36" t="n">
         <v>4.7</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>1.5</v>
       </c>
       <c r="G37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H37" t="n">
         <v>7.4</v>
@@ -7559,10 +7559,10 @@
         <v>8.6</v>
       </c>
       <c r="J37" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K37" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L37" t="n">
         <v>1.33</v>
@@ -7589,7 +7589,7 @@
         <v>3.4</v>
       </c>
       <c r="T37" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U37" t="n">
         <v>1.65</v>
@@ -7598,7 +7598,7 @@
         <v>1.13</v>
       </c>
       <c r="W37" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="X37" t="n">
         <v>15.5</v>
@@ -7631,7 +7631,7 @@
         <v>12.5</v>
       </c>
       <c r="AH37" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI37" t="n">
         <v>150</v>
@@ -7661,10 +7661,10 @@
         <v>18</v>
       </c>
       <c r="AR37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT37" t="n">
         <v>6.4</v>
@@ -7673,10 +7673,10 @@
         <v>8.6</v>
       </c>
       <c r="AV37" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AW37" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX37" t="n">
         <v>7.2</v>
@@ -7688,7 +7688,7 @@
         <v>4.4</v>
       </c>
       <c r="BA37" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB37" t="n">
         <v>11.5</v>
@@ -7700,17 +7700,17 @@
         <v>4.6</v>
       </c>
       <c r="BE37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF37" t="n">
         <v>7.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -7741,25 +7741,25 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G38" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="I38" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="J38" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K38" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="L38" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M38" t="n">
         <v>1.06</v>
@@ -7783,16 +7783,16 @@
         <v>3.05</v>
       </c>
       <c r="T38" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="U38" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="V38" t="n">
         <v>1.09</v>
       </c>
       <c r="W38" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="X38" t="n">
         <v>19.5</v>
@@ -7807,19 +7807,19 @@
         <v>1000</v>
       </c>
       <c r="AB38" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD38" t="n">
         <v>1000</v>
       </c>
       <c r="AE38" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AF38" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AG38" t="n">
         <v>12</v>
@@ -7828,10 +7828,10 @@
         <v>1000</v>
       </c>
       <c r="AI38" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AJ38" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK38" t="n">
         <v>19</v>
@@ -7840,10 +7840,10 @@
         <v>1000</v>
       </c>
       <c r="AM38" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN38" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AO38" t="n">
         <v>1000</v>
@@ -7858,34 +7858,34 @@
         <v>4.9</v>
       </c>
       <c r="AS38" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT38" t="n">
         <v>6.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV38" t="n">
         <v>4.6</v>
       </c>
       <c r="AW38" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX38" t="n">
         <v>7</v>
       </c>
       <c r="AY38" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AZ38" t="n">
         <v>4.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB38" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC38" t="n">
         <v>12.5</v>
@@ -7894,17 +7894,17 @@
         <v>4.7</v>
       </c>
       <c r="BE38" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF38" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG38" t="n">
         <v>5.1</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -8326,13 +8326,13 @@
         <v>3.25</v>
       </c>
       <c r="G41" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="H41" t="n">
         <v>2.42</v>
       </c>
       <c r="I41" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="J41" t="n">
         <v>3</v>
@@ -8347,67 +8347,67 @@
         <v>1.11</v>
       </c>
       <c r="N41" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O41" t="n">
         <v>1.48</v>
       </c>
       <c r="P41" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="R41" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S41" t="n">
         <v>4.8</v>
       </c>
       <c r="T41" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="U41" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="V41" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W41" t="n">
         <v>1.37</v>
       </c>
       <c r="X41" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y41" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z41" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AA41" t="n">
         <v>1000</v>
       </c>
       <c r="AB41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AD41" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE41" t="n">
         <v>1000</v>
       </c>
       <c r="AF41" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG41" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI41" t="n">
         <v>1000</v>
@@ -8425,68 +8425,68 @@
         <v>1000</v>
       </c>
       <c r="AN41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP41" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AT41" t="n">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU41" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV41" t="n">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AW41" t="n">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.03</v>
+        <v>19.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>1.03</v>
+        <v>5.8</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="BC41" t="n">
-        <v>1.03</v>
+        <v>5.7</v>
       </c>
       <c r="BD41" t="n">
-        <v>1.02</v>
+        <v>5.9</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.03</v>
+        <v>6</v>
       </c>
       <c r="BG41" t="n">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>
@@ -8517,22 +8517,22 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="G42" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="H42" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I42" t="n">
         <v>3.4</v>
       </c>
       <c r="J42" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
       <c r="K42" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L42" t="n">
         <v>1.01</v>
@@ -8541,16 +8541,16 @@
         <v>1.12</v>
       </c>
       <c r="N42" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="O42" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P42" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="R42" t="n">
         <v>1.18</v>
@@ -8568,7 +8568,7 @@
         <v>1.44</v>
       </c>
       <c r="W42" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X42" t="n">
         <v>10.5</v>
@@ -8583,7 +8583,7 @@
         <v>70</v>
       </c>
       <c r="AB42" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC42" t="n">
         <v>8.4</v>
@@ -8625,16 +8625,16 @@
         <v>75</v>
       </c>
       <c r="AP42" t="n">
-        <v>7.2</v>
+        <v>3.05</v>
       </c>
       <c r="AQ42" t="n">
         <v>7.4</v>
       </c>
       <c r="AR42" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AS42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
@@ -8649,38 +8649,38 @@
         <v>4</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AY42" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BA42" t="n">
         <v>4.1</v>
       </c>
       <c r="BB42" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC42" t="n">
         <v>4</v>
       </c>
-      <c r="BC42" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG42" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 01:59:29</t>
+          <t>2026-03-08 04:19:56</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,16 +757,16 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.7</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1.71</v>
       </c>
       <c r="H2" t="n">
         <v>5.3</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
         <v>4.4</v>
@@ -775,40 +775,40 @@
         <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S2" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -826,13 +826,13 @@
         <v>12</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD2" t="n">
         <v>22</v>
       </c>
       <c r="AE2" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF2" t="n">
         <v>13</v>
@@ -847,7 +847,7 @@
         <v>65</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AK2" t="n">
         <v>16.5</v>
@@ -856,28 +856,28 @@
         <v>30</v>
       </c>
       <c r="AM2" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AO2" t="n">
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ2" t="n">
         <v>19</v>
       </c>
       <c r="AR2" t="n">
-        <v>7.4</v>
+        <v>38</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
         <v>9</v>
@@ -886,7 +886,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>6.8</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF2" t="n">
         <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T3" t="n">
         <v>1.01</v>
@@ -1059,52 +1059,52 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -1169,22 +1169,22 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.08</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.07</v>
       </c>
       <c r="Q4" t="n">
         <v>1.54</v>
       </c>
       <c r="R4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="I5" t="n">
         <v>2.32</v>
@@ -1390,7 +1390,7 @@
         <v>1.76</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1477,7 +1477,7 @@
         <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>5.2</v>
       </c>
       <c r="BA5" t="n">
         <v>5.8</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="G6" t="n">
         <v>26</v>
@@ -1545,43 +1545,43 @@
         <v>1.25</v>
       </c>
       <c r="J6" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="U6" t="n">
         <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="W6" t="n">
         <v>1.04</v>
@@ -1596,7 +1596,7 @@
         <v>8</v>
       </c>
       <c r="AA6" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
@@ -1605,7 +1605,7 @@
         <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1641,7 +1641,7 @@
         <v>5.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.8</v>
@@ -1650,53 +1650,53 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AU6" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AZ6" t="n">
         <v>30</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BG6" t="n">
         <v>3.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="J7" t="n">
         <v>3.1</v>
@@ -1775,43 +1775,43 @@
         <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Z7" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AA7" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AB7" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AC7" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AD7" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE7" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AF7" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AG7" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AI7" t="n">
         <v>1000</v>
@@ -1835,22 +1835,22 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ7" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AR7" t="n">
         <v>4.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT7" t="n">
         <v>4.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AV7" t="n">
         <v>4.2</v>
@@ -1859,38 +1859,38 @@
         <v>5.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC7" t="n">
         <v>6</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE7" t="n">
         <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
         <v>1.07</v>
       </c>
       <c r="S8" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="T8" t="n">
         <v>1.01</v>
@@ -2029,52 +2029,52 @@
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -2115,67 +2115,67 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="G9" t="n">
-        <v>1.67</v>
+        <v>1.49</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
         <v>5.2</v>
       </c>
       <c r="L9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="O9" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="P9" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="R9" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="V9" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="W9" t="n">
-        <v>2.48</v>
+        <v>3</v>
       </c>
       <c r="X9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y9" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="Z9" t="n">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
@@ -2184,46 +2184,46 @@
         <v>7.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AD9" t="n">
+        <v>55</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH9" t="n">
         <v>44</v>
       </c>
-      <c r="AE9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>40</v>
-      </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AK9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AQ9" t="n">
         <v>3.85</v>
@@ -2232,13 +2232,13 @@
         <v>4.2</v>
       </c>
       <c r="AS9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV9" t="n">
         <v>4</v>
@@ -2247,7 +2247,7 @@
         <v>4.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AY9" t="n">
         <v>3.25</v>
@@ -2259,26 +2259,26 @@
         <v>4.3</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="BC9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BD9" t="n">
         <v>4.1</v>
       </c>
       <c r="BE9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -2321,10 +2321,10 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="K10" t="n">
-        <v>950</v>
+        <v>980</v>
       </c>
       <c r="L10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G11" t="n">
         <v>6.8</v>
@@ -2512,10 +2512,10 @@
         <v>1.77</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="J11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K11" t="n">
         <v>3.75</v>
@@ -2551,7 +2551,7 @@
         <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="W11" t="n">
         <v>1.18</v>
@@ -2662,11 +2662,11 @@
         <v>3.2</v>
       </c>
       <c r="BG11" t="n">
-        <v>3.2</v>
+        <v>5.1</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
@@ -2805,52 +2805,52 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -2903,13 +2903,13 @@
         <v>16.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2921,16 +2921,16 @@
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="Q13" t="n">
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
         <v>2.54</v>
@@ -2942,37 +2942,37 @@
         <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="X13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Z13" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AA13" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD13" t="n">
         <v>60</v>
       </c>
       <c r="AE13" t="n">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="AF13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH13" t="n">
         <v>50</v>
@@ -2981,46 +2981,46 @@
         <v>350</v>
       </c>
       <c r="AJ13" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AM13" t="n">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="AN13" t="n">
         <v>7.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>920</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4.7</v>
+        <v>28</v>
       </c>
       <c r="AR13" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT13" t="n">
         <v>5.7</v>
       </c>
       <c r="AU13" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AW13" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -3029,10 +3029,10 @@
         <v>10</v>
       </c>
       <c r="AZ13" t="n">
-        <v>4.8</v>
+        <v>34</v>
       </c>
       <c r="BA13" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BB13" t="n">
         <v>8.800000000000001</v>
@@ -3041,20 +3041,20 @@
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="BE13" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF13" t="n">
         <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -3085,13 +3085,13 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
         <v>2.72</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
         <v>3.65</v>
@@ -3100,7 +3100,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.52</v>
@@ -3130,13 +3130,13 @@
         <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V14" t="n">
         <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="X14" t="n">
         <v>11</v>
@@ -3145,40 +3145,40 @@
         <v>12</v>
       </c>
       <c r="Z14" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AA14" t="n">
         <v>70</v>
       </c>
       <c r="AB14" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AC14" t="n">
         <v>7.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE14" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AF14" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AG14" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AH14" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AI14" t="n">
         <v>70</v>
       </c>
       <c r="AJ14" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AK14" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AL14" t="n">
         <v>60</v>
@@ -3187,7 +3187,7 @@
         <v>160</v>
       </c>
       <c r="AN14" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AO14" t="n">
         <v>65</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -3297,7 +3297,7 @@
         <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
@@ -3306,7 +3306,7 @@
         <v>1.38</v>
       </c>
       <c r="O15" t="n">
-        <v>1.45</v>
+        <v>1.02</v>
       </c>
       <c r="P15" t="n">
         <v>1.38</v>
@@ -3387,52 +3387,52 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -3476,16 +3476,16 @@
         <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I16" t="n">
         <v>2.44</v>
       </c>
       <c r="J16" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="K16" t="n">
         <v>4.1</v>
@@ -3503,16 +3503,16 @@
         <v>1.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q16" t="n">
         <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S16" t="n">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="T16" t="n">
         <v>1.64</v>
@@ -3521,10 +3521,10 @@
         <v>2.34</v>
       </c>
       <c r="V16" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
         <v>23</v>
@@ -3581,7 +3581,7 @@
         <v>18.5</v>
       </c>
       <c r="AP16" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AQ16" t="n">
         <v>10.5</v>
@@ -3596,31 +3596,31 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AW16" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AX16" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AY16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ16" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>23</v>
+        <v>3.75</v>
       </c>
       <c r="BB16" t="n">
         <v>3.9</v>
       </c>
       <c r="BC16" t="n">
-        <v>24</v>
+        <v>3.75</v>
       </c>
       <c r="BD16" t="n">
         <v>3.85</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -3667,58 +3667,58 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.92</v>
+        <v>2.08</v>
       </c>
       <c r="G17" t="n">
-        <v>2.48</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>2.82</v>
+        <v>3.45</v>
       </c>
       <c r="I17" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="J17" t="n">
-        <v>3.05</v>
+        <v>3.5</v>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>3.95</v>
       </c>
       <c r="L17" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M17" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>1.85</v>
+        <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="P17" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.26</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>1.26</v>
+        <v>3.1</v>
       </c>
       <c r="T17" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="V17" t="n">
-        <v>1.26</v>
+        <v>1.34</v>
       </c>
       <c r="W17" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
         <v>1000</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -3861,170 +3861,170 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.46</v>
+        <v>2.3</v>
       </c>
       <c r="G18" t="n">
-        <v>2.92</v>
+        <v>2.6</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="J18" t="n">
         <v>3.3</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L18" t="n">
         <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>1.74</v>
+        <v>3.65</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P18" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="R18" t="n">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V18" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="X18" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y18" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AA18" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC18" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK18" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL18" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO18" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BD18" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BG18" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
         <v>3.8</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="H19" t="n">
         <v>2.16</v>
@@ -4067,10 +4067,10 @@
         <v>2.36</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.43</v>
@@ -4085,7 +4085,7 @@
         <v>1.46</v>
       </c>
       <c r="P19" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q19" t="n">
         <v>2.36</v>
@@ -4103,43 +4103,43 @@
         <v>1.86</v>
       </c>
       <c r="V19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="W19" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
         <v>12</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z19" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AB19" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE19" t="n">
         <v>36</v>
       </c>
       <c r="AF19" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AG19" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AI19" t="n">
         <v>65</v>
@@ -4160,7 +4160,7 @@
         <v>100</v>
       </c>
       <c r="AO19" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AP19" t="n">
         <v>8.800000000000001</v>
@@ -4172,7 +4172,7 @@
         <v>11.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4184,10 +4184,10 @@
         <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AX19" t="n">
-        <v>3.9</v>
+        <v>4.8</v>
       </c>
       <c r="AY19" t="n">
         <v>14.5</v>
@@ -4196,29 +4196,29 @@
         <v>18.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB19" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE19" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="BF19" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BG19" t="n">
         <v>19</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -4255,7 +4255,7 @@
         <v>1.98</v>
       </c>
       <c r="H20" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I20" t="n">
         <v>5</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4452,7 @@
         <v>2.06</v>
       </c>
       <c r="I21" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
@@ -4491,10 +4491,10 @@
         <v>2.2</v>
       </c>
       <c r="V21" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
         <v>20</v>
@@ -4593,7 +4593,7 @@
         <v>36</v>
       </c>
       <c r="BD21" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
         <v>7.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -4643,16 +4643,16 @@
         <v>2.34</v>
       </c>
       <c r="H22" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J22" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4688,13 +4688,13 @@
         <v>1.29</v>
       </c>
       <c r="W22" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X22" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z22" t="n">
         <v>1000</v>
@@ -4703,10 +4703,10 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AD22" t="n">
         <v>1000</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AK22" t="n">
         <v>1000</v>
@@ -4739,68 +4739,68 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AO22" t="n">
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ22" t="n">
-        <v>3.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="AU22" t="n">
-        <v>6.4</v>
+        <v>2.9</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="AW22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BE22" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX22" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BD22" t="n">
+      <c r="BF22" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BG22" t="n">
         <v>4</v>
       </c>
-      <c r="BE22" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BG22" t="n">
-        <v>38</v>
-      </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>3.6</v>
       </c>
       <c r="H23" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
@@ -4882,7 +4882,7 @@
         <v>1.57</v>
       </c>
       <c r="W23" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X23" t="n">
         <v>14.5</v>
@@ -4957,7 +4957,7 @@
         <v>2.9</v>
       </c>
       <c r="AV23" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AW23" t="n">
         <v>3.85</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
         <v>2.14</v>
@@ -5043,7 +5043,7 @@
         <v>3.6</v>
       </c>
       <c r="L24" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
@@ -5055,10 +5055,10 @@
         <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5067,10 +5067,10 @@
         <v>4.1</v>
       </c>
       <c r="T24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U24" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
         <v>1.27</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G25" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H25" t="n">
         <v>2.84</v>
-      </c>
-      <c r="H25" t="n">
-        <v>2.86</v>
       </c>
       <c r="I25" t="n">
         <v>3.25</v>
       </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5252,7 +5252,7 @@
         <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R25" t="n">
         <v>1.26</v>
@@ -5267,10 +5267,10 @@
         <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X25" t="n">
         <v>13.5</v>
@@ -5366,10 +5366,10 @@
         <v>5.1</v>
       </c>
       <c r="BC25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BD25" t="n">
-        <v>38</v>
+        <v>5.2</v>
       </c>
       <c r="BE25" t="n">
         <v>5.5</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -5422,13 +5422,13 @@
         <v>2.98</v>
       </c>
       <c r="I26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J26" t="n">
-        <v>4</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L26" t="n">
         <v>1.22</v>
@@ -5437,16 +5437,16 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="O26" t="n">
         <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R26" t="n">
         <v>1.72</v>
@@ -5455,7 +5455,7 @@
         <v>2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="U26" t="n">
         <v>2.72</v>
@@ -5479,13 +5479,13 @@
         <v>60</v>
       </c>
       <c r="AB26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC26" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AE26" t="n">
         <v>34</v>
@@ -5521,16 +5521,16 @@
         <v>19</v>
       </c>
       <c r="AP26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AR26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AS26" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT26" t="n">
         <v>4</v>
@@ -5542,7 +5542,7 @@
         <v>11</v>
       </c>
       <c r="AW26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AX26" t="n">
         <v>4.1</v>
@@ -5554,19 +5554,19 @@
         <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB26" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BC26" t="n">
         <v>4.1</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE26" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF26" t="n">
         <v>7.2</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>1.53</v>
       </c>
       <c r="I27" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="J27" t="n">
         <v>3.7</v>
@@ -5625,7 +5625,7 @@
         <v>4.3</v>
       </c>
       <c r="L27" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
         <v>1.1</v>
@@ -5646,16 +5646,16 @@
         <v>1.21</v>
       </c>
       <c r="S27" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="T27" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V27" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="W27" t="n">
         <v>1.11</v>
@@ -5718,7 +5718,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AR27" t="n">
         <v>6.6</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -5801,55 +5801,55 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.94</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>4.3</v>
       </c>
       <c r="H28" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="I28" t="n">
-        <v>2.42</v>
+        <v>2.22</v>
       </c>
       <c r="J28" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>1.5</v>
+        <v>2.86</v>
       </c>
       <c r="O28" t="n">
         <v>1.46</v>
       </c>
       <c r="P28" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="R28" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>2.12</v>
+        <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="V28" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="W28" t="n">
         <v>1.3</v>
@@ -5882,7 +5882,7 @@
         <v>32</v>
       </c>
       <c r="AG28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH28" t="n">
         <v>27</v>
@@ -5891,25 +5891,25 @@
         <v>55</v>
       </c>
       <c r="AJ28" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AK28" t="n">
         <v>75</v>
       </c>
       <c r="AL28" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM28" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN28" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AO28" t="n">
         <v>29</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
@@ -5918,10 +5918,10 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AU28" t="n">
         <v>6.4</v>
@@ -5930,41 +5930,41 @@
         <v>4</v>
       </c>
       <c r="AW28" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX28" t="n">
         <v>5.2</v>
       </c>
-      <c r="AX28" t="n">
+      <c r="AY28" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AZ28" t="n">
         <v>5.1</v>
       </c>
-      <c r="AY28" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>5</v>
-      </c>
       <c r="BA28" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BB28" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BD28" t="n">
         <v>5.9</v>
       </c>
-      <c r="BC28" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF28" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BG28" t="n">
         <v>17</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -5998,7 +5998,7 @@
         <v>1.9</v>
       </c>
       <c r="G29" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
         <v>4.6</v>
@@ -6010,10 +6010,10 @@
         <v>2.92</v>
       </c>
       <c r="K29" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="M29" t="n">
         <v>1.11</v>
@@ -6025,7 +6025,7 @@
         <v>1.5</v>
       </c>
       <c r="P29" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q29" t="n">
         <v>2.5</v>
@@ -6040,13 +6040,13 @@
         <v>2.14</v>
       </c>
       <c r="U29" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V29" t="n">
         <v>1.22</v>
       </c>
       <c r="W29" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
         <v>11</v>
@@ -6067,7 +6067,7 @@
         <v>8.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AE29" t="n">
         <v>110</v>
@@ -6079,7 +6079,7 @@
         <v>12.5</v>
       </c>
       <c r="AH29" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI29" t="n">
         <v>130</v>
@@ -6103,19 +6103,19 @@
         <v>170</v>
       </c>
       <c r="AP29" t="n">
-        <v>3.85</v>
+        <v>7.8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>3.15</v>
+        <v>5.6</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
@@ -6124,41 +6124,41 @@
         <v>18</v>
       </c>
       <c r="AW29" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AX29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY29" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AZ29" t="n">
         <v>18</v>
       </c>
       <c r="BA29" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BB29" t="n">
-        <v>4.9</v>
+        <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF29" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BG29" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -6189,58 +6189,58 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="G30" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="H30" t="n">
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="J30" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="K30" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="L30" t="n">
         <v>1.43</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.47</v>
       </c>
-      <c r="O30" t="n">
-        <v>1.45</v>
-      </c>
       <c r="P30" t="n">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.16</v>
+        <v>2.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S30" t="n">
-        <v>2.16</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V30" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W30" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X30" t="n">
         <v>1000</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -6386,52 +6386,52 @@
         <v>1.58</v>
       </c>
       <c r="G31" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H31" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="J31" t="n">
         <v>3.8</v>
       </c>
       <c r="K31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L31" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M31" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>1.63</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="R31" t="n">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W31" t="n">
         <v>2.4</v>
@@ -6449,7 +6449,7 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC31" t="n">
         <v>10.5</v>
@@ -6500,13 +6500,13 @@
         <v>4.8</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT31" t="n">
         <v>5.6</v>
       </c>
       <c r="AU31" t="n">
-        <v>7</v>
+        <v>3.45</v>
       </c>
       <c r="AV31" t="n">
         <v>4.4</v>
@@ -6521,16 +6521,16 @@
         <v>7.8</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB31" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BD31" t="n">
         <v>4.7</v>
@@ -6539,14 +6539,14 @@
         <v>5</v>
       </c>
       <c r="BF31" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -6622,7 +6622,7 @@
         <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
         <v>1.09</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -6771,73 +6771,73 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="G33" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="H33" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="I33" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J33" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="K33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N33" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="P33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="S33" t="n">
         <v>4.2</v>
       </c>
-      <c r="L33" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P33" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S33" t="n">
-        <v>4.1</v>
-      </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V33" t="n">
         <v>1.83</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
       </c>
       <c r="Y33" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AA33" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB33" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC33" t="n">
         <v>1000</v>
@@ -6855,7 +6855,7 @@
         <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="AT33" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.01</v>
+        <v>1.46</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="H34" t="n">
         <v>3.55</v>
@@ -6998,25 +6998,25 @@
         <v>1.86</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R34" t="n">
         <v>1.34</v>
       </c>
       <c r="S34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="U34" t="n">
         <v>2.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -7159,40 +7159,40 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G35" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="H35" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="I35" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="J35" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="K35" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="L35" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O35" t="n">
         <v>1.24</v>
       </c>
       <c r="P35" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R35" t="n">
         <v>1.49</v>
@@ -7201,16 +7201,16 @@
         <v>2.78</v>
       </c>
       <c r="T35" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U35" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="X35" t="n">
         <v>24</v>
@@ -7219,10 +7219,10 @@
         <v>26</v>
       </c>
       <c r="Z35" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA35" t="n">
-        <v>160</v>
+        <v>210</v>
       </c>
       <c r="AB35" t="n">
         <v>10</v>
@@ -7243,16 +7243,16 @@
         <v>10.5</v>
       </c>
       <c r="AH35" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AI35" t="n">
         <v>90</v>
       </c>
       <c r="AJ35" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="AK35" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL35" t="n">
         <v>34</v>
@@ -7261,10 +7261,10 @@
         <v>130</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO35" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AP35" t="n">
         <v>17</v>
@@ -7273,10 +7273,10 @@
         <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS35" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT35" t="n">
         <v>8.4</v>
@@ -7288,7 +7288,7 @@
         <v>21</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AX35" t="n">
         <v>8.6</v>
@@ -7297,32 +7297,32 @@
         <v>9</v>
       </c>
       <c r="AZ35" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC35" t="n">
         <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BE35" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="BG35" t="n">
-        <v>55</v>
+        <v>6.8</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -7353,70 +7353,70 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="G36" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H36" t="n">
         <v>2.74</v>
       </c>
       <c r="I36" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J36" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L36" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
         <v>1.12</v>
       </c>
       <c r="N36" t="n">
-        <v>2.7</v>
+        <v>2.92</v>
       </c>
       <c r="O36" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="P36" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R36" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U36" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="V36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W36" t="n">
         <v>1.51</v>
       </c>
-      <c r="W36" t="n">
-        <v>1.48</v>
-      </c>
       <c r="X36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y36" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z36" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA36" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB36" t="n">
         <v>9.4</v>
@@ -7425,64 +7425,64 @@
         <v>7.8</v>
       </c>
       <c r="AD36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AE36" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF36" t="n">
         <v>18</v>
       </c>
       <c r="AG36" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH36" t="n">
         <v>23</v>
       </c>
       <c r="AI36" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>50</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL36" t="n">
         <v>65</v>
       </c>
-      <c r="AJ36" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK36" t="n">
+      <c r="AM36" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>42</v>
+      </c>
+      <c r="AO36" t="n">
         <v>44</v>
       </c>
-      <c r="AL36" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>50</v>
-      </c>
       <c r="AP36" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AQ36" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AR36" t="n">
         <v>15</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT36" t="n">
         <v>7.8</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV36" t="n">
         <v>11</v>
       </c>
       <c r="AW36" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AX36" t="n">
         <v>15</v>
@@ -7491,32 +7491,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA36" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB36" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BC36" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="BD36" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE36" t="n">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BG36" t="n">
-        <v>32</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -7550,13 +7550,13 @@
         <v>2.3</v>
       </c>
       <c r="G37" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H37" t="n">
         <v>3.65</v>
       </c>
       <c r="I37" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J37" t="n">
         <v>3.35</v>
@@ -7589,16 +7589,16 @@
         <v>4.4</v>
       </c>
       <c r="T37" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U37" t="n">
         <v>1.97</v>
       </c>
       <c r="V37" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W37" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="X37" t="n">
         <v>11</v>
@@ -7688,7 +7688,7 @@
         <v>18.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB37" t="n">
         <v>27</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G38" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H38" t="n">
         <v>4.8</v>
@@ -7753,7 +7753,7 @@
         <v>4.9</v>
       </c>
       <c r="J38" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K38" t="n">
         <v>3.6</v>
@@ -7765,7 +7765,7 @@
         <v>1.09</v>
       </c>
       <c r="N38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O38" t="n">
         <v>1.43</v>
@@ -7786,10 +7786,10 @@
         <v>2.06</v>
       </c>
       <c r="U38" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V38" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W38" t="n">
         <v>2.04</v>
@@ -7801,7 +7801,7 @@
         <v>14.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA38" t="n">
         <v>120</v>
@@ -7858,7 +7858,7 @@
         <v>30</v>
       </c>
       <c r="AS38" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT38" t="n">
         <v>7</v>
@@ -7870,13 +7870,13 @@
         <v>17.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX38" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
         <v>20</v>
@@ -7900,11 +7900,11 @@
         <v>15.5</v>
       </c>
       <c r="BG38" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
         <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.22</v>
+        <v>2.12</v>
       </c>
       <c r="R39" t="n">
         <v>1.3</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -8144,7 +8144,7 @@
         <v>1.02</v>
       </c>
       <c r="K40" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O40" t="n">
         <v>1.35</v>
@@ -8237,52 +8237,52 @@
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AQ40" t="n">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR40" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS40" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT40" t="n">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU40" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV40" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW40" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AX40" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY40" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ40" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA40" t="n">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BB40" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BC40" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD40" t="n">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE40" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF40" t="n">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>1.78</v>
       </c>
       <c r="G41" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="H41" t="n">
         <v>4.9</v>
@@ -8374,7 +8374,7 @@
         <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="X41" t="n">
         <v>13.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -8520,13 +8520,13 @@
         <v>3.35</v>
       </c>
       <c r="G42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H42" t="n">
         <v>2.3</v>
       </c>
       <c r="I42" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="J42" t="n">
         <v>2.94</v>
@@ -8538,58 +8538,58 @@
         <v>1.47</v>
       </c>
       <c r="M42" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N42" t="n">
-        <v>1.46</v>
+        <v>2.68</v>
       </c>
       <c r="O42" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P42" t="n">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="R42" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U42" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V42" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W42" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="X42" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Y42" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="Z42" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AA42" t="n">
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE42" t="n">
         <v>1000</v>
@@ -8598,7 +8598,7 @@
         <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH42" t="n">
         <v>1000</v>
@@ -8616,7 +8616,7 @@
         <v>1000</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN42" t="n">
         <v>1000</v>
@@ -8625,62 +8625,62 @@
         <v>1000</v>
       </c>
       <c r="AP42" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR42" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AS42" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT42" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AU42" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV42" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AW42" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX42" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AY42" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AZ42" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BC42" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BD42" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BG42" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -8711,31 +8711,31 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="G43" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H43" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="I43" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="J43" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="K43" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L43" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="M43" t="n">
         <v>1.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O43" t="n">
         <v>1.44</v>
@@ -8759,22 +8759,22 @@
         <v>1.92</v>
       </c>
       <c r="V43" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W43" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="X43" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="Y43" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z43" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA43" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AB43" t="n">
         <v>14</v>
@@ -8813,7 +8813,7 @@
         <v>150</v>
       </c>
       <c r="AN43" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AO43" t="n">
         <v>27</v>
@@ -8822,59 +8822,59 @@
         <v>4.2</v>
       </c>
       <c r="AQ43" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS43" t="n">
         <v>3.75</v>
       </c>
-      <c r="AR43" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AS43" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AT43" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AU43" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AV43" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AW43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ43" t="n">
         <v>5.4</v>
       </c>
-      <c r="AX43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>5</v>
-      </c>
       <c r="BA43" t="n">
-        <v>5.8</v>
+        <v>3.85</v>
       </c>
       <c r="BB43" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>6</v>
+        <v>2.72</v>
       </c>
       <c r="BD43" t="n">
-        <v>6</v>
+        <v>2.74</v>
       </c>
       <c r="BE43" t="n">
-        <v>3.65</v>
+        <v>2.52</v>
       </c>
       <c r="BF43" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BG43" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -8908,7 +8908,7 @@
         <v>1.51</v>
       </c>
       <c r="G44" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H44" t="n">
         <v>7.4</v>
@@ -8920,7 +8920,7 @@
         <v>4.3</v>
       </c>
       <c r="K44" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L44" t="n">
         <v>1.33</v>
@@ -8929,19 +8929,19 @@
         <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O44" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P44" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R44" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S44" t="n">
         <v>3.5</v>
@@ -8950,28 +8950,28 @@
         <v>2.12</v>
       </c>
       <c r="U44" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="V44" t="n">
         <v>1.13</v>
       </c>
       <c r="W44" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="X44" t="n">
         <v>15.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Z44" t="n">
         <v>440</v>
       </c>
       <c r="AA44" t="n">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="AB44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC44" t="n">
         <v>10.5</v>
@@ -8983,37 +8983,37 @@
         <v>1000</v>
       </c>
       <c r="AF44" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG44" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH44" t="n">
         <v>48</v>
       </c>
       <c r="AI44" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AJ44" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL44" t="n">
         <v>160</v>
       </c>
       <c r="AM44" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN44" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AO44" t="n">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="AP44" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ44" t="n">
         <v>15</v>
@@ -9028,22 +9028,22 @@
         <v>6.6</v>
       </c>
       <c r="AU44" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AW44" t="n">
         <v>40</v>
       </c>
       <c r="AX44" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ44" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="BA44" t="n">
         <v>42</v>
@@ -9052,7 +9052,7 @@
         <v>11.5</v>
       </c>
       <c r="BC44" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="BD44" t="n">
         <v>26</v>
@@ -9061,14 +9061,14 @@
         <v>46</v>
       </c>
       <c r="BF44" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG44" t="n">
         <v>46</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
         <v>4.4</v>
       </c>
       <c r="K45" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L45" t="n">
         <v>1.32</v>
@@ -9141,7 +9141,7 @@
         <v>3.05</v>
       </c>
       <c r="T45" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
       <c r="U45" t="n">
         <v>1.8</v>
@@ -9207,7 +9207,7 @@
         <v>1000</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.1</v>
+        <v>13.5</v>
       </c>
       <c r="AQ45" t="n">
         <v>4.5</v>
@@ -9234,7 +9234,7 @@
         <v>7</v>
       </c>
       <c r="AY45" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
         <v>4.5</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
         <v>1.02</v>
       </c>
       <c r="K46" t="n">
-        <v>110</v>
+        <v>950</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9317,7 +9317,7 @@
         <v>1.01</v>
       </c>
       <c r="N46" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O46" t="n">
         <v>1.31</v>
@@ -9401,52 +9401,52 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ46" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR46" t="n">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS46" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="AT46" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AU46" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AV46" t="n">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW46" t="n">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AX46" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY46" t="n">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ46" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BA46" t="n">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BB46" t="n">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC46" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD46" t="n">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BE46" t="n">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BF46" t="n">
         <v>1.01</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -9487,22 +9487,22 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="H47" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="I47" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="J47" t="n">
-        <v>2.16</v>
+        <v>2.98</v>
       </c>
       <c r="K47" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9535,10 +9535,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -9684,16 +9684,16 @@
         <v>1.21</v>
       </c>
       <c r="G48" t="n">
-        <v>110</v>
+        <v>1.94</v>
       </c>
       <c r="H48" t="n">
         <v>3.55</v>
       </c>
       <c r="I48" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>1.06</v>
+        <v>2.62</v>
       </c>
       <c r="K48" t="n">
         <v>1000</v>
@@ -9705,7 +9705,7 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.25</v>
+        <v>1.03</v>
       </c>
       <c r="O48" t="n">
         <v>1.35</v>
@@ -9732,7 +9732,7 @@
         <v>1.14</v>
       </c>
       <c r="W48" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -9881,10 +9881,10 @@
         <v>3.65</v>
       </c>
       <c r="H49" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I49" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -9899,31 +9899,31 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="O49" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P49" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="R49" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="S49" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T49" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U49" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="V49" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
         <v>1.37</v>
@@ -9986,7 +9986,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.1</v>
+        <v>6.8</v>
       </c>
       <c r="AR49" t="n">
         <v>3.65</v>
@@ -10034,11 +10034,11 @@
         <v>4.4</v>
       </c>
       <c r="BG49" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>2.76</v>
       </c>
       <c r="G50" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H50" t="n">
         <v>2.9</v>
@@ -10102,7 +10102,7 @@
         <v>1.52</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.34</v>
+        <v>2.64</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
@@ -10111,10 +10111,10 @@
         <v>4.8</v>
       </c>
       <c r="T50" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="U50" t="n">
-        <v>1.79</v>
+        <v>1.64</v>
       </c>
       <c r="V50" t="n">
         <v>1.45</v>
@@ -10192,7 +10192,7 @@
         <v>3</v>
       </c>
       <c r="AU50" t="n">
-        <v>2.88</v>
+        <v>6.2</v>
       </c>
       <c r="AV50" t="n">
         <v>3.45</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-08 09:01:24</t>
+          <t>2026-03-08 11:19:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="F2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G2" t="n">
         <v>1.69</v>
       </c>
-      <c r="G2" t="n">
-        <v>1.7</v>
-      </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
         <v>4.5</v>
@@ -787,28 +787,28 @@
         <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T2" t="n">
         <v>1.75</v>
       </c>
       <c r="U2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -868,7 +868,7 @@
         <v>19</v>
       </c>
       <c r="AQ2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR2" t="n">
         <v>38</v>
@@ -886,7 +886,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -898,7 +898,7 @@
         <v>16.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
         <v>15</v>
@@ -907,7 +907,7 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE2" t="n">
         <v>8.6</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1178,13 +1178,13 @@
         <v>1.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R4" t="n">
         <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="T4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
         <v>1.68</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R5" t="n">
         <v>1.25</v>
@@ -1390,7 +1390,7 @@
         <v>1.76</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
         <v>13</v>
@@ -1426,7 +1426,7 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
@@ -1441,10 +1441,10 @@
         <v>170</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
         <v>9.4</v>
@@ -1453,7 +1453,7 @@
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS5" t="n">
         <v>22</v>
@@ -1480,10 +1480,10 @@
         <v>5.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BB5" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BC5" t="n">
         <v>5.9</v>
@@ -1492,17 +1492,17 @@
         <v>6</v>
       </c>
       <c r="BE5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF5" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="BG5" t="n">
         <v>5.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="G6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
         <v>1.22</v>
       </c>
       <c r="I6" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="J6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="K6" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="L6" t="n">
         <v>1.26</v>
@@ -1572,7 +1572,7 @@
         <v>1.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="T6" t="n">
         <v>2.54</v>
@@ -1581,7 +1581,7 @@
         <v>1.56</v>
       </c>
       <c r="V6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="W6" t="n">
         <v>1.04</v>
@@ -1641,7 +1641,7 @@
         <v>5.4</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ6" t="n">
         <v>6.8</v>
@@ -1650,53 +1650,53 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="AU6" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AY6" t="n">
         <v>5.2</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>5</v>
       </c>
       <c r="AZ6" t="n">
         <v>30</v>
       </c>
       <c r="BA6" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BD6" t="n">
         <v>4.1</v>
       </c>
-      <c r="BC6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BE6" t="n">
-        <v>5.3</v>
+        <v>4.2</v>
       </c>
       <c r="BF6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
         <v>3.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>940</v>
+        <v>980</v>
       </c>
       <c r="H8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="I8" t="n">
         <v>950</v>
       </c>
       <c r="J8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -2115,64 +2115,64 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="G9" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="H9" t="n">
-        <v>1.09</v>
+        <v>10</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="K9" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>2.86</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="U9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="X9" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="Y9" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="Z9" t="n">
         <v>130</v>
@@ -2193,92 +2193,92 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG9" t="n">
         <v>13</v>
       </c>
       <c r="AH9" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL9" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>980</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AQ9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU9" t="n">
         <v>3.85</v>
       </c>
-      <c r="AR9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS9" t="n">
+      <c r="AV9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC9" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT9" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>4</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AY9" t="n">
+      <c r="BD9" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE9" t="n">
         <v>3.25</v>
       </c>
-      <c r="AZ9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BF9" t="n">
-        <v>3.15</v>
+        <v>6.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
         <v>980</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -2730,13 +2730,13 @@
         <v>1.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="R12" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S12" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2900,7 @@
         <v>13.5</v>
       </c>
       <c r="I13" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="J13" t="n">
         <v>5.1</v>
@@ -2909,7 +2909,7 @@
         <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2921,13 +2921,13 @@
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
         <v>2.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
         <v>3.65</v>
@@ -2939,7 +2939,7 @@
         <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
         <v>3.7</v>
@@ -2996,7 +2996,7 @@
         <v>7.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>920</v>
+        <v>880</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -3088,28 +3088,28 @@
         <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H14" t="n">
         <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L14" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M14" t="n">
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O14" t="n">
         <v>1.47</v>
@@ -3130,10 +3130,10 @@
         <v>1.98</v>
       </c>
       <c r="U14" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
         <v>1.59</v>
@@ -3199,56 +3199,56 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AS14" t="n">
         <v>8</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AU14" t="n">
         <v>6.2</v>
       </c>
       <c r="AV14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>6.4</v>
+        <v>15.5</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
       </c>
       <c r="BB14" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC14" t="n">
         <v>7.2</v>
       </c>
       <c r="BD14" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE14" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BF14" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BG14" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
         <v>1.38</v>
       </c>
       <c r="O15" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P15" t="n">
         <v>1.38</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
         <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
         <v>2.44</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -3721,116 +3721,116 @@
         <v>1.79</v>
       </c>
       <c r="X17" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA17" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH17" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI17" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK17" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL17" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM17" t="n">
         <v>1000</v>
       </c>
       <c r="AN17" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AT17" t="n">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC17" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BD17" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -3861,61 +3861,61 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="G18" t="n">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
         <v>3</v>
       </c>
-      <c r="I18" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L18" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.3</v>
-      </c>
       <c r="T18" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="U18" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="n">
         <v>14.5</v>
@@ -3939,46 +3939,46 @@
         <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AG18" t="n">
         <v>14</v>
       </c>
       <c r="AH18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK18" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AO18" t="n">
         <v>36</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT18" t="n">
         <v>9.4</v>
@@ -3990,7 +3990,7 @@
         <v>11</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AX18" t="n">
         <v>13.5</v>
@@ -3999,16 +3999,16 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA18" t="n">
         <v>4.7</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.4</v>
+        <v>20</v>
       </c>
       <c r="BD18" t="n">
         <v>4.6</v>
@@ -4017,14 +4017,14 @@
         <v>4.9</v>
       </c>
       <c r="BF18" t="n">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="BG18" t="n">
         <v>21</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
         <v>4.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="I19" t="n">
         <v>2.36</v>
@@ -4070,7 +4070,7 @@
         <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
         <v>1.43</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -4252,28 +4252,28 @@
         <v>1.93</v>
       </c>
       <c r="G20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H20" t="n">
         <v>4.9</v>
       </c>
       <c r="I20" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="J20" t="n">
         <v>3.45</v>
       </c>
       <c r="K20" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
       </c>
       <c r="N20" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O20" t="n">
         <v>1.35</v>
@@ -4327,25 +4327,25 @@
         <v>1000</v>
       </c>
       <c r="AF20" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG20" t="n">
         <v>11</v>
       </c>
       <c r="AH20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
         <v>23</v>
       </c>
       <c r="AL20" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM20" t="n">
         <v>140</v>
@@ -4366,7 +4366,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AT20" t="n">
         <v>7.4</v>
@@ -4378,7 +4378,7 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
@@ -4390,7 +4390,7 @@
         <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB20" t="n">
         <v>19</v>
@@ -4399,20 +4399,20 @@
         <v>18.5</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE20" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF20" t="n">
         <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G21" t="n">
         <v>4.1</v>
@@ -4455,13 +4455,13 @@
         <v>2.14</v>
       </c>
       <c r="J21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K21" t="n">
         <v>3.8</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M21" t="n">
         <v>1.06</v>
@@ -4506,7 +4506,7 @@
         <v>14.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AB21" t="n">
         <v>16.5</v>
@@ -4521,7 +4521,7 @@
         <v>23</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AG21" t="n">
         <v>16.5</v>
@@ -4530,13 +4530,13 @@
         <v>18</v>
       </c>
       <c r="AI21" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AJ21" t="n">
         <v>75</v>
       </c>
       <c r="AK21" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AL21" t="n">
         <v>55</v>
@@ -4590,10 +4590,10 @@
         <v>7.4</v>
       </c>
       <c r="BC21" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="BD21" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="BE21" t="n">
         <v>7.6</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="H22" t="n">
         <v>3.75</v>
       </c>
       <c r="I22" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L22" t="n">
         <v>1.44</v>
@@ -4685,10 +4685,10 @@
         <v>1.96</v>
       </c>
       <c r="V22" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="X22" t="n">
         <v>15</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4831,7 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="G23" t="n">
         <v>3.6</v>
@@ -4843,13 +4843,13 @@
         <v>2.76</v>
       </c>
       <c r="J23" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="K23" t="n">
         <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4867,7 +4867,7 @@
         <v>2.2</v>
       </c>
       <c r="R23" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
         <v>3.95</v>
@@ -4882,7 +4882,7 @@
         <v>1.57</v>
       </c>
       <c r="W23" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X23" t="n">
         <v>14.5</v>
@@ -4891,7 +4891,7 @@
         <v>11.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4900,7 +4900,7 @@
         <v>13.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD23" t="n">
         <v>14.5</v>
@@ -4936,31 +4936,31 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AT23" t="n">
         <v>3.25</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX23" t="n">
         <v>15.5</v>
@@ -4969,32 +4969,32 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BA23" t="n">
         <v>4</v>
       </c>
       <c r="BB23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC23" t="n">
         <v>4</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>3.95</v>
       </c>
       <c r="BD23" t="n">
         <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BG23" t="n">
         <v>20</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -5040,10 +5040,10 @@
         <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
         <v>1.09</v>
@@ -5055,10 +5055,10 @@
         <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5085,7 +5085,7 @@
         <v>16.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>40</v>
+        <v>980</v>
       </c>
       <c r="AA24" t="n">
         <v>130</v>
@@ -5115,10 +5115,10 @@
         <v>95</v>
       </c>
       <c r="AJ24" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AK24" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AL24" t="n">
         <v>60</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.52</v>
+        <v>2.4</v>
       </c>
       <c r="G25" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="I25" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L25" t="n">
         <v>1.01</v>
@@ -5252,7 +5252,7 @@
         <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R25" t="n">
         <v>1.26</v>
@@ -5267,10 +5267,10 @@
         <v>1.94</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="W25" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X25" t="n">
         <v>13.5</v>
@@ -5294,7 +5294,7 @@
         <v>16.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AF25" t="n">
         <v>21</v>
@@ -5303,16 +5303,16 @@
         <v>13</v>
       </c>
       <c r="AH25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="AI25" t="n">
         <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AK25" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AL25" t="n">
         <v>55</v>
@@ -5330,13 +5330,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ25" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AS25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5345,16 +5345,16 @@
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AW25" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AY25" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AZ25" t="n">
         <v>17</v>
@@ -5363,26 +5363,26 @@
         <v>42</v>
       </c>
       <c r="BB25" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="BC25" t="n">
-        <v>24</v>
+        <v>4.8</v>
       </c>
       <c r="BD25" t="n">
+        <v>38</v>
+      </c>
+      <c r="BE25" t="n">
         <v>5.2</v>
       </c>
-      <c r="BE25" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BF25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG25" t="n">
         <v>25</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G26" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H26" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="J26" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K26" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L26" t="n">
         <v>1.22</v>
@@ -5437,43 +5437,43 @@
         <v>1.02</v>
       </c>
       <c r="N26" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="O26" t="n">
         <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R26" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="T26" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="U26" t="n">
         <v>2.72</v>
       </c>
       <c r="V26" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="X26" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="Y26" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="Z26" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AA26" t="n">
         <v>60</v>
@@ -5488,28 +5488,28 @@
         <v>17.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AF26" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AG26" t="n">
         <v>14</v>
       </c>
       <c r="AH26" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AI26" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AJ26" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AL26" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AM26" t="n">
         <v>55</v>
@@ -5518,7 +5518,7 @@
         <v>11</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AP26" t="n">
         <v>4.4</v>
@@ -5569,14 +5569,14 @@
         <v>4.6</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="I27" t="n">
         <v>1.63</v>
@@ -5622,10 +5622,10 @@
         <v>3.7</v>
       </c>
       <c r="K27" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M27" t="n">
         <v>1.1</v>
@@ -5670,7 +5670,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA27" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AB27" t="n">
         <v>24</v>
@@ -5682,16 +5682,16 @@
         <v>11.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AF27" t="n">
         <v>80</v>
       </c>
       <c r="AG27" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AH27" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AI27" t="n">
         <v>75</v>
@@ -5712,7 +5712,7 @@
         <v>500</v>
       </c>
       <c r="AO27" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AP27" t="n">
         <v>8.800000000000001</v>
@@ -5727,7 +5727,7 @@
         <v>12.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AU27" t="n">
         <v>8.199999999999999</v>
@@ -5736,16 +5736,16 @@
         <v>9.4</v>
       </c>
       <c r="AW27" t="n">
-        <v>17.5</v>
+        <v>4.8</v>
       </c>
       <c r="AX27" t="n">
         <v>5.7</v>
       </c>
       <c r="AY27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>5.3</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>5.2</v>
       </c>
       <c r="BA27" t="n">
         <v>5.7</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H28" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="I28" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
         <v>3.5</v>
@@ -5846,25 +5846,25 @@
         <v>1.84</v>
       </c>
       <c r="U28" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="V28" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W28" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="X28" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="Y28" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="Z28" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AA28" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AB28" t="n">
         <v>15</v>
@@ -5873,16 +5873,16 @@
         <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>970</v>
+        <v>980</v>
       </c>
       <c r="AE28" t="n">
-        <v>34</v>
+        <v>980</v>
       </c>
       <c r="AF28" t="n">
-        <v>32</v>
+        <v>980</v>
       </c>
       <c r="AG28" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AH28" t="n">
         <v>27</v>
@@ -5906,10 +5906,10 @@
         <v>120</v>
       </c>
       <c r="AO28" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AP28" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
@@ -5921,40 +5921,40 @@
         <v>5.2</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AU28" t="n">
         <v>6.4</v>
       </c>
       <c r="AV28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AW28" t="n">
         <v>5.3</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY28" t="n">
-        <v>4.9</v>
+        <v>15</v>
       </c>
       <c r="AZ28" t="n">
         <v>5.1</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB28" t="n">
         <v>6</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD28" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF28" t="n">
         <v>6</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -6055,7 +6055,7 @@
         <v>14.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AA29" t="n">
         <v>170</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -6189,13 +6189,13 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G30" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="I30" t="n">
         <v>6.4</v>
@@ -6225,10 +6225,10 @@
         <v>2.38</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T30" t="n">
         <v>2.08</v>
@@ -6240,13 +6240,13 @@
         <v>1.19</v>
       </c>
       <c r="W30" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X30" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6255,7 +6255,7 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC30" t="n">
         <v>1000</v>
@@ -6267,10 +6267,10 @@
         <v>1000</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>2.58</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>2.9</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>2.8</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
         <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="R31" t="n">
         <v>1.29</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -6577,28 +6577,28 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="H32" t="n">
         <v>7.4</v>
       </c>
       <c r="I32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>5.3</v>
+        <v>4.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
         <v>3.1</v>
@@ -6613,28 +6613,28 @@
         <v>2.18</v>
       </c>
       <c r="R32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T32" t="n">
         <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V32" t="n">
         <v>1.09</v>
       </c>
       <c r="W32" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="X32" t="n">
         <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="Z32" t="n">
         <v>100</v>
@@ -6646,10 +6646,10 @@
         <v>7.4</v>
       </c>
       <c r="AC32" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>44</v>
+        <v>980</v>
       </c>
       <c r="AE32" t="n">
         <v>230</v>
@@ -6661,7 +6661,7 @@
         <v>12.5</v>
       </c>
       <c r="AH32" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AI32" t="n">
         <v>210</v>
@@ -6670,7 +6670,7 @@
         <v>16</v>
       </c>
       <c r="AK32" t="n">
-        <v>24</v>
+        <v>980</v>
       </c>
       <c r="AL32" t="n">
         <v>65</v>
@@ -6685,16 +6685,16 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="AQ32" t="n">
         <v>4</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AT32" t="n">
         <v>5.5</v>
@@ -6703,44 +6703,44 @@
         <v>3.35</v>
       </c>
       <c r="AV32" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ32" t="n">
         <v>4.2</v>
       </c>
-      <c r="AW32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BA32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BB32" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BC32" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BF32" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="G33" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="H33" t="n">
         <v>2.04</v>
@@ -6783,16 +6783,16 @@
         <v>2.22</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>2.78</v>
       </c>
       <c r="K33" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="N33" t="n">
         <v>2.72</v>
@@ -6810,76 +6810,76 @@
         <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T33" t="n">
         <v>2.08</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="V33" t="n">
         <v>1.83</v>
       </c>
       <c r="W33" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="X33" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y33" t="n">
         <v>8.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO33" t="n">
         <v>32</v>
       </c>
-      <c r="AB33" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP33" t="n">
-        <v>1.54</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.2</v>
@@ -6888,53 +6888,53 @@
         <v>10</v>
       </c>
       <c r="AS33" t="n">
-        <v>1.47</v>
+        <v>19.5</v>
       </c>
       <c r="AT33" t="n">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU33" t="n">
-        <v>1.54</v>
+        <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>1.54</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.54</v>
+        <v>20</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.54</v>
+        <v>3.9</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.54</v>
+        <v>13.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.46</v>
+        <v>3.75</v>
       </c>
       <c r="BA33" t="n">
-        <v>1.54</v>
+        <v>38</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.51</v>
+        <v>4.1</v>
       </c>
       <c r="BD33" t="n">
-        <v>1.54</v>
+        <v>4.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.53</v>
+        <v>4.2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.54</v>
+        <v>4.2</v>
       </c>
       <c r="BG33" t="n">
-        <v>1.54</v>
+        <v>18.5</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H34" t="n">
         <v>3.55</v>
@@ -6992,7 +6992,7 @@
         <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P34" t="n">
         <v>1.86</v>
@@ -7016,7 +7016,7 @@
         <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7073,62 +7073,62 @@
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT34" t="n">
         <v>4.5</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>4.1</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW34" t="n">
-        <v>5.6</v>
+        <v>32</v>
       </c>
       <c r="AX34" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AZ34" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BA34" t="n">
-        <v>5.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB34" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BD34" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="BF34" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="BG34" t="n">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="G35" t="n">
         <v>1.54</v>
@@ -7168,16 +7168,16 @@
         <v>6.6</v>
       </c>
       <c r="I35" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J35" t="n">
         <v>4.7</v>
       </c>
       <c r="K35" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
@@ -7189,7 +7189,7 @@
         <v>1.24</v>
       </c>
       <c r="P35" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q35" t="n">
         <v>1.71</v>
@@ -7198,19 +7198,19 @@
         <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="T35" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="U35" t="n">
         <v>2.02</v>
       </c>
       <c r="V35" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W35" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X35" t="n">
         <v>24</v>
@@ -7261,7 +7261,7 @@
         <v>130</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO35" t="n">
         <v>110</v>
@@ -7273,10 +7273,10 @@
         <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS35" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT35" t="n">
         <v>8.4</v>
@@ -7288,7 +7288,7 @@
         <v>21</v>
       </c>
       <c r="AW35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AX35" t="n">
         <v>8.6</v>
@@ -7300,7 +7300,7 @@
         <v>19</v>
       </c>
       <c r="BA35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB35" t="n">
         <v>11.5</v>
@@ -7309,20 +7309,20 @@
         <v>13.5</v>
       </c>
       <c r="BD35" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF35" t="n">
         <v>6</v>
       </c>
       <c r="BG35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -7359,7 +7359,7 @@
         <v>2.96</v>
       </c>
       <c r="H36" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="I36" t="n">
         <v>2.92</v>
@@ -7368,25 +7368,25 @@
         <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M36" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N36" t="n">
         <v>2.92</v>
       </c>
       <c r="O36" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P36" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="R36" t="n">
         <v>1.23</v>
@@ -7395,7 +7395,7 @@
         <v>4.4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U36" t="n">
         <v>1.91</v>
@@ -7410,7 +7410,7 @@
         <v>11</v>
       </c>
       <c r="Y36" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z36" t="n">
         <v>18</v>
@@ -7419,7 +7419,7 @@
         <v>50</v>
       </c>
       <c r="AB36" t="n">
-        <v>9.4</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
         <v>7.8</v>
@@ -7440,7 +7440,7 @@
         <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ36" t="n">
         <v>50</v>
@@ -7449,7 +7449,7 @@
         <v>40</v>
       </c>
       <c r="AL36" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM36" t="n">
         <v>160</v>
@@ -7464,16 +7464,16 @@
         <v>9</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AR36" t="n">
         <v>15</v>
       </c>
       <c r="AS36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AT36" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU36" t="n">
         <v>6.6</v>
@@ -7491,32 +7491,32 @@
         <v>11.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="BA36" t="n">
-        <v>10</v>
+        <v>7.2</v>
       </c>
       <c r="BB36" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="BC36" t="n">
         <v>30</v>
       </c>
       <c r="BD36" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="BE36" t="n">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="BF36" t="n">
-        <v>9.6</v>
+        <v>25</v>
       </c>
       <c r="BG36" t="n">
-        <v>9.800000000000001</v>
+        <v>6.8</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -7559,34 +7559,34 @@
         <v>3.7</v>
       </c>
       <c r="J37" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K37" t="n">
         <v>3.35</v>
       </c>
-      <c r="K37" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M37" t="n">
         <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O37" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="P37" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R37" t="n">
         <v>1.27</v>
       </c>
       <c r="S37" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T37" t="n">
         <v>1.99</v>
@@ -7598,7 +7598,7 @@
         <v>1.37</v>
       </c>
       <c r="W37" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="X37" t="n">
         <v>11</v>
@@ -7637,7 +7637,7 @@
         <v>65</v>
       </c>
       <c r="AJ37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK37" t="n">
         <v>28</v>
@@ -7658,7 +7658,7 @@
         <v>10</v>
       </c>
       <c r="AQ37" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR37" t="n">
         <v>22</v>
@@ -7667,7 +7667,7 @@
         <v>48</v>
       </c>
       <c r="AT37" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU37" t="n">
         <v>7</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
         <v>85</v>
       </c>
       <c r="AJ38" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK38" t="n">
         <v>23</v>
@@ -7870,10 +7870,10 @@
         <v>17.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="AX38" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY38" t="n">
         <v>9.800000000000001</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -7938,10 +7938,10 @@
         <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="I39" t="n">
         <v>4.3</v>
@@ -7968,7 +7968,7 @@
         <v>1.78</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R39" t="n">
         <v>1.3</v>
@@ -7986,7 +7986,7 @@
         <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="X39" t="n">
         <v>12</v>
@@ -8031,7 +8031,7 @@
         <v>25</v>
       </c>
       <c r="AL39" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AM39" t="n">
         <v>130</v>
@@ -8061,7 +8061,7 @@
         <v>6.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW39" t="n">
         <v>8.4</v>
@@ -8091,14 +8091,14 @@
         <v>9.4</v>
       </c>
       <c r="BF39" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="BG39" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
         <v>1.04</v>
       </c>
       <c r="G40" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="H40" t="n">
         <v>1.04</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -8323,7 +8323,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="G41" t="n">
         <v>1.95</v>
@@ -8338,10 +8338,10 @@
         <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M41" t="n">
         <v>1.09</v>
@@ -8383,7 +8383,7 @@
         <v>16</v>
       </c>
       <c r="Z41" t="n">
-        <v>42</v>
+        <v>980</v>
       </c>
       <c r="AA41" t="n">
         <v>190</v>
@@ -8419,7 +8419,7 @@
         <v>24</v>
       </c>
       <c r="AL41" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AM41" t="n">
         <v>210</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -8520,19 +8520,19 @@
         <v>3.35</v>
       </c>
       <c r="G42" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="H42" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="I42" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="J42" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K42" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="L42" t="n">
         <v>1.47</v>
@@ -8550,13 +8550,13 @@
         <v>1.56</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R42" t="n">
         <v>1.2</v>
       </c>
       <c r="S42" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="T42" t="n">
         <v>1.98</v>
@@ -8565,10 +8565,10 @@
         <v>1.8</v>
       </c>
       <c r="V42" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="W42" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="X42" t="n">
         <v>11</v>
@@ -8583,7 +8583,7 @@
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC42" t="n">
         <v>8.199999999999999</v>
@@ -8634,7 +8634,7 @@
         <v>10</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AT42" t="n">
         <v>9</v>
@@ -8646,41 +8646,41 @@
         <v>10</v>
       </c>
       <c r="AW42" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX42" t="n">
         <v>4.6</v>
       </c>
-      <c r="AX42" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AY42" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB42" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BC42" t="n">
         <v>5</v>
       </c>
-      <c r="BC42" t="n">
-        <v>4.9</v>
-      </c>
       <c r="BD42" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE42" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF42" t="n">
         <v>5.1</v>
       </c>
-      <c r="BF42" t="n">
-        <v>5</v>
-      </c>
       <c r="BG42" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -8711,28 +8711,28 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G43" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="H43" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I43" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="J43" t="n">
-        <v>2.94</v>
+        <v>2.76</v>
       </c>
       <c r="K43" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L43" t="n">
         <v>1.44</v>
       </c>
       <c r="M43" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N43" t="n">
         <v>2.92</v>
@@ -8759,46 +8759,46 @@
         <v>1.92</v>
       </c>
       <c r="V43" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="W43" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="X43" t="n">
-        <v>10</v>
+        <v>980</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.800000000000001</v>
+        <v>980</v>
       </c>
       <c r="Z43" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="AA43" t="n">
-        <v>36</v>
+        <v>980</v>
       </c>
       <c r="AB43" t="n">
-        <v>14</v>
+        <v>980</v>
       </c>
       <c r="AC43" t="n">
         <v>8</v>
       </c>
       <c r="AD43" t="n">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="AE43" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AF43" t="n">
-        <v>30</v>
+        <v>980</v>
       </c>
       <c r="AG43" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="AH43" t="n">
-        <v>22</v>
+        <v>980</v>
       </c>
       <c r="AI43" t="n">
-        <v>50</v>
+        <v>980</v>
       </c>
       <c r="AJ43" t="n">
         <v>90</v>
@@ -8816,7 +8816,7 @@
         <v>90</v>
       </c>
       <c r="AO43" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AP43" t="n">
         <v>4.2</v>
@@ -8828,7 +8828,7 @@
         <v>5</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.75</v>
+        <v>6</v>
       </c>
       <c r="AT43" t="n">
         <v>4.8</v>
@@ -8852,19 +8852,19 @@
         <v>5.4</v>
       </c>
       <c r="BA43" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BB43" t="n">
         <v>6.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="BE43" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BF43" t="n">
         <v>6.6</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -8977,7 +8977,7 @@
         <v>10.5</v>
       </c>
       <c r="AD44" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AE44" t="n">
         <v>1000</v>
@@ -8989,7 +8989,7 @@
         <v>10.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>48</v>
+        <v>980</v>
       </c>
       <c r="AI44" t="n">
         <v>150</v>
@@ -9001,7 +9001,7 @@
         <v>22</v>
       </c>
       <c r="AL44" t="n">
-        <v>160</v>
+        <v>980</v>
       </c>
       <c r="AM44" t="n">
         <v>200</v>
@@ -9031,7 +9031,7 @@
         <v>8.4</v>
       </c>
       <c r="AV44" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AW44" t="n">
         <v>40</v>
@@ -9055,7 +9055,7 @@
         <v>13</v>
       </c>
       <c r="BD44" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BE44" t="n">
         <v>46</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -9129,10 +9129,10 @@
         <v>1.28</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="R45" t="n">
         <v>1.38</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>3</v>
       </c>
       <c r="G47" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="H47" t="n">
         <v>2.52</v>
@@ -9502,7 +9502,7 @@
         <v>2.98</v>
       </c>
       <c r="K47" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,146 +9511,146 @@
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>1.46</v>
+        <v>2.74</v>
       </c>
       <c r="O47" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P47" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="R47" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S47" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="V47" t="n">
         <v>1.53</v>
       </c>
       <c r="W47" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ47" t="n">
         <v>1000</v>
       </c>
       <c r="AK47" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AL47" t="n">
         <v>1000</v>
       </c>
       <c r="AM47" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AN47" t="n">
         <v>1000</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AP47" t="n">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ47" t="n">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR47" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AT47" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU47" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV47" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY47" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ47" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BG47" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.21</v>
+        <v>1.64</v>
       </c>
       <c r="G48" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="H48" t="n">
-        <v>3.55</v>
+        <v>5.6</v>
       </c>
       <c r="I48" t="n">
-        <v>9.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>2.62</v>
+        <v>3.6</v>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,22 +9705,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>1.03</v>
+        <v>3.2</v>
       </c>
       <c r="O48" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P48" t="n">
-        <v>1.08</v>
+        <v>1.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R48" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="S48" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9732,7 +9732,7 @@
         <v>1.14</v>
       </c>
       <c r="W48" t="n">
-        <v>2.06</v>
+        <v>2.22</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9747,28 +9747,28 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD48" t="n">
         <v>1000</v>
       </c>
       <c r="AE48" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF48" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH48" t="n">
         <v>1000</v>
       </c>
       <c r="AI48" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ48" t="n">
         <v>1000</v>
@@ -9780,7 +9780,7 @@
         <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN48" t="n">
         <v>1000</v>
@@ -9789,62 +9789,62 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ48" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AR48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AV48" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AW48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX48" t="n">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AY48" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="AZ48" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BA48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB48" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BD48" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF48" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>3.25</v>
       </c>
       <c r="G49" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="H49" t="n">
         <v>2.44</v>
       </c>
       <c r="I49" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
@@ -9893,7 +9893,7 @@
         <v>3.35</v>
       </c>
       <c r="L49" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
         <v>1.11</v>
@@ -9908,7 +9908,7 @@
         <v>1.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.42</v>
+        <v>2.26</v>
       </c>
       <c r="R49" t="n">
         <v>1.22</v>
@@ -9986,7 +9986,7 @@
         <v>8.4</v>
       </c>
       <c r="AQ49" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR49" t="n">
         <v>3.65</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>2.76</v>
       </c>
       <c r="G50" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="H50" t="n">
         <v>2.9</v>
@@ -10084,7 +10084,7 @@
         <v>2.94</v>
       </c>
       <c r="K50" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L50" t="n">
         <v>1.49</v>
@@ -10093,7 +10093,7 @@
         <v>1.13</v>
       </c>
       <c r="N50" t="n">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="O50" t="n">
         <v>1.55</v>
@@ -10102,7 +10102,7 @@
         <v>1.52</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.64</v>
+        <v>2.46</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-08 11:19:17</t>
+          <t>2026-03-08 13:33:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I2" t="n">
         <v>5.7</v>
@@ -772,7 +772,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.33</v>
@@ -796,10 +796,10 @@
         <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
         <v>2.22</v>
@@ -808,7 +808,7 @@
         <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="X2" t="n">
         <v>24</v>
@@ -835,13 +835,13 @@
         <v>75</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG2" t="n">
         <v>10</v>
       </c>
       <c r="AH2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI2" t="n">
         <v>65</v>
@@ -853,10 +853,10 @@
         <v>16.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="AN2" t="n">
         <v>7.8</v>
@@ -865,16 +865,16 @@
         <v>70</v>
       </c>
       <c r="AP2" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AQ2" t="n">
         <v>20</v>
       </c>
       <c r="AR2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -886,7 +886,7 @@
         <v>18.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="AX2" t="n">
         <v>10</v>
@@ -907,20 +907,20 @@
         <v>14.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BE2" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>6.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -954,16 +954,16 @@
         <v>1.02</v>
       </c>
       <c r="G3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="n">
         <v>1.02</v>
       </c>
       <c r="I3" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="J3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K3" t="n">
         <v>950</v>
@@ -975,7 +975,7 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
         <v>1.01</v>
@@ -990,13 +990,13 @@
         <v>1.07</v>
       </c>
       <c r="S3" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U3" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V3" t="n">
         <v>1.01</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1157,7 @@
         <v>1000</v>
       </c>
       <c r="J4" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K4" t="n">
         <v>1000</v>
@@ -1169,13 +1169,13 @@
         <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O4" t="n">
         <v>1.01</v>
       </c>
       <c r="P4" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q4" t="n">
         <v>1.53</v>
@@ -1184,13 +1184,13 @@
         <v>1.08</v>
       </c>
       <c r="S4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="T4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V4" t="n">
         <v>1.01</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H5" t="n">
         <v>2.22</v>
       </c>
       <c r="I5" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
@@ -1363,13 +1363,13 @@
         <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="P5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="Q5" t="n">
         <v>2.28</v>
@@ -1381,7 +1381,7 @@
         <v>4.4</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="U5" t="n">
         <v>1.92</v>
@@ -1426,7 +1426,7 @@
         <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
         <v>1000</v>
@@ -1453,7 +1453,7 @@
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
         <v>22</v>
@@ -1465,44 +1465,44 @@
         <v>6.6</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AY5" t="n">
         <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>42</v>
+      </c>
+      <c r="BD5" t="n">
         <v>6.2</v>
       </c>
-      <c r="BC5" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>6</v>
-      </c>
       <c r="BE5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF5" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>13.5</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
         <v>23</v>
@@ -1542,13 +1542,13 @@
         <v>1.22</v>
       </c>
       <c r="I6" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="J6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K6" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.26</v>
@@ -1566,7 +1566,7 @@
         <v>2.26</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="R6" t="n">
         <v>1.5</v>
@@ -1578,13 +1578,13 @@
         <v>2.54</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
@@ -1650,16 +1650,16 @@
         <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AT6" t="n">
-        <v>32</v>
+        <v>5.1</v>
       </c>
       <c r="AU6" t="n">
         <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AW6" t="n">
         <v>4.2</v>
@@ -1671,32 +1671,32 @@
         <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>30</v>
+        <v>5.2</v>
       </c>
       <c r="BA6" t="n">
         <v>5.1</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
         <v>3.7</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -1727,43 +1727,43 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
         <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="P7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S7" t="n">
         <v>4.7</v>
@@ -1775,16 +1775,16 @@
         <v>1.65</v>
       </c>
       <c r="V7" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>980</v>
+        <v>6.8</v>
       </c>
       <c r="Z7" t="n">
         <v>980</v>
@@ -1793,7 +1793,7 @@
         <v>980</v>
       </c>
       <c r="AB7" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AC7" t="n">
         <v>980</v>
@@ -1805,7 +1805,7 @@
         <v>980</v>
       </c>
       <c r="AF7" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
         <v>980</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AP7" t="n">
-        <v>4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ7" t="n">
         <v>3.3</v>
       </c>
       <c r="AR7" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="AT7" t="n">
         <v>4.4</v>
       </c>
       <c r="AU7" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>4.9</v>
       </c>
       <c r="AX7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC7" t="n">
         <v>5.5</v>
       </c>
-      <c r="AY7" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>6</v>
-      </c>
       <c r="BD7" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="BG7" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -1924,16 +1924,16 @@
         <v>1.02</v>
       </c>
       <c r="G8" t="n">
-        <v>980</v>
+        <v>990</v>
       </c>
       <c r="H8" t="n">
         <v>1.01</v>
       </c>
       <c r="I8" t="n">
-        <v>950</v>
+        <v>990</v>
       </c>
       <c r="J8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
         <v>950</v>
@@ -1945,28 +1945,28 @@
         <v>1.01</v>
       </c>
       <c r="N8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P8" t="n">
         <v>1.08</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Q8" t="n">
         <v>1.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="S8" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="T8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V8" t="n">
         <v>1.01</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -2115,79 +2115,79 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="G9" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="H9" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="I9" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K9" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="V9" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="W9" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="X9" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
         <v>980</v>
       </c>
       <c r="Z9" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD9" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
@@ -2223,43 +2223,43 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ9" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AS9" t="n">
         <v>5.3</v>
       </c>
       <c r="AT9" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
         <v>3.85</v>
       </c>
       <c r="AV9" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AW9" t="n">
         <v>5.3</v>
       </c>
       <c r="AX9" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AY9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="AZ9" t="n">
         <v>4.8</v>
       </c>
       <c r="BA9" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="BC9" t="n">
         <v>4.3</v>
@@ -2268,17 +2268,17 @@
         <v>5</v>
       </c>
       <c r="BE9" t="n">
-        <v>3.25</v>
+        <v>5.3</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BG9" t="n">
         <v>5.3</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -2315,13 +2315,13 @@
         <v>1000</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K10" t="n">
         <v>980</v>
@@ -2351,10 +2351,10 @@
         <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U10" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V10" t="n">
         <v>1.01</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -2503,58 +2503,58 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="G11" t="n">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="H11" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="I11" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
         <v>1.49</v>
       </c>
       <c r="M11" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O11" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P11" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="R11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S11" t="n">
         <v>4.8</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="V11" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="W11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2575,7 +2575,7 @@
         <v>1000</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE11" t="n">
         <v>1000</v>
@@ -2614,59 +2614,59 @@
         <v>4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AR11" t="n">
         <v>4</v>
       </c>
       <c r="AS11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AV11" t="n">
         <v>4.3</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX11" t="n">
-        <v>5.6</v>
+        <v>3.45</v>
       </c>
       <c r="AY11" t="n">
         <v>5.3</v>
       </c>
       <c r="AZ11" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BA11" t="n">
         <v>3.5</v>
       </c>
       <c r="BB11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC11" t="n">
         <v>3.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.55</v>
       </c>
       <c r="BD11" t="n">
         <v>3.6</v>
       </c>
       <c r="BE11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG11" t="n">
         <v>3.2</v>
       </c>
-      <c r="BF11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
         <v>1.02</v>
       </c>
       <c r="I12" t="n">
-        <v>940</v>
+        <v>990</v>
       </c>
       <c r="J12" t="n">
         <v>1.02</v>
@@ -2721,13 +2721,13 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="O12" t="n">
         <v>1.01</v>
       </c>
       <c r="P12" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q12" t="n">
         <v>1.47</v>
@@ -2739,10 +2739,10 @@
         <v>1.47</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12" t="n">
         <v>1.01</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>1.34</v>
       </c>
       <c r="G13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="I13" t="n">
         <v>15.5</v>
@@ -2909,7 +2909,7 @@
         <v>5.4</v>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
@@ -2939,7 +2939,7 @@
         <v>1.6</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
         <v>3.7</v>
@@ -2954,28 +2954,28 @@
         <v>140</v>
       </c>
       <c r="AA13" t="n">
-        <v>990</v>
+        <v>970</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="n">
         <v>60</v>
       </c>
       <c r="AE13" t="n">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AG13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AI13" t="n">
         <v>350</v>
@@ -2984,7 +2984,7 @@
         <v>10</v>
       </c>
       <c r="AK13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL13" t="n">
         <v>65</v>
@@ -2996,7 +2996,7 @@
         <v>7.4</v>
       </c>
       <c r="AO13" t="n">
-        <v>880</v>
+        <v>830</v>
       </c>
       <c r="AP13" t="n">
         <v>12</v>
@@ -3005,22 +3005,22 @@
         <v>28</v>
       </c>
       <c r="AR13" t="n">
-        <v>6.2</v>
+        <v>7.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AT13" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU13" t="n">
         <v>11</v>
       </c>
       <c r="AV13" t="n">
-        <v>5.8</v>
+        <v>46</v>
       </c>
       <c r="AW13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
@@ -3032,7 +3032,7 @@
         <v>34</v>
       </c>
       <c r="BA13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BB13" t="n">
         <v>8.800000000000001</v>
@@ -3041,20 +3041,20 @@
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>5.9</v>
+        <v>50</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.4</v>
+        <v>8</v>
       </c>
       <c r="BF13" t="n">
         <v>6.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -3091,16 +3091,16 @@
         <v>2.7</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="I14" t="n">
         <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.53</v>
@@ -3109,13 +3109,13 @@
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O14" t="n">
         <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
         <v>2.4</v>
@@ -3127,7 +3127,7 @@
         <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
         <v>1.89</v>
@@ -3154,7 +3154,7 @@
         <v>980</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.4</v>
+        <v>980</v>
       </c>
       <c r="AD14" t="n">
         <v>980</v>
@@ -3193,31 +3193,31 @@
         <v>65</v>
       </c>
       <c r="AP14" t="n">
-        <v>8.4</v>
+        <v>5.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AR14" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AS14" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AX14" t="n">
-        <v>6.2</v>
+        <v>13</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -3226,29 +3226,29 @@
         <v>15.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>7.2</v>
+        <v>25</v>
       </c>
       <c r="BD14" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BE14" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BG14" t="n">
-        <v>8</v>
+        <v>2.3</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -3282,55 +3282,55 @@
         <v>2.1</v>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="H15" t="n">
         <v>3</v>
       </c>
       <c r="I15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="J15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="K15" t="n">
         <v>5.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="O15" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="P15" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R15" t="n">
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.28</v>
+        <v>2.74</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W15" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="X15" t="n">
         <v>1000</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -3482,13 +3482,13 @@
         <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J16" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
         <v>1.29</v>
@@ -3524,37 +3524,37 @@
         <v>1.7</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AA16" t="n">
         <v>38</v>
       </c>
       <c r="AB16" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE16" t="n">
         <v>28</v>
       </c>
       <c r="AF16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>19.5</v>
@@ -3563,19 +3563,19 @@
         <v>40</v>
       </c>
       <c r="AJ16" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
         <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM16" t="n">
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO16" t="n">
         <v>18.5</v>
@@ -3590,7 +3590,7 @@
         <v>12</v>
       </c>
       <c r="AS16" t="n">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="AT16" t="n">
         <v>11</v>
@@ -3614,19 +3614,19 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="BB16" t="n">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="BC16" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.85</v>
+        <v>5.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="BF16" t="n">
         <v>19.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
         <v>2.28</v>
@@ -3694,7 +3694,7 @@
         <v>3.95</v>
       </c>
       <c r="O17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P17" t="n">
         <v>2.02</v>
@@ -3724,7 +3724,7 @@
         <v>19.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z17" t="n">
         <v>34</v>
@@ -3736,7 +3736,7 @@
         <v>13</v>
       </c>
       <c r="AC17" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD17" t="n">
         <v>18.5</v>
@@ -3745,13 +3745,13 @@
         <v>55</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI17" t="n">
         <v>60</v>
@@ -3781,10 +3781,10 @@
         <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AS17" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AT17" t="n">
         <v>9.199999999999999</v>
@@ -3796,7 +3796,7 @@
         <v>13</v>
       </c>
       <c r="AW17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AX17" t="n">
         <v>12.5</v>
@@ -3808,29 +3808,29 @@
         <v>14.5</v>
       </c>
       <c r="BA17" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC17" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>3.95</v>
-      </c>
       <c r="BD17" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="BE17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="BF17" t="n">
         <v>11</v>
       </c>
       <c r="BG17" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -3861,25 +3861,25 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.34</v>
+        <v>2.24</v>
       </c>
       <c r="G18" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="H18" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K18" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M18" t="n">
         <v>1.05</v>
@@ -3894,7 +3894,7 @@
         <v>2.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R18" t="n">
         <v>1.41</v>
@@ -3903,16 +3903,16 @@
         <v>3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="U18" t="n">
         <v>2.24</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="W18" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="X18" t="n">
         <v>21</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>1.93</v>
       </c>
       <c r="G20" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H20" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="I20" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J20" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L20" t="n">
         <v>1.44</v>
@@ -4300,119 +4300,119 @@
         <v>1.25</v>
       </c>
       <c r="W20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X20" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y20" t="n">
         <v>18</v>
       </c>
       <c r="Z20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AA20" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC20" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF20" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
         <v>21</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM20" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN20" t="n">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AT20" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU20" t="n">
         <v>7.4</v>
       </c>
-      <c r="AU20" t="n">
-        <v>7.2</v>
-      </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AX20" t="n">
         <v>10</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>6.8</v>
+        <v>10.5</v>
       </c>
       <c r="BB20" t="n">
         <v>19</v>
       </c>
       <c r="BC20" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BF20" t="n">
         <v>13</v>
       </c>
       <c r="BG20" t="n">
-        <v>6.8</v>
+        <v>9.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -4455,7 +4455,7 @@
         <v>2.14</v>
       </c>
       <c r="J21" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K21" t="n">
         <v>3.8</v>
@@ -4470,7 +4470,7 @@
         <v>4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P21" t="n">
         <v>2.04</v>
@@ -4482,10 +4482,10 @@
         <v>1.41</v>
       </c>
       <c r="S21" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T21" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="U21" t="n">
         <v>2.2</v>
@@ -4494,7 +4494,7 @@
         <v>1.87</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X21" t="n">
         <v>20</v>
@@ -4548,7 +4548,7 @@
         <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AP21" t="n">
         <v>14.5</v>
@@ -4584,29 +4584,29 @@
         <v>14.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC21" t="n">
+        <v>36</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF21" t="n">
         <v>7</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>7</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>6.8</v>
       </c>
       <c r="BG21" t="n">
         <v>10</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -4637,25 +4637,25 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G22" t="n">
         <v>2.24</v>
       </c>
       <c r="H22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I22" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
       </c>
       <c r="K22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="M22" t="n">
         <v>1.08</v>
@@ -4667,13 +4667,13 @@
         <v>1.37</v>
       </c>
       <c r="P22" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="R22" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
         <v>3.4</v>
@@ -4682,10 +4682,10 @@
         <v>1.86</v>
       </c>
       <c r="U22" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
         <v>1.8</v>
@@ -4718,7 +4718,7 @@
         <v>1000</v>
       </c>
       <c r="AG22" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH22" t="n">
         <v>1000</v>
@@ -4727,7 +4727,7 @@
         <v>1000</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>1000</v>
       </c>
       <c r="AP22" t="n">
-        <v>3.25</v>
+        <v>4.1</v>
       </c>
       <c r="AQ22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
-        <v>3.75</v>
+        <v>4.8</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AT22" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
       <c r="AV22" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="AW22" t="n">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="AX22" t="n">
         <v>9.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="AZ22" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="BA22" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
         <v>19.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="BF22" t="n">
         <v>14.5</v>
       </c>
       <c r="BG22" t="n">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="G23" t="n">
         <v>3.6</v>
       </c>
       <c r="H23" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I23" t="n">
         <v>2.76</v>
       </c>
       <c r="J23" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="K23" t="n">
         <v>3.65</v>
       </c>
       <c r="L23" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M23" t="n">
         <v>1.09</v>
@@ -4864,19 +4864,19 @@
         <v>1.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S23" t="n">
-        <v>3.95</v>
+        <v>3.55</v>
       </c>
       <c r="T23" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="V23" t="n">
         <v>1.57</v>
@@ -4939,28 +4939,28 @@
         <v>36</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AQ23" t="n">
-        <v>3.15</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>3.55</v>
+        <v>11.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="AV23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AW23" t="n">
-        <v>3.9</v>
+        <v>22</v>
       </c>
       <c r="AX23" t="n">
         <v>15.5</v>
@@ -4969,32 +4969,32 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BA23" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB23" t="n">
         <v>4</v>
       </c>
-      <c r="BB23" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BC23" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BD23" t="n">
         <v>4</v>
       </c>
       <c r="BE23" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BF23" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="BG23" t="n">
         <v>20</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
         <v>2.02</v>
       </c>
       <c r="G24" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H24" t="n">
         <v>4.2</v>
@@ -5040,7 +5040,7 @@
         <v>3.3</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
         <v>1.47</v>
@@ -5049,16 +5049,16 @@
         <v>1.09</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>1.41</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="R24" t="n">
         <v>1.25</v>
@@ -5076,7 +5076,7 @@
         <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X24" t="n">
         <v>13.5</v>
@@ -5091,10 +5091,10 @@
         <v>130</v>
       </c>
       <c r="AB24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD24" t="n">
         <v>22</v>
@@ -5139,10 +5139,10 @@
         <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="AT24" t="n">
         <v>6.8</v>
@@ -5151,44 +5151,44 @@
         <v>6.6</v>
       </c>
       <c r="AV24" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AX24" t="n">
         <v>10</v>
       </c>
       <c r="AY24" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="AZ24" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BB24" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BC24" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF24" t="n">
         <v>14.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -5219,31 +5219,31 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="H25" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="I25" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="K25" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L25" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O25" t="n">
         <v>1.4</v>
@@ -5252,7 +5252,7 @@
         <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
         <v>1.26</v>
@@ -5264,10 +5264,10 @@
         <v>1.86</v>
       </c>
       <c r="U25" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V25" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="W25" t="n">
         <v>1.59</v>
@@ -5285,7 +5285,7 @@
         <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC25" t="n">
         <v>8.800000000000001</v>
@@ -5297,22 +5297,22 @@
         <v>980</v>
       </c>
       <c r="AF25" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AG25" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AI25" t="n">
         <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AK25" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AL25" t="n">
         <v>55</v>
@@ -5321,7 +5321,7 @@
         <v>150</v>
       </c>
       <c r="AN25" t="n">
-        <v>38</v>
+        <v>980</v>
       </c>
       <c r="AO25" t="n">
         <v>50</v>
@@ -5333,10 +5333,10 @@
         <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>4.3</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="AT25" t="n">
         <v>8</v>
@@ -5345,44 +5345,44 @@
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AW25" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AX25" t="n">
-        <v>4.3</v>
+        <v>13.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>3.8</v>
+        <v>10</v>
       </c>
       <c r="AZ25" t="n">
         <v>17</v>
       </c>
       <c r="BA25" t="n">
-        <v>42</v>
+        <v>5.8</v>
       </c>
       <c r="BB25" t="n">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="BC25" t="n">
-        <v>4.8</v>
+        <v>25</v>
       </c>
       <c r="BD25" t="n">
-        <v>38</v>
+        <v>5.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BF25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BG25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -5461,7 +5461,7 @@
         <v>2.72</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W26" t="n">
         <v>1.75</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -5652,7 +5652,7 @@
         <v>2.38</v>
       </c>
       <c r="U27" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="V27" t="n">
         <v>2.58</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -5819,13 +5819,13 @@
         <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M28" t="n">
         <v>1.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O28" t="n">
         <v>1.46</v>
@@ -5843,10 +5843,10 @@
         <v>4</v>
       </c>
       <c r="T28" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="U28" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="V28" t="n">
         <v>1.83</v>
@@ -5885,7 +5885,7 @@
         <v>980</v>
       </c>
       <c r="AH28" t="n">
-        <v>27</v>
+        <v>980</v>
       </c>
       <c r="AI28" t="n">
         <v>55</v>
@@ -5909,7 +5909,7 @@
         <v>980</v>
       </c>
       <c r="AP28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
@@ -5918,53 +5918,53 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AW28" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AY28" t="n">
         <v>15</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC28" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BD28" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF28" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BG28" t="n">
         <v>17</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -6022,22 +6022,22 @@
         <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
         <v>1.54</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R29" t="n">
         <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U29" t="n">
         <v>1.71</v>
@@ -6049,10 +6049,10 @@
         <v>1.9</v>
       </c>
       <c r="X29" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z29" t="n">
         <v>980</v>
@@ -6073,10 +6073,10 @@
         <v>110</v>
       </c>
       <c r="AF29" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG29" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH29" t="n">
         <v>27</v>
@@ -6085,7 +6085,7 @@
         <v>130</v>
       </c>
       <c r="AJ29" t="n">
-        <v>29</v>
+        <v>980</v>
       </c>
       <c r="AK29" t="n">
         <v>32</v>
@@ -6103,19 +6103,19 @@
         <v>170</v>
       </c>
       <c r="AP29" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ29" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>5.5</v>
+        <v>24</v>
       </c>
       <c r="AS29" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
         <v>6.6</v>
@@ -6124,41 +6124,41 @@
         <v>18</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AX29" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AY29" t="n">
-        <v>4.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>18</v>
+        <v>5.9</v>
       </c>
       <c r="BA29" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB29" t="n">
         <v>21</v>
       </c>
       <c r="BC29" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD29" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BG29" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -6189,25 +6189,25 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.76</v>
+        <v>1.87</v>
       </c>
       <c r="G30" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="H30" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="J30" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K30" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
         <v>1.09</v>
@@ -6228,7 +6228,7 @@
         <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="T30" t="n">
         <v>2.08</v>
@@ -6237,10 +6237,10 @@
         <v>1.76</v>
       </c>
       <c r="V30" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="X30" t="n">
         <v>11.5</v>
@@ -6258,7 +6258,7 @@
         <v>7.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>2.44</v>
+        <v>3.6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>2.58</v>
+        <v>3.95</v>
       </c>
       <c r="AR30" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.2</v>
+        <v>5.4</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.05</v>
+        <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.74</v>
+        <v>4.3</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AX30" t="n">
-        <v>2.48</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY30" t="n">
-        <v>2.48</v>
+        <v>8.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2.78</v>
+        <v>4.4</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.05</v>
+        <v>5</v>
       </c>
       <c r="BB30" t="n">
-        <v>2.78</v>
+        <v>17.5</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.8</v>
+        <v>19</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.05</v>
+        <v>4.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>3.05</v>
+        <v>5.1</v>
       </c>
       <c r="BF30" t="n">
         <v>15.5</v>
       </c>
       <c r="BG30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="G31" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="H31" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="I31" t="n">
         <v>8.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="K31" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
         <v>1.38</v>
@@ -6407,13 +6407,13 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
         <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="Q31" t="n">
         <v>1.96</v>
@@ -6425,7 +6425,7 @@
         <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U31" t="n">
         <v>1.79</v>
@@ -6434,10 +6434,10 @@
         <v>1.13</v>
       </c>
       <c r="W31" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="X31" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y31" t="n">
         <v>1000</v>
@@ -6491,7 +6491,7 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>9.800000000000001</v>
+        <v>3.8</v>
       </c>
       <c r="AQ31" t="n">
         <v>15</v>
@@ -6515,13 +6515,13 @@
         <v>5</v>
       </c>
       <c r="AX31" t="n">
-        <v>3.45</v>
+        <v>6.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>7.8</v>
+        <v>3.6</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.3</v>
+        <v>18.5</v>
       </c>
       <c r="BA31" t="n">
         <v>4.9</v>
@@ -6530,7 +6530,7 @@
         <v>12</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD31" t="n">
         <v>4.7</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -6577,25 +6577,25 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="G32" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H32" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I32" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J32" t="n">
         <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L32" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M32" t="n">
         <v>1.09</v>
@@ -6616,43 +6616,43 @@
         <v>1.26</v>
       </c>
       <c r="S32" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="T32" t="n">
         <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W32" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="X32" t="n">
         <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="Z32" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
       </c>
       <c r="AB32" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="AC32" t="n">
         <v>11.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AE32" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AF32" t="n">
         <v>9</v>
@@ -6664,13 +6664,13 @@
         <v>980</v>
       </c>
       <c r="AI32" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ32" t="n">
         <v>16</v>
       </c>
       <c r="AK32" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AL32" t="n">
         <v>65</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AQ32" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="AT32" t="n">
         <v>5.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AW32" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AX32" t="n">
-        <v>3.1</v>
+        <v>6.6</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="AZ32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BB32" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BC32" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BE32" t="n">
-        <v>4.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.7</v>
+        <v>5.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -6762,103 +6762,103 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="G33" t="n">
-        <v>5.6</v>
+        <v>2.38</v>
       </c>
       <c r="H33" t="n">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="I33" t="n">
-        <v>2.22</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N33" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="P33" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.46</v>
+        <v>1.93</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S33" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="U33" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="V33" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.72</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="Y33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC33" t="n">
         <v>8.6</v>
       </c>
-      <c r="Z33" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>34</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>9</v>
-      </c>
       <c r="AD33" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AE33" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AG33" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AH33" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AI33" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
         <v>1000</v>
@@ -6876,65 +6876,65 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.199999999999999</v>
+        <v>5.1</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="AS33" t="n">
-        <v>19.5</v>
+        <v>7</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="AU33" t="n">
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="AY33" t="n">
-        <v>13.5</v>
+        <v>4.7</v>
       </c>
       <c r="AZ33" t="n">
-        <v>3.75</v>
+        <v>5.4</v>
       </c>
       <c r="BA33" t="n">
         <v>38</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="BF33" t="n">
-        <v>4.2</v>
+        <v>12.5</v>
       </c>
       <c r="BG33" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -6956,103 +6956,103 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="G34" t="n">
-        <v>2.38</v>
+        <v>5.1</v>
       </c>
       <c r="H34" t="n">
-        <v>3.55</v>
+        <v>2.02</v>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>2.26</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="T34" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="W34" t="n">
-        <v>1.75</v>
+        <v>1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ34" t="n">
         <v>1000</v>
@@ -7070,65 +7070,65 @@
         <v>1000</v>
       </c>
       <c r="AO34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS34" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="AX34" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.7</v>
+        <v>13.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.4</v>
+        <v>16.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>6.8</v>
+        <v>4.1</v>
       </c>
       <c r="BB34" t="n">
-        <v>6.2</v>
+        <v>4.2</v>
       </c>
       <c r="BC34" t="n">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="BD34" t="n">
-        <v>6.4</v>
+        <v>4.2</v>
       </c>
       <c r="BE34" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="BF34" t="n">
-        <v>12.5</v>
+        <v>4.2</v>
       </c>
       <c r="BG34" t="n">
-        <v>6.6</v>
+        <v>18</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -7162,16 +7162,16 @@
         <v>1.51</v>
       </c>
       <c r="G35" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="H35" t="n">
         <v>6.6</v>
       </c>
       <c r="I35" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="J35" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="K35" t="n">
         <v>5.1</v>
@@ -7192,13 +7192,13 @@
         <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R35" t="n">
         <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T35" t="n">
         <v>1.86</v>
@@ -7207,10 +7207,10 @@
         <v>2.02</v>
       </c>
       <c r="V35" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W35" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="X35" t="n">
         <v>24</v>
@@ -7270,7 +7270,7 @@
         <v>17</v>
       </c>
       <c r="AQ35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR35" t="n">
         <v>6.6</v>
@@ -7285,7 +7285,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW35" t="n">
         <v>7</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -7353,13 +7353,13 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G36" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H36" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="I36" t="n">
         <v>2.92</v>
@@ -7371,25 +7371,25 @@
         <v>3.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="M36" t="n">
         <v>1.1</v>
       </c>
       <c r="N36" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O36" t="n">
         <v>1.43</v>
       </c>
       <c r="P36" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q36" t="n">
         <v>2.24</v>
       </c>
       <c r="R36" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S36" t="n">
         <v>4.4</v>
@@ -7398,19 +7398,19 @@
         <v>1.94</v>
       </c>
       <c r="U36" t="n">
-        <v>1.91</v>
+        <v>1.94</v>
       </c>
       <c r="V36" t="n">
         <v>1.52</v>
       </c>
       <c r="W36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="X36" t="n">
         <v>11</v>
       </c>
       <c r="Y36" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z36" t="n">
         <v>18</v>
@@ -7419,7 +7419,7 @@
         <v>50</v>
       </c>
       <c r="AB36" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AC36" t="n">
         <v>7.8</v>
@@ -7428,7 +7428,7 @@
         <v>13</v>
       </c>
       <c r="AE36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF36" t="n">
         <v>18</v>
@@ -7437,43 +7437,43 @@
         <v>13.5</v>
       </c>
       <c r="AH36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI36" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ36" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AK36" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL36" t="n">
         <v>60</v>
       </c>
       <c r="AM36" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AN36" t="n">
         <v>42</v>
       </c>
       <c r="AO36" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP36" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ36" t="n">
         <v>8.4</v>
       </c>
       <c r="AR36" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AS36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AT36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AU36" t="n">
         <v>6.6</v>
@@ -7491,13 +7491,13 @@
         <v>11.5</v>
       </c>
       <c r="AZ36" t="n">
-        <v>6</v>
+        <v>18.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>7.2</v>
+        <v>9</v>
       </c>
       <c r="BB36" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="BC36" t="n">
         <v>30</v>
@@ -7506,17 +7506,17 @@
         <v>42</v>
       </c>
       <c r="BE36" t="n">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="BF36" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="BG36" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="G37" t="n">
         <v>2.3</v>
       </c>
-      <c r="G37" t="n">
-        <v>2.34</v>
-      </c>
       <c r="H37" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I37" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K37" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L37" t="n">
         <v>1.51</v>
@@ -7571,10 +7571,10 @@
         <v>1.1</v>
       </c>
       <c r="N37" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P37" t="n">
         <v>1.71</v>
@@ -7589,16 +7589,16 @@
         <v>4.6</v>
       </c>
       <c r="T37" t="n">
-        <v>1.99</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="V37" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W37" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="X37" t="n">
         <v>11</v>
@@ -7637,7 +7637,7 @@
         <v>65</v>
       </c>
       <c r="AJ37" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK37" t="n">
         <v>28</v>
@@ -7649,7 +7649,7 @@
         <v>130</v>
       </c>
       <c r="AN37" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO37" t="n">
         <v>60</v>
@@ -7685,16 +7685,16 @@
         <v>10.5</v>
       </c>
       <c r="AZ37" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="BB37" t="n">
         <v>27</v>
       </c>
       <c r="BC37" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD37" t="n">
         <v>42</v>
@@ -7703,14 +7703,14 @@
         <v>42</v>
       </c>
       <c r="BF37" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG37" t="n">
         <v>30</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="G38" t="n">
         <v>1.96</v>
-      </c>
-      <c r="G38" t="n">
-        <v>1.97</v>
       </c>
       <c r="H38" t="n">
         <v>4.8</v>
@@ -7774,7 +7774,7 @@
         <v>1.74</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R38" t="n">
         <v>1.27</v>
@@ -7789,7 +7789,7 @@
         <v>1.9</v>
       </c>
       <c r="V38" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W38" t="n">
         <v>2.04</v>
@@ -7870,7 +7870,7 @@
         <v>17.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX38" t="n">
         <v>10</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>2.1</v>
       </c>
       <c r="G39" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H39" t="n">
         <v>4.1</v>
@@ -7947,7 +7947,7 @@
         <v>4.3</v>
       </c>
       <c r="J39" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K39" t="n">
         <v>3.5</v>
@@ -7974,7 +7974,7 @@
         <v>1.3</v>
       </c>
       <c r="S39" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="T39" t="n">
         <v>1.86</v>
@@ -7986,7 +7986,7 @@
         <v>1.3</v>
       </c>
       <c r="W39" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X39" t="n">
         <v>12</v>
@@ -8070,7 +8070,7 @@
         <v>11.5</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AZ39" t="n">
         <v>16.5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -8129,170 +8129,170 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.04</v>
+        <v>2.04</v>
       </c>
       <c r="G40" t="n">
-        <v>980</v>
+        <v>2.56</v>
       </c>
       <c r="H40" t="n">
-        <v>1.04</v>
+        <v>3.15</v>
       </c>
       <c r="I40" t="n">
-        <v>500</v>
+        <v>4.8</v>
       </c>
       <c r="J40" t="n">
-        <v>1.02</v>
+        <v>2.88</v>
       </c>
       <c r="K40" t="n">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L40" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M40" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N40" t="n">
-        <v>1.25</v>
+        <v>2.68</v>
       </c>
       <c r="O40" t="n">
         <v>1.35</v>
       </c>
       <c r="P40" t="n">
-        <v>1.24</v>
+        <v>1.64</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.35</v>
+        <v>1.9</v>
       </c>
       <c r="R40" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S40" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="T40" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="U40" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V40" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="W40" t="n">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="X40" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y40" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z40" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA40" t="n">
         <v>1000</v>
       </c>
       <c r="AB40" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AC40" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD40" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF40" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AG40" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH40" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI40" t="n">
         <v>1000</v>
       </c>
       <c r="AJ40" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK40" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL40" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM40" t="n">
         <v>1000</v>
       </c>
       <c r="AN40" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AO40" t="n">
         <v>1000</v>
       </c>
       <c r="AP40" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AR40" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS40" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT40" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="AU40" t="n">
-        <v>1.01</v>
+        <v>2.94</v>
       </c>
       <c r="AV40" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX40" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AY40" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="AZ40" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BA40" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB40" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BC40" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BD40" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BE40" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF40" t="n">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BG40" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>1.83</v>
       </c>
       <c r="G41" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="H41" t="n">
         <v>4.9</v>
@@ -8338,10 +8338,10 @@
         <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L41" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
         <v>1.09</v>
@@ -8377,7 +8377,7 @@
         <v>2.06</v>
       </c>
       <c r="X41" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y41" t="n">
         <v>16</v>
@@ -8401,7 +8401,7 @@
         <v>110</v>
       </c>
       <c r="AF41" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AG41" t="n">
         <v>11</v>
@@ -8437,10 +8437,10 @@
         <v>12.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>6.2</v>
+        <v>30</v>
       </c>
       <c r="AS41" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT41" t="n">
         <v>6.2</v>
@@ -8452,7 +8452,7 @@
         <v>18</v>
       </c>
       <c r="AW41" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AX41" t="n">
         <v>8.800000000000001</v>
@@ -8464,29 +8464,29 @@
         <v>19.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BB41" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BC41" t="n">
         <v>19.5</v>
       </c>
       <c r="BD41" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE41" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF41" t="n">
         <v>12.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
         <v>2.34</v>
       </c>
       <c r="I42" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="J42" t="n">
         <v>2.96</v>
@@ -8565,28 +8565,28 @@
         <v>1.8</v>
       </c>
       <c r="V42" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="W42" t="n">
         <v>1.34</v>
       </c>
       <c r="X42" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y42" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="Z42" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA42" t="n">
         <v>1000</v>
       </c>
       <c r="AB42" t="n">
-        <v>12</v>
+        <v>980</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD42" t="n">
         <v>14</v>
@@ -8598,7 +8598,7 @@
         <v>1000</v>
       </c>
       <c r="AG42" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AH42" t="n">
         <v>1000</v>
@@ -8634,7 +8634,7 @@
         <v>10</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="AT42" t="n">
         <v>9</v>
@@ -8646,41 +8646,41 @@
         <v>10</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BA42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB42" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BC42" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD42" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BF42" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -8714,7 +8714,7 @@
         <v>3.9</v>
       </c>
       <c r="G43" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="H43" t="n">
         <v>2.2</v>
@@ -8723,7 +8723,7 @@
         <v>2.34</v>
       </c>
       <c r="J43" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="K43" t="n">
         <v>3.25</v>
@@ -8768,7 +8768,7 @@
         <v>980</v>
       </c>
       <c r="Y43" t="n">
-        <v>980</v>
+        <v>8.6</v>
       </c>
       <c r="Z43" t="n">
         <v>980</v>
@@ -8780,7 +8780,7 @@
         <v>980</v>
       </c>
       <c r="AC43" t="n">
-        <v>8</v>
+        <v>980</v>
       </c>
       <c r="AD43" t="n">
         <v>980</v>
@@ -8819,62 +8819,62 @@
         <v>980</v>
       </c>
       <c r="AP43" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AQ43" t="n">
         <v>4.2</v>
       </c>
-      <c r="AQ43" t="n">
-        <v>3.95</v>
-      </c>
       <c r="AR43" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV43" t="n">
         <v>5</v>
       </c>
-      <c r="AS43" t="n">
+      <c r="AW43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AY43" t="n">
         <v>6</v>
       </c>
-      <c r="AT43" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU43" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV43" t="n">
+      <c r="AZ43" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB43" t="n">
         <v>4.5</v>
       </c>
-      <c r="AW43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AX43" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY43" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ43" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BA43" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BB43" t="n">
+      <c r="BC43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BG43" t="n">
         <v>6.6</v>
       </c>
-      <c r="BC43" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BD43" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="BE43" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BF43" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BG43" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -8950,7 +8950,7 @@
         <v>2.12</v>
       </c>
       <c r="U44" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V44" t="n">
         <v>1.13</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G45" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="H45" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J45" t="n">
         <v>4.4</v>
       </c>
       <c r="K45" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L45" t="n">
         <v>1.32</v>
@@ -9123,16 +9123,16 @@
         <v>1.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="O45" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P45" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="R45" t="n">
         <v>1.38</v>
@@ -9147,13 +9147,13 @@
         <v>1.8</v>
       </c>
       <c r="V45" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W45" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="X45" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y45" t="n">
         <v>1000</v>
@@ -9165,7 +9165,7 @@
         <v>1000</v>
       </c>
       <c r="AB45" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC45" t="n">
         <v>12.5</v>
@@ -9177,7 +9177,7 @@
         <v>190</v>
       </c>
       <c r="AF45" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AG45" t="n">
         <v>12</v>
@@ -9189,10 +9189,10 @@
         <v>160</v>
       </c>
       <c r="AJ45" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK45" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AL45" t="n">
         <v>1000</v>
@@ -9210,13 +9210,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AR45" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AS45" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AT45" t="n">
         <v>6.6</v>
@@ -9225,10 +9225,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV45" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW45" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX45" t="n">
         <v>7</v>
@@ -9237,10 +9237,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ45" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA45" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BB45" t="n">
         <v>10.5</v>
@@ -9249,20 +9249,20 @@
         <v>13.5</v>
       </c>
       <c r="BD45" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE45" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF45" t="n">
         <v>5.9</v>
       </c>
       <c r="BG45" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -9293,58 +9293,58 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="G46" t="n">
-        <v>500</v>
+        <v>1.75</v>
       </c>
       <c r="H46" t="n">
-        <v>1.04</v>
+        <v>5</v>
       </c>
       <c r="I46" t="n">
-        <v>500</v>
+        <v>6.8</v>
       </c>
       <c r="J46" t="n">
-        <v>1.02</v>
+        <v>3.55</v>
       </c>
       <c r="K46" t="n">
-        <v>950</v>
+        <v>4.9</v>
       </c>
       <c r="L46" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M46" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>1.25</v>
+        <v>3.15</v>
       </c>
       <c r="O46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R46" t="n">
         <v>1.31</v>
       </c>
-      <c r="P46" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="R46" t="n">
-        <v>1.18</v>
-      </c>
       <c r="S46" t="n">
-        <v>1.31</v>
+        <v>2.98</v>
       </c>
       <c r="T46" t="n">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V46" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W46" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9401,62 +9401,62 @@
         <v>1000</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="AT46" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AU46" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BA46" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC46" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BD46" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG46" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -9496,13 +9496,13 @@
         <v>2.52</v>
       </c>
       <c r="I47" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="J47" t="n">
         <v>2.98</v>
       </c>
       <c r="K47" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9520,22 +9520,22 @@
         <v>1.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="R47" t="n">
         <v>1.21</v>
       </c>
       <c r="S47" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T47" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U47" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V47" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W47" t="n">
         <v>1.4</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -9681,28 +9681,28 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="G48" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="H48" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="I48" t="n">
         <v>8</v>
       </c>
       <c r="J48" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="K48" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L48" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M48" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N48" t="n">
         <v>3.2</v>
@@ -9711,28 +9711,28 @@
         <v>1.36</v>
       </c>
       <c r="P48" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R48" t="n">
         <v>1.28</v>
       </c>
       <c r="S48" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="T48" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U48" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="V48" t="n">
         <v>1.14</v>
       </c>
       <c r="W48" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9780,7 +9780,7 @@
         <v>1000</v>
       </c>
       <c r="AM48" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN48" t="n">
         <v>1000</v>
@@ -9828,7 +9828,7 @@
         <v>3.6</v>
       </c>
       <c r="BC48" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BD48" t="n">
         <v>4</v>
@@ -9837,14 +9837,14 @@
         <v>4.2</v>
       </c>
       <c r="BF48" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG48" t="n">
         <v>4.2</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -9878,19 +9878,19 @@
         <v>3.25</v>
       </c>
       <c r="G49" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="H49" t="n">
         <v>2.44</v>
       </c>
       <c r="I49" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J49" t="n">
         <v>3</v>
       </c>
       <c r="K49" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L49" t="n">
         <v>1.44</v>
@@ -9908,13 +9908,13 @@
         <v>1.6</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R49" t="n">
         <v>1.22</v>
       </c>
       <c r="S49" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T49" t="n">
         <v>2</v>
@@ -9923,10 +9923,10 @@
         <v>1.86</v>
       </c>
       <c r="V49" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W49" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X49" t="n">
         <v>11.5</v>
@@ -9944,7 +9944,7 @@
         <v>12.5</v>
       </c>
       <c r="AC49" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD49" t="n">
         <v>14.5</v>
@@ -9989,25 +9989,25 @@
         <v>7.2</v>
       </c>
       <c r="AR49" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AS49" t="n">
         <v>4.2</v>
       </c>
       <c r="AT49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="AU49" t="n">
         <v>3</v>
       </c>
       <c r="AV49" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX49" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY49" t="n">
         <v>13</v>
@@ -10016,19 +10016,19 @@
         <v>18</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BB49" t="n">
         <v>4.4</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD49" t="n">
         <v>4.4</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF49" t="n">
         <v>4.4</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>
@@ -10072,7 +10072,7 @@
         <v>2.76</v>
       </c>
       <c r="G50" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H50" t="n">
         <v>2.9</v>
@@ -10084,16 +10084,16 @@
         <v>2.94</v>
       </c>
       <c r="K50" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L50" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M50" t="n">
         <v>1.13</v>
       </c>
       <c r="N50" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="O50" t="n">
         <v>1.55</v>
@@ -10102,13 +10102,13 @@
         <v>1.52</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="R50" t="n">
         <v>1.18</v>
       </c>
       <c r="S50" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T50" t="n">
         <v>1.91</v>
@@ -10120,7 +10120,7 @@
         <v>1.45</v>
       </c>
       <c r="W50" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="X50" t="n">
         <v>10.5</v>
@@ -10153,7 +10153,7 @@
         <v>16.5</v>
       </c>
       <c r="AH50" t="n">
-        <v>28</v>
+        <v>980</v>
       </c>
       <c r="AI50" t="n">
         <v>90</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-08 13:33:25</t>
+          <t>2026-03-08 15:45:03</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -760,34 +760,34 @@
         <v>1.69</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="H2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I2" t="n">
         <v>5.5</v>
-      </c>
-      <c r="I2" t="n">
-        <v>5.7</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P2" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="Q2" t="n">
         <v>1.74</v>
@@ -796,25 +796,25 @@
         <v>1.54</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U2" t="n">
         <v>2.22</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
         <v>55</v>
@@ -826,10 +826,10 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>65</v>
@@ -844,13 +844,13 @@
         <v>18.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ2" t="n">
         <v>17</v>
       </c>
       <c r="AK2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AL2" t="n">
         <v>28</v>
@@ -859,7 +859,7 @@
         <v>80</v>
       </c>
       <c r="AN2" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO2" t="n">
         <v>65</v>
@@ -874,13 +874,13 @@
         <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
@@ -898,29 +898,29 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BB2" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC2" t="n">
         <v>15</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>14.5</v>
       </c>
       <c r="BD2" t="n">
         <v>27</v>
       </c>
       <c r="BE2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BG2" t="n">
         <v>50</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I3" t="n">
         <v>65</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K3" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="L3" t="n">
         <v>1.01</v>
@@ -975,19 +975,19 @@
         <v>1.03</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q3" t="n">
         <v>1.54</v>
       </c>
       <c r="R3" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S3" t="n">
         <v>2.36</v>
@@ -999,11 +999,11 @@
         <v>1.11</v>
       </c>
       <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
         <v>1.01</v>
       </c>
-      <c r="W3" t="n">
-        <v>2.52</v>
-      </c>
       <c r="X3" t="n">
         <v>1000</v>
       </c>
@@ -1059,62 +1059,62 @@
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BF3" t="n">
         <v>1.01</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1145,16 +1145,16 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>1.67</v>
+        <v>110</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
         <v>3</v>
@@ -1193,10 +1193,10 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
@@ -1378,7 +1378,7 @@
         <v>1.09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.05</v>
+        <v>1.52</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1390,7 +1390,7 @@
         <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1533,16 +1533,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H6" t="n">
         <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.2</v>
@@ -1551,43 +1551,43 @@
         <v>3.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="M6" t="n">
         <v>1.1</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>1.46</v>
       </c>
       <c r="P6" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="T6" t="n">
-        <v>1.96</v>
+        <v>2.02</v>
       </c>
       <c r="U6" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W6" t="n">
         <v>1.33</v>
       </c>
       <c r="X6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
         <v>8.199999999999999</v>
@@ -1608,31 +1608,31 @@
         <v>12</v>
       </c>
       <c r="AE6" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AF6" t="n">
         <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AH6" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AM6" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
         <v>1000</v>
@@ -1650,7 +1650,7 @@
         <v>11.5</v>
       </c>
       <c r="AS6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
@@ -1662,22 +1662,22 @@
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX6" t="n">
         <v>19.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.7</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="BC6" t="n">
         <v>44</v>
@@ -1686,17 +1686,17 @@
         <v>55</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.6</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
         <v>55</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.4</v>
+        <v>21</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1727,52 +1727,52 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="I7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="J7" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="K7" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
       </c>
       <c r="M7" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="S7" t="n">
-        <v>2.72</v>
+        <v>2.46</v>
       </c>
       <c r="T7" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
         <v>5.3</v>
@@ -1790,19 +1790,19 @@
         <v>8</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AF7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="AP7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ7" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ7" t="n">
-        <v>3.45</v>
-      </c>
       <c r="AR7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX7" t="n">
         <v>5.8</v>
       </c>
-      <c r="AS7" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.2</v>
-      </c>
       <c r="AY7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG7" t="n">
         <v>3.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
         <v>1.82</v>
       </c>
       <c r="I8" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="J8" t="n">
         <v>3.1</v>
@@ -1945,7 +1945,7 @@
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="O8" t="n">
         <v>1.51</v>
@@ -1960,7 +1960,7 @@
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>2.24</v>
@@ -1969,34 +1969,34 @@
         <v>1.66</v>
       </c>
       <c r="V8" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="W8" t="n">
         <v>1.2</v>
       </c>
       <c r="X8" t="n">
-        <v>10.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AB8" t="n">
         <v>17</v>
       </c>
       <c r="AC8" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AD8" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AE8" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AF8" t="n">
         <v>1000</v>
@@ -2026,65 +2026,65 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>980</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="AS8" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AT8" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU8" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="AW8" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AY8" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="AZ8" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>5.8</v>
+        <v>7.8</v>
       </c>
       <c r="BE8" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BG8" t="n">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2312,19 +2312,19 @@
         <v>1.42</v>
       </c>
       <c r="G10" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I10" t="n">
         <v>11.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
         <v>1.37</v>
@@ -2333,34 +2333,34 @@
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
         <v>1.1</v>
       </c>
       <c r="W10" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
@@ -2378,7 +2378,7 @@
         <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AD10" t="n">
         <v>980</v>
@@ -2390,7 +2390,7 @@
         <v>8.4</v>
       </c>
       <c r="AG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH10" t="n">
         <v>980</v>
@@ -2399,7 +2399,7 @@
         <v>1000</v>
       </c>
       <c r="AJ10" t="n">
-        <v>980</v>
+        <v>18</v>
       </c>
       <c r="AK10" t="n">
         <v>980</v>
@@ -2411,16 +2411,16 @@
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AR10" t="n">
         <v>5.1</v>
@@ -2429,10 +2429,10 @@
         <v>5.3</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AV10" t="n">
         <v>4.8</v>
@@ -2444,7 +2444,7 @@
         <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>3.85</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
         <v>4.8</v>
@@ -2453,7 +2453,7 @@
         <v>5.2</v>
       </c>
       <c r="BB10" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BC10" t="n">
         <v>4.3</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.04</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>1.09</v>
+        <v>2.16</v>
       </c>
       <c r="I11" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1</v>
+        <v>2.72</v>
       </c>
       <c r="K11" t="n">
-        <v>980</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
         <v>1.01</v>
@@ -2551,10 +2551,10 @@
         <v>1.11</v>
       </c>
       <c r="V11" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="X11" t="n">
         <v>1000</v>
@@ -2572,7 +2572,7 @@
         <v>1000</v>
       </c>
       <c r="AC11" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2697,82 +2697,82 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>5.1</v>
+        <v>4.5</v>
       </c>
       <c r="G12" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="I12" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="M12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="P12" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="V12" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="W12" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y12" t="n">
         <v>6.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AD12" t="n">
         <v>12.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF12" t="n">
         <v>1000</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="AT12" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AV12" t="n">
         <v>4.7</v>
       </c>
-      <c r="AU12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AW12" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="AX12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY12" t="n">
         <v>5.8</v>
       </c>
-      <c r="AY12" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>6</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>3.65</v>
+        <v>5</v>
       </c>
       <c r="BE12" t="n">
-        <v>3.65</v>
+        <v>7</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.65</v>
+        <v>5.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.02</v>
+        <v>1.39</v>
       </c>
       <c r="G13" t="n">
         <v>990</v>
       </c>
       <c r="H13" t="n">
-        <v>1.02</v>
+        <v>3.5</v>
       </c>
       <c r="I13" t="n">
         <v>990</v>
       </c>
       <c r="J13" t="n">
-        <v>1.02</v>
+        <v>2.96</v>
       </c>
       <c r="K13" t="n">
         <v>950</v>
@@ -2927,7 +2927,7 @@
         <v>1.47</v>
       </c>
       <c r="R13" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S13" t="n">
         <v>1.47</v>
@@ -2939,7 +2939,7 @@
         <v>1.11</v>
       </c>
       <c r="V13" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W13" t="n">
         <v>1.01</v>
@@ -2981,7 +2981,7 @@
         <v>1000</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK13" t="n">
         <v>1000</v>
@@ -2999,62 +2999,62 @@
         <v>1000</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="AS13" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="AW13" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="AX13" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="AY13" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AZ13" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BA13" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BB13" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3085,43 +3085,43 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="G14" t="n">
         <v>1.36</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="I14" t="n">
         <v>15.5</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="K14" t="n">
         <v>5.4</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M14" t="n">
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O14" t="n">
         <v>1.34</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
         <v>2</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S14" t="n">
         <v>3.65</v>
@@ -3130,16 +3130,16 @@
         <v>2.54</v>
       </c>
       <c r="U14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="V14" t="n">
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="Y14" t="n">
         <v>38</v>
@@ -3148,22 +3148,22 @@
         <v>140</v>
       </c>
       <c r="AA14" t="n">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="AB14" t="n">
         <v>7.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AD14" t="n">
         <v>55</v>
       </c>
       <c r="AE14" t="n">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="AF14" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AG14" t="n">
         <v>11.5</v>
@@ -3175,46 +3175,46 @@
         <v>350</v>
       </c>
       <c r="AJ14" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AK14" t="n">
         <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>65</v>
+        <v>330</v>
       </c>
       <c r="AM14" t="n">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="AN14" t="n">
         <v>7.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>830</v>
+        <v>770</v>
       </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AS14" t="n">
-        <v>7.8</v>
+        <v>10.5</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="AX14" t="n">
         <v>6</v>
@@ -3226,29 +3226,29 @@
         <v>34</v>
       </c>
       <c r="BA14" t="n">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
         <v>15.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="BE14" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="BF14" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>16.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3279,40 +3279,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="G15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="H15" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="O15" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="P15" t="n">
         <v>1.67</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="R15" t="n">
         <v>1.23</v>
@@ -3321,22 +3321,22 @@
         <v>4.7</v>
       </c>
       <c r="T15" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.67</v>
+        <v>1.61</v>
       </c>
       <c r="X15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Z15" t="n">
         <v>980</v>
@@ -3348,7 +3348,7 @@
         <v>980</v>
       </c>
       <c r="AC15" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
         <v>980</v>
@@ -3357,7 +3357,7 @@
         <v>980</v>
       </c>
       <c r="AF15" t="n">
-        <v>980</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>980</v>
@@ -3387,25 +3387,25 @@
         <v>65</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AQ15" t="n">
         <v>9</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.76</v>
+        <v>2.06</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU15" t="n">
         <v>6.4</v>
       </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AW15" t="n">
         <v>8.6</v>
@@ -3420,10 +3420,10 @@
         <v>6.8</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.76</v>
+        <v>2.06</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC15" t="n">
         <v>25</v>
@@ -3432,17 +3432,17 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BE15" t="n">
-        <v>9.800000000000001</v>
+        <v>32</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.02</v>
+        <v>7.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.74</v>
+        <v>2.06</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
         <v>4.3</v>
       </c>
       <c r="J16" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K16" t="n">
         <v>3.75</v>
@@ -3527,7 +3527,7 @@
         <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3542,7 +3542,7 @@
         <v>1000</v>
       </c>
       <c r="AC16" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3581,62 +3581,62 @@
         <v>1000</v>
       </c>
       <c r="AP16" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AQ16" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="AR16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AT16" t="n">
         <v>4.4</v>
       </c>
-      <c r="AS16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AU16" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="AX16" t="n">
-        <v>3.95</v>
+        <v>6.4</v>
       </c>
       <c r="AY16" t="n">
-        <v>3.8</v>
+        <v>7.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="BA16" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="BB16" t="n">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>4.9</v>
+        <v>2.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.1</v>
+        <v>3.35</v>
       </c>
       <c r="BF16" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5</v>
+        <v>2.24</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3739,7 +3739,7 @@
         <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AE17" t="n">
         <v>26</v>
@@ -3769,7 +3769,7 @@
         <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AO17" t="n">
         <v>18.5</v>
@@ -3808,19 +3808,19 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BB17" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BD17" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BF17" t="n">
         <v>19.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G18" t="n">
         <v>2.28</v>
@@ -3915,22 +3915,22 @@
         <v>1.79</v>
       </c>
       <c r="X18" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="Y18" t="n">
         <v>18</v>
       </c>
       <c r="Z18" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AA18" t="n">
         <v>85</v>
       </c>
       <c r="AB18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD18" t="n">
         <v>18.5</v>
@@ -3939,10 +3939,10 @@
         <v>50</v>
       </c>
       <c r="AF18" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH18" t="n">
         <v>19.5</v>
@@ -3951,7 +3951,7 @@
         <v>60</v>
       </c>
       <c r="AJ18" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK18" t="n">
         <v>27</v>
@@ -3960,7 +3960,7 @@
         <v>42</v>
       </c>
       <c r="AM18" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN18" t="n">
         <v>18</v>
@@ -3975,10 +3975,10 @@
         <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>4.3</v>
+        <v>5</v>
       </c>
       <c r="AT18" t="n">
         <v>9.199999999999999</v>
@@ -3990,7 +3990,7 @@
         <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="AX18" t="n">
         <v>12.5</v>
@@ -4002,29 +4002,29 @@
         <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>4.3</v>
+        <v>23</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.95</v>
+        <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BF18" t="n">
         <v>11</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="G19" t="n">
         <v>2.46</v>
@@ -4064,13 +4064,13 @@
         <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>3.55</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.3</v>
@@ -4103,7 +4103,7 @@
         <v>2.24</v>
       </c>
       <c r="V19" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W19" t="n">
         <v>1.68</v>
@@ -4130,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="AE19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF19" t="n">
         <v>19</v>
@@ -4154,7 +4154,7 @@
         <v>42</v>
       </c>
       <c r="AM19" t="n">
-        <v>95</v>
+        <v>200</v>
       </c>
       <c r="AN19" t="n">
         <v>20</v>
@@ -4172,7 +4172,7 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -4184,7 +4184,7 @@
         <v>11</v>
       </c>
       <c r="AW19" t="n">
-        <v>4.9</v>
+        <v>16</v>
       </c>
       <c r="AX19" t="n">
         <v>13.5</v>
@@ -4196,19 +4196,19 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BB19" t="n">
-        <v>5.1</v>
+        <v>14.5</v>
       </c>
       <c r="BC19" t="n">
         <v>20</v>
       </c>
       <c r="BD19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE19" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>5</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -4249,13 +4249,13 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G20" t="n">
         <v>4.3</v>
       </c>
       <c r="H20" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="I20" t="n">
         <v>2.32</v>
@@ -4264,7 +4264,7 @@
         <v>3.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -4279,7 +4279,7 @@
         <v>1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q20" t="n">
         <v>2.36</v>
@@ -4294,7 +4294,7 @@
         <v>2</v>
       </c>
       <c r="U20" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V20" t="n">
         <v>1.75</v>
@@ -4324,7 +4324,7 @@
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AF20" t="n">
         <v>28</v>
@@ -4348,7 +4348,7 @@
         <v>95</v>
       </c>
       <c r="AM20" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN20" t="n">
         <v>100</v>
@@ -4366,7 +4366,7 @@
         <v>11.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AT20" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
         <v>10</v>
       </c>
       <c r="AW20" t="n">
-        <v>5.3</v>
+        <v>14.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="AY20" t="n">
         <v>14.5</v>
@@ -4390,29 +4390,29 @@
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BB20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC20" t="n">
         <v>5.6</v>
       </c>
-      <c r="BC20" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BD20" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BE20" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF20" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>5.6</v>
       </c>
       <c r="BG20" t="n">
         <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="G21" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H21" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J21" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L21" t="n">
         <v>1.43</v>
@@ -4467,58 +4467,58 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X21" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="Z21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA21" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AB21" t="n">
         <v>8.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AF21" t="n">
         <v>11.5</v>
@@ -4527,16 +4527,16 @@
         <v>10.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
         <v>42</v>
@@ -4545,22 +4545,22 @@
         <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>13.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AS21" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -4569,44 +4569,44 @@
         <v>7.2</v>
       </c>
       <c r="AV21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX21" t="n">
         <v>10</v>
       </c>
       <c r="AY21" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="BB21" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="BC21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD21" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>11.5</v>
+        <v>28</v>
       </c>
       <c r="BF21" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>11</v>
+        <v>14.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.9</v>
-      </c>
-      <c r="G22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.8</v>
       </c>
       <c r="L22" t="n">
         <v>1.37</v>
@@ -4667,10 +4667,10 @@
         <v>1.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="R22" t="n">
         <v>1.41</v>
@@ -4679,128 +4679,128 @@
         <v>3.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V22" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X22" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
       </c>
       <c r="Z22" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>980</v>
+        <v>25</v>
       </c>
       <c r="AB22" t="n">
         <v>16.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="AF22" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AG22" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AJ22" t="n">
         <v>75</v>
       </c>
       <c r="AK22" t="n">
-        <v>980</v>
+        <v>44</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
       </c>
       <c r="AM22" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO22" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AP22" t="n">
         <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT22" t="n">
         <v>13.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AW22" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX22" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AY22" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>29</v>
+      </c>
+      <c r="BB22" t="n">
         <v>13.5</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BC22" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="BD22" t="n">
-        <v>40</v>
+        <v>12.5</v>
       </c>
       <c r="BE22" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="BF22" t="n">
         <v>34</v>
       </c>
       <c r="BG22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -4843,7 +4843,7 @@
         <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K23" t="n">
         <v>3.6</v>
@@ -4855,16 +4855,16 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P23" t="n">
         <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
@@ -4873,16 +4873,16 @@
         <v>3.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W23" t="n">
-        <v>1.84</v>
+        <v>1.81</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -4891,7 +4891,7 @@
         <v>16</v>
       </c>
       <c r="Z23" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4921,10 +4921,10 @@
         <v>1000</v>
       </c>
       <c r="AJ23" t="n">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="AK23" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>3.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ23" t="n">
-        <v>9.800000000000001</v>
+        <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>4.6</v>
+        <v>5.3</v>
       </c>
       <c r="AS23" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.5</v>
+        <v>7.4</v>
       </c>
       <c r="AU23" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
       </c>
       <c r="AY23" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="BA23" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="BB23" t="n">
-        <v>19.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC23" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE23" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BF23" t="n">
-        <v>14.5</v>
+        <v>4.9</v>
       </c>
       <c r="BG23" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -5025,37 +5025,37 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="I24" t="n">
         <v>2.86</v>
       </c>
       <c r="J24" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K24" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P24" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="Q24" t="n">
         <v>2.18</v>
@@ -5064,25 +5064,25 @@
         <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T24" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="U24" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X24" t="n">
         <v>11</v>
       </c>
       <c r="Y24" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Z24" t="n">
         <v>1000</v>
@@ -5094,22 +5094,22 @@
         <v>13.5</v>
       </c>
       <c r="AC24" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF24" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AG24" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="AH24" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI24" t="n">
         <v>1000</v>
@@ -5130,31 +5130,31 @@
         <v>1000</v>
       </c>
       <c r="AO24" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP24" t="n">
-        <v>3.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
       <c r="AR24" t="n">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU24" t="n">
         <v>6.2</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.7</v>
+        <v>7</v>
       </c>
       <c r="AW24" t="n">
-        <v>4.3</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>15.5</v>
@@ -5163,32 +5163,32 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>4</v>
+        <v>10.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="BB24" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BC24" t="n">
-        <v>4.5</v>
+        <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF24" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="BG24" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -5237,7 +5237,7 @@
         <v>3.6</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
@@ -5252,10 +5252,10 @@
         <v>1.7</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="S25" t="n">
         <v>4.1</v>
@@ -5288,13 +5288,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC25" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD25" t="n">
         <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AF25" t="n">
         <v>980</v>
@@ -5303,10 +5303,10 @@
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AI25" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
@@ -5333,10 +5333,10 @@
         <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS25" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT25" t="n">
         <v>6.8</v>
@@ -5345,44 +5345,44 @@
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW25" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BA25" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BC25" t="n">
         <v>6.6</v>
       </c>
-      <c r="BB25" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>5.6</v>
-      </c>
       <c r="BD25" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE25" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF25" t="n">
         <v>14.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -5413,16 +5413,16 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="G26" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="H26" t="n">
         <v>3.15</v>
       </c>
       <c r="I26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>3.35</v>
@@ -5431,7 +5431,7 @@
         <v>3.45</v>
       </c>
       <c r="L26" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
@@ -5443,10 +5443,10 @@
         <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R26" t="n">
         <v>1.26</v>
@@ -5458,64 +5458,64 @@
         <v>1.86</v>
       </c>
       <c r="U26" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X26" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
       </c>
       <c r="AC26" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AD26" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF26" t="n">
         <v>16.5</v>
       </c>
-      <c r="AE26" t="n">
-        <v>980</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AG26" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>20</v>
       </c>
       <c r="AI26" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AK26" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AM26" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>980</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
         <v>50</v>
@@ -5524,59 +5524,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="AX26" t="n">
         <v>13.5</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA26" t="n">
-        <v>6.6</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="BC26" t="n">
         <v>26</v>
       </c>
       <c r="BD26" t="n">
-        <v>6</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF26" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="BG26" t="n">
-        <v>28</v>
+        <v>8.6</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5610,19 @@
         <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H27" t="n">
         <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K27" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L27" t="n">
         <v>1.22</v>
@@ -5643,19 +5643,19 @@
         <v>1.41</v>
       </c>
       <c r="R27" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="S27" t="n">
-        <v>2.12</v>
+        <v>2.04</v>
       </c>
       <c r="T27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="U27" t="n">
         <v>2.8</v>
       </c>
       <c r="V27" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W27" t="n">
         <v>1.8</v>
@@ -5664,7 +5664,7 @@
         <v>980</v>
       </c>
       <c r="Y27" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="Z27" t="n">
         <v>980</v>
@@ -5691,7 +5691,7 @@
         <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>16.5</v>
+        <v>60</v>
       </c>
       <c r="AI27" t="n">
         <v>980</v>
@@ -5715,19 +5715,19 @@
         <v>19</v>
       </c>
       <c r="AP27" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AR27" t="n">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.9</v>
+        <v>14</v>
       </c>
       <c r="AU27" t="n">
         <v>9.199999999999999</v>
@@ -5736,10 +5736,10 @@
         <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
@@ -5748,19 +5748,19 @@
         <v>12</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BB27" t="n">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BD27" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF27" t="n">
         <v>7.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -5801,40 +5801,40 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="G28" t="n">
         <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="I28" t="n">
         <v>1.63</v>
       </c>
       <c r="J28" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="O28" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P28" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R28" t="n">
         <v>1.21</v>
@@ -5846,16 +5846,16 @@
         <v>2.38</v>
       </c>
       <c r="U28" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="W28" t="n">
         <v>1.11</v>
       </c>
       <c r="X28" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="Y28" t="n">
         <v>6.8</v>
@@ -5864,22 +5864,22 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AA28" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="AB28" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="AC28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD28" t="n">
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>980</v>
+        <v>27</v>
       </c>
       <c r="AF28" t="n">
-        <v>75</v>
+        <v>420</v>
       </c>
       <c r="AG28" t="n">
         <v>980</v>
@@ -5888,7 +5888,7 @@
         <v>980</v>
       </c>
       <c r="AI28" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AJ28" t="n">
         <v>470</v>
@@ -5906,13 +5906,13 @@
         <v>500</v>
       </c>
       <c r="AO28" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AP28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AR28" t="n">
         <v>6.6</v>
@@ -5921,7 +5921,7 @@
         <v>12.5</v>
       </c>
       <c r="AT28" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AU28" t="n">
         <v>8.199999999999999</v>
@@ -5930,41 +5930,41 @@
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>4.9</v>
+        <v>11.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>5.3</v>
+        <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BC28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BE28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF28" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BG28" t="n">
         <v>11.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -5998,13 +5998,13 @@
         <v>4</v>
       </c>
       <c r="G29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I29" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="J29" t="n">
         <v>3.15</v>
@@ -6013,7 +6013,7 @@
         <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
@@ -6034,25 +6034,25 @@
         <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="T29" t="n">
         <v>2</v>
       </c>
       <c r="U29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.8</v>
       </c>
-      <c r="V29" t="n">
-        <v>1.83</v>
-      </c>
       <c r="W29" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X29" t="n">
-        <v>980</v>
+        <v>18.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="Z29" t="n">
         <v>980</v>
@@ -6061,7 +6061,7 @@
         <v>980</v>
       </c>
       <c r="AB29" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC29" t="n">
         <v>8</v>
@@ -6070,40 +6070,40 @@
         <v>980</v>
       </c>
       <c r="AE29" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AF29" t="n">
         <v>980</v>
       </c>
       <c r="AG29" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AH29" t="n">
         <v>980</v>
       </c>
       <c r="AI29" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AJ29" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK29" t="n">
-        <v>75</v>
+        <v>370</v>
       </c>
       <c r="AL29" t="n">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="AM29" t="n">
         <v>190</v>
       </c>
       <c r="AN29" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AO29" t="n">
         <v>980</v>
       </c>
       <c r="AP29" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.4</v>
@@ -6112,53 +6112,53 @@
         <v>10</v>
       </c>
       <c r="AS29" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT29" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="AU29" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV29" t="n">
         <v>6.4</v>
       </c>
-      <c r="AV29" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AW29" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="AX29" t="n">
-        <v>5.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.2</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
-        <v>5.3</v>
+        <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB29" t="n">
-        <v>6.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC29" t="n">
-        <v>6.2</v>
+        <v>8.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE29" t="n">
-        <v>6.6</v>
+        <v>9.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BG29" t="n">
         <v>17</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="G30" t="n">
         <v>2.12</v>
@@ -6198,16 +6198,16 @@
         <v>4.6</v>
       </c>
       <c r="I30" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J30" t="n">
         <v>3.1</v>
       </c>
       <c r="K30" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L30" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
@@ -6231,13 +6231,13 @@
         <v>5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U30" t="n">
         <v>1.73</v>
       </c>
       <c r="V30" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W30" t="n">
         <v>1.9</v>
@@ -6252,13 +6252,13 @@
         <v>980</v>
       </c>
       <c r="AA30" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AB30" t="n">
         <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AD30" t="n">
         <v>23</v>
@@ -6273,10 +6273,10 @@
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="AI30" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ30" t="n">
         <v>980</v>
@@ -6288,13 +6288,13 @@
         <v>60</v>
       </c>
       <c r="AM30" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN30" t="n">
         <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AP30" t="n">
         <v>8</v>
@@ -6303,10 +6303,10 @@
         <v>10</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.4</v>
+        <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT30" t="n">
         <v>5.7</v>
@@ -6318,41 +6318,41 @@
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX30" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY30" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5.9</v>
+        <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BB30" t="n">
         <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BD30" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BF30" t="n">
-        <v>5.9</v>
+        <v>17</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -6392,7 +6392,7 @@
         <v>4.9</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="J31" t="n">
         <v>3</v>
@@ -6416,7 +6416,7 @@
         <v>1.61</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="R31" t="n">
         <v>1.22</v>
@@ -6431,7 +6431,7 @@
         <v>1.76</v>
       </c>
       <c r="V31" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W31" t="n">
         <v>2</v>
@@ -6455,7 +6455,7 @@
         <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
@@ -6467,16 +6467,16 @@
         <v>12.5</v>
       </c>
       <c r="AH31" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI31" t="n">
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AK31" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AL31" t="n">
         <v>1000</v>
@@ -6485,19 +6485,19 @@
         <v>1000</v>
       </c>
       <c r="AN31" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AO31" t="n">
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="AQ31" t="n">
-        <v>10.5</v>
+        <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AS31" t="n">
         <v>5.1</v>
@@ -6509,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>4.7</v>
       </c>
       <c r="AW31" t="n">
         <v>5</v>
@@ -6521,7 +6521,7 @@
         <v>8.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA31" t="n">
         <v>5</v>
@@ -6530,13 +6530,13 @@
         <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF31" t="n">
         <v>15.5</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G32" t="n">
         <v>1.71</v>
@@ -6592,7 +6592,7 @@
         <v>3.7</v>
       </c>
       <c r="K32" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L32" t="n">
         <v>1.38</v>
@@ -6634,7 +6634,7 @@
         <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z32" t="n">
         <v>1000</v>
@@ -6667,13 +6667,13 @@
         <v>1000</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AK32" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL32" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -6685,25 +6685,25 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>9.6</v>
+        <v>5.8</v>
       </c>
       <c r="AQ32" t="n">
         <v>15</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT32" t="n">
         <v>5.6</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.45</v>
+        <v>5.1</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AW32" t="n">
         <v>5</v>
@@ -6712,35 +6712,35 @@
         <v>6.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AZ32" t="n">
         <v>18.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB32" t="n">
         <v>12</v>
       </c>
       <c r="BC32" t="n">
-        <v>4.2</v>
+        <v>10</v>
       </c>
       <c r="BD32" t="n">
         <v>4.7</v>
       </c>
       <c r="BE32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF32" t="n">
         <v>9</v>
       </c>
       <c r="BG32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -6771,13 +6771,13 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G33" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H33" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I33" t="n">
         <v>9.199999999999999</v>
@@ -6786,7 +6786,7 @@
         <v>4</v>
       </c>
       <c r="K33" t="n">
-        <v>5.2</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
         <v>1.38</v>
@@ -6816,7 +6816,7 @@
         <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V33" t="n">
         <v>1.12</v>
@@ -6864,7 +6864,7 @@
         <v>16</v>
       </c>
       <c r="AK33" t="n">
-        <v>980</v>
+        <v>24</v>
       </c>
       <c r="AL33" t="n">
         <v>65</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AT33" t="n">
         <v>5.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AV33" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AX33" t="n">
-        <v>3.4</v>
+        <v>6.8</v>
       </c>
       <c r="AY33" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AZ33" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BC33" t="n">
         <v>4.7</v>
       </c>
-      <c r="BA33" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BD33" t="n">
-        <v>5</v>
+        <v>5.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="BF33" t="n">
-        <v>3.85</v>
+        <v>9.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
         <v>2.12</v>
       </c>
       <c r="G34" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="H34" t="n">
         <v>3.55</v>
@@ -6983,7 +6983,7 @@
         <v>3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
@@ -7016,119 +7016,119 @@
         <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="X34" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y34" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="Z34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA34" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB34" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AD34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE34" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AF34" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AG34" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH34" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI34" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK34" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
       </c>
       <c r="AM34" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN34" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO34" t="n">
         <v>1000</v>
       </c>
       <c r="AP34" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="AQ34" t="n">
-        <v>5.1</v>
+        <v>11.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AT34" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AX34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AY34" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AZ34" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="BA34" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BB34" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB34" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BC34" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>9</v>
+      </c>
+      <c r="BF34" t="n">
         <v>5.8</v>
       </c>
-      <c r="BD34" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>7</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG34" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -7171,10 +7171,10 @@
         <v>2.2</v>
       </c>
       <c r="J35" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K35" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L35" t="n">
         <v>1.45</v>
@@ -7216,10 +7216,10 @@
         <v>10</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z35" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA35" t="n">
         <v>34</v>
@@ -7246,7 +7246,7 @@
         <v>28</v>
       </c>
       <c r="AI35" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ35" t="n">
         <v>1000</v>
@@ -7291,38 +7291,38 @@
         <v>20</v>
       </c>
       <c r="AX35" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AY35" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ35" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC35" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="BF35" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG35" t="n">
         <v>18</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -7356,13 +7356,13 @@
         <v>1.51</v>
       </c>
       <c r="G36" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J36" t="n">
         <v>4.6</v>
@@ -7371,7 +7371,7 @@
         <v>4.9</v>
       </c>
       <c r="L36" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M36" t="n">
         <v>1.05</v>
@@ -7386,34 +7386,34 @@
         <v>2.3</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R36" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S36" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U36" t="n">
         <v>2.06</v>
       </c>
       <c r="V36" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W36" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X36" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y36" t="n">
         <v>28</v>
       </c>
       <c r="Z36" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AA36" t="n">
         <v>210</v>
@@ -7422,13 +7422,13 @@
         <v>10</v>
       </c>
       <c r="AC36" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE36" t="n">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="AF36" t="n">
         <v>10.5</v>
@@ -7440,7 +7440,7 @@
         <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>90</v>
+        <v>400</v>
       </c>
       <c r="AJ36" t="n">
         <v>14.5</v>
@@ -7455,34 +7455,34 @@
         <v>130</v>
       </c>
       <c r="AN36" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO36" t="n">
         <v>110</v>
       </c>
       <c r="AP36" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ36" t="n">
         <v>22</v>
       </c>
       <c r="AR36" t="n">
-        <v>7.6</v>
+        <v>40</v>
       </c>
       <c r="AS36" t="n">
-        <v>8.4</v>
+        <v>36</v>
       </c>
       <c r="AT36" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AV36" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX36" t="n">
         <v>8.6</v>
@@ -7494,7 +7494,7 @@
         <v>19</v>
       </c>
       <c r="BA36" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BB36" t="n">
         <v>11.5</v>
@@ -7503,20 +7503,20 @@
         <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="BE36" t="n">
-        <v>8.199999999999999</v>
+        <v>29</v>
       </c>
       <c r="BF36" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -7556,13 +7556,13 @@
         <v>2.2</v>
       </c>
       <c r="I37" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="J37" t="n">
         <v>2.92</v>
       </c>
       <c r="K37" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7574,31 +7574,31 @@
         <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="R37" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="T37" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U37" t="n">
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="W37" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="X37" t="n">
         <v>17.5</v>
@@ -7634,83 +7634,83 @@
         <v>27</v>
       </c>
       <c r="AI37" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AJ37" t="n">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="AK37" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="AL37" t="n">
-        <v>80</v>
+        <v>250</v>
       </c>
       <c r="AM37" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AN37" t="n">
         <v>1000</v>
       </c>
       <c r="AO37" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AP37" t="n">
-        <v>2.28</v>
+        <v>6.4</v>
       </c>
       <c r="AQ37" t="n">
-        <v>2.18</v>
+        <v>5.1</v>
       </c>
       <c r="AR37" t="n">
         <v>10</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.46</v>
+        <v>2.82</v>
       </c>
       <c r="AT37" t="n">
         <v>10</v>
       </c>
       <c r="AU37" t="n">
-        <v>2.08</v>
+        <v>4.4</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.24</v>
+        <v>6.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.44</v>
+        <v>2.76</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.44</v>
+        <v>2.78</v>
       </c>
       <c r="AY37" t="n">
-        <v>2.32</v>
+        <v>8.4</v>
       </c>
       <c r="AZ37" t="n">
         <v>11.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.52</v>
+        <v>20</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.52</v>
+        <v>18</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="BE37" t="n">
-        <v>2.62</v>
+        <v>26</v>
       </c>
       <c r="BF37" t="n">
-        <v>2.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG37" t="n">
-        <v>2.6</v>
+        <v>13.5</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -7753,52 +7753,52 @@
         <v>2.96</v>
       </c>
       <c r="J38" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K38" t="n">
         <v>3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O38" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="P38" t="n">
         <v>1.66</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="R38" t="n">
         <v>1.24</v>
       </c>
       <c r="S38" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="T38" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="U38" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V38" t="n">
         <v>1.51</v>
       </c>
       <c r="W38" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X38" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="Y38" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z38" t="n">
         <v>18</v>
@@ -7807,7 +7807,7 @@
         <v>50</v>
       </c>
       <c r="AB38" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC38" t="n">
         <v>7.8</v>
@@ -7828,7 +7828,7 @@
         <v>21</v>
       </c>
       <c r="AI38" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AJ38" t="n">
         <v>48</v>
@@ -7849,7 +7849,7 @@
         <v>42</v>
       </c>
       <c r="AP38" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ38" t="n">
         <v>8.4</v>
@@ -7858,7 +7858,7 @@
         <v>15.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AT38" t="n">
         <v>8.6</v>
@@ -7867,22 +7867,22 @@
         <v>6.6</v>
       </c>
       <c r="AV38" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AW38" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AX38" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AY38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA38" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="BB38" t="n">
         <v>29</v>
@@ -7891,20 +7891,20 @@
         <v>30</v>
       </c>
       <c r="BD38" t="n">
-        <v>9.4</v>
+        <v>46</v>
       </c>
       <c r="BE38" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BF38" t="n">
         <v>30</v>
       </c>
       <c r="BG38" t="n">
-        <v>8.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -7944,7 +7944,7 @@
         <v>3.7</v>
       </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J39" t="n">
         <v>3.3</v>
@@ -7962,7 +7962,7 @@
         <v>3.2</v>
       </c>
       <c r="O39" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="P39" t="n">
         <v>1.74</v>
@@ -7977,13 +7977,13 @@
         <v>4.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="U39" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W39" t="n">
         <v>1.75</v>
@@ -8019,7 +8019,7 @@
         <v>11.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI39" t="n">
         <v>65</v>
@@ -8040,7 +8040,7 @@
         <v>24</v>
       </c>
       <c r="AO39" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP39" t="n">
         <v>10</v>
@@ -8049,7 +8049,7 @@
         <v>10.5</v>
       </c>
       <c r="AR39" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS39" t="n">
         <v>50</v>
@@ -8061,7 +8061,7 @@
         <v>6.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW39" t="n">
         <v>44</v>
@@ -8073,10 +8073,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ39" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BB39" t="n">
         <v>27</v>
@@ -8088,7 +8088,7 @@
         <v>40</v>
       </c>
       <c r="BE39" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF39" t="n">
         <v>21</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -8129,10 +8129,10 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.97</v>
-      </c>
-      <c r="G40" t="n">
-        <v>1.98</v>
       </c>
       <c r="H40" t="n">
         <v>4.7</v>
@@ -8141,10 +8141,10 @@
         <v>4.8</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K40" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.49</v>
@@ -8159,7 +8159,7 @@
         <v>1.43</v>
       </c>
       <c r="P40" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q40" t="n">
         <v>2.28</v>
@@ -8171,7 +8171,7 @@
         <v>4.4</v>
       </c>
       <c r="T40" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U40" t="n">
         <v>1.9</v>
@@ -8204,7 +8204,7 @@
         <v>19</v>
       </c>
       <c r="AE40" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF40" t="n">
         <v>11</v>
@@ -8228,13 +8228,13 @@
         <v>46</v>
       </c>
       <c r="AM40" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AN40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO40" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AP40" t="n">
         <v>10</v>
@@ -8267,7 +8267,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA40" t="n">
         <v>36</v>
@@ -8279,20 +8279,20 @@
         <v>21</v>
       </c>
       <c r="BD40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE40" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="BF40" t="n">
         <v>16</v>
       </c>
       <c r="BG40" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G41" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H41" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I41" t="n">
         <v>4.2</v>
@@ -8338,7 +8338,7 @@
         <v>3.4</v>
       </c>
       <c r="K41" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L41" t="n">
         <v>1.46</v>
@@ -8347,7 +8347,7 @@
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
         <v>1.38</v>
@@ -8359,37 +8359,37 @@
         <v>2.16</v>
       </c>
       <c r="R41" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S41" t="n">
         <v>3.95</v>
       </c>
       <c r="T41" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U41" t="n">
         <v>2.04</v>
       </c>
       <c r="V41" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="X41" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y41" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AA41" t="n">
         <v>85</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC41" t="n">
         <v>7.4</v>
@@ -8401,7 +8401,7 @@
         <v>55</v>
       </c>
       <c r="AF41" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG41" t="n">
         <v>10.5</v>
@@ -8416,19 +8416,19 @@
         <v>28</v>
       </c>
       <c r="AK41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL41" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM41" t="n">
         <v>130</v>
       </c>
       <c r="AN41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AO41" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AP41" t="n">
         <v>10.5</v>
@@ -8437,10 +8437,10 @@
         <v>12</v>
       </c>
       <c r="AR41" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS41" t="n">
-        <v>14.5</v>
+        <v>48</v>
       </c>
       <c r="AT41" t="n">
         <v>7.8</v>
@@ -8452,7 +8452,7 @@
         <v>15</v>
       </c>
       <c r="AW41" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AX41" t="n">
         <v>11</v>
@@ -8461,32 +8461,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BB41" t="n">
         <v>24</v>
       </c>
       <c r="BC41" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD41" t="n">
         <v>36</v>
       </c>
       <c r="BE41" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="BF41" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -8517,64 +8517,64 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G42" t="n">
-        <v>2.56</v>
+        <v>2.36</v>
       </c>
       <c r="H42" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J42" t="n">
         <v>3.15</v>
       </c>
-      <c r="I42" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="J42" t="n">
-        <v>2.88</v>
-      </c>
       <c r="K42" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
       </c>
       <c r="N42" t="n">
-        <v>2.68</v>
+        <v>3.1</v>
       </c>
       <c r="O42" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P42" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="R42" t="n">
         <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>1.02</v>
+        <v>3.45</v>
       </c>
       <c r="T42" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="U42" t="n">
         <v>1.94</v>
       </c>
       <c r="V42" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W42" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="X42" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Y42" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z42" t="n">
         <v>34</v>
@@ -8586,7 +8586,7 @@
         <v>10.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
         <v>19.5</v>
@@ -8601,10 +8601,10 @@
         <v>13.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ42" t="n">
         <v>36</v>
@@ -8619,68 +8619,68 @@
         <v>1000</v>
       </c>
       <c r="AN42" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO42" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.3</v>
+        <v>10</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.35</v>
+        <v>10.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>3.8</v>
+        <v>20</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AT42" t="n">
-        <v>3.05</v>
+        <v>7.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>2.94</v>
+        <v>5.8</v>
       </c>
       <c r="AV42" t="n">
-        <v>3.5</v>
+        <v>13.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="AX42" t="n">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="AY42" t="n">
-        <v>3.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ42" t="n">
-        <v>3.6</v>
+        <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB42" t="n">
-        <v>3.8</v>
+        <v>6.8</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.75</v>
+        <v>21</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.1</v>
+        <v>4.8</v>
       </c>
       <c r="BF42" t="n">
-        <v>3.65</v>
+        <v>17.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -8711,25 +8711,25 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="G43" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H43" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I43" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J43" t="n">
         <v>3.4</v>
       </c>
       <c r="K43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L43" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -8759,13 +8759,13 @@
         <v>1.81</v>
       </c>
       <c r="V43" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W43" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X43" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Y43" t="n">
         <v>16</v>
@@ -8786,7 +8786,7 @@
         <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="AF43" t="n">
         <v>11</v>
@@ -8798,7 +8798,7 @@
         <v>25</v>
       </c>
       <c r="AI43" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AJ43" t="n">
         <v>22</v>
@@ -8810,7 +8810,7 @@
         <v>980</v>
       </c>
       <c r="AM43" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN43" t="n">
         <v>18.5</v>
@@ -8825,10 +8825,10 @@
         <v>12.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AS43" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AT43" t="n">
         <v>6.2</v>
@@ -8840,7 +8840,7 @@
         <v>18</v>
       </c>
       <c r="AW43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX43" t="n">
         <v>8.800000000000001</v>
@@ -8852,29 +8852,29 @@
         <v>19.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BB43" t="n">
-        <v>5.8</v>
+        <v>18</v>
       </c>
       <c r="BC43" t="n">
         <v>19.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>7.6</v>
+        <v>28</v>
       </c>
       <c r="BF43" t="n">
         <v>12.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -8908,10 +8908,10 @@
         <v>3.35</v>
       </c>
       <c r="G44" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H44" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I44" t="n">
         <v>2.66</v>
@@ -8929,7 +8929,7 @@
         <v>1.11</v>
       </c>
       <c r="N44" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="O44" t="n">
         <v>1.48</v>
@@ -8938,7 +8938,7 @@
         <v>1.56</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R44" t="n">
         <v>1.2</v>
@@ -8950,13 +8950,13 @@
         <v>1.98</v>
       </c>
       <c r="U44" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V44" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W44" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X44" t="n">
         <v>9.800000000000001</v>
@@ -8965,34 +8965,34 @@
         <v>8.4</v>
       </c>
       <c r="Z44" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA44" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AB44" t="n">
-        <v>980</v>
+        <v>20</v>
       </c>
       <c r="AC44" t="n">
         <v>7.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AE44" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF44" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG44" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH44" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI44" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ44" t="n">
         <v>1000</v>
@@ -9019,10 +9019,10 @@
         <v>6.8</v>
       </c>
       <c r="AR44" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT44" t="n">
         <v>9</v>
@@ -9034,41 +9034,41 @@
         <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>6.6</v>
+        <v>14.5</v>
       </c>
       <c r="AX44" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY44" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="AZ44" t="n">
-        <v>6</v>
+        <v>11.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB44" t="n">
         <v>7.6</v>
       </c>
       <c r="BC44" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE44" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BF44" t="n">
         <v>7.8</v>
       </c>
-      <c r="BF44" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BG44" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G45" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="H45" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="I45" t="n">
         <v>2.38</v>
       </c>
       <c r="J45" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="K45" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L45" t="n">
         <v>1.44</v>
@@ -9123,13 +9123,13 @@
         <v>1.11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="O45" t="n">
         <v>1.44</v>
       </c>
       <c r="P45" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="Q45" t="n">
         <v>2.32</v>
@@ -9144,43 +9144,43 @@
         <v>1.91</v>
       </c>
       <c r="U45" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="V45" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W45" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="X45" t="n">
-        <v>980</v>
+        <v>19</v>
       </c>
       <c r="Y45" t="n">
-        <v>980</v>
+        <v>14.5</v>
       </c>
       <c r="Z45" t="n">
-        <v>980</v>
+        <v>40</v>
       </c>
       <c r="AA45" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AB45" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AC45" t="n">
-        <v>980</v>
+        <v>14</v>
       </c>
       <c r="AD45" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AE45" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AF45" t="n">
         <v>980</v>
       </c>
       <c r="AG45" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AH45" t="n">
         <v>980</v>
@@ -9189,80 +9189,80 @@
         <v>980</v>
       </c>
       <c r="AJ45" t="n">
-        <v>90</v>
+        <v>900</v>
       </c>
       <c r="AK45" t="n">
-        <v>65</v>
+        <v>250</v>
       </c>
       <c r="AL45" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AM45" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN45" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AO45" t="n">
         <v>980</v>
       </c>
       <c r="AP45" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AQ45" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR45" t="n">
-        <v>5.8</v>
+        <v>11</v>
       </c>
       <c r="AS45" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT45" t="n">
         <v>10</v>
       </c>
       <c r="AU45" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AV45" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AW45" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX45" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AY45" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC45" t="n">
         <v>6.2</v>
       </c>
-      <c r="AZ45" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BA45" t="n">
+      <c r="BD45" t="n">
         <v>4.3</v>
       </c>
-      <c r="BB45" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>1.93</v>
-      </c>
       <c r="BE45" t="n">
-        <v>1.83</v>
+        <v>9.4</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.82</v>
+        <v>8.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>1.58</v>
       </c>
       <c r="H46" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
         <v>8.4</v>
@@ -9308,10 +9308,10 @@
         <v>4.2</v>
       </c>
       <c r="K46" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
@@ -9347,7 +9347,7 @@
         <v>2.74</v>
       </c>
       <c r="X46" t="n">
-        <v>18.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y46" t="n">
         <v>23</v>
@@ -9362,7 +9362,7 @@
         <v>7.6</v>
       </c>
       <c r="AC46" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD46" t="n">
         <v>46</v>
@@ -9377,7 +9377,7 @@
         <v>10.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>46</v>
+        <v>980</v>
       </c>
       <c r="AI46" t="n">
         <v>140</v>
@@ -9395,7 +9395,7 @@
         <v>200</v>
       </c>
       <c r="AN46" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AO46" t="n">
         <v>220</v>
@@ -9419,7 +9419,7 @@
         <v>8.6</v>
       </c>
       <c r="AV46" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AW46" t="n">
         <v>40</v>
@@ -9440,7 +9440,7 @@
         <v>11.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD46" t="n">
         <v>32</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -9532,7 +9532,7 @@
         <v>2.04</v>
       </c>
       <c r="U47" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="V47" t="n">
         <v>1.09</v>
@@ -9541,10 +9541,10 @@
         <v>3.15</v>
       </c>
       <c r="X47" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Z47" t="n">
         <v>1000</v>
@@ -9553,34 +9553,34 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC47" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
       </c>
       <c r="AE47" t="n">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="AF47" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG47" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH47" t="n">
         <v>1000</v>
       </c>
       <c r="AI47" t="n">
-        <v>160</v>
+        <v>520</v>
       </c>
       <c r="AJ47" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK47" t="n">
-        <v>18.5</v>
+        <v>34</v>
       </c>
       <c r="AL47" t="n">
         <v>1000</v>
@@ -9589,7 +9589,7 @@
         <v>200</v>
       </c>
       <c r="AN47" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
@@ -9598,13 +9598,13 @@
         <v>13.5</v>
       </c>
       <c r="AQ47" t="n">
-        <v>4.7</v>
+        <v>12.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>5.3</v>
+        <v>8.4</v>
       </c>
       <c r="AS47" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT47" t="n">
         <v>6.6</v>
@@ -9613,10 +9613,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV47" t="n">
-        <v>4.9</v>
+        <v>14.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX47" t="n">
         <v>7</v>
@@ -9625,10 +9625,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ47" t="n">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB47" t="n">
         <v>10.5</v>
@@ -9637,20 +9637,20 @@
         <v>13.5</v>
       </c>
       <c r="BD47" t="n">
-        <v>5</v>
+        <v>19.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>5.4</v>
+        <v>28</v>
       </c>
       <c r="BF47" t="n">
         <v>5.9</v>
       </c>
       <c r="BG47" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -9687,19 +9687,19 @@
         <v>1.71</v>
       </c>
       <c r="H48" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
         <v>6.8</v>
       </c>
       <c r="J48" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K48" t="n">
         <v>4.9</v>
       </c>
       <c r="L48" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="M48" t="n">
         <v>1.07</v>
@@ -9729,7 +9729,7 @@
         <v>1.89</v>
       </c>
       <c r="V48" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W48" t="n">
         <v>2.4</v>
@@ -9750,7 +9750,7 @@
         <v>1000</v>
       </c>
       <c r="AC48" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AD48" t="n">
         <v>1000</v>
@@ -9789,62 +9789,62 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AQ48" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AR48" t="n">
-        <v>4.7</v>
+        <v>2.12</v>
       </c>
       <c r="AS48" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AV48" t="n">
-        <v>4.3</v>
+        <v>2.68</v>
       </c>
       <c r="AW48" t="n">
-        <v>4.9</v>
+        <v>2.18</v>
       </c>
       <c r="AX48" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AY48" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AZ48" t="n">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="BA48" t="n">
-        <v>4.9</v>
+        <v>2.18</v>
       </c>
       <c r="BB48" t="n">
-        <v>4.2</v>
+        <v>2.64</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.2</v>
+        <v>2.66</v>
       </c>
       <c r="BD48" t="n">
-        <v>4.6</v>
+        <v>2.12</v>
       </c>
       <c r="BE48" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="BF48" t="n">
-        <v>3.8</v>
+        <v>2.86</v>
       </c>
       <c r="BG48" t="n">
-        <v>3.2</v>
+        <v>1.84</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G49" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="H49" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="I49" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J49" t="n">
         <v>3</v>
       </c>
-      <c r="G49" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="H49" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="I49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="J49" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K49" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,7 +9899,7 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="O49" t="n">
         <v>1.47</v>
@@ -9920,40 +9920,40 @@
         <v>1.98</v>
       </c>
       <c r="U49" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="V49" t="n">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W49" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="X49" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="Y49" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AB49" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC49" t="n">
         <v>8.6</v>
       </c>
       <c r="AD49" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AF49" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG49" t="n">
         <v>17.5</v>
@@ -9962,28 +9962,28 @@
         <v>26</v>
       </c>
       <c r="AI49" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ49" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK49" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AL49" t="n">
         <v>1000</v>
       </c>
       <c r="AM49" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN49" t="n">
         <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AP49" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ49" t="n">
         <v>7.4</v>
@@ -9992,7 +9992,7 @@
         <v>13.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>3.95</v>
+        <v>4.6</v>
       </c>
       <c r="AT49" t="n">
         <v>8.4</v>
@@ -10004,7 +10004,7 @@
         <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="AX49" t="n">
         <v>17.5</v>
@@ -10016,29 +10016,29 @@
         <v>18</v>
       </c>
       <c r="BA49" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BB49" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BC49" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="BD49" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="BF49" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="BG49" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G50" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="H50" t="n">
         <v>5.8</v>
@@ -10081,7 +10081,7 @@
         <v>8</v>
       </c>
       <c r="J50" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K50" t="n">
         <v>3.8</v>
@@ -10102,13 +10102,13 @@
         <v>1.74</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="R50" t="n">
         <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
@@ -10117,10 +10117,10 @@
         <v>1.81</v>
       </c>
       <c r="V50" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W50" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -10269,13 +10269,13 @@
         <v>3.6</v>
       </c>
       <c r="H51" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I51" t="n">
         <v>2.64</v>
       </c>
       <c r="J51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K51" t="n">
         <v>3.3</v>
@@ -10296,13 +10296,13 @@
         <v>1.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="R51" t="n">
         <v>1.22</v>
       </c>
       <c r="S51" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="T51" t="n">
         <v>2</v>
@@ -10332,7 +10332,7 @@
         <v>12.5</v>
       </c>
       <c r="AC51" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD51" t="n">
         <v>14.5</v>
@@ -10350,7 +10350,7 @@
         <v>26</v>
       </c>
       <c r="AI51" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ51" t="n">
         <v>85</v>
@@ -10377,25 +10377,25 @@
         <v>7.2</v>
       </c>
       <c r="AR51" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="AS51" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="AT51" t="n">
-        <v>3.35</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU51" t="n">
-        <v>3</v>
+        <v>6.4</v>
       </c>
       <c r="AV51" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="AW51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX51" t="n">
         <v>4.1</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>3.95</v>
       </c>
       <c r="AY51" t="n">
         <v>13</v>
@@ -10404,29 +10404,29 @@
         <v>18</v>
       </c>
       <c r="BA51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BC51" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BE51" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BF51" t="n">
         <v>4.5</v>
       </c>
-      <c r="BF51" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BG51" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>
@@ -10460,7 +10460,7 @@
         <v>2.76</v>
       </c>
       <c r="G52" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="H52" t="n">
         <v>2.9</v>
@@ -10481,7 +10481,7 @@
         <v>1.13</v>
       </c>
       <c r="N52" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="O52" t="n">
         <v>1.55</v>
@@ -10496,7 +10496,7 @@
         <v>1.18</v>
       </c>
       <c r="S52" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="T52" t="n">
         <v>1.91</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-08 17:55:29</t>
+          <t>2026-03-08 20:05:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="H2" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I2" t="n">
         <v>5.5</v>
@@ -772,7 +772,7 @@
         <v>4.3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.34</v>
@@ -781,43 +781,43 @@
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
         <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T2" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="V2" t="n">
         <v>1.22</v>
       </c>
       <c r="W2" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AA2" t="n">
         <v>140</v>
@@ -826,7 +826,7 @@
         <v>10.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD2" t="n">
         <v>21</v>
@@ -853,16 +853,16 @@
         <v>16.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM2" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AO2" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP2" t="n">
         <v>18.5</v>
@@ -874,7 +874,7 @@
         <v>40</v>
       </c>
       <c r="AS2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
         <v>9.6</v>
@@ -898,7 +898,7 @@
         <v>17</v>
       </c>
       <c r="BA2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
@@ -913,14 +913,14 @@
         <v>18</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BG2" t="n">
         <v>50</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -951,58 +951,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56</v>
+        <v>1.41</v>
       </c>
       <c r="H3" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>12.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K3" t="n">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M3" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V3" t="n">
         <v>1.1</v>
       </c>
-      <c r="O3" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S3" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.02</v>
-      </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="X3" t="n">
         <v>1000</v>
@@ -1020,7 +1020,7 @@
         <v>1000</v>
       </c>
       <c r="AC3" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD3" t="n">
         <v>1000</v>
@@ -1041,7 +1041,7 @@
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
         <v>1000</v>
@@ -1053,13 +1053,13 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.09</v>
+        <v>2</v>
       </c>
       <c r="AQ3" t="n">
         <v>4.2</v>
@@ -1071,10 +1071,10 @@
         <v>4.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.09</v>
+        <v>2.34</v>
       </c>
       <c r="AV3" t="n">
         <v>4.2</v>
@@ -1083,38 +1083,38 @@
         <v>4.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.09</v>
+        <v>4.1</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.09</v>
+        <v>4.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.09</v>
+        <v>2.98</v>
       </c>
       <c r="BA3" t="n">
         <v>4.2</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.09</v>
+        <v>5.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.09</v>
+        <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.09</v>
+        <v>3</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.09</v>
+        <v>2.08</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>110</v>
+        <v>1.83</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
         <v>30</v>
@@ -1181,7 +1181,7 @@
         <v>1.9</v>
       </c>
       <c r="R4" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="S4" t="n">
         <v>1.9</v>
@@ -1196,7 +1196,7 @@
         <v>1.03</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="X4" t="n">
         <v>1000</v>
@@ -1214,7 +1214,7 @@
         <v>1000</v>
       </c>
       <c r="AC4" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AD4" t="n">
         <v>1000</v>
@@ -1247,58 +1247,58 @@
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO4" t="n">
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AS4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AV4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BB4" t="n">
         <v>1.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BD4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="BF4" t="n">
         <v>1.13</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
         <v>1000</v>
       </c>
       <c r="H5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>870</v>
       </c>
       <c r="J5" t="n">
         <v>2.6</v>
@@ -1363,13 +1363,13 @@
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="O5" t="n">
         <v>1.06</v>
       </c>
       <c r="P5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Q5" t="n">
         <v>1.52</v>
@@ -1378,7 +1378,7 @@
         <v>1.09</v>
       </c>
       <c r="S5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="T5" t="n">
         <v>1.11</v>
@@ -1387,7 +1387,7 @@
         <v>1.11</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
         <v>1.04</v>
@@ -1408,7 +1408,7 @@
         <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AD5" t="n">
         <v>1000</v>
@@ -1447,62 +1447,62 @@
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.04</v>
+        <v>1.15</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.05</v>
+        <v>1.16</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.05</v>
+        <v>1.17</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.05</v>
+        <v>1.55</v>
       </c>
       <c r="BG5" t="n">
         <v>1.55</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1536,70 +1536,70 @@
         <v>3.85</v>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H6" t="n">
         <v>2.24</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="J6" t="n">
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L6" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="O6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="R6" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="T6" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="W6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AB6" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC6" t="n">
         <v>7.6</v>
@@ -1611,7 +1611,7 @@
         <v>30</v>
       </c>
       <c r="AF6" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AG6" t="n">
         <v>20</v>
@@ -1620,16 +1620,16 @@
         <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AJ6" t="n">
         <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AL6" t="n">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
         <v>580</v>
@@ -1638,13 +1638,13 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AP6" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>11.5</v>
@@ -1656,31 +1656,31 @@
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>19.5</v>
       </c>
-      <c r="AY6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>15</v>
-      </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BD6" t="n">
         <v>55</v>
@@ -1692,11 +1692,11 @@
         <v>55</v>
       </c>
       <c r="BG6" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
         <v>28</v>
@@ -1739,10 +1739,10 @@
         <v>1.23</v>
       </c>
       <c r="J7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="L7" t="n">
         <v>1.26</v>
@@ -1751,28 +1751,28 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O7" t="n">
         <v>1.24</v>
       </c>
       <c r="P7" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="R7" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="S7" t="n">
         <v>2.46</v>
       </c>
       <c r="T7" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="V7" t="n">
         <v>5.3</v>
@@ -1835,62 +1835,62 @@
         <v>4.9</v>
       </c>
       <c r="AP7" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA7" t="n">
         <v>5.6</v>
       </c>
-      <c r="AU7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AY7" t="n">
+      <c r="BB7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD7" t="n">
         <v>6</v>
       </c>
-      <c r="AZ7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG7" t="n">
         <v>3.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -1933,10 +1933,10 @@
         <v>1.99</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>1.47</v>
@@ -1960,16 +1960,16 @@
         <v>1.19</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T8" t="n">
         <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="V8" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W8" t="n">
         <v>1.2</v>
@@ -2032,59 +2032,59 @@
         <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AR8" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY8" t="n">
         <v>6.4</v>
       </c>
-      <c r="AX8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AZ8" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA8" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
         <v>7.8</v>
       </c>
       <c r="BD8" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.02</v>
+        <v>1.79</v>
       </c>
       <c r="G9" t="n">
         <v>990</v>
       </c>
       <c r="H9" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="I9" t="n">
         <v>990</v>
       </c>
       <c r="J9" t="n">
-        <v>1.03</v>
+        <v>2.62</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>8.6</v>
       </c>
       <c r="L9" t="n">
         <v>1.01</v>
@@ -2184,7 +2184,7 @@
         <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AD9" t="n">
         <v>1000</v>
@@ -2223,62 +2223,62 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>1.55</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2321,28 +2321,28 @@
         <v>11.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L10" t="n">
         <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O10" t="n">
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R10" t="n">
         <v>1.27</v>
@@ -2351,10 +2351,10 @@
         <v>3.85</v>
       </c>
       <c r="T10" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="V10" t="n">
         <v>1.1</v>
@@ -2363,13 +2363,13 @@
         <v>3</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="Y10" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="Z10" t="n">
-        <v>110</v>
+        <v>480</v>
       </c>
       <c r="AA10" t="n">
         <v>1000</v>
@@ -2378,7 +2378,7 @@
         <v>7.4</v>
       </c>
       <c r="AC10" t="n">
-        <v>12.5</v>
+        <v>21</v>
       </c>
       <c r="AD10" t="n">
         <v>980</v>
@@ -2387,13 +2387,13 @@
         <v>1000</v>
       </c>
       <c r="AF10" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="AG10" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>980</v>
+        <v>180</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2402,77 +2402,77 @@
         <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>980</v>
+        <v>22</v>
       </c>
       <c r="AL10" t="n">
-        <v>65</v>
+        <v>380</v>
       </c>
       <c r="AM10" t="n">
         <v>1000</v>
       </c>
       <c r="AN10" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="AO10" t="n">
         <v>1000</v>
       </c>
       <c r="AP10" t="n">
-        <v>4.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>5.1</v>
+        <v>6.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AT10" t="n">
         <v>5.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>4</v>
+        <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="AW10" t="n">
-        <v>5.3</v>
+        <v>6.8</v>
       </c>
       <c r="AX10" t="n">
         <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA10" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BB10" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
         <v>7.2</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2509,10 +2509,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="I11" t="n">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="J11" t="n">
         <v>2.72</v>
@@ -2530,19 +2530,19 @@
         <v>1.25</v>
       </c>
       <c r="O11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="P11" t="n">
         <v>1.24</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="R11" t="n">
         <v>1.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="T11" t="n">
         <v>1.11</v>
@@ -2557,7 +2557,7 @@
         <v>1.44</v>
       </c>
       <c r="X11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Y11" t="n">
         <v>1000</v>
@@ -2614,49 +2614,49 @@
         <v>6.2</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AU11" t="n">
         <v>4.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.16</v>
+        <v>1.33</v>
       </c>
       <c r="BF11" t="n">
         <v>1.55</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2697,13 +2697,13 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="G12" t="n">
         <v>5.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="I12" t="n">
         <v>2.06</v>
@@ -2712,7 +2712,7 @@
         <v>3.2</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -2760,7 +2760,7 @@
         <v>19</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB12" t="n">
         <v>26</v>
@@ -2814,7 +2814,7 @@
         <v>4.4</v>
       </c>
       <c r="AS12" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>5</v>
@@ -2832,13 +2832,13 @@
         <v>4.7</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BB12" t="n">
         <v>5.2</v>
@@ -2847,10 +2847,10 @@
         <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="BF12" t="n">
         <v>5.2</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -2897,7 +2897,7 @@
         <v>990</v>
       </c>
       <c r="H13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
         <v>990</v>
@@ -3005,7 +3005,7 @@
         <v>1.71</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AS13" t="n">
         <v>1.77</v>
@@ -3017,7 +3017,7 @@
         <v>5.6</v>
       </c>
       <c r="AV13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AW13" t="n">
         <v>1.77</v>
@@ -3038,10 +3038,10 @@
         <v>6.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="BD13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BE13" t="n">
         <v>1.77</v>
@@ -3050,11 +3050,11 @@
         <v>3.85</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>1.33</v>
       </c>
       <c r="G14" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="H14" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="I14" t="n">
         <v>15.5</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="L14" t="n">
         <v>1.34</v>
@@ -3136,7 +3136,7 @@
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="X14" t="n">
         <v>14</v>
@@ -3148,7 +3148,7 @@
         <v>140</v>
       </c>
       <c r="AA14" t="n">
-        <v>960</v>
+        <v>940</v>
       </c>
       <c r="AB14" t="n">
         <v>7.8</v>
@@ -3181,7 +3181,7 @@
         <v>22</v>
       </c>
       <c r="AL14" t="n">
-        <v>330</v>
+        <v>65</v>
       </c>
       <c r="AM14" t="n">
         <v>390</v>
@@ -3190,19 +3190,19 @@
         <v>7.4</v>
       </c>
       <c r="AO14" t="n">
-        <v>770</v>
+        <v>740</v>
       </c>
       <c r="AP14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ14" t="n">
         <v>28</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS14" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AT14" t="n">
         <v>5.9</v>
@@ -3214,7 +3214,7 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AX14" t="n">
         <v>6</v>
@@ -3226,10 +3226,10 @@
         <v>34</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC14" t="n">
         <v>15.5</v>
@@ -3238,17 +3238,17 @@
         <v>50</v>
       </c>
       <c r="BE14" t="n">
-        <v>11.5</v>
+        <v>16</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3279,16 +3279,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="G15" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="I15" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="J15" t="n">
         <v>3.05</v>
@@ -3297,19 +3297,19 @@
         <v>3.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M15" t="n">
         <v>1.11</v>
       </c>
       <c r="N15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
         <v>1.45</v>
       </c>
       <c r="P15" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="Q15" t="n">
         <v>2.36</v>
@@ -3318,7 +3318,7 @@
         <v>1.23</v>
       </c>
       <c r="S15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="T15" t="n">
         <v>1.94</v>
@@ -3327,13 +3327,13 @@
         <v>1.92</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W15" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="X15" t="n">
-        <v>10.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y15" t="n">
         <v>13</v>
@@ -3342,16 +3342,16 @@
         <v>980</v>
       </c>
       <c r="AA15" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>980</v>
+        <v>15</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AE15" t="n">
         <v>980</v>
@@ -3360,13 +3360,13 @@
         <v>17</v>
       </c>
       <c r="AG15" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AH15" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>70</v>
+        <v>380</v>
       </c>
       <c r="AJ15" t="n">
         <v>980</v>
@@ -3375,74 +3375,74 @@
         <v>980</v>
       </c>
       <c r="AL15" t="n">
-        <v>60</v>
+        <v>980</v>
       </c>
       <c r="AM15" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AN15" t="n">
         <v>980</v>
       </c>
       <c r="AO15" t="n">
-        <v>65</v>
+        <v>160</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AR15" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.06</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="AU15" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>13</v>
+        <v>7.6</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.06</v>
+        <v>9.4</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="BC15" t="n">
-        <v>25</v>
+        <v>9.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BF15" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.06</v>
+        <v>9</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
         <v>1.61</v>
       </c>
       <c r="X16" t="n">
-        <v>90</v>
+        <v>17.5</v>
       </c>
       <c r="Y16" t="n">
         <v>1000</v>
@@ -3539,10 +3539,10 @@
         <v>1000</v>
       </c>
       <c r="AB16" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AC16" t="n">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AD16" t="n">
         <v>1000</v>
@@ -3563,7 +3563,7 @@
         <v>1000</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK16" t="n">
         <v>1000</v>
@@ -3590,7 +3590,7 @@
         <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="AT16" t="n">
         <v>4.4</v>
@@ -3599,10 +3599,10 @@
         <v>4.9</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>4</v>
+        <v>2.64</v>
       </c>
       <c r="AX16" t="n">
         <v>6.4</v>
@@ -3611,32 +3611,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.24</v>
+        <v>2.48</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="BE16" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3667,43 +3667,43 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="I17" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="J17" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K17" t="n">
         <v>4</v>
       </c>
       <c r="L17" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M17" t="n">
         <v>1.05</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O17" t="n">
         <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="Q17" t="n">
         <v>1.73</v>
       </c>
       <c r="R17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
         <v>2.84</v>
@@ -3715,10 +3715,10 @@
         <v>2.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="W17" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
@@ -3730,7 +3730,7 @@
         <v>19</v>
       </c>
       <c r="AA17" t="n">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="AB17" t="n">
         <v>18</v>
@@ -3745,10 +3745,10 @@
         <v>26</v>
       </c>
       <c r="AF17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AH17" t="n">
         <v>19.5</v>
@@ -3757,7 +3757,7 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AK17" t="n">
         <v>42</v>
@@ -3769,7 +3769,7 @@
         <v>90</v>
       </c>
       <c r="AN17" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO17" t="n">
         <v>18.5</v>
@@ -3796,7 +3796,7 @@
         <v>10</v>
       </c>
       <c r="AW17" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX17" t="n">
         <v>21</v>
@@ -3808,16 +3808,16 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BC17" t="n">
         <v>5.4</v>
       </c>
-      <c r="BB17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BD17" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE17" t="n">
         <v>5.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
         <v>1.71</v>
       </c>
       <c r="U18" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
         <v>1.35</v>
@@ -3978,7 +3978,7 @@
         <v>13</v>
       </c>
       <c r="AS18" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AT18" t="n">
         <v>9.199999999999999</v>
@@ -3990,7 +3990,7 @@
         <v>13</v>
       </c>
       <c r="AW18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX18" t="n">
         <v>12.5</v>
@@ -4011,7 +4011,7 @@
         <v>11.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE18" t="n">
         <v>5.1</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4061,13 +4061,13 @@
         <v>2.46</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K19" t="n">
         <v>4.1</v>
@@ -4088,7 +4088,7 @@
         <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R19" t="n">
         <v>1.41</v>
@@ -4121,7 +4121,7 @@
         <v>60</v>
       </c>
       <c r="AB19" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC19" t="n">
         <v>9.6</v>
@@ -4172,7 +4172,7 @@
         <v>20</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AT19" t="n">
         <v>9.4</v>
@@ -4208,7 +4208,7 @@
         <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4258,10 +4258,10 @@
         <v>2.16</v>
       </c>
       <c r="I20" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J20" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K20" t="n">
         <v>3.4</v>
@@ -4297,7 +4297,7 @@
         <v>1.89</v>
       </c>
       <c r="V20" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W20" t="n">
         <v>1.31</v>
@@ -4306,7 +4306,7 @@
         <v>12</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z20" t="n">
         <v>15.5</v>
@@ -4390,29 +4390,29 @@
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BC20" t="n">
         <v>5.6</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE20" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BG20" t="n">
         <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4443,16 +4443,16 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G21" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="I21" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J21" t="n">
         <v>3.5</v>
@@ -4467,34 +4467,34 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O21" t="n">
         <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="Q21" t="n">
         <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
         <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U21" t="n">
         <v>2.02</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W21" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>12.5</v>
@@ -4530,28 +4530,28 @@
         <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>190</v>
+        <v>75</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
       </c>
       <c r="AK21" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="AL21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM21" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO21" t="n">
         <v>75</v>
       </c>
       <c r="AP21" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AQ21" t="n">
         <v>13.5</v>
@@ -4560,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="AS21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -4572,19 +4572,19 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY21" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4596,17 +4596,17 @@
         <v>34</v>
       </c>
       <c r="BE21" t="n">
-        <v>28</v>
+        <v>18.5</v>
       </c>
       <c r="BF21" t="n">
         <v>14.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.85</v>
-      </c>
-      <c r="G22" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.9</v>
       </c>
       <c r="L22" t="n">
         <v>1.37</v>
@@ -4664,7 +4664,7 @@
         <v>4.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="P22" t="n">
         <v>2.1</v>
@@ -4676,16 +4676,16 @@
         <v>1.41</v>
       </c>
       <c r="S22" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="U22" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="W22" t="n">
         <v>1.34</v>
@@ -4712,7 +4712,7 @@
         <v>10.5</v>
       </c>
       <c r="AE22" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="AF22" t="n">
         <v>29</v>
@@ -4730,7 +4730,7 @@
         <v>75</v>
       </c>
       <c r="AK22" t="n">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="AL22" t="n">
         <v>55</v>
@@ -4760,7 +4760,7 @@
         <v>13.5</v>
       </c>
       <c r="AU22" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV22" t="n">
         <v>9.6</v>
@@ -4784,7 +4784,7 @@
         <v>13.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BD22" t="n">
         <v>12.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -4855,13 +4855,13 @@
         <v>1.08</v>
       </c>
       <c r="N23" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O23" t="n">
         <v>1.36</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
         <v>1.99</v>
@@ -4876,13 +4876,13 @@
         <v>1.84</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -4891,7 +4891,7 @@
         <v>16</v>
       </c>
       <c r="Z23" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AA23" t="n">
         <v>1000</v>
@@ -4903,28 +4903,28 @@
         <v>9.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AE23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG23" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI23" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ23" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AK23" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,7 +4933,7 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AO23" t="n">
         <v>1000</v>
@@ -4945,10 +4945,10 @@
         <v>7</v>
       </c>
       <c r="AR23" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT23" t="n">
         <v>7.4</v>
@@ -4960,7 +4960,7 @@
         <v>9</v>
       </c>
       <c r="AW23" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AX23" t="n">
         <v>9.6</v>
@@ -4969,32 +4969,32 @@
         <v>6.2</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BA23" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="BB23" t="n">
         <v>6.8</v>
       </c>
       <c r="BC23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BD23" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE23" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF23" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG23" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -5031,19 +5031,19 @@
         <v>3.4</v>
       </c>
       <c r="H24" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="I24" t="n">
         <v>2.86</v>
       </c>
       <c r="J24" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="K24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L24" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
@@ -5064,7 +5064,7 @@
         <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="T24" t="n">
         <v>1.81</v>
@@ -5076,16 +5076,16 @@
         <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
         <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -5094,49 +5094,49 @@
         <v>13.5</v>
       </c>
       <c r="AC24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP24" t="n">
         <v>7.8</v>
       </c>
-      <c r="AD24" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>110</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AR24" t="n">
         <v>7.6</v>
@@ -5154,7 +5154,7 @@
         <v>7</v>
       </c>
       <c r="AW24" t="n">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AX24" t="n">
         <v>15.5</v>
@@ -5163,7 +5163,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA24" t="n">
         <v>7.4</v>
@@ -5178,17 +5178,17 @@
         <v>7.2</v>
       </c>
       <c r="BE24" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG24" t="n">
         <v>22</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -5219,13 +5219,13 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G25" t="n">
         <v>2.1</v>
       </c>
       <c r="H25" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I25" t="n">
         <v>4.8</v>
@@ -5234,10 +5234,10 @@
         <v>3.35</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
@@ -5282,7 +5282,7 @@
         <v>980</v>
       </c>
       <c r="AA25" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="AB25" t="n">
         <v>8.199999999999999</v>
@@ -5294,37 +5294,37 @@
         <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>85</v>
+        <v>370</v>
       </c>
       <c r="AF25" t="n">
-        <v>980</v>
+        <v>23</v>
       </c>
       <c r="AG25" t="n">
         <v>11.5</v>
       </c>
       <c r="AH25" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI25" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AJ25" t="n">
         <v>30</v>
       </c>
       <c r="AK25" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AL25" t="n">
         <v>980</v>
       </c>
       <c r="AM25" t="n">
-        <v>170</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AO25" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AP25" t="n">
         <v>9.4</v>
@@ -5333,7 +5333,7 @@
         <v>11</v>
       </c>
       <c r="AR25" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AS25" t="n">
         <v>8.4</v>
@@ -5348,41 +5348,41 @@
         <v>15</v>
       </c>
       <c r="AW25" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>6.6</v>
+        <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE25" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BF25" t="n">
         <v>14.5</v>
       </c>
       <c r="BG25" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -5413,31 +5413,31 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="G26" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H26" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K26" t="n">
         <v>3.4</v>
       </c>
-      <c r="J26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K26" t="n">
-        <v>3.45</v>
-      </c>
       <c r="L26" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>1.4</v>
@@ -5461,22 +5461,22 @@
         <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X26" t="n">
         <v>11.5</v>
       </c>
       <c r="Y26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA26" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AB26" t="n">
         <v>11</v>
@@ -5491,7 +5491,7 @@
         <v>55</v>
       </c>
       <c r="AF26" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AG26" t="n">
         <v>12</v>
@@ -5503,19 +5503,19 @@
         <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>38</v>
+        <v>95</v>
       </c>
       <c r="AK26" t="n">
         <v>32</v>
       </c>
       <c r="AL26" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AM26" t="n">
         <v>130</v>
       </c>
       <c r="AN26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AO26" t="n">
         <v>50</v>
@@ -5527,7 +5527,7 @@
         <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS26" t="n">
         <v>20</v>
@@ -5536,28 +5536,28 @@
         <v>8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV26" t="n">
         <v>12</v>
       </c>
       <c r="AW26" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="AX26" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="BC26" t="n">
         <v>26</v>
@@ -5566,17 +5566,17 @@
         <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BF26" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="BG26" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G27" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="I27" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K27" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="L27" t="n">
         <v>1.22</v>
@@ -5637,130 +5637,130 @@
         <v>1.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="Q27" t="n">
         <v>1.41</v>
       </c>
       <c r="R27" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="S27" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
       <c r="T27" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="U27" t="n">
-        <v>2.8</v>
+        <v>2.94</v>
       </c>
       <c r="V27" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="W27" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="X27" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="Y27" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="Z27" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AA27" t="n">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="AB27" t="n">
-        <v>980</v>
+        <v>32</v>
       </c>
       <c r="AC27" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>980</v>
+        <v>80</v>
       </c>
       <c r="AF27" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AG27" t="n">
         <v>13</v>
       </c>
       <c r="AH27" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
         <v>980</v>
       </c>
       <c r="AK27" t="n">
-        <v>980</v>
+        <v>50</v>
       </c>
       <c r="AL27" t="n">
-        <v>980</v>
+        <v>65</v>
       </c>
       <c r="AM27" t="n">
-        <v>980</v>
+        <v>580</v>
       </c>
       <c r="AN27" t="n">
         <v>9.6</v>
       </c>
       <c r="AO27" t="n">
-        <v>19</v>
+        <v>980</v>
       </c>
       <c r="AP27" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="AS27" t="n">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU27" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV27" t="n">
         <v>11</v>
       </c>
       <c r="AW27" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="AX27" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AY27" t="n">
         <v>10</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>5.9</v>
+        <v>16</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="BE27" t="n">
-        <v>6.4</v>
+        <v>20</v>
       </c>
       <c r="BF27" t="n">
         <v>7.4</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
         <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="I28" t="n">
         <v>1.63</v>
@@ -5816,10 +5816,10 @@
         <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L28" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M28" t="n">
         <v>1.11</v>
@@ -5843,10 +5843,10 @@
         <v>4.7</v>
       </c>
       <c r="T28" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="V28" t="n">
         <v>2.56</v>
@@ -5858,13 +5858,13 @@
         <v>10</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="Z28" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AA28" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="AB28" t="n">
         <v>38</v>
@@ -5876,13 +5876,13 @@
         <v>11.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AF28" t="n">
         <v>420</v>
       </c>
       <c r="AG28" t="n">
-        <v>980</v>
+        <v>95</v>
       </c>
       <c r="AH28" t="n">
         <v>980</v>
@@ -5894,13 +5894,13 @@
         <v>470</v>
       </c>
       <c r="AK28" t="n">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="AL28" t="n">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AM28" t="n">
-        <v>360</v>
+        <v>580</v>
       </c>
       <c r="AN28" t="n">
         <v>500</v>
@@ -5909,10 +5909,10 @@
         <v>36</v>
       </c>
       <c r="AP28" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="AR28" t="n">
         <v>6.6</v>
@@ -5930,10 +5930,10 @@
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="AX28" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5942,29 +5942,29 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BB28" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC28" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BD28" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="BE28" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BF28" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BG28" t="n">
         <v>11.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="I29" t="n">
         <v>2.24</v>
@@ -6010,10 +6010,10 @@
         <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L29" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
@@ -6031,7 +6031,7 @@
         <v>2.36</v>
       </c>
       <c r="R29" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S29" t="n">
         <v>4.7</v>
@@ -6055,37 +6055,37 @@
         <v>7.8</v>
       </c>
       <c r="Z29" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AA29" t="n">
-        <v>980</v>
+        <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>14.5</v>
+        <v>23</v>
       </c>
       <c r="AC29" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>980</v>
+        <v>21</v>
       </c>
       <c r="AE29" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF29" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AG29" t="n">
         <v>34</v>
       </c>
       <c r="AH29" t="n">
-        <v>980</v>
+        <v>60</v>
       </c>
       <c r="AI29" t="n">
         <v>980</v>
       </c>
       <c r="AJ29" t="n">
-        <v>120</v>
+        <v>900</v>
       </c>
       <c r="AK29" t="n">
         <v>370</v>
@@ -6094,16 +6094,16 @@
         <v>380</v>
       </c>
       <c r="AM29" t="n">
-        <v>190</v>
+        <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>260</v>
+        <v>500</v>
       </c>
       <c r="AO29" t="n">
         <v>980</v>
       </c>
       <c r="AP29" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AQ29" t="n">
         <v>6.4</v>
@@ -6124,10 +6124,10 @@
         <v>6.4</v>
       </c>
       <c r="AW29" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY29" t="n">
         <v>15</v>
@@ -6136,29 +6136,29 @@
         <v>11.5</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB29" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BC29" t="n">
-        <v>8.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BG29" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -6246,13 +6246,13 @@
         <v>10.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="n">
         <v>980</v>
       </c>
       <c r="AA30" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB30" t="n">
         <v>6.8</v>
@@ -6261,10 +6261,10 @@
         <v>8</v>
       </c>
       <c r="AD30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE30" t="n">
-        <v>110</v>
+        <v>240</v>
       </c>
       <c r="AF30" t="n">
         <v>11.5</v>
@@ -6273,22 +6273,22 @@
         <v>12</v>
       </c>
       <c r="AH30" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="AI30" t="n">
-        <v>120</v>
+        <v>260</v>
       </c>
       <c r="AJ30" t="n">
-        <v>980</v>
+        <v>26</v>
       </c>
       <c r="AK30" t="n">
         <v>32</v>
       </c>
       <c r="AL30" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="AM30" t="n">
-        <v>220</v>
+        <v>580</v>
       </c>
       <c r="AN30" t="n">
         <v>26</v>
@@ -6306,10 +6306,10 @@
         <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AU30" t="n">
         <v>6.6</v>
@@ -6318,7 +6318,7 @@
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX30" t="n">
         <v>9.4</v>
@@ -6330,29 +6330,29 @@
         <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB30" t="n">
         <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD30" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BF30" t="n">
         <v>17</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -6392,10 +6392,10 @@
         <v>4.9</v>
       </c>
       <c r="I31" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="J31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K31" t="n">
         <v>3.6</v>
@@ -6428,7 +6428,7 @@
         <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
         <v>1.21</v>
@@ -6443,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="Z31" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA31" t="n">
         <v>1000</v>
@@ -6455,7 +6455,7 @@
         <v>9</v>
       </c>
       <c r="AD31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
@@ -6473,13 +6473,13 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>90</v>
+        <v>48</v>
       </c>
       <c r="AK31" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AL31" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AM31" t="n">
         <v>1000</v>
@@ -6497,10 +6497,10 @@
         <v>7</v>
       </c>
       <c r="AR31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT31" t="n">
         <v>5.4</v>
@@ -6509,10 +6509,10 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW31" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX31" t="n">
         <v>8.199999999999999</v>
@@ -6521,32 +6521,32 @@
         <v>8.4</v>
       </c>
       <c r="AZ31" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB31" t="n">
         <v>17.5</v>
       </c>
       <c r="BC31" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BE31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF31" t="n">
         <v>15.5</v>
       </c>
       <c r="BG31" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
         <v>6.6</v>
       </c>
       <c r="I32" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J32" t="n">
         <v>3.7</v>
@@ -6607,7 +6607,7 @@
         <v>1.37</v>
       </c>
       <c r="P32" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q32" t="n">
         <v>2.12</v>
@@ -6637,7 +6637,7 @@
         <v>34</v>
       </c>
       <c r="Z32" t="n">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AA32" t="n">
         <v>1000</v>
@@ -6649,7 +6649,7 @@
         <v>10.5</v>
       </c>
       <c r="AD32" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE32" t="n">
         <v>1000</v>
@@ -6661,7 +6661,7 @@
         <v>12</v>
       </c>
       <c r="AH32" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AI32" t="n">
         <v>1000</v>
@@ -6670,10 +6670,10 @@
         <v>27</v>
       </c>
       <c r="AK32" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AL32" t="n">
-        <v>980</v>
+        <v>300</v>
       </c>
       <c r="AM32" t="n">
         <v>1000</v>
@@ -6691,10 +6691,10 @@
         <v>15</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AS32" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT32" t="n">
         <v>5.6</v>
@@ -6706,19 +6706,19 @@
         <v>4.6</v>
       </c>
       <c r="AW32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AX32" t="n">
-        <v>6.8</v>
+        <v>4.4</v>
       </c>
       <c r="AY32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="AZ32" t="n">
-        <v>18.5</v>
+        <v>4.5</v>
       </c>
       <c r="BA32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BB32" t="n">
         <v>12</v>
@@ -6727,10 +6727,10 @@
         <v>10</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BF32" t="n">
         <v>9</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -6783,16 +6783,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L33" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="M33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N33" t="n">
         <v>3.1</v>
@@ -6801,13 +6801,13 @@
         <v>1.4</v>
       </c>
       <c r="P33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q33" t="n">
         <v>2.18</v>
       </c>
       <c r="R33" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S33" t="n">
         <v>4.1</v>
@@ -6816,22 +6816,22 @@
         <v>2.3</v>
       </c>
       <c r="U33" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="V33" t="n">
         <v>1.12</v>
       </c>
       <c r="W33" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X33" t="n">
         <v>14.5</v>
       </c>
       <c r="Y33" t="n">
-        <v>980</v>
+        <v>46</v>
       </c>
       <c r="Z33" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AA33" t="n">
         <v>1000</v>
@@ -6846,7 +6846,7 @@
         <v>980</v>
       </c>
       <c r="AE33" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AF33" t="n">
         <v>9</v>
@@ -6858,7 +6858,7 @@
         <v>980</v>
       </c>
       <c r="AI33" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AJ33" t="n">
         <v>16</v>
@@ -6867,7 +6867,7 @@
         <v>24</v>
       </c>
       <c r="AL33" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
@@ -6879,62 +6879,62 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR33" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT33" t="n">
         <v>5.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AV33" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX33" t="n">
         <v>6.8</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AZ33" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BB33" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BC33" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF33" t="n">
         <v>9.6</v>
       </c>
       <c r="BG33" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -6956,179 +6956,179 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Atalanta B</t>
+          <t>Nuovo Campobasso</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="G34" t="n">
-        <v>2.38</v>
+        <v>4.8</v>
       </c>
       <c r="H34" t="n">
-        <v>3.55</v>
+        <v>2.04</v>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>2.2</v>
       </c>
       <c r="J34" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="L34" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="M34" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="N34" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="P34" t="n">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.93</v>
+        <v>2.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="S34" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
       <c r="T34" t="n">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="U34" t="n">
-        <v>2.1</v>
+        <v>1.79</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="W34" t="n">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="X34" t="n">
-        <v>15.5</v>
+        <v>10</v>
       </c>
       <c r="Y34" t="n">
-        <v>27</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z34" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AA34" t="n">
-        <v>900</v>
+        <v>34</v>
       </c>
       <c r="AB34" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC34" t="n">
-        <v>12</v>
+        <v>8.6</v>
       </c>
       <c r="AD34" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="AE34" t="n">
-        <v>170</v>
+        <v>34</v>
       </c>
       <c r="AF34" t="n">
+        <v>40</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH34" t="n">
         <v>28</v>
       </c>
-      <c r="AG34" t="n">
-        <v>17</v>
-      </c>
-      <c r="AH34" t="n">
+      <c r="AI34" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>95</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO34" t="n">
         <v>32</v>
       </c>
-      <c r="AI34" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>80</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>1000</v>
-      </c>
       <c r="AP34" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ34" t="n">
-        <v>11.5</v>
+        <v>6.2</v>
       </c>
       <c r="AR34" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="AS34" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.6</v>
+        <v>10.5</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
       </c>
       <c r="AV34" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW34" t="n">
-        <v>7.4</v>
+        <v>20</v>
       </c>
       <c r="AX34" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="AY34" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AZ34" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BA34" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="BB34" t="n">
-        <v>6.8</v>
+        <v>5.4</v>
       </c>
       <c r="BC34" t="n">
-        <v>6.8</v>
+        <v>5.3</v>
       </c>
       <c r="BD34" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="BE34" t="n">
-        <v>9</v>
+        <v>5.4</v>
       </c>
       <c r="BF34" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.4</v>
+        <v>18</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -7150,179 +7150,179 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Nuovo Campobasso</t>
+          <t>Atalanta B</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>4.2</v>
+        <v>2.12</v>
       </c>
       <c r="G35" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="H35" t="n">
-        <v>2.04</v>
+        <v>3.55</v>
       </c>
       <c r="I35" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>3.15</v>
       </c>
       <c r="K35" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="L35" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="M35" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="N35" t="n">
-        <v>2.72</v>
+        <v>3.6</v>
       </c>
       <c r="O35" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="P35" t="n">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.44</v>
+        <v>1.93</v>
       </c>
       <c r="R35" t="n">
-        <v>1.21</v>
+        <v>1.34</v>
       </c>
       <c r="S35" t="n">
-        <v>4.8</v>
+        <v>3.3</v>
       </c>
       <c r="T35" t="n">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="U35" t="n">
-        <v>1.79</v>
+        <v>2.1</v>
       </c>
       <c r="V35" t="n">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1.26</v>
+        <v>1.76</v>
       </c>
       <c r="X35" t="n">
-        <v>10</v>
+        <v>15.5</v>
       </c>
       <c r="Y35" t="n">
-        <v>8.199999999999999</v>
+        <v>27</v>
       </c>
       <c r="Z35" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AA35" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB35" t="n">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>8.6</v>
+        <v>12</v>
       </c>
       <c r="AD35" t="n">
-        <v>13.5</v>
+        <v>500</v>
       </c>
       <c r="AE35" t="n">
-        <v>34</v>
+        <v>170</v>
       </c>
       <c r="AF35" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AG35" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>65</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS35" t="n">
         <v>23</v>
       </c>
-      <c r="AH35" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>32</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>19.5</v>
-      </c>
       <c r="AT35" t="n">
-        <v>10.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU35" t="n">
         <v>6.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AW35" t="n">
-        <v>20</v>
+        <v>7.6</v>
       </c>
       <c r="AX35" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AY35" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="AZ35" t="n">
-        <v>5</v>
+        <v>10.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>4.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB35" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BC35" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD35" t="n">
-        <v>5.1</v>
+        <v>7.6</v>
       </c>
       <c r="BE35" t="n">
-        <v>5.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF35" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BG35" t="n">
-        <v>18</v>
+        <v>7.6</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="H36" t="n">
         <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J36" t="n">
         <v>4.6</v>
       </c>
       <c r="K36" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L36" t="n">
         <v>1.33</v>
@@ -7401,10 +7401,10 @@
         <v>2.06</v>
       </c>
       <c r="V36" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="X36" t="n">
         <v>21</v>
@@ -7425,13 +7425,13 @@
         <v>11.5</v>
       </c>
       <c r="AD36" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE36" t="n">
         <v>230</v>
       </c>
       <c r="AF36" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG36" t="n">
         <v>10</v>
@@ -7446,13 +7446,13 @@
         <v>14.5</v>
       </c>
       <c r="AK36" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AL36" t="n">
         <v>34</v>
       </c>
       <c r="AM36" t="n">
-        <v>130</v>
+        <v>390</v>
       </c>
       <c r="AN36" t="n">
         <v>7.2</v>
@@ -7467,7 +7467,7 @@
         <v>22</v>
       </c>
       <c r="AR36" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AS36" t="n">
         <v>36</v>
@@ -7476,13 +7476,13 @@
         <v>8.6</v>
       </c>
       <c r="AU36" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV36" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW36" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="AX36" t="n">
         <v>8.6</v>
@@ -7503,7 +7503,7 @@
         <v>13</v>
       </c>
       <c r="BD36" t="n">
-        <v>16</v>
+        <v>9.6</v>
       </c>
       <c r="BE36" t="n">
         <v>29</v>
@@ -7512,11 +7512,11 @@
         <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -7556,10 +7556,10 @@
         <v>2.2</v>
       </c>
       <c r="I37" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J37" t="n">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="K37" t="n">
         <v>3.75</v>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O37" t="n">
         <v>1.37</v>
@@ -7580,22 +7580,22 @@
         <v>1.68</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
       </c>
       <c r="S37" t="n">
-        <v>1.93</v>
+        <v>2.18</v>
       </c>
       <c r="T37" t="n">
-        <v>1.96</v>
+        <v>1.58</v>
       </c>
       <c r="U37" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V37" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="W37" t="n">
         <v>1.3</v>
@@ -7634,19 +7634,19 @@
         <v>27</v>
       </c>
       <c r="AI37" t="n">
+        <v>150</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>500</v>
+      </c>
+      <c r="AK37" t="n">
         <v>160</v>
       </c>
-      <c r="AJ37" t="n">
-        <v>440</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>170</v>
-      </c>
       <c r="AL37" t="n">
-        <v>250</v>
+        <v>190</v>
       </c>
       <c r="AM37" t="n">
-        <v>430</v>
+        <v>580</v>
       </c>
       <c r="AN37" t="n">
         <v>1000</v>
@@ -7655,7 +7655,7 @@
         <v>30</v>
       </c>
       <c r="AP37" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ37" t="n">
         <v>5.1</v>
@@ -7664,22 +7664,22 @@
         <v>10</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AT37" t="n">
         <v>10</v>
       </c>
       <c r="AU37" t="n">
-        <v>4.4</v>
+        <v>5.7</v>
       </c>
       <c r="AV37" t="n">
         <v>6.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="AX37" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AY37" t="n">
         <v>8.4</v>
@@ -7691,13 +7691,13 @@
         <v>20</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BC37" t="n">
         <v>18</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="BE37" t="n">
         <v>26</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -7744,55 +7744,55 @@
         <v>2.76</v>
       </c>
       <c r="G38" t="n">
-        <v>2.98</v>
+        <v>2.88</v>
       </c>
       <c r="H38" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I38" t="n">
         <v>2.96</v>
       </c>
       <c r="J38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K38" t="n">
         <v>3.45</v>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="O38" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="P38" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R38" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S38" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="T38" t="n">
         <v>2.02</v>
       </c>
       <c r="U38" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="V38" t="n">
         <v>1.51</v>
       </c>
       <c r="W38" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="X38" t="n">
         <v>10</v>
@@ -7801,31 +7801,31 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA38" t="n">
         <v>50</v>
       </c>
       <c r="AB38" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD38" t="n">
         <v>13</v>
       </c>
       <c r="AE38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF38" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG38" t="n">
         <v>13.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI38" t="n">
         <v>60</v>
@@ -7834,19 +7834,19 @@
         <v>48</v>
       </c>
       <c r="AK38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL38" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AM38" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN38" t="n">
         <v>42</v>
       </c>
       <c r="AO38" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AP38" t="n">
         <v>9.199999999999999</v>
@@ -7858,19 +7858,19 @@
         <v>15.5</v>
       </c>
       <c r="AS38" t="n">
-        <v>11.5</v>
+        <v>42</v>
       </c>
       <c r="AT38" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV38" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW38" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AX38" t="n">
         <v>15.5</v>
@@ -7879,32 +7879,32 @@
         <v>12</v>
       </c>
       <c r="AZ38" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="BA38" t="n">
-        <v>11.5</v>
+        <v>50</v>
       </c>
       <c r="BB38" t="n">
         <v>29</v>
       </c>
       <c r="BC38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD38" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BE38" t="n">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="BF38" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="BG38" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>2.3</v>
       </c>
       <c r="G39" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H39" t="n">
         <v>3.7</v>
@@ -7965,7 +7965,7 @@
         <v>1.43</v>
       </c>
       <c r="P39" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
         <v>2.3</v>
@@ -7980,7 +7980,7 @@
         <v>1.97</v>
       </c>
       <c r="U39" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V39" t="n">
         <v>1.36</v>
@@ -7998,10 +7998,10 @@
         <v>24</v>
       </c>
       <c r="AA39" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AB39" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC39" t="n">
         <v>7.2</v>
@@ -8010,7 +8010,7 @@
         <v>15.5</v>
       </c>
       <c r="AE39" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF39" t="n">
         <v>13</v>
@@ -8019,19 +8019,19 @@
         <v>11.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI39" t="n">
         <v>65</v>
       </c>
       <c r="AJ39" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK39" t="n">
         <v>27</v>
       </c>
       <c r="AL39" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM39" t="n">
         <v>130</v>
@@ -8046,16 +8046,16 @@
         <v>10</v>
       </c>
       <c r="AQ39" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR39" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS39" t="n">
         <v>50</v>
       </c>
       <c r="AT39" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU39" t="n">
         <v>6.8</v>
@@ -8082,13 +8082,13 @@
         <v>27</v>
       </c>
       <c r="BC39" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD39" t="n">
         <v>40</v>
       </c>
       <c r="BE39" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF39" t="n">
         <v>21</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -8129,16 +8129,16 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.96</v>
       </c>
-      <c r="G40" t="n">
-        <v>1.97</v>
-      </c>
       <c r="H40" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I40" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="J40" t="n">
         <v>3.55</v>
@@ -8150,16 +8150,16 @@
         <v>1.49</v>
       </c>
       <c r="M40" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N40" t="n">
         <v>3.25</v>
       </c>
       <c r="O40" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="P40" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q40" t="n">
         <v>2.28</v>
@@ -8174,13 +8174,13 @@
         <v>2.04</v>
       </c>
       <c r="U40" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V40" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W40" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X40" t="n">
         <v>11</v>
@@ -8195,7 +8195,7 @@
         <v>120</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC40" t="n">
         <v>7.8</v>
@@ -8207,7 +8207,7 @@
         <v>70</v>
       </c>
       <c r="AF40" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG40" t="n">
         <v>10.5</v>
@@ -8219,19 +8219,19 @@
         <v>85</v>
       </c>
       <c r="AJ40" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK40" t="n">
         <v>23</v>
       </c>
       <c r="AL40" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM40" t="n">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="AN40" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AO40" t="n">
         <v>90</v>
@@ -8258,7 +8258,7 @@
         <v>17.5</v>
       </c>
       <c r="AW40" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AX40" t="n">
         <v>10</v>
@@ -8267,10 +8267,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA40" t="n">
-        <v>36</v>
+        <v>70</v>
       </c>
       <c r="BB40" t="n">
         <v>20</v>
@@ -8285,14 +8285,14 @@
         <v>75</v>
       </c>
       <c r="BF40" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG40" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -8323,22 +8323,22 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G41" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="H41" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
         <v>4.2</v>
       </c>
       <c r="J41" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K41" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L41" t="n">
         <v>1.46</v>
@@ -8347,16 +8347,16 @@
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O41" t="n">
         <v>1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R41" t="n">
         <v>1.31</v>
@@ -8371,10 +8371,10 @@
         <v>2.04</v>
       </c>
       <c r="V41" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W41" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="X41" t="n">
         <v>12</v>
@@ -8389,16 +8389,16 @@
         <v>85</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AC41" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD41" t="n">
         <v>16.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF41" t="n">
         <v>12.5</v>
@@ -8407,43 +8407,43 @@
         <v>10.5</v>
       </c>
       <c r="AH41" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN41" t="n">
         <v>19</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>70</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>25</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>48</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>130</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>21</v>
       </c>
       <c r="AO41" t="n">
         <v>65</v>
       </c>
       <c r="AP41" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ41" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS41" t="n">
         <v>48</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU41" t="n">
         <v>7</v>
@@ -8455,13 +8455,13 @@
         <v>36</v>
       </c>
       <c r="AX41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY41" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ41" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA41" t="n">
         <v>44</v>
@@ -8470,7 +8470,7 @@
         <v>24</v>
       </c>
       <c r="BC41" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD41" t="n">
         <v>36</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         <v>3.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
@@ -8556,7 +8556,7 @@
         <v>1.27</v>
       </c>
       <c r="S42" t="n">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="T42" t="n">
         <v>1.84</v>
@@ -8580,34 +8580,34 @@
         <v>34</v>
       </c>
       <c r="AA42" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB42" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC42" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD42" t="n">
-        <v>19.5</v>
+        <v>17</v>
       </c>
       <c r="AE42" t="n">
         <v>65</v>
       </c>
       <c r="AF42" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AG42" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH42" t="n">
         <v>21</v>
       </c>
       <c r="AI42" t="n">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="AJ42" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AK42" t="n">
         <v>32</v>
@@ -8616,7 +8616,7 @@
         <v>55</v>
       </c>
       <c r="AM42" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN42" t="n">
         <v>26</v>
@@ -8631,22 +8631,22 @@
         <v>10.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.7</v>
+        <v>6.2</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
       </c>
       <c r="AU42" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV42" t="n">
         <v>13.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AX42" t="n">
         <v>11</v>
@@ -8658,29 +8658,29 @@
         <v>16</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
       <c r="BB42" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BC42" t="n">
         <v>21</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="BE42" t="n">
-        <v>4.8</v>
+        <v>6.2</v>
       </c>
       <c r="BF42" t="n">
         <v>17.5</v>
       </c>
       <c r="BG42" t="n">
-        <v>4.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         <v>3.7</v>
       </c>
       <c r="L43" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -8771,7 +8771,7 @@
         <v>16</v>
       </c>
       <c r="Z43" t="n">
-        <v>980</v>
+        <v>130</v>
       </c>
       <c r="AA43" t="n">
         <v>190</v>
@@ -8807,10 +8807,10 @@
         <v>24</v>
       </c>
       <c r="AL43" t="n">
-        <v>980</v>
+        <v>290</v>
       </c>
       <c r="AM43" t="n">
-        <v>200</v>
+        <v>580</v>
       </c>
       <c r="AN43" t="n">
         <v>18.5</v>
@@ -8825,7 +8825,7 @@
         <v>12.5</v>
       </c>
       <c r="AR43" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AS43" t="n">
         <v>8.4</v>
@@ -8840,7 +8840,7 @@
         <v>18</v>
       </c>
       <c r="AW43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX43" t="n">
         <v>8.800000000000001</v>
@@ -8852,7 +8852,7 @@
         <v>19.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB43" t="n">
         <v>18</v>
@@ -8861,10 +8861,10 @@
         <v>19.5</v>
       </c>
       <c r="BD43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BE43" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="BF43" t="n">
         <v>12.5</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -8971,16 +8971,16 @@
         <v>95</v>
       </c>
       <c r="AB44" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="AC44" t="n">
         <v>7.6</v>
       </c>
       <c r="AD44" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="AE44" t="n">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="AF44" t="n">
         <v>70</v>
@@ -9004,7 +9004,7 @@
         <v>1000</v>
       </c>
       <c r="AM44" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN44" t="n">
         <v>1000</v>
@@ -9022,7 +9022,7 @@
         <v>10.5</v>
       </c>
       <c r="AS44" t="n">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="AT44" t="n">
         <v>9</v>
@@ -9046,29 +9046,29 @@
         <v>11.5</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BB44" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BC44" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD44" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF44" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BG44" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>3.95</v>
       </c>
       <c r="G45" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="H45" t="n">
         <v>2.26</v>
@@ -9114,7 +9114,7 @@
         <v>2.92</v>
       </c>
       <c r="K45" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L45" t="n">
         <v>1.44</v>
@@ -9123,7 +9123,7 @@
         <v>1.11</v>
       </c>
       <c r="N45" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="O45" t="n">
         <v>1.44</v>
@@ -9147,10 +9147,10 @@
         <v>1.98</v>
       </c>
       <c r="V45" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W45" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X45" t="n">
         <v>19</v>
@@ -9165,10 +9165,10 @@
         <v>900</v>
       </c>
       <c r="AB45" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="AC45" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD45" t="n">
         <v>23</v>
@@ -9195,13 +9195,13 @@
         <v>250</v>
       </c>
       <c r="AL45" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AM45" t="n">
         <v>500</v>
       </c>
       <c r="AN45" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO45" t="n">
         <v>980</v>
@@ -9228,7 +9228,7 @@
         <v>7</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX45" t="n">
         <v>10.5</v>
@@ -9240,19 +9240,19 @@
         <v>9</v>
       </c>
       <c r="BA45" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC45" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BB45" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BD45" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BE45" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BF45" t="n">
         <v>8.4</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -9293,52 +9293,52 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G46" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I46" t="n">
         <v>8.4</v>
       </c>
       <c r="J46" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K46" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
       </c>
       <c r="N46" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O46" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P46" t="n">
         <v>2</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.97</v>
+        <v>1.93</v>
       </c>
       <c r="R46" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T46" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="V46" t="n">
         <v>1.13</v>
@@ -9350,34 +9350,34 @@
         <v>15.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="Z46" t="n">
-        <v>480</v>
+        <v>170</v>
       </c>
       <c r="AA46" t="n">
         <v>280</v>
       </c>
       <c r="AB46" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AC46" t="n">
         <v>10.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AE46" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AF46" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG46" t="n">
         <v>10.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>980</v>
+        <v>42</v>
       </c>
       <c r="AI46" t="n">
         <v>140</v>
@@ -9386,10 +9386,10 @@
         <v>14</v>
       </c>
       <c r="AK46" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AL46" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AM46" t="n">
         <v>200</v>
@@ -9398,25 +9398,25 @@
         <v>9</v>
       </c>
       <c r="AO46" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AP46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ46" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AR46" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS46" t="n">
         <v>48</v>
       </c>
       <c r="AT46" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU46" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AV46" t="n">
         <v>18.5</v>
@@ -9425,13 +9425,13 @@
         <v>40</v>
       </c>
       <c r="AX46" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY46" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ46" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="BA46" t="n">
         <v>40</v>
@@ -9446,7 +9446,7 @@
         <v>32</v>
       </c>
       <c r="BE46" t="n">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="BF46" t="n">
         <v>8</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>1.41</v>
       </c>
       <c r="G47" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="H47" t="n">
         <v>9.800000000000001</v>
@@ -9520,7 +9520,7 @@
         <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="R47" t="n">
         <v>1.38</v>
@@ -9535,7 +9535,7 @@
         <v>1.87</v>
       </c>
       <c r="V47" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W47" t="n">
         <v>3.15</v>
@@ -9559,7 +9559,7 @@
         <v>11.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AE47" t="n">
         <v>210</v>
@@ -9580,10 +9580,10 @@
         <v>13</v>
       </c>
       <c r="AK47" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>980</v>
       </c>
       <c r="AM47" t="n">
         <v>200</v>
@@ -9595,13 +9595,13 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ47" t="n">
         <v>12.5</v>
       </c>
       <c r="AR47" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS47" t="n">
         <v>9.199999999999999</v>
@@ -9616,7 +9616,7 @@
         <v>14.5</v>
       </c>
       <c r="AW47" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX47" t="n">
         <v>7</v>
@@ -9625,7 +9625,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ47" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BA47" t="n">
         <v>8.800000000000001</v>
@@ -9640,17 +9640,17 @@
         <v>19.5</v>
       </c>
       <c r="BE47" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BF47" t="n">
         <v>5.9</v>
       </c>
       <c r="BG47" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -9681,61 +9681,61 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="G48" t="n">
-        <v>1.71</v>
+        <v>1.96</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I48" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="J48" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K48" t="n">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="L48" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="M48" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N48" t="n">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="O48" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="P48" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.86</v>
+        <v>2.06</v>
       </c>
       <c r="R48" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="S48" t="n">
-        <v>2.98</v>
+        <v>3.6</v>
       </c>
       <c r="T48" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U48" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="V48" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W48" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="X48" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y48" t="n">
         <v>1000</v>
@@ -9747,7 +9747,7 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AC48" t="n">
         <v>14</v>
@@ -9762,7 +9762,7 @@
         <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AH48" t="n">
         <v>1000</v>
@@ -9783,68 +9783,68 @@
         <v>1000</v>
       </c>
       <c r="AN48" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AO48" t="n">
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="AQ48" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="AS48" t="n">
-        <v>2.2</v>
+        <v>3.35</v>
       </c>
       <c r="AT48" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AU48" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="AV48" t="n">
-        <v>2.68</v>
+        <v>4.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="AX48" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AY48" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AZ48" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="BA48" t="n">
-        <v>2.18</v>
+        <v>2.98</v>
       </c>
       <c r="BB48" t="n">
-        <v>2.64</v>
+        <v>5.1</v>
       </c>
       <c r="BC48" t="n">
-        <v>2.66</v>
+        <v>4.4</v>
       </c>
       <c r="BD48" t="n">
-        <v>2.12</v>
+        <v>2.98</v>
       </c>
       <c r="BE48" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="BF48" t="n">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="BG48" t="n">
-        <v>1.84</v>
+        <v>5.3</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -9875,22 +9875,22 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="H49" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="I49" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="J49" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K49" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="L49" t="n">
         <v>1.01</v>
@@ -9899,7 +9899,7 @@
         <v>1.11</v>
       </c>
       <c r="N49" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O49" t="n">
         <v>1.47</v>
@@ -9920,13 +9920,13 @@
         <v>1.98</v>
       </c>
       <c r="U49" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V49" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="X49" t="n">
         <v>10.5</v>
@@ -9941,7 +9941,7 @@
         <v>48</v>
       </c>
       <c r="AB49" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC49" t="n">
         <v>8.6</v>
@@ -9992,10 +9992,10 @@
         <v>13.5</v>
       </c>
       <c r="AS49" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU49" t="n">
         <v>6.2</v>
@@ -10004,7 +10004,7 @@
         <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AX49" t="n">
         <v>17.5</v>
@@ -10016,29 +10016,29 @@
         <v>18</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BB49" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BC49" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BD49" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BF49" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G50" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="H50" t="n">
         <v>5.8</v>
       </c>
       <c r="I50" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="J50" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K50" t="n">
         <v>3.8</v>
@@ -10096,10 +10096,10 @@
         <v>3.2</v>
       </c>
       <c r="O50" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P50" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q50" t="n">
         <v>1.92</v>
@@ -10108,7 +10108,7 @@
         <v>1.28</v>
       </c>
       <c r="S50" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
@@ -10117,13 +10117,13 @@
         <v>1.81</v>
       </c>
       <c r="V50" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W50" t="n">
         <v>2.26</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y50" t="n">
         <v>1000</v>
@@ -10147,7 +10147,7 @@
         <v>130</v>
       </c>
       <c r="AF50" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AG50" t="n">
         <v>12.5</v>
@@ -10171,16 +10171,16 @@
         <v>190</v>
       </c>
       <c r="AN50" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AO50" t="n">
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AR50" t="n">
         <v>4</v>
@@ -10192,31 +10192,31 @@
         <v>6.2</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AV50" t="n">
         <v>3.75</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX50" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="AY50" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AZ50" t="n">
         <v>3.75</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB50" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BC50" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BD50" t="n">
         <v>4</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
         <v>3.6</v>
       </c>
       <c r="H51" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I51" t="n">
         <v>2.64</v>
@@ -10287,22 +10287,22 @@
         <v>1.11</v>
       </c>
       <c r="N51" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="O51" t="n">
         <v>1.48</v>
       </c>
       <c r="P51" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R51" t="n">
         <v>1.22</v>
       </c>
       <c r="S51" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="T51" t="n">
         <v>2</v>
@@ -10311,10 +10311,10 @@
         <v>1.86</v>
       </c>
       <c r="V51" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W51" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X51" t="n">
         <v>11.5</v>
@@ -10407,13 +10407,13 @@
         <v>4.5</v>
       </c>
       <c r="BB51" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BC51" t="n">
         <v>4.5</v>
       </c>
       <c r="BD51" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE51" t="n">
         <v>4.7</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>
@@ -10457,10 +10457,10 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G52" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H52" t="n">
         <v>2.9</v>
@@ -10469,10 +10469,10 @@
         <v>3.2</v>
       </c>
       <c r="J52" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="K52" t="n">
-        <v>3.75</v>
+        <v>3.45</v>
       </c>
       <c r="L52" t="n">
         <v>1.49</v>
@@ -10481,22 +10481,22 @@
         <v>1.13</v>
       </c>
       <c r="N52" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="O52" t="n">
         <v>1.55</v>
       </c>
       <c r="P52" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.64</v>
+        <v>2.56</v>
       </c>
       <c r="R52" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S52" t="n">
-        <v>4.8</v>
+        <v>5.3</v>
       </c>
       <c r="T52" t="n">
         <v>1.91</v>
@@ -10508,7 +10508,7 @@
         <v>1.45</v>
       </c>
       <c r="W52" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="X52" t="n">
         <v>10.5</v>
@@ -10529,22 +10529,22 @@
         <v>8.6</v>
       </c>
       <c r="AD52" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF52" t="n">
         <v>22</v>
       </c>
       <c r="AG52" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH52" t="n">
         <v>980</v>
       </c>
       <c r="AI52" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ52" t="n">
         <v>65</v>
@@ -10556,71 +10556,71 @@
         <v>85</v>
       </c>
       <c r="AM52" t="n">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="AN52" t="n">
         <v>65</v>
       </c>
       <c r="AO52" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="AR52" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT52" t="n">
-        <v>3</v>
+        <v>7.4</v>
       </c>
       <c r="AU52" t="n">
         <v>6.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AW52" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AX52" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AY52" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="BA52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BC52" t="n">
         <v>4.1</v>
       </c>
-      <c r="BB52" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>4</v>
-      </c>
       <c r="BD52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE52" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BF52" t="n">
         <v>4.2</v>
       </c>
-      <c r="BF52" t="n">
-        <v>4</v>
-      </c>
       <c r="BG52" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-08 20:05:35</t>
+          <t>2026-03-08 22:14:33</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -743,7 +743,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>00:06:00</t>
+          <t>00:06:26</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -757,170 +757,170 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="G2" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="H2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="J2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K2" t="n">
         <v>4.3</v>
       </c>
-      <c r="K2" t="n">
-        <v>4.4</v>
-      </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.91</v>
       </c>
       <c r="R2" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="S2" t="n">
-        <v>2.86</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="U2" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="X2" t="n">
-        <v>19.5</v>
+        <v>15.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Z2" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA2" t="n">
         <v>140</v>
       </c>
       <c r="AB2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF2" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AG2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX2" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>29</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>85</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>40</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>10</v>
       </c>
       <c r="AY2" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BB2" t="n">
         <v>15.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE2" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="BF2" t="n">
-        <v>7.6</v>
+        <v>9.6</v>
       </c>
       <c r="BG2" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L3" t="n">
         <v>1.31</v>
@@ -975,22 +975,22 @@
         <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="O3" t="n">
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S3" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="T3" t="n">
         <v>1.96</v>
@@ -999,13 +999,13 @@
         <v>1.86</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W3" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="X3" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="Y3" t="n">
         <v>1000</v>
@@ -1062,7 +1062,7 @@
         <v>2</v>
       </c>
       <c r="AQ3" t="n">
-        <v>4.2</v>
+        <v>21</v>
       </c>
       <c r="AR3" t="n">
         <v>4.2</v>
@@ -1074,7 +1074,7 @@
         <v>4.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.34</v>
+        <v>1.98</v>
       </c>
       <c r="AV3" t="n">
         <v>4.2</v>
@@ -1089,7 +1089,7 @@
         <v>4.9</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2.98</v>
+        <v>2.62</v>
       </c>
       <c r="BA3" t="n">
         <v>4.2</v>
@@ -1101,10 +1101,10 @@
         <v>6.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="BE3" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="BF3" t="n">
         <v>4.5</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.32</v>
+        <v>1.66</v>
       </c>
       <c r="G4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="H4" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S4" t="n">
         <v>3.9</v>
       </c>
-      <c r="I4" t="n">
-        <v>30</v>
-      </c>
-      <c r="J4" t="n">
-        <v>3</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="T4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF4" t="n">
         <v>5</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>980</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.13</v>
-      </c>
       <c r="BG4" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1339,170 +1339,170 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="H5" t="n">
-        <v>1.91</v>
+        <v>2.84</v>
       </c>
       <c r="I5" t="n">
-        <v>870</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>3.45</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>1.11</v>
+        <v>2.36</v>
       </c>
       <c r="O5" t="n">
-        <v>1.06</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.52</v>
+        <v>2.48</v>
       </c>
       <c r="R5" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="T5" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="W5" t="n">
-        <v>1.04</v>
+        <v>1.46</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>980</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AO5" t="n">
         <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.15</v>
+        <v>3.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.17</v>
+        <v>3.9</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.15</v>
+        <v>4.9</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.16</v>
+        <v>5.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.17</v>
+        <v>3.8</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.14</v>
+        <v>3.55</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.15</v>
+        <v>4.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.15</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.15</v>
+        <v>5.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.15</v>
+        <v>5.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.16</v>
+        <v>6</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.16</v>
+        <v>5.7</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.16</v>
+        <v>5.6</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.16</v>
+        <v>5.9</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.17</v>
+        <v>6.2</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.55</v>
+        <v>5.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.55</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1533,10 +1533,10 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H6" t="n">
         <v>2.24</v>
@@ -1548,7 +1548,7 @@
         <v>3.2</v>
       </c>
       <c r="K6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L6" t="n">
         <v>1.52</v>
@@ -1557,28 +1557,28 @@
         <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="O6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="T6" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V6" t="n">
         <v>1.78</v>
@@ -1587,31 +1587,31 @@
         <v>1.32</v>
       </c>
       <c r="X6" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Y6" t="n">
         <v>7.8</v>
       </c>
       <c r="Z6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AB6" t="n">
         <v>12</v>
       </c>
       <c r="AC6" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF6" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AG6" t="n">
         <v>20</v>
@@ -1620,83 +1620,83 @@
         <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AJ6" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AK6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>580</v>
+        <v>170</v>
       </c>
       <c r="AN6" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AO6" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR6" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AY6" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AZ6" t="n">
         <v>19.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB6" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="BC6" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BD6" t="n">
-        <v>55</v>
+        <v>14.5</v>
       </c>
       <c r="BE6" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="BF6" t="n">
-        <v>55</v>
+        <v>11.5</v>
       </c>
       <c r="BG6" t="n">
-        <v>8.4</v>
+        <v>22</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1751,28 +1751,28 @@
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S7" t="n">
-        <v>2.46</v>
+        <v>2.68</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="U7" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V7" t="n">
         <v>5.3</v>
@@ -1787,16 +1787,16 @@
         <v>9.199999999999999</v>
       </c>
       <c r="Z7" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB7" t="n">
         <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
         <v>1000</v>
@@ -1832,7 +1832,7 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AP7" t="n">
         <v>14</v>
@@ -1841,56 +1841,56 @@
         <v>4.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS7" t="n">
-        <v>4.5</v>
+        <v>7.6</v>
       </c>
       <c r="AT7" t="n">
-        <v>34</v>
+        <v>6.6</v>
       </c>
       <c r="AU7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW7" t="n">
         <v>11.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.7</v>
       </c>
       <c r="AX7" t="n">
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AZ7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BB7" t="n">
         <v>5.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BD7" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BF7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -1921,25 +1921,25 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="G8" t="n">
         <v>6.2</v>
       </c>
       <c r="H8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I8" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
@@ -1951,10 +1951,10 @@
         <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
         <v>1.19</v>
@@ -1966,7 +1966,7 @@
         <v>2.24</v>
       </c>
       <c r="U8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="V8" t="n">
         <v>2.02</v>
@@ -2026,7 +2026,7 @@
         <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP8" t="n">
         <v>7.6</v>
@@ -2047,13 +2047,13 @@
         <v>4.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.6</v>
+        <v>21</v>
       </c>
       <c r="AX8" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AY8" t="n">
         <v>6.4</v>
@@ -2068,23 +2068,23 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD8" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BF8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>18</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2115,170 +2115,170 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.79</v>
+        <v>1.94</v>
       </c>
       <c r="G9" t="n">
-        <v>990</v>
+        <v>2.22</v>
       </c>
       <c r="H9" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="I9" t="n">
-        <v>990</v>
+        <v>5.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>8.6</v>
+        <v>3.6</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N9" t="n">
-        <v>1.1</v>
+        <v>2.42</v>
       </c>
       <c r="O9" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>1.09</v>
+        <v>1.55</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.05</v>
+        <v>3.6</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="U9" t="n">
-        <v>1.11</v>
+        <v>1.73</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.81</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.11</v>
+        <v>4.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.11</v>
+        <v>5.1</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.11</v>
+        <v>6.8</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.11</v>
+        <v>7.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.11</v>
+        <v>3.9</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.11</v>
+        <v>7.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.11</v>
+        <v>4.9</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.09</v>
+        <v>6.2</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.11</v>
+        <v>7.8</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.11</v>
+        <v>6.4</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.11</v>
+        <v>6.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.11</v>
+        <v>7.2</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.11</v>
+        <v>8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.11</v>
+        <v>6.2</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.55</v>
+        <v>7.8</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G10" t="n">
         <v>1.5</v>
@@ -2321,7 +2321,7 @@
         <v>11.5</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K10" t="n">
         <v>5.1</v>
@@ -2339,13 +2339,13 @@
         <v>1.38</v>
       </c>
       <c r="P10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="R10" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S10" t="n">
         <v>3.85</v>
@@ -2366,7 +2366,7 @@
         <v>27</v>
       </c>
       <c r="Y10" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="Z10" t="n">
         <v>480</v>
@@ -2393,7 +2393,7 @@
         <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>180</v>
+        <v>100</v>
       </c>
       <c r="AI10" t="n">
         <v>1000</v>
@@ -2402,7 +2402,7 @@
         <v>18</v>
       </c>
       <c r="AK10" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="AL10" t="n">
         <v>380</v>
@@ -2420,59 +2420,59 @@
         <v>5.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>6.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AS10" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT10" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AU10" t="n">
         <v>6.2</v>
       </c>
       <c r="AV10" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="AX10" t="n">
         <v>6.2</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AZ10" t="n">
-        <v>6.2</v>
+        <v>18</v>
       </c>
       <c r="BA10" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD10" t="n">
         <v>7</v>
       </c>
-      <c r="BB10" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE10" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BG10" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2503,170 +2503,170 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="G11" t="n">
-        <v>8.800000000000001</v>
+        <v>2.84</v>
       </c>
       <c r="H11" t="n">
-        <v>2.4</v>
+        <v>2.82</v>
       </c>
       <c r="I11" t="n">
-        <v>110</v>
+        <v>3.25</v>
       </c>
       <c r="J11" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="M11" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="O11" t="n">
         <v>1.35</v>
       </c>
       <c r="P11" t="n">
-        <v>1.24</v>
+        <v>1.77</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.35</v>
+        <v>2.02</v>
       </c>
       <c r="R11" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>1.35</v>
+        <v>3.7</v>
       </c>
       <c r="T11" t="n">
-        <v>1.11</v>
+        <v>1.78</v>
       </c>
       <c r="U11" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="W11" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="X11" t="n">
-        <v>500</v>
+        <v>13.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z11" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC11" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AJ11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AL11" t="n">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AM11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN11" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO11" t="n">
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>6.2</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.3</v>
+        <v>9.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.31</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU11" t="n">
-        <v>4.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV11" t="n">
-        <v>1.31</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>1.33</v>
+        <v>18</v>
       </c>
       <c r="AX11" t="n">
-        <v>1.33</v>
+        <v>14.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>1.31</v>
+        <v>10</v>
       </c>
       <c r="AZ11" t="n">
-        <v>1.3</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>1.33</v>
+        <v>14.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>1.33</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.33</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>1.55</v>
+        <v>6.8</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.55</v>
+        <v>7</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="G12" t="n">
         <v>5.5</v>
       </c>
       <c r="H12" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="I12" t="n">
         <v>2.06</v>
       </c>
       <c r="J12" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L12" t="n">
         <v>1.51</v>
@@ -2721,7 +2721,7 @@
         <v>1.12</v>
       </c>
       <c r="N12" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O12" t="n">
         <v>1.54</v>
@@ -2730,19 +2730,19 @@
         <v>1.53</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R12" t="n">
         <v>1.19</v>
       </c>
       <c r="S12" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="T12" t="n">
         <v>2.24</v>
       </c>
       <c r="U12" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="V12" t="n">
         <v>1.94</v>
@@ -2757,7 +2757,7 @@
         <v>6.8</v>
       </c>
       <c r="Z12" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="AA12" t="n">
         <v>900</v>
@@ -2805,62 +2805,62 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AR12" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AS12" t="n">
         <v>6</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX12" t="n">
         <v>3.9</v>
       </c>
-      <c r="AV12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.7</v>
-      </c>
       <c r="AY12" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AZ12" t="n">
         <v>6</v>
       </c>
       <c r="BA12" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BB12" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BC12" t="n">
         <v>7</v>
       </c>
       <c r="BD12" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BE12" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -2894,10 +2894,10 @@
         <v>1.39</v>
       </c>
       <c r="G13" t="n">
-        <v>990</v>
+        <v>520</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="I13" t="n">
         <v>990</v>
@@ -2921,10 +2921,10 @@
         <v>1.01</v>
       </c>
       <c r="P13" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.47</v>
+        <v>1.02</v>
       </c>
       <c r="R13" t="n">
         <v>1.09</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>1.37</v>
       </c>
       <c r="H14" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="I14" t="n">
         <v>15.5</v>
@@ -3100,7 +3100,7 @@
         <v>4.9</v>
       </c>
       <c r="K14" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L14" t="n">
         <v>1.34</v>
@@ -3109,7 +3109,7 @@
         <v>1.07</v>
       </c>
       <c r="N14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O14" t="n">
         <v>1.34</v>
@@ -3118,16 +3118,16 @@
         <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="R14" t="n">
         <v>1.33</v>
       </c>
       <c r="S14" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
         <v>1.6</v>
@@ -3136,10 +3136,10 @@
         <v>1.06</v>
       </c>
       <c r="W14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="X14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="Y14" t="n">
         <v>38</v>
@@ -3163,13 +3163,13 @@
         <v>370</v>
       </c>
       <c r="AF14" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="AG14" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AH14" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AI14" t="n">
         <v>350</v>
@@ -3193,19 +3193,19 @@
         <v>740</v>
       </c>
       <c r="AP14" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR14" t="n">
-        <v>16</v>
+        <v>10.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AT14" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU14" t="n">
         <v>11.5</v>
@@ -3214,10 +3214,10 @@
         <v>21</v>
       </c>
       <c r="AW14" t="n">
-        <v>12</v>
+        <v>7.8</v>
       </c>
       <c r="AX14" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AY14" t="n">
         <v>10</v>
@@ -3226,7 +3226,7 @@
         <v>34</v>
       </c>
       <c r="BA14" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BB14" t="n">
         <v>8.800000000000001</v>
@@ -3238,17 +3238,17 @@
         <v>50</v>
       </c>
       <c r="BE14" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BF14" t="n">
         <v>6.4</v>
       </c>
       <c r="BG14" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
         <v>2.56</v>
       </c>
       <c r="H15" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I15" t="n">
         <v>3.8</v>
@@ -3300,31 +3300,31 @@
         <v>1.53</v>
       </c>
       <c r="M15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="O15" t="n">
         <v>1.45</v>
       </c>
       <c r="P15" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R15" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="T15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="U15" t="n">
         <v>1.94</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.92</v>
       </c>
       <c r="V15" t="n">
         <v>1.36</v>
@@ -3345,10 +3345,10 @@
         <v>500</v>
       </c>
       <c r="AB15" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD15" t="n">
         <v>30</v>
@@ -3366,7 +3366,7 @@
         <v>60</v>
       </c>
       <c r="AI15" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ15" t="n">
         <v>980</v>
@@ -3384,65 +3384,65 @@
         <v>980</v>
       </c>
       <c r="AO15" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AP15" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ15" t="n">
         <v>10</v>
       </c>
       <c r="AR15" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS15" t="n">
-        <v>10</v>
-      </c>
       <c r="AT15" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AU15" t="n">
         <v>6.2</v>
       </c>
       <c r="AV15" t="n">
-        <v>8.4</v>
+        <v>11.5</v>
       </c>
       <c r="AW15" t="n">
         <v>20</v>
       </c>
       <c r="AX15" t="n">
-        <v>7.6</v>
+        <v>11.5</v>
       </c>
       <c r="AY15" t="n">
         <v>10</v>
       </c>
       <c r="AZ15" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BA15" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD15" t="n">
         <v>10</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>10.5</v>
       </c>
       <c r="BE15" t="n">
         <v>29</v>
       </c>
       <c r="BF15" t="n">
-        <v>6.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
         <v>2.26</v>
       </c>
       <c r="G16" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H16" t="n">
         <v>3.4</v>
@@ -3524,7 +3524,7 @@
         <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X16" t="n">
         <v>17.5</v>
@@ -3590,7 +3590,7 @@
         <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="AT16" t="n">
         <v>4.4</v>
@@ -3602,7 +3602,7 @@
         <v>5.6</v>
       </c>
       <c r="AW16" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="AX16" t="n">
         <v>6.4</v>
@@ -3614,29 +3614,29 @@
         <v>6</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
       <c r="BB16" t="n">
         <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>6.4</v>
+        <v>3.6</v>
       </c>
       <c r="BD16" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="BE16" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="BF16" t="n">
         <v>6.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -3673,16 +3673,16 @@
         <v>3.6</v>
       </c>
       <c r="H17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="I17" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J17" t="n">
         <v>3.7</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L17" t="n">
         <v>1.28</v>
@@ -3715,10 +3715,10 @@
         <v>2.34</v>
       </c>
       <c r="V17" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="W17" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X17" t="n">
         <v>20</v>
@@ -3733,7 +3733,7 @@
         <v>80</v>
       </c>
       <c r="AB17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AC17" t="n">
         <v>9</v>
@@ -3757,7 +3757,7 @@
         <v>38</v>
       </c>
       <c r="AJ17" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AK17" t="n">
         <v>42</v>
@@ -3793,10 +3793,10 @@
         <v>7.8</v>
       </c>
       <c r="AV17" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW17" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX17" t="n">
         <v>21</v>
@@ -3808,19 +3808,19 @@
         <v>14</v>
       </c>
       <c r="BA17" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE17" t="n">
         <v>5.5</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>5.6</v>
       </c>
       <c r="BF17" t="n">
         <v>19.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4064,7 +4064,7 @@
         <v>3.05</v>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J19" t="n">
         <v>3.6</v>
@@ -4088,7 +4088,7 @@
         <v>2.04</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="R19" t="n">
         <v>1.41</v>
@@ -4097,7 +4097,7 @@
         <v>3</v>
       </c>
       <c r="T19" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
         <v>2.24</v>
@@ -4196,7 +4196,7 @@
         <v>13.5</v>
       </c>
       <c r="BA19" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BB19" t="n">
         <v>14.5</v>
@@ -4208,7 +4208,7 @@
         <v>18</v>
       </c>
       <c r="BE19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BF19" t="n">
         <v>13.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>3.8</v>
       </c>
       <c r="G20" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H20" t="n">
         <v>2.16</v>
@@ -4264,7 +4264,7 @@
         <v>3.15</v>
       </c>
       <c r="K20" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L20" t="n">
         <v>1.43</v>
@@ -4273,28 +4273,28 @@
         <v>1.11</v>
       </c>
       <c r="N20" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O20" t="n">
         <v>1.46</v>
       </c>
       <c r="P20" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="R20" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S20" t="n">
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="U20" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V20" t="n">
         <v>1.76</v>
@@ -4312,28 +4312,28 @@
         <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AB20" t="n">
         <v>13.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="AD20" t="n">
         <v>13</v>
       </c>
       <c r="AE20" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AF20" t="n">
         <v>28</v>
       </c>
       <c r="AG20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>55</v>
@@ -4342,7 +4342,7 @@
         <v>110</v>
       </c>
       <c r="AK20" t="n">
-        <v>65</v>
+        <v>370</v>
       </c>
       <c r="AL20" t="n">
         <v>95</v>
@@ -4375,7 +4375,7 @@
         <v>6.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW20" t="n">
         <v>14.5</v>
@@ -4390,29 +4390,29 @@
         <v>18.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BB20" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BC20" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BD20" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BF20" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BG20" t="n">
         <v>19</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4467,28 +4467,28 @@
         <v>1.08</v>
       </c>
       <c r="N21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.37</v>
       </c>
       <c r="P21" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S21" t="n">
         <v>3.9</v>
       </c>
       <c r="T21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="U21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>1.26</v>
@@ -4530,25 +4530,25 @@
         <v>20</v>
       </c>
       <c r="AI21" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AJ21" t="n">
         <v>23</v>
       </c>
       <c r="AK21" t="n">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="AL21" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM21" t="n">
-        <v>580</v>
+        <v>130</v>
       </c>
       <c r="AN21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AO21" t="n">
-        <v>75</v>
+        <v>270</v>
       </c>
       <c r="AP21" t="n">
         <v>11.5</v>
@@ -4560,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="AS21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
         <v>7.6</v>
@@ -4572,7 +4572,7 @@
         <v>16</v>
       </c>
       <c r="AW21" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AX21" t="n">
         <v>10.5</v>
@@ -4584,7 +4584,7 @@
         <v>17</v>
       </c>
       <c r="BA21" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BB21" t="n">
         <v>20</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="G22" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H22" t="n">
         <v>2.1</v>
@@ -4670,28 +4670,28 @@
         <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
         <v>3.15</v>
       </c>
       <c r="T22" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V22" t="n">
         <v>1.89</v>
       </c>
       <c r="W22" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y22" t="n">
         <v>11</v>
@@ -4724,7 +4724,7 @@
         <v>17</v>
       </c>
       <c r="AI22" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AJ22" t="n">
         <v>75</v>
@@ -4748,7 +4748,7 @@
         <v>14.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR22" t="n">
         <v>12</v>
@@ -4757,7 +4757,7 @@
         <v>22</v>
       </c>
       <c r="AT22" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AU22" t="n">
         <v>7.8</v>
@@ -4784,7 +4784,7 @@
         <v>13.5</v>
       </c>
       <c r="BC22" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BD22" t="n">
         <v>12.5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>2.1</v>
       </c>
       <c r="G23" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="H23" t="n">
         <v>3.8</v>
@@ -4843,7 +4843,7 @@
         <v>4.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K23" t="n">
         <v>3.6</v>
@@ -4879,10 +4879,10 @@
         <v>2.02</v>
       </c>
       <c r="V23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W23" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="X23" t="n">
         <v>15</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -5025,25 +5025,25 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H24" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="I24" t="n">
         <v>2.86</v>
       </c>
       <c r="J24" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="K24" t="n">
         <v>3.35</v>
       </c>
       <c r="L24" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="M24" t="n">
         <v>1.1</v>
@@ -5064,7 +5064,7 @@
         <v>1.28</v>
       </c>
       <c r="S24" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="T24" t="n">
         <v>1.81</v>
@@ -5076,16 +5076,16 @@
         <v>1.54</v>
       </c>
       <c r="W24" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="X24" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y24" t="n">
         <v>10.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AA24" t="n">
         <v>1000</v>
@@ -5097,7 +5097,7 @@
         <v>7.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AE24" t="n">
         <v>80</v>
@@ -5136,13 +5136,13 @@
         <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR24" t="n">
         <v>7.6</v>
       </c>
       <c r="AS24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT24" t="n">
         <v>5.8</v>
@@ -5154,7 +5154,7 @@
         <v>7</v>
       </c>
       <c r="AW24" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX24" t="n">
         <v>15.5</v>
@@ -5166,16 +5166,16 @@
         <v>13</v>
       </c>
       <c r="BA24" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB24" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BC24" t="n">
         <v>18</v>
       </c>
       <c r="BD24" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE24" t="n">
         <v>28</v>
@@ -5184,11 +5184,11 @@
         <v>7.4</v>
       </c>
       <c r="BG24" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
         <v>1.99</v>
       </c>
       <c r="G25" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H25" t="n">
         <v>4.3</v>
@@ -5237,7 +5237,7 @@
         <v>3.5</v>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M25" t="n">
         <v>1.09</v>
@@ -5249,10 +5249,10 @@
         <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R25" t="n">
         <v>1.26</v>
@@ -5264,13 +5264,13 @@
         <v>1.96</v>
       </c>
       <c r="U25" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V25" t="n">
         <v>1.27</v>
       </c>
       <c r="W25" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X25" t="n">
         <v>11.5</v>
@@ -5291,7 +5291,7 @@
         <v>8</v>
       </c>
       <c r="AD25" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="AE25" t="n">
         <v>370</v>
@@ -5300,7 +5300,7 @@
         <v>23</v>
       </c>
       <c r="AG25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH25" t="n">
         <v>60</v>
@@ -5309,7 +5309,7 @@
         <v>380</v>
       </c>
       <c r="AJ25" t="n">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="AK25" t="n">
         <v>65</v>
@@ -5336,7 +5336,7 @@
         <v>13</v>
       </c>
       <c r="AS25" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT25" t="n">
         <v>6.8</v>
@@ -5348,7 +5348,7 @@
         <v>15</v>
       </c>
       <c r="AW25" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX25" t="n">
         <v>10</v>
@@ -5360,7 +5360,7 @@
         <v>14</v>
       </c>
       <c r="BA25" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB25" t="n">
         <v>11.5</v>
@@ -5369,7 +5369,7 @@
         <v>11.5</v>
       </c>
       <c r="BD25" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE25" t="n">
         <v>28</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -5416,10 +5416,10 @@
         <v>2.54</v>
       </c>
       <c r="G26" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I26" t="n">
         <v>3.3</v>
@@ -5431,49 +5431,49 @@
         <v>3.4</v>
       </c>
       <c r="L26" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="M26" t="n">
         <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O26" t="n">
         <v>1.4</v>
       </c>
       <c r="P26" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R26" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S26" t="n">
         <v>3.65</v>
       </c>
       <c r="T26" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V26" t="n">
         <v>1.44</v>
       </c>
       <c r="W26" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="X26" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y26" t="n">
         <v>14</v>
       </c>
       <c r="Z26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AA26" t="n">
         <v>60</v>
@@ -5485,7 +5485,7 @@
         <v>7.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>55</v>
@@ -5497,25 +5497,25 @@
         <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI26" t="n">
         <v>65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AK26" t="n">
-        <v>32</v>
+        <v>80</v>
       </c>
       <c r="AL26" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM26" t="n">
-        <v>130</v>
+        <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO26" t="n">
         <v>50</v>
@@ -5527,19 +5527,19 @@
         <v>10</v>
       </c>
       <c r="AR26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AS26" t="n">
         <v>20</v>
       </c>
       <c r="AT26" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW26" t="n">
         <v>29</v>
@@ -5548,16 +5548,16 @@
         <v>14</v>
       </c>
       <c r="AY26" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ26" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
       </c>
       <c r="BB26" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC26" t="n">
         <v>26</v>
@@ -5566,17 +5566,17 @@
         <v>38</v>
       </c>
       <c r="BE26" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BF26" t="n">
         <v>23</v>
       </c>
       <c r="BG26" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -5607,13 +5607,13 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G27" t="n">
         <v>2.32</v>
       </c>
       <c r="H27" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
         <v>3.45</v>
@@ -5682,13 +5682,13 @@
         <v>24</v>
       </c>
       <c r="AE27" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF27" t="n">
         <v>55</v>
       </c>
       <c r="AG27" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="AH27" t="n">
         <v>14</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -5801,43 +5801,43 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="I28" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M28" t="n">
         <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="P28" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R28" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
         <v>4.7</v>
@@ -5849,10 +5849,10 @@
         <v>1.51</v>
       </c>
       <c r="V28" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="W28" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X28" t="n">
         <v>10</v>
@@ -5861,10 +5861,10 @@
         <v>6</v>
       </c>
       <c r="Z28" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AA28" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AB28" t="n">
         <v>38</v>
@@ -5894,10 +5894,10 @@
         <v>470</v>
       </c>
       <c r="AK28" t="n">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="AL28" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="n">
         <v>580</v>
@@ -5909,7 +5909,7 @@
         <v>36</v>
       </c>
       <c r="AP28" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ28" t="n">
         <v>5.1</v>
@@ -5930,10 +5930,10 @@
         <v>9.4</v>
       </c>
       <c r="AW28" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX28" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY28" t="n">
         <v>26</v>
@@ -5942,29 +5942,29 @@
         <v>17</v>
       </c>
       <c r="BA28" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="BB28" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC28" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BD28" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BE28" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF28" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG28" t="n">
         <v>11.5</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -6001,7 +6001,7 @@
         <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I29" t="n">
         <v>2.24</v>
@@ -6013,19 +6013,19 @@
         <v>3.45</v>
       </c>
       <c r="L29" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="M29" t="n">
         <v>1.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O29" t="n">
         <v>1.46</v>
       </c>
       <c r="P29" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q29" t="n">
         <v>2.36</v>
@@ -6061,7 +6061,7 @@
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>23</v>
+        <v>980</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
@@ -6127,7 +6127,7 @@
         <v>22</v>
       </c>
       <c r="AX29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY29" t="n">
         <v>15</v>
@@ -6139,16 +6139,16 @@
         <v>9</v>
       </c>
       <c r="BB29" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BC29" t="n">
         <v>9.6</v>
       </c>
       <c r="BD29" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BE29" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="BF29" t="n">
         <v>10</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -6225,10 +6225,10 @@
         <v>2.54</v>
       </c>
       <c r="R30" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T30" t="n">
         <v>2.14</v>
@@ -6258,7 +6258,7 @@
         <v>6.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AD30" t="n">
         <v>22</v>
@@ -6276,10 +6276,10 @@
         <v>46</v>
       </c>
       <c r="AI30" t="n">
-        <v>260</v>
+        <v>700</v>
       </c>
       <c r="AJ30" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="AK30" t="n">
         <v>32</v>
@@ -6294,10 +6294,10 @@
         <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>160</v>
+        <v>700</v>
       </c>
       <c r="AP30" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ30" t="n">
         <v>10</v>
@@ -6306,10 +6306,10 @@
         <v>24</v>
       </c>
       <c r="AS30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT30" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU30" t="n">
         <v>6.6</v>
@@ -6318,7 +6318,7 @@
         <v>18</v>
       </c>
       <c r="AW30" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX30" t="n">
         <v>9.4</v>
@@ -6330,29 +6330,29 @@
         <v>22</v>
       </c>
       <c r="BA30" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BB30" t="n">
         <v>21</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE30" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30" t="n">
         <v>17</v>
       </c>
       <c r="BG30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -6509,7 +6509,7 @@
         <v>6</v>
       </c>
       <c r="AV31" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW31" t="n">
         <v>5.1</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -6703,7 +6703,7 @@
         <v>5.1</v>
       </c>
       <c r="AV32" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AW32" t="n">
         <v>5.1</v>
@@ -6730,7 +6730,7 @@
         <v>4.8</v>
       </c>
       <c r="BE32" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF32" t="n">
         <v>9</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G33" t="n">
         <v>1.58</v>
@@ -6786,7 +6786,7 @@
         <v>4.1</v>
       </c>
       <c r="K33" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L33" t="n">
         <v>1.45</v>
@@ -6879,10 +6879,10 @@
         <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ33" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR33" t="n">
         <v>5.7</v>
@@ -6894,7 +6894,7 @@
         <v>5.5</v>
       </c>
       <c r="AU33" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AV33" t="n">
         <v>5.2</v>
@@ -6906,7 +6906,7 @@
         <v>6.8</v>
       </c>
       <c r="AY33" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AZ33" t="n">
         <v>5.2</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -6980,7 +6980,7 @@
         <v>3.1</v>
       </c>
       <c r="K34" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L34" t="n">
         <v>1.45</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -7162,7 +7162,7 @@
         <v>2.12</v>
       </c>
       <c r="G35" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="H35" t="n">
         <v>3.55</v>
@@ -7177,7 +7177,7 @@
         <v>3.7</v>
       </c>
       <c r="L35" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="M35" t="n">
         <v>1.07</v>
@@ -7210,7 +7210,7 @@
         <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="X35" t="n">
         <v>15.5</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -7353,19 +7353,19 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="G36" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="H36" t="n">
         <v>7</v>
       </c>
       <c r="I36" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="J36" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K36" t="n">
         <v>5</v>
@@ -7377,22 +7377,22 @@
         <v>1.05</v>
       </c>
       <c r="N36" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O36" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P36" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R36" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S36" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T36" t="n">
         <v>1.87</v>
@@ -7404,7 +7404,7 @@
         <v>1.15</v>
       </c>
       <c r="W36" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="X36" t="n">
         <v>21</v>
@@ -7434,19 +7434,19 @@
         <v>10</v>
       </c>
       <c r="AG36" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH36" t="n">
         <v>23</v>
       </c>
       <c r="AI36" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AJ36" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK36" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL36" t="n">
         <v>34</v>
@@ -7455,7 +7455,7 @@
         <v>390</v>
       </c>
       <c r="AN36" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO36" t="n">
         <v>110</v>
@@ -7467,7 +7467,7 @@
         <v>22</v>
       </c>
       <c r="AR36" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="AS36" t="n">
         <v>36</v>
@@ -7479,10 +7479,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV36" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AW36" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AX36" t="n">
         <v>8.6</v>
@@ -7512,11 +7512,11 @@
         <v>6.4</v>
       </c>
       <c r="BG36" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="G37" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I37" t="n">
-        <v>2.64</v>
+        <v>2.36</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K37" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,16 +7571,16 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="O37" t="n">
         <v>1.37</v>
       </c>
       <c r="P37" t="n">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.94</v>
+        <v>2.06</v>
       </c>
       <c r="R37" t="n">
         <v>1.18</v>
@@ -7589,16 +7589,16 @@
         <v>2.18</v>
       </c>
       <c r="T37" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="U37" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V37" t="n">
-        <v>1.61</v>
+        <v>1.73</v>
       </c>
       <c r="W37" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="X37" t="n">
         <v>17.5</v>
@@ -7625,7 +7625,7 @@
         <v>36</v>
       </c>
       <c r="AF37" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AG37" t="n">
         <v>21</v>
@@ -7664,7 +7664,7 @@
         <v>10</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="AT37" t="n">
         <v>10</v>
@@ -7676,7 +7676,7 @@
         <v>6.4</v>
       </c>
       <c r="AW37" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="AX37" t="n">
         <v>2.8</v>
@@ -7691,13 +7691,13 @@
         <v>20</v>
       </c>
       <c r="BB37" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BC37" t="n">
         <v>18</v>
       </c>
       <c r="BD37" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BE37" t="n">
         <v>26</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -7744,10 +7744,10 @@
         <v>2.76</v>
       </c>
       <c r="G38" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="H38" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="n">
         <v>2.96</v>
@@ -7765,7 +7765,7 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O38" t="n">
         <v>1.47</v>
@@ -7786,7 +7786,7 @@
         <v>2.02</v>
       </c>
       <c r="U38" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V38" t="n">
         <v>1.51</v>
@@ -7795,13 +7795,13 @@
         <v>1.53</v>
       </c>
       <c r="X38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y38" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="Z38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA38" t="n">
         <v>50</v>
@@ -7819,7 +7819,7 @@
         <v>40</v>
       </c>
       <c r="AF38" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG38" t="n">
         <v>13.5</v>
@@ -7855,22 +7855,22 @@
         <v>8.4</v>
       </c>
       <c r="AR38" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AS38" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="AT38" t="n">
         <v>7.8</v>
       </c>
       <c r="AU38" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV38" t="n">
         <v>12</v>
       </c>
       <c r="AW38" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AX38" t="n">
         <v>15.5</v>
@@ -7879,13 +7879,13 @@
         <v>12</v>
       </c>
       <c r="AZ38" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA38" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="BB38" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BC38" t="n">
         <v>32</v>
@@ -7894,17 +7894,17 @@
         <v>23</v>
       </c>
       <c r="BE38" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BF38" t="n">
         <v>34</v>
       </c>
       <c r="BG38" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -7935,16 +7935,16 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G39" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H39" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="I39" t="n">
         <v>3.7</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3.75</v>
       </c>
       <c r="J39" t="n">
         <v>3.3</v>
@@ -7959,19 +7959,19 @@
         <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O39" t="n">
         <v>1.43</v>
       </c>
       <c r="P39" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="R39" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S39" t="n">
         <v>4.4</v>
@@ -7980,13 +7980,13 @@
         <v>1.97</v>
       </c>
       <c r="U39" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V39" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W39" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X39" t="n">
         <v>11</v>
@@ -8013,19 +8013,19 @@
         <v>48</v>
       </c>
       <c r="AF39" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AG39" t="n">
         <v>11.5</v>
       </c>
       <c r="AH39" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AI39" t="n">
         <v>65</v>
       </c>
       <c r="AJ39" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK39" t="n">
         <v>27</v>
@@ -8052,7 +8052,7 @@
         <v>22</v>
       </c>
       <c r="AS39" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AT39" t="n">
         <v>8.199999999999999</v>
@@ -8061,7 +8061,7 @@
         <v>6.8</v>
       </c>
       <c r="AV39" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AW39" t="n">
         <v>44</v>
@@ -8076,7 +8076,7 @@
         <v>17.5</v>
       </c>
       <c r="BA39" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB39" t="n">
         <v>27</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G40" t="n">
         <v>1.95</v>
       </c>
-      <c r="G40" t="n">
-        <v>1.96</v>
-      </c>
       <c r="H40" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="I40" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="J40" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K40" t="n">
         <v>3.55</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3.6</v>
       </c>
       <c r="L40" t="n">
         <v>1.49</v>
@@ -8159,7 +8159,7 @@
         <v>1.42</v>
       </c>
       <c r="P40" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q40" t="n">
         <v>2.28</v>
@@ -8174,7 +8174,7 @@
         <v>2.04</v>
       </c>
       <c r="U40" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="V40" t="n">
         <v>1.25</v>
@@ -8195,16 +8195,16 @@
         <v>120</v>
       </c>
       <c r="AB40" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AC40" t="n">
         <v>7.8</v>
       </c>
       <c r="AD40" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF40" t="n">
         <v>10.5</v>
@@ -8222,19 +8222,19 @@
         <v>21</v>
       </c>
       <c r="AK40" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL40" t="n">
         <v>44</v>
       </c>
       <c r="AM40" t="n">
-        <v>140</v>
+        <v>500</v>
       </c>
       <c r="AN40" t="n">
         <v>17</v>
       </c>
       <c r="AO40" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AP40" t="n">
         <v>10</v>
@@ -8246,7 +8246,7 @@
         <v>30</v>
       </c>
       <c r="AS40" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AT40" t="n">
         <v>7</v>
@@ -8261,13 +8261,13 @@
         <v>60</v>
       </c>
       <c r="AX40" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY40" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ40" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA40" t="n">
         <v>70</v>
@@ -8285,14 +8285,14 @@
         <v>75</v>
       </c>
       <c r="BF40" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BG40" t="n">
         <v>80</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -8323,16 +8323,16 @@
         </is>
       </c>
       <c r="F41" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="G41" t="n">
         <v>2.12</v>
-      </c>
-      <c r="G41" t="n">
-        <v>2.14</v>
       </c>
       <c r="H41" t="n">
         <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J41" t="n">
         <v>3.45</v>
@@ -8347,7 +8347,7 @@
         <v>1.09</v>
       </c>
       <c r="N41" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O41" t="n">
         <v>1.38</v>
@@ -8356,7 +8356,7 @@
         <v>1.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R41" t="n">
         <v>1.31</v>
@@ -8365,40 +8365,40 @@
         <v>3.95</v>
       </c>
       <c r="T41" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="U41" t="n">
         <v>2.04</v>
       </c>
       <c r="V41" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W41" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X41" t="n">
         <v>12</v>
       </c>
       <c r="Y41" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA41" t="n">
         <v>85</v>
       </c>
       <c r="AB41" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC41" t="n">
         <v>7.6</v>
       </c>
       <c r="AD41" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE41" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF41" t="n">
         <v>12.5</v>
@@ -8407,10 +8407,10 @@
         <v>10.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI41" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AJ41" t="n">
         <v>27</v>
@@ -8425,37 +8425,37 @@
         <v>120</v>
       </c>
       <c r="AN41" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO41" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AP41" t="n">
         <v>11</v>
       </c>
       <c r="AQ41" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR41" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS41" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AW41" t="n">
         <v>48</v>
       </c>
-      <c r="AT41" t="n">
-        <v>8</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>7</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>15</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>36</v>
-      </c>
       <c r="AX41" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AY41" t="n">
         <v>9.800000000000001</v>
@@ -8464,10 +8464,10 @@
         <v>17.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="BB41" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BC41" t="n">
         <v>21</v>
@@ -8476,17 +8476,17 @@
         <v>36</v>
       </c>
       <c r="BE41" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BF41" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BG41" t="n">
         <v>50</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         <v>3.75</v>
       </c>
       <c r="L42" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="M42" t="n">
         <v>1.08</v>
@@ -8580,7 +8580,7 @@
         <v>34</v>
       </c>
       <c r="AA42" t="n">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="AB42" t="n">
         <v>9.199999999999999</v>
@@ -8631,10 +8631,10 @@
         <v>10.5</v>
       </c>
       <c r="AR42" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="AS42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT42" t="n">
         <v>7.2</v>
@@ -8646,7 +8646,7 @@
         <v>13.5</v>
       </c>
       <c r="AW42" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AX42" t="n">
         <v>11</v>
@@ -8670,7 +8670,7 @@
         <v>6</v>
       </c>
       <c r="BE42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF42" t="n">
         <v>17.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
         <v>3.7</v>
       </c>
       <c r="L43" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M43" t="n">
         <v>1.09</v>
@@ -8786,7 +8786,7 @@
         <v>23</v>
       </c>
       <c r="AE43" t="n">
-        <v>480</v>
+        <v>230</v>
       </c>
       <c r="AF43" t="n">
         <v>11</v>
@@ -8822,13 +8822,13 @@
         <v>9.6</v>
       </c>
       <c r="AQ43" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AR43" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AS43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AT43" t="n">
         <v>6.2</v>
@@ -8840,7 +8840,7 @@
         <v>18</v>
       </c>
       <c r="AW43" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AX43" t="n">
         <v>8.800000000000001</v>
@@ -8852,7 +8852,7 @@
         <v>19.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BB43" t="n">
         <v>18</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
         <v>2.38</v>
       </c>
       <c r="J45" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="K45" t="n">
         <v>3.1</v>
@@ -9156,7 +9156,7 @@
         <v>19</v>
       </c>
       <c r="Y45" t="n">
-        <v>14.5</v>
+        <v>980</v>
       </c>
       <c r="Z45" t="n">
         <v>40</v>
@@ -9216,19 +9216,19 @@
         <v>11</v>
       </c>
       <c r="AS45" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT45" t="n">
         <v>10</v>
       </c>
       <c r="AU45" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AV45" t="n">
         <v>7</v>
       </c>
       <c r="AW45" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AX45" t="n">
         <v>10.5</v>
@@ -9240,29 +9240,29 @@
         <v>9</v>
       </c>
       <c r="BA45" t="n">
-        <v>8</v>
+        <v>5.8</v>
       </c>
       <c r="BB45" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC45" t="n">
-        <v>8.199999999999999</v>
+        <v>5.9</v>
       </c>
       <c r="BD45" t="n">
-        <v>5.4</v>
+        <v>4.7</v>
       </c>
       <c r="BE45" t="n">
-        <v>9</v>
+        <v>6.2</v>
       </c>
       <c r="BF45" t="n">
         <v>8.4</v>
       </c>
       <c r="BG45" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -9311,7 +9311,7 @@
         <v>4.7</v>
       </c>
       <c r="L46" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="M46" t="n">
         <v>1.07</v>
@@ -9338,7 +9338,7 @@
         <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V46" t="n">
         <v>1.13</v>
@@ -9365,7 +9365,7 @@
         <v>10.5</v>
       </c>
       <c r="AD46" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AE46" t="n">
         <v>990</v>
@@ -9386,7 +9386,7 @@
         <v>14</v>
       </c>
       <c r="AK46" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AL46" t="n">
         <v>110</v>
@@ -9428,13 +9428,13 @@
         <v>7.2</v>
       </c>
       <c r="AY46" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ46" t="n">
         <v>18</v>
       </c>
       <c r="BA46" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="BB46" t="n">
         <v>11.5</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -9681,25 +9681,25 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="G48" t="n">
-        <v>1.96</v>
+        <v>1.88</v>
       </c>
       <c r="H48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I48" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J48" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K48" t="n">
         <v>4.6</v>
       </c>
-      <c r="I48" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="J48" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K48" t="n">
-        <v>4</v>
-      </c>
       <c r="L48" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M48" t="n">
         <v>1.08</v>
@@ -9711,7 +9711,7 @@
         <v>1.38</v>
       </c>
       <c r="P48" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q48" t="n">
         <v>2.06</v>
@@ -9720,7 +9720,7 @@
         <v>1.27</v>
       </c>
       <c r="S48" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="T48" t="n">
         <v>1.92</v>
@@ -9729,10 +9729,10 @@
         <v>1.87</v>
       </c>
       <c r="V48" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="W48" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="X48" t="n">
         <v>90</v>
@@ -9747,7 +9747,7 @@
         <v>1000</v>
       </c>
       <c r="AB48" t="n">
-        <v>15.5</v>
+        <v>29</v>
       </c>
       <c r="AC48" t="n">
         <v>14</v>
@@ -9762,7 +9762,7 @@
         <v>1000</v>
       </c>
       <c r="AG48" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AH48" t="n">
         <v>1000</v>
@@ -9789,62 +9789,62 @@
         <v>1000</v>
       </c>
       <c r="AP48" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="AQ48" t="n">
         <v>4.5</v>
       </c>
       <c r="AR48" t="n">
-        <v>3.25</v>
+        <v>2.12</v>
       </c>
       <c r="AS48" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AZ48" t="n">
         <v>3.35</v>
       </c>
-      <c r="AT48" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>4.4</v>
-      </c>
       <c r="BA48" t="n">
-        <v>2.98</v>
+        <v>2.12</v>
       </c>
       <c r="BB48" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BC48" t="n">
-        <v>4.4</v>
+        <v>3.15</v>
       </c>
       <c r="BD48" t="n">
-        <v>2.98</v>
+        <v>2.12</v>
       </c>
       <c r="BE48" t="n">
-        <v>4.2</v>
+        <v>2.76</v>
       </c>
       <c r="BF48" t="n">
         <v>4.1</v>
       </c>
       <c r="BG48" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>3.2</v>
       </c>
       <c r="G49" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="H49" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="I49" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J49" t="n">
         <v>3.05</v>
@@ -9920,10 +9920,10 @@
         <v>1.98</v>
       </c>
       <c r="U49" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V49" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W49" t="n">
         <v>1.4</v>
@@ -9935,13 +9935,13 @@
         <v>10</v>
       </c>
       <c r="Z49" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="AB49" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC49" t="n">
         <v>8.6</v>
@@ -9950,7 +9950,7 @@
         <v>15</v>
       </c>
       <c r="AE49" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AF49" t="n">
         <v>25</v>
@@ -9959,10 +9959,10 @@
         <v>17.5</v>
       </c>
       <c r="AH49" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI49" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AJ49" t="n">
         <v>900</v>
@@ -9980,19 +9980,19 @@
         <v>1000</v>
       </c>
       <c r="AO49" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP49" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR49" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AS49" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AT49" t="n">
         <v>8.800000000000001</v>
@@ -10004,7 +10004,7 @@
         <v>10.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AX49" t="n">
         <v>17.5</v>
@@ -10016,29 +10016,29 @@
         <v>18</v>
       </c>
       <c r="BA49" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BB49" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC49" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BD49" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BE49" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BF49" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -10102,7 +10102,7 @@
         <v>1.75</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R50" t="n">
         <v>1.28</v>
@@ -10147,7 +10147,7 @@
         <v>130</v>
       </c>
       <c r="AF50" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG50" t="n">
         <v>12.5</v>
@@ -10177,10 +10177,10 @@
         <v>1000</v>
       </c>
       <c r="AP50" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AQ50" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AR50" t="n">
         <v>4</v>
@@ -10192,31 +10192,31 @@
         <v>6.2</v>
       </c>
       <c r="AU50" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="AV50" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="AW50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX50" t="n">
         <v>3.35</v>
       </c>
       <c r="AY50" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AZ50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BC50" t="n">
         <v>3.75</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>3.7</v>
       </c>
       <c r="BD50" t="n">
         <v>4</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -10302,7 +10302,7 @@
         <v>1.22</v>
       </c>
       <c r="S51" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="T51" t="n">
         <v>2</v>
@@ -10380,7 +10380,7 @@
         <v>3.8</v>
       </c>
       <c r="AS51" t="n">
-        <v>25</v>
+        <v>4.7</v>
       </c>
       <c r="AT51" t="n">
         <v>8.800000000000001</v>
@@ -10422,11 +10422,11 @@
         <v>4.5</v>
       </c>
       <c r="BG51" t="n">
-        <v>21</v>
+        <v>4.4</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>
@@ -10475,7 +10475,7 @@
         <v>3.45</v>
       </c>
       <c r="L52" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M52" t="n">
         <v>1.13</v>
@@ -10502,7 +10502,7 @@
         <v>1.91</v>
       </c>
       <c r="U52" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="V52" t="n">
         <v>1.45</v>
@@ -10532,7 +10532,7 @@
         <v>16.5</v>
       </c>
       <c r="AE52" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AF52" t="n">
         <v>22</v>
@@ -10550,7 +10550,7 @@
         <v>65</v>
       </c>
       <c r="AK52" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AL52" t="n">
         <v>85</v>
@@ -10565,16 +10565,16 @@
         <v>70</v>
       </c>
       <c r="AP52" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="AQ52" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="AR52" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AS52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT52" t="n">
         <v>7.4</v>
@@ -10583,44 +10583,44 @@
         <v>6.2</v>
       </c>
       <c r="AV52" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="AW52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX52" t="n">
         <v>4.1</v>
       </c>
-      <c r="AX52" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AY52" t="n">
-        <v>3.5</v>
+        <v>10.5</v>
       </c>
       <c r="AZ52" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BA52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC52" t="n">
         <v>4.2</v>
       </c>
-      <c r="BB52" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC52" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD52" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE52" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BF52" t="n">
         <v>4.4</v>
       </c>
-      <c r="BF52" t="n">
-        <v>4.2</v>
-      </c>
       <c r="BG52" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-08 22:14:33</t>
+          <t>2026-03-09 00:24:14</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,25 +757,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="G2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="H2" t="n">
         <v>9.4</v>
       </c>
       <c r="I2" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="J2" t="n">
         <v>5.1</v>
       </c>
       <c r="K2" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
@@ -784,31 +784,31 @@
         <v>4.8</v>
       </c>
       <c r="O2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P2" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="R2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S2" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
         <v>1.97</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V2" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -865,7 +865,7 @@
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.15</v>
+        <v>3.7</v>
       </c>
       <c r="AQ2" t="n">
         <v>4.2</v>
@@ -883,7 +883,7 @@
         <v>5.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>14</v>
+        <v>4.2</v>
       </c>
       <c r="AW2" t="n">
         <v>4.2</v>
@@ -895,7 +895,7 @@
         <v>4.9</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="BA2" t="n">
         <v>4.2</v>
@@ -907,20 +907,20 @@
         <v>6.8</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="BG2" t="n">
         <v>4.2</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -951,76 +951,76 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="G3" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H3" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I3" t="n">
         <v>7</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="R3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S3" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="U3" t="n">
-        <v>1.76</v>
+        <v>1.71</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W3" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y3" t="n">
         <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AA3" t="n">
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD3" t="n">
         <v>26</v>
@@ -1035,16 +1035,16 @@
         <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="AI3" t="n">
         <v>1000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AK3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL3" t="n">
         <v>1000</v>
@@ -1053,22 +1053,22 @@
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AO3" t="n">
         <v>1000</v>
       </c>
       <c r="AP3" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.4</v>
+        <v>13.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>34</v>
+        <v>7.2</v>
       </c>
       <c r="AS3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT3" t="n">
         <v>5.9</v>
@@ -1080,10 +1080,10 @@
         <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>4.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY3" t="n">
         <v>8.6</v>
@@ -1092,29 +1092,29 @@
         <v>20</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
         <v>15</v>
       </c>
       <c r="BC3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD3" t="n">
         <v>7.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BF3" t="n">
-        <v>11.5</v>
+        <v>5.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1145,22 +1145,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="G4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K4" t="n">
         <v>3.25</v>
-      </c>
-      <c r="H4" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="K4" t="n">
-        <v>3.35</v>
       </c>
       <c r="L4" t="n">
         <v>1.56</v>
@@ -1169,64 +1169,64 @@
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
         <v>1.55</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
         <v>1.19</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="V4" t="n">
         <v>1.5</v>
       </c>
       <c r="W4" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X4" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Z4" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AB4" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>46</v>
+        <v>130</v>
       </c>
       <c r="AF4" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH4" t="n">
         <v>24</v>
@@ -1235,34 +1235,34 @@
         <v>260</v>
       </c>
       <c r="AJ4" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>160</v>
+        <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AO4" t="n">
         <v>55</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AR4" t="n">
         <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>16.5</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>7.6</v>
@@ -1271,44 +1271,44 @@
         <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AW4" t="n">
-        <v>18.5</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AZ4" t="n">
         <v>18</v>
       </c>
       <c r="BA4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF4" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB4" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BG4" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1339,16 +1339,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="J5" t="n">
         <v>3.25</v>
@@ -1363,22 +1363,22 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="O5" t="n">
         <v>1.49</v>
       </c>
       <c r="P5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="T5" t="n">
         <v>2.08</v>
@@ -1387,13 +1387,13 @@
         <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="W5" t="n">
         <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y5" t="n">
         <v>7.6</v>
@@ -1420,7 +1420,7 @@
         <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
@@ -1429,7 +1429,7 @@
         <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK5" t="n">
         <v>60</v>
@@ -1438,7 +1438,7 @@
         <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="AN5" t="n">
         <v>80</v>
@@ -1447,10 +1447,10 @@
         <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AR5" t="n">
         <v>11</v>
@@ -1474,22 +1474,22 @@
         <v>23</v>
       </c>
       <c r="AY5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="BC5" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="BD5" t="n">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="BE5" t="n">
         <v>38</v>
@@ -1498,11 +1498,11 @@
         <v>16</v>
       </c>
       <c r="BG5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G6" t="n">
         <v>27</v>
       </c>
       <c r="H6" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="J6" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="K6" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>1.32</v>
@@ -1557,31 +1557,31 @@
         <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O6" t="n">
         <v>1.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="R6" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="U6" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V6" t="n">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="W6" t="n">
         <v>1.04</v>
@@ -1590,13 +1590,13 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>9.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
@@ -1605,13 +1605,13 @@
         <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AG6" t="n">
         <v>1000</v>
@@ -1638,19 +1638,19 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="AP6" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
         <v>18.5</v>
@@ -1662,41 +1662,41 @@
         <v>10.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="AY6" t="n">
-        <v>7.6</v>
+        <v>26</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.8</v>
+        <v>11.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
-        <v>5.6</v>
+        <v>4.2</v>
       </c>
       <c r="BE6" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BF6" t="n">
         <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="H7" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="I7" t="n">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="J7" t="n">
         <v>3.3</v>
@@ -1751,55 +1751,55 @@
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P7" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="R7" t="n">
         <v>1.19</v>
       </c>
       <c r="S7" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="V7" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="X7" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Y7" t="n">
         <v>6.6</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
         <v>46</v>
       </c>
       <c r="AB7" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="AC7" t="n">
-        <v>13.5</v>
+        <v>8</v>
       </c>
       <c r="AD7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE7" t="n">
         <v>65</v>
@@ -1808,7 +1808,7 @@
         <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>980</v>
+        <v>48</v>
       </c>
       <c r="AH7" t="n">
         <v>65</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>5.7</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>6.6</v>
+        <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="AW7" t="n">
         <v>21</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>65</v>
+      </c>
+      <c r="BD7" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BB7" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE7" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF7" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
         <v>2.06</v>
       </c>
       <c r="G8" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H8" t="n">
         <v>4.1</v>
@@ -1933,34 +1933,34 @@
         <v>4.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.5</v>
       </c>
       <c r="L8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="n">
         <v>2.1</v>
@@ -1969,10 +1969,10 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X8" t="n">
         <v>9.4</v>
@@ -1981,7 +1981,7 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA8" t="n">
         <v>900</v>
@@ -1999,10 +1999,10 @@
         <v>1000</v>
       </c>
       <c r="AF8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AG8" t="n">
         <v>12</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>11.5</v>
       </c>
       <c r="AH8" t="n">
         <v>24</v>
@@ -2011,7 +2011,7 @@
         <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,59 +2032,59 @@
         <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>5.7</v>
       </c>
       <c r="AR8" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT8" t="n">
         <v>6</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="AV8" t="n">
         <v>16</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="AY8" t="n">
         <v>9.6</v>
       </c>
       <c r="AZ8" t="n">
-        <v>20</v>
+        <v>7.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>12</v>
+        <v>7.6</v>
       </c>
       <c r="BD8" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BG8" t="n">
         <v>9.4</v>
       </c>
-      <c r="BE8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>10</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2115,16 +2115,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="G9" t="n">
         <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J9" t="n">
         <v>4.4</v>
@@ -2145,7 +2145,7 @@
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q9" t="n">
         <v>2.12</v>
@@ -2184,7 +2184,7 @@
         <v>7.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AD9" t="n">
         <v>980</v>
@@ -2193,10 +2193,10 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>11.5</v>
       </c>
       <c r="AG9" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AH9" t="n">
         <v>980</v>
@@ -2211,13 +2211,13 @@
         <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>380</v>
+        <v>980</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
@@ -2226,25 +2226,25 @@
         <v>6.2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT9" t="n">
         <v>4.5</v>
       </c>
-      <c r="AT9" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AU9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV9" t="n">
         <v>16</v>
       </c>
       <c r="AW9" t="n">
-        <v>9.6</v>
+        <v>19.5</v>
       </c>
       <c r="AX9" t="n">
         <v>6.2</v>
@@ -2256,29 +2256,29 @@
         <v>9</v>
       </c>
       <c r="BA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB9" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>8.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BE9" t="n">
         <v>10</v>
       </c>
       <c r="BF9" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2312,61 +2312,61 @@
         <v>2.48</v>
       </c>
       <c r="G10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="H10" t="n">
         <v>2.78</v>
       </c>
-      <c r="H10" t="n">
-        <v>2.8</v>
-      </c>
       <c r="I10" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
         <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="M10" t="n">
         <v>1.08</v>
       </c>
       <c r="N10" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O10" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P10" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="S10" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="T10" t="n">
         <v>1.72</v>
       </c>
       <c r="U10" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W10" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X10" t="n">
         <v>15</v>
       </c>
       <c r="Y10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z10" t="n">
         <v>21</v>
@@ -2375,16 +2375,16 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE10" t="n">
-        <v>180</v>
+        <v>95</v>
       </c>
       <c r="AF10" t="n">
         <v>18</v>
@@ -2393,7 +2393,7 @@
         <v>12.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI10" t="n">
         <v>230</v>
@@ -2405,31 +2405,31 @@
         <v>110</v>
       </c>
       <c r="AL10" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AM10" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AO10" t="n">
         <v>500</v>
       </c>
       <c r="AP10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
       </c>
       <c r="AS10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT10" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>6.6</v>
@@ -2447,32 +2447,32 @@
         <v>10</v>
       </c>
       <c r="AZ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BB10" t="n">
-        <v>9.4</v>
+        <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="BD10" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H11" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="I11" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
         <v>3.15</v>
@@ -2527,43 +2527,43 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="P11" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="T11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="U11" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="V11" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="W11" t="n">
         <v>1.22</v>
       </c>
       <c r="X11" t="n">
-        <v>17.5</v>
+        <v>8.4</v>
       </c>
       <c r="Y11" t="n">
-        <v>12</v>
+        <v>6.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
         <v>900</v>
@@ -2587,7 +2587,7 @@
         <v>1000</v>
       </c>
       <c r="AH11" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AI11" t="n">
         <v>1000</v>
@@ -2608,19 +2608,19 @@
         <v>1000</v>
       </c>
       <c r="AO11" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR11" t="n">
         <v>6.6</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="AT11" t="n">
         <v>11</v>
@@ -2629,44 +2629,44 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW11" t="n">
+        <v>22</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG11" t="n">
         <v>10</v>
       </c>
-      <c r="AX11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2697,100 +2697,100 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="G12" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K12" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M12" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N12" t="n">
         <v>2.72</v>
       </c>
       <c r="O12" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S12" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="U12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="V12" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="X12" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y12" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Z12" t="n">
-        <v>80</v>
+        <v>190</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD12" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG12" t="n">
         <v>11.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AK12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL12" t="n">
         <v>65</v>
@@ -2799,68 +2799,68 @@
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT12" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
       <c r="AU12" t="n">
         <v>5.6</v>
       </c>
       <c r="AV12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC12" t="n">
         <v>7.6</v>
       </c>
-      <c r="AW12" t="n">
-        <v>9</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BA12" t="n">
+      <c r="BD12" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BB12" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="BF12" t="n">
-        <v>5.8</v>
+        <v>13.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -2891,170 +2891,170 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="G13" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="P13" t="n">
         <v>1.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R13" t="n">
         <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T13" t="n">
-        <v>2.52</v>
+        <v>2.3</v>
       </c>
       <c r="U13" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="X13" t="n">
         <v>14</v>
       </c>
       <c r="Y13" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Z13" t="n">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AA13" t="n">
-        <v>730</v>
+        <v>640</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC13" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AD13" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>380</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL13" t="n">
         <v>55</v>
       </c>
-      <c r="AE13" t="n">
-        <v>340</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>44</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>290</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>22</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>60</v>
-      </c>
       <c r="AM13" t="n">
-        <v>390</v>
+        <v>280</v>
       </c>
       <c r="AN13" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AO13" t="n">
-        <v>1000</v>
+        <v>420</v>
       </c>
       <c r="AP13" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
+        <v>26</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>30</v>
       </c>
-      <c r="AR13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>21</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY13" t="n">
+      <c r="BA13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB13" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>8.800000000000001</v>
       </c>
       <c r="BC13" t="n">
         <v>15.5</v>
       </c>
       <c r="BD13" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="BE13" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BF13" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H14" t="n">
         <v>3.4</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
         <v>3.2</v>
@@ -3115,10 +3115,10 @@
         <v>1.46</v>
       </c>
       <c r="P14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
@@ -3127,22 +3127,22 @@
         <v>4.8</v>
       </c>
       <c r="T14" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U14" t="n">
         <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X14" t="n">
         <v>17.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="Z14" t="n">
         <v>980</v>
@@ -3154,16 +3154,16 @@
         <v>15</v>
       </c>
       <c r="AC14" t="n">
-        <v>11.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>980</v>
+        <v>30</v>
       </c>
       <c r="AE14" t="n">
         <v>980</v>
       </c>
       <c r="AF14" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="AG14" t="n">
         <v>23</v>
@@ -3178,13 +3178,13 @@
         <v>980</v>
       </c>
       <c r="AK14" t="n">
-        <v>980</v>
+        <v>110</v>
       </c>
       <c r="AL14" t="n">
         <v>980</v>
       </c>
       <c r="AM14" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN14" t="n">
         <v>980</v>
@@ -3196,16 +3196,16 @@
         <v>7</v>
       </c>
       <c r="AQ14" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AR14" t="n">
         <v>15.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AT14" t="n">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AU14" t="n">
         <v>6.2</v>
@@ -3226,29 +3226,29 @@
         <v>13.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="BC14" t="n">
         <v>14.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BE14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>2.72</v>
       </c>
       <c r="G15" t="n">
-        <v>2.52</v>
+        <v>2.9</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>2.98</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J15" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="K15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L15" t="n">
         <v>1.58</v>
@@ -3303,16 +3303,16 @@
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="O15" t="n">
         <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
@@ -3324,28 +3324,28 @@
         <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="V15" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="X15" t="n">
-        <v>17.5</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AC15" t="n">
         <v>14</v>
@@ -3363,13 +3363,13 @@
         <v>1000</v>
       </c>
       <c r="AH15" t="n">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK15" t="n">
         <v>1000</v>
@@ -3381,34 +3381,34 @@
         <v>1000</v>
       </c>
       <c r="AN15" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AO15" t="n">
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AQ15" t="n">
         <v>5.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>5.1</v>
+        <v>2.6</v>
       </c>
       <c r="AT15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AW15" t="n">
         <v>4.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>4.3</v>
       </c>
       <c r="AX15" t="n">
         <v>6.4</v>
@@ -3417,32 +3417,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.46</v>
+        <v>4.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.84</v>
+        <v>8.6</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.05</v>
+        <v>3.95</v>
       </c>
       <c r="BE15" t="n">
-        <v>2.72</v>
+        <v>3.4</v>
       </c>
       <c r="BF15" t="n">
         <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.7</v>
+        <v>2.36</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
         <v>3.5</v>
@@ -3488,37 +3488,37 @@
         <v>3.75</v>
       </c>
       <c r="K16" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L16" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="O16" t="n">
         <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="R16" t="n">
         <v>1.49</v>
       </c>
       <c r="S16" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="V16" t="n">
         <v>1.76</v>
@@ -3536,13 +3536,13 @@
         <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>80</v>
+        <v>29</v>
       </c>
       <c r="AB16" t="n">
         <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD16" t="n">
         <v>13</v>
@@ -3551,7 +3551,7 @@
         <v>24</v>
       </c>
       <c r="AF16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG16" t="n">
         <v>16.5</v>
@@ -3569,16 +3569,16 @@
         <v>42</v>
       </c>
       <c r="AL16" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM16" t="n">
         <v>90</v>
       </c>
       <c r="AN16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AO16" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="AP16" t="n">
         <v>16</v>
@@ -3596,7 +3596,7 @@
         <v>11</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AV16" t="n">
         <v>9.6</v>
@@ -3614,19 +3614,19 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BB16" t="n">
         <v>5.7</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>5.8</v>
       </c>
       <c r="BC16" t="n">
         <v>29</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BF16" t="n">
         <v>19.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
         <v>3.5</v>
@@ -3700,7 +3700,7 @@
         <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
@@ -3784,7 +3784,7 @@
         <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>5.5</v>
+        <v>29</v>
       </c>
       <c r="AT17" t="n">
         <v>9.4</v>
@@ -3793,13 +3793,13 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>13</v>
+        <v>8.6</v>
       </c>
       <c r="AW17" t="n">
         <v>18</v>
       </c>
       <c r="AX17" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AY17" t="n">
         <v>9.6</v>
@@ -3808,10 +3808,10 @@
         <v>15</v>
       </c>
       <c r="BA17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC17" t="n">
         <v>12</v>
@@ -3820,7 +3820,7 @@
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -3876,13 +3876,13 @@
         <v>3.6</v>
       </c>
       <c r="K18" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L18" t="n">
         <v>1.37</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
         <v>4.2</v>
@@ -3903,10 +3903,10 @@
         <v>3.1</v>
       </c>
       <c r="T18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
         <v>1.44</v>
@@ -3915,7 +3915,7 @@
         <v>1.68</v>
       </c>
       <c r="X18" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="Y18" t="n">
         <v>14.5</v>
@@ -3927,7 +3927,7 @@
         <v>60</v>
       </c>
       <c r="AB18" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AC18" t="n">
         <v>9.4</v>
@@ -3936,13 +3936,13 @@
         <v>15.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AF18" t="n">
         <v>18.5</v>
       </c>
       <c r="AG18" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>20</v>
@@ -3966,7 +3966,7 @@
         <v>20</v>
       </c>
       <c r="AO18" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP18" t="n">
         <v>14.5</v>
@@ -4002,7 +4002,7 @@
         <v>13.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>6</v>
+        <v>19.5</v>
       </c>
       <c r="BB18" t="n">
         <v>14.5</v>
@@ -4014,7 +4014,7 @@
         <v>28</v>
       </c>
       <c r="BE18" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF18" t="n">
         <v>13.5</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4061,16 +4061,16 @@
         <v>4.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="I19" t="n">
         <v>2.28</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L19" t="n">
         <v>1.52</v>
@@ -4079,16 +4079,16 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>1.45</v>
       </c>
       <c r="P19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="R19" t="n">
         <v>1.24</v>
@@ -4106,7 +4106,7 @@
         <v>1.78</v>
       </c>
       <c r="W19" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X19" t="n">
         <v>12</v>
@@ -4133,16 +4133,16 @@
         <v>29</v>
       </c>
       <c r="AF19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG19" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="AJ19" t="n">
         <v>110</v>
@@ -4166,13 +4166,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AQ19" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AR19" t="n">
         <v>11.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4187,7 +4187,7 @@
         <v>15</v>
       </c>
       <c r="AX19" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY19" t="n">
         <v>14.5</v>
@@ -4196,29 +4196,29 @@
         <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>6.4</v>
+        <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BC19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE19" t="n">
         <v>7</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>6.8</v>
       </c>
       <c r="BF19" t="n">
         <v>12.5</v>
       </c>
       <c r="BG19" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4252,7 +4252,7 @@
         <v>1.98</v>
       </c>
       <c r="G20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H20" t="n">
         <v>4.6</v>
@@ -4261,7 +4261,7 @@
         <v>4.7</v>
       </c>
       <c r="J20" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K20" t="n">
         <v>3.6</v>
@@ -4285,22 +4285,22 @@
         <v>2.12</v>
       </c>
       <c r="R20" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S20" t="n">
         <v>3.9</v>
       </c>
       <c r="T20" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="U20" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
         <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X20" t="n">
         <v>12.5</v>
@@ -4315,16 +4315,16 @@
         <v>110</v>
       </c>
       <c r="AB20" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC20" t="n">
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AF20" t="n">
         <v>11.5</v>
@@ -4360,16 +4360,16 @@
         <v>11.5</v>
       </c>
       <c r="AQ20" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AR20" t="n">
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
@@ -4378,7 +4378,7 @@
         <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>15.5</v>
+        <v>44</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="BF20" t="n">
         <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>16.5</v>
+        <v>28</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
         <v>2.08</v>
       </c>
       <c r="I21" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.85</v>
       </c>
       <c r="L21" t="n">
         <v>1.38</v>
@@ -4467,13 +4467,13 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
         <v>1.87</v>
@@ -4482,16 +4482,16 @@
         <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T21" t="n">
         <v>1.75</v>
       </c>
       <c r="U21" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V21" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="W21" t="n">
         <v>1.33</v>
@@ -4503,7 +4503,7 @@
         <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AA21" t="n">
         <v>25</v>
@@ -4512,7 +4512,7 @@
         <v>16</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
         <v>10.5</v>
@@ -4521,10 +4521,10 @@
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG21" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH21" t="n">
         <v>17</v>
@@ -4533,7 +4533,7 @@
         <v>34</v>
       </c>
       <c r="AJ21" t="n">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AK21" t="n">
         <v>44</v>
@@ -4545,10 +4545,10 @@
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AP21" t="n">
         <v>14.5</v>
@@ -4560,13 +4560,13 @@
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
@@ -4575,38 +4575,38 @@
         <v>18.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY21" t="n">
         <v>14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
       </c>
       <c r="BB21" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="BC21" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BD21" t="n">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="BE21" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF21" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BG21" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>2.18</v>
       </c>
       <c r="H22" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="I22" t="n">
         <v>4.2</v>
@@ -4664,22 +4664,22 @@
         <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P22" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q22" t="n">
         <v>2.16</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T22" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="U22" t="n">
         <v>2</v>
@@ -4712,7 +4712,7 @@
         <v>500</v>
       </c>
       <c r="AE22" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF22" t="n">
         <v>500</v>
@@ -4742,7 +4742,7 @@
         <v>85</v>
       </c>
       <c r="AO22" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP22" t="n">
         <v>6.2</v>
@@ -4751,10 +4751,10 @@
         <v>7</v>
       </c>
       <c r="AR22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AS22" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AT22" t="n">
         <v>7.4</v>
@@ -4766,16 +4766,16 @@
         <v>9</v>
       </c>
       <c r="AW22" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BA22" t="n">
         <v>6</v>
@@ -4784,23 +4784,23 @@
         <v>13</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BE22" t="n">
         <v>6.2</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BG22" t="n">
         <v>6.2</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
         <v>2.66</v>
       </c>
       <c r="I23" t="n">
-        <v>2.82</v>
+        <v>2.72</v>
       </c>
       <c r="J23" t="n">
         <v>3.1</v>
@@ -4861,7 +4861,7 @@
         <v>1.39</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q23" t="n">
         <v>2.22</v>
@@ -4873,19 +4873,19 @@
         <v>4.1</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="U23" t="n">
         <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="W23" t="n">
         <v>1.45</v>
       </c>
       <c r="X23" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
         <v>10.5</v>
@@ -4936,7 +4936,7 @@
         <v>1000</v>
       </c>
       <c r="AO23" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP23" t="n">
         <v>9.4</v>
@@ -4945,25 +4945,25 @@
         <v>5.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS23" t="n">
-        <v>16</v>
+        <v>8.4</v>
       </c>
       <c r="AT23" t="n">
-        <v>5.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU23" t="n">
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="AW23" t="n">
         <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>15.5</v>
+        <v>11</v>
       </c>
       <c r="AY23" t="n">
         <v>11.5</v>
@@ -4975,7 +4975,7 @@
         <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC23" t="n">
         <v>18.5</v>
@@ -4987,14 +4987,14 @@
         <v>28</v>
       </c>
       <c r="BF23" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG23" t="n">
-        <v>9.199999999999999</v>
+        <v>22</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5025,19 +5025,19 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="H24" t="n">
         <v>4.4</v>
       </c>
       <c r="I24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J24" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
         <v>3.5</v>
@@ -5052,37 +5052,37 @@
         <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="P24" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T24" t="n">
-        <v>1.99</v>
+        <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="V24" t="n">
         <v>1.27</v>
       </c>
       <c r="W24" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="X24" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y24" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="Z24" t="n">
         <v>980</v>
@@ -5091,7 +5091,7 @@
         <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AC24" t="n">
         <v>8</v>
@@ -5106,16 +5106,16 @@
         <v>23</v>
       </c>
       <c r="AG24" t="n">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>380</v>
+        <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>120</v>
+        <v>980</v>
       </c>
       <c r="AK24" t="n">
         <v>65</v>
@@ -5127,37 +5127,37 @@
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="AO24" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AR24" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AS24" t="n">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="AT24" t="n">
         <v>6.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AW24" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>9.4</v>
+        <v>5.9</v>
       </c>
       <c r="AY24" t="n">
         <v>6.2</v>
@@ -5166,29 +5166,29 @@
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>8.199999999999999</v>
+        <v>70</v>
       </c>
       <c r="BB24" t="n">
-        <v>11.5</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
         <v>11.5</v>
       </c>
       <c r="BD24" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BE24" t="n">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BF24" t="n">
-        <v>6.8</v>
+        <v>17.5</v>
       </c>
       <c r="BG24" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
       <c r="G25" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
         <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="J25" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K25" t="n">
         <v>3.3</v>
-      </c>
-      <c r="K25" t="n">
-        <v>3.35</v>
       </c>
       <c r="L25" t="n">
         <v>1.49</v>
@@ -5243,73 +5243,73 @@
         <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O25" t="n">
         <v>1.41</v>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R25" t="n">
         <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T25" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U25" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W25" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="X25" t="n">
         <v>11</v>
       </c>
       <c r="Y25" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AA25" t="n">
         <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
       </c>
       <c r="AD25" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AE25" t="n">
         <v>55</v>
       </c>
       <c r="AF25" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>65</v>
+        <v>150</v>
       </c>
       <c r="AJ25" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AK25" t="n">
         <v>32</v>
@@ -5324,7 +5324,7 @@
         <v>30</v>
       </c>
       <c r="AO25" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -5333,56 +5333,56 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AX25" t="n">
         <v>14.5</v>
       </c>
       <c r="AY25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
         <v>16.5</v>
       </c>
       <c r="BA25" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="BB25" t="n">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="BC25" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BD25" t="n">
         <v>40</v>
       </c>
       <c r="BE25" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BG25" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
         <v>3.4</v>
       </c>
       <c r="J26" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5440,7 +5440,7 @@
         <v>6.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
         <v>2.88</v>
@@ -5458,10 +5458,10 @@
         <v>1.46</v>
       </c>
       <c r="U26" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="V26" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W26" t="n">
         <v>1.78</v>
@@ -5470,7 +5470,7 @@
         <v>80</v>
       </c>
       <c r="Y26" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="Z26" t="n">
         <v>80</v>
@@ -5479,13 +5479,13 @@
         <v>300</v>
       </c>
       <c r="AB26" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>24</v>
+        <v>15.5</v>
       </c>
       <c r="AE26" t="n">
         <v>75</v>
@@ -5518,10 +5518,10 @@
         <v>9.6</v>
       </c>
       <c r="AO26" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AP26" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ26" t="n">
         <v>18.5</v>
@@ -5530,13 +5530,13 @@
         <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>8.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT26" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AU26" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV26" t="n">
         <v>12.5</v>
@@ -5545,7 +5545,7 @@
         <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>10.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY26" t="n">
         <v>10</v>
@@ -5554,29 +5554,29 @@
         <v>11</v>
       </c>
       <c r="BA26" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="BB26" t="n">
         <v>14.5</v>
       </c>
       <c r="BC26" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="BD26" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="BE26" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BF26" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BG26" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
         <v>1.55</v>
       </c>
       <c r="I27" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="J27" t="n">
         <v>3.9</v>
@@ -5634,13 +5634,13 @@
         <v>2.88</v>
       </c>
       <c r="O27" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="R27" t="n">
         <v>1.22</v>
@@ -5649,7 +5649,7 @@
         <v>5.1</v>
       </c>
       <c r="T27" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U27" t="n">
         <v>1.57</v>
@@ -5661,7 +5661,7 @@
         <v>1.11</v>
       </c>
       <c r="X27" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.8</v>
@@ -5670,7 +5670,7 @@
         <v>7.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AB27" t="n">
         <v>21</v>
@@ -5688,10 +5688,10 @@
         <v>80</v>
       </c>
       <c r="AG27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AH27" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AI27" t="n">
         <v>70</v>
@@ -5703,19 +5703,19 @@
         <v>230</v>
       </c>
       <c r="AL27" t="n">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="AM27" t="n">
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="AO27" t="n">
         <v>13.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AQ27" t="n">
         <v>5.3</v>
@@ -5724,7 +5724,7 @@
         <v>6.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT27" t="n">
         <v>19</v>
@@ -5739,38 +5739,38 @@
         <v>19.5</v>
       </c>
       <c r="AX27" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AY27" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AZ27" t="n">
         <v>30</v>
       </c>
       <c r="BA27" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB27" t="n">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BC27" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BD27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BE27" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BF27" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="BG27" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5801,16 +5801,16 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G28" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="H28" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="I28" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J28" t="n">
         <v>3.25</v>
@@ -5828,7 +5828,7 @@
         <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="P28" t="n">
         <v>1.64</v>
@@ -5837,31 +5837,31 @@
         <v>2.46</v>
       </c>
       <c r="R28" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S28" t="n">
         <v>4.8</v>
       </c>
       <c r="T28" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U28" t="n">
         <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W28" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X28" t="n">
         <v>18.5</v>
       </c>
       <c r="Y28" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="Z28" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="AA28" t="n">
         <v>900</v>
@@ -5879,7 +5879,7 @@
         <v>65</v>
       </c>
       <c r="AF28" t="n">
-        <v>90</v>
+        <v>980</v>
       </c>
       <c r="AG28" t="n">
         <v>34</v>
@@ -5903,13 +5903,13 @@
         <v>580</v>
       </c>
       <c r="AN28" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO28" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
@@ -5924,10 +5924,10 @@
         <v>10.5</v>
       </c>
       <c r="AU28" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV28" t="n">
         <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>6.4</v>
       </c>
       <c r="AW28" t="n">
         <v>22</v>
@@ -5936,35 +5936,35 @@
         <v>11.5</v>
       </c>
       <c r="AY28" t="n">
-        <v>9</v>
+        <v>13.5</v>
       </c>
       <c r="AZ28" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB28" t="n">
-        <v>9.4</v>
+        <v>13</v>
       </c>
       <c r="BC28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG28" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD28" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -5995,40 +5995,40 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J29" t="n">
         <v>3.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L29" t="n">
         <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="O29" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="P29" t="n">
         <v>1.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="R29" t="n">
         <v>1.2</v>
@@ -6037,22 +6037,22 @@
         <v>5.3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U29" t="n">
         <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X29" t="n">
         <v>10.5</v>
       </c>
       <c r="Y29" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z29" t="n">
         <v>95</v>
@@ -6061,13 +6061,13 @@
         <v>900</v>
       </c>
       <c r="AB29" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AC29" t="n">
         <v>7.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="AE29" t="n">
         <v>700</v>
@@ -6109,22 +6109,22 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>24</v>
+        <v>7.8</v>
       </c>
       <c r="AS29" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT29" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU29" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -6133,32 +6133,32 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA29" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD29" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB29" t="n">
-        <v>21</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>8</v>
-      </c>
       <c r="BE29" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BF29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BG29" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
         <v>1.48</v>
@@ -6222,7 +6222,7 @@
         <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="R30" t="n">
         <v>1.22</v>
@@ -6231,7 +6231,7 @@
         <v>4.8</v>
       </c>
       <c r="T30" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="U30" t="n">
         <v>1.79</v>
@@ -6255,7 +6255,7 @@
         <v>1000</v>
       </c>
       <c r="AB30" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AC30" t="n">
         <v>9</v>
@@ -6273,13 +6273,13 @@
         <v>12.5</v>
       </c>
       <c r="AH30" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AI30" t="n">
         <v>1000</v>
       </c>
       <c r="AJ30" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AK30" t="n">
         <v>65</v>
@@ -6291,7 +6291,7 @@
         <v>1000</v>
       </c>
       <c r="AN30" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>1000</v>
@@ -6300,59 +6300,59 @@
         <v>5.1</v>
       </c>
       <c r="AQ30" t="n">
-        <v>7</v>
+        <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AT30" t="n">
         <v>6</v>
       </c>
       <c r="AU30" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="AW30" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AX30" t="n">
-        <v>8.199999999999999</v>
+        <v>5.6</v>
       </c>
       <c r="AY30" t="n">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>5.6</v>
+        <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="BB30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BF30" t="n">
         <v>6</v>
       </c>
-      <c r="BC30" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BD30" t="n">
-        <v>6</v>
-      </c>
-      <c r="BE30" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF30" t="n">
-        <v>5.3</v>
-      </c>
       <c r="BG30" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -6383,16 +6383,16 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="G31" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="H31" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I31" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
         <v>3.8</v>
@@ -6401,19 +6401,19 @@
         <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M31" t="n">
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O31" t="n">
         <v>1.36</v>
       </c>
       <c r="P31" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="Q31" t="n">
         <v>2.12</v>
@@ -6422,22 +6422,22 @@
         <v>1.3</v>
       </c>
       <c r="S31" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T31" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="V31" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W31" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="X31" t="n">
-        <v>26</v>
+        <v>90</v>
       </c>
       <c r="Y31" t="n">
         <v>1000</v>
@@ -6449,19 +6449,19 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF31" t="n">
         <v>15</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>20</v>
       </c>
       <c r="AG31" t="n">
         <v>21</v>
@@ -6473,7 +6473,7 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="AK31" t="n">
         <v>1000</v>
@@ -6491,62 +6491,62 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AQ31" t="n">
         <v>8.4</v>
       </c>
       <c r="AR31" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>5.7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT31" t="n">
-        <v>6.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AX31" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY31" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>7</v>
+        <v>14.5</v>
       </c>
       <c r="BA31" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="BE31" t="n">
         <v>12.5</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC31" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD31" t="n">
-        <v>3</v>
-      </c>
-      <c r="BE31" t="n">
-        <v>13</v>
       </c>
       <c r="BF31" t="n">
         <v>9</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -6586,13 +6586,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J32" t="n">
         <v>4.1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L32" t="n">
         <v>1.48</v>
@@ -6604,7 +6604,7 @@
         <v>3.15</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
         <v>1.73</v>
@@ -6616,13 +6616,13 @@
         <v>1.27</v>
       </c>
       <c r="S32" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U32" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="V32" t="n">
         <v>1.12</v>
@@ -6634,7 +6634,7 @@
         <v>14.5</v>
       </c>
       <c r="Y32" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="Z32" t="n">
         <v>190</v>
@@ -6658,7 +6658,7 @@
         <v>9</v>
       </c>
       <c r="AG32" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="AH32" t="n">
         <v>980</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>5.2</v>
+        <v>17.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AT32" t="n">
         <v>5.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX32" t="n">
         <v>6.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AZ32" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BA32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD32" t="n">
         <v>6.2</v>
       </c>
-      <c r="BB32" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BE32" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF32" t="n">
         <v>9.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -6771,79 +6771,79 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="G33" t="n">
-        <v>5.3</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>1.93</v>
+        <v>2.34</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>2.46</v>
       </c>
       <c r="J33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K33" t="n">
         <v>3.3</v>
       </c>
-      <c r="K33" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L33" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P33" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.44</v>
+        <v>2.52</v>
       </c>
       <c r="R33" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="S33" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="U33" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="V33" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="W33" t="n">
-        <v>1.23</v>
+        <v>1.34</v>
       </c>
       <c r="X33" t="n">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="Z33" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>34</v>
+        <v>900</v>
       </c>
       <c r="AB33" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AC33" t="n">
         <v>9</v>
       </c>
       <c r="AD33" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AE33" t="n">
         <v>34</v>
@@ -6852,22 +6852,22 @@
         <v>40</v>
       </c>
       <c r="AG33" t="n">
-        <v>23</v>
+        <v>18.5</v>
       </c>
       <c r="AH33" t="n">
         <v>28</v>
       </c>
       <c r="AI33" t="n">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>200</v>
+        <v>480</v>
       </c>
       <c r="AL33" t="n">
-        <v>260</v>
+        <v>1000</v>
       </c>
       <c r="AM33" t="n">
         <v>1000</v>
@@ -6876,22 +6876,22 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ33" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AR33" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT33" t="n">
         <v>9.199999999999999</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>10.5</v>
       </c>
       <c r="AU33" t="n">
         <v>6.6</v>
@@ -6903,38 +6903,38 @@
         <v>13</v>
       </c>
       <c r="AX33" t="n">
-        <v>5.7</v>
+        <v>13.5</v>
       </c>
       <c r="AY33" t="n">
-        <v>10.5</v>
+        <v>13.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.4</v>
+        <v>23</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="BD33" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
       <c r="BE33" t="n">
-        <v>5.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF33" t="n">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BG33" t="n">
-        <v>17.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H34" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="L34" t="n">
         <v>1.41</v>
@@ -7013,7 +7013,7 @@
         <v>2.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W34" t="n">
         <v>1.78</v>
@@ -7022,7 +7022,7 @@
         <v>90</v>
       </c>
       <c r="Y34" t="n">
-        <v>500</v>
+        <v>27</v>
       </c>
       <c r="Z34" t="n">
         <v>500</v>
@@ -7040,13 +7040,13 @@
         <v>500</v>
       </c>
       <c r="AE34" t="n">
-        <v>170</v>
+        <v>500</v>
       </c>
       <c r="AF34" t="n">
         <v>28</v>
       </c>
       <c r="AG34" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AH34" t="n">
         <v>32</v>
@@ -7058,7 +7058,7 @@
         <v>900</v>
       </c>
       <c r="AK34" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AL34" t="n">
         <v>1000</v>
@@ -7079,10 +7079,10 @@
         <v>11.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS34" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AT34" t="n">
         <v>5.6</v>
@@ -7094,7 +7094,7 @@
         <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="AX34" t="n">
         <v>7</v>
@@ -7106,29 +7106,29 @@
         <v>10.5</v>
       </c>
       <c r="BA34" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BD34" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB34" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BE34" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF34" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG34" t="n">
         <v>7.4</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -7159,22 +7159,22 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="G35" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="H35" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I35" t="n">
         <v>7.2</v>
       </c>
       <c r="J35" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L35" t="n">
         <v>1.34</v>
@@ -7183,7 +7183,7 @@
         <v>1.04</v>
       </c>
       <c r="N35" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O35" t="n">
         <v>1.23</v>
@@ -7192,106 +7192,106 @@
         <v>2.38</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R35" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S35" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="T35" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U35" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="V35" t="n">
         <v>1.16</v>
       </c>
       <c r="W35" t="n">
-        <v>2.84</v>
+        <v>2.78</v>
       </c>
       <c r="X35" t="n">
         <v>22</v>
       </c>
       <c r="Y35" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Z35" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="AA35" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB35" t="n">
         <v>10</v>
       </c>
       <c r="AC35" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AE35" t="n">
-        <v>230</v>
+        <v>85</v>
       </c>
       <c r="AF35" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG35" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AH35" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI35" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AJ35" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AK35" t="n">
         <v>15</v>
       </c>
       <c r="AL35" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM35" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AN35" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AO35" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP35" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS35" t="n">
         <v>19.5</v>
       </c>
-      <c r="AQ35" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>22</v>
+      </c>
+      <c r="AW35" t="n">
         <v>42</v>
       </c>
-      <c r="AS35" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>19</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>50</v>
-      </c>
       <c r="AX35" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AY35" t="n">
         <v>9.199999999999999</v>
@@ -7300,10 +7300,10 @@
         <v>18.5</v>
       </c>
       <c r="BA35" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB35" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC35" t="n">
         <v>14</v>
@@ -7312,17 +7312,17 @@
         <v>26</v>
       </c>
       <c r="BE35" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G36" t="n">
         <v>3.7</v>
@@ -7368,7 +7368,7 @@
         <v>3.45</v>
       </c>
       <c r="K36" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.45</v>
@@ -7377,10 +7377,10 @@
         <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O36" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P36" t="n">
         <v>1.84</v>
@@ -7407,19 +7407,19 @@
         <v>1.37</v>
       </c>
       <c r="X36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z36" t="n">
         <v>15</v>
       </c>
       <c r="AA36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB36" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC36" t="n">
         <v>8.199999999999999</v>
@@ -7428,7 +7428,7 @@
         <v>12</v>
       </c>
       <c r="AE36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF36" t="n">
         <v>26</v>
@@ -7437,28 +7437,28 @@
         <v>16</v>
       </c>
       <c r="AH36" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI36" t="n">
         <v>44</v>
       </c>
       <c r="AJ36" t="n">
-        <v>75</v>
+        <v>440</v>
       </c>
       <c r="AK36" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AL36" t="n">
         <v>60</v>
       </c>
       <c r="AM36" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN36" t="n">
         <v>75</v>
       </c>
       <c r="AO36" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP36" t="n">
         <v>11</v>
@@ -7473,7 +7473,7 @@
         <v>23</v>
       </c>
       <c r="AT36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AU36" t="n">
         <v>6.8</v>
@@ -7482,7 +7482,7 @@
         <v>9.6</v>
       </c>
       <c r="AW36" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX36" t="n">
         <v>21</v>
@@ -7494,29 +7494,29 @@
         <v>16</v>
       </c>
       <c r="BA36" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="BB36" t="n">
+        <v>24</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>29</v>
+      </c>
+      <c r="BD36" t="n">
         <v>23</v>
       </c>
-      <c r="BC36" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BE36" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="BF36" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG36" t="n">
         <v>18</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -7547,67 +7547,67 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G37" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H37" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K37" t="n">
         <v>3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M37" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P37" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="R37" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U37" t="n">
         <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="W37" t="n">
         <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z37" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA37" t="n">
         <v>50</v>
@@ -7628,7 +7628,7 @@
         <v>17</v>
       </c>
       <c r="AG37" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH37" t="n">
         <v>22</v>
@@ -7637,7 +7637,7 @@
         <v>65</v>
       </c>
       <c r="AJ37" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK37" t="n">
         <v>38</v>
@@ -7646,31 +7646,31 @@
         <v>60</v>
       </c>
       <c r="AM37" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN37" t="n">
         <v>42</v>
       </c>
       <c r="AO37" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AP37" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ37" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR37" t="n">
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AT37" t="n">
         <v>8</v>
       </c>
       <c r="AU37" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AV37" t="n">
         <v>12</v>
@@ -7679,38 +7679,38 @@
         <v>34</v>
       </c>
       <c r="AX37" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AY37" t="n">
         <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="BB37" t="n">
-        <v>13.5</v>
+        <v>40</v>
       </c>
       <c r="BC37" t="n">
         <v>32</v>
       </c>
       <c r="BD37" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BE37" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BF37" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="BG37" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -7741,64 +7741,64 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G38" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="H38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I38" t="n">
         <v>3.65</v>
       </c>
-      <c r="I38" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K38" t="n">
         <v>3.3</v>
       </c>
-      <c r="K38" t="n">
-        <v>3.35</v>
-      </c>
       <c r="L38" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="O38" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="P38" t="n">
         <v>1.76</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="R38" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S38" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="T38" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U38" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="V38" t="n">
         <v>1.37</v>
       </c>
       <c r="W38" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="X38" t="n">
         <v>11</v>
       </c>
       <c r="Y38" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Z38" t="n">
         <v>24</v>
@@ -7825,25 +7825,25 @@
         <v>11.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI38" t="n">
         <v>60</v>
       </c>
       <c r="AJ38" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AK38" t="n">
         <v>27</v>
       </c>
       <c r="AL38" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM38" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO38" t="n">
         <v>60</v>
@@ -7852,7 +7852,7 @@
         <v>10</v>
       </c>
       <c r="AQ38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR38" t="n">
         <v>22</v>
@@ -7888,23 +7888,23 @@
         <v>27</v>
       </c>
       <c r="BC38" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD38" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BE38" t="n">
         <v>100</v>
       </c>
       <c r="BF38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BG38" t="n">
         <v>50</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -7941,10 +7941,10 @@
         <v>1.95</v>
       </c>
       <c r="H39" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I39" t="n">
         <v>4.9</v>
-      </c>
-      <c r="I39" t="n">
-        <v>5</v>
       </c>
       <c r="J39" t="n">
         <v>3.55</v>
@@ -7953,13 +7953,13 @@
         <v>3.6</v>
       </c>
       <c r="L39" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
         <v>1.1</v>
       </c>
       <c r="N39" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
         <v>1.42</v>
@@ -8001,13 +8001,13 @@
         <v>120</v>
       </c>
       <c r="AB39" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC39" t="n">
         <v>7.8</v>
       </c>
       <c r="AD39" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE39" t="n">
         <v>75</v>
@@ -8052,7 +8052,7 @@
         <v>30</v>
       </c>
       <c r="AS39" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AT39" t="n">
         <v>7.2</v>
@@ -8088,17 +8088,17 @@
         <v>40</v>
       </c>
       <c r="BE39" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="BF39" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BG39" t="n">
         <v>85</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -8132,28 +8132,28 @@
         <v>2.12</v>
       </c>
       <c r="G40" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="H40" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="I40" t="n">
         <v>4</v>
       </c>
-      <c r="I40" t="n">
-        <v>4.2</v>
-      </c>
       <c r="J40" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
         <v>3.55</v>
       </c>
       <c r="L40" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M40" t="n">
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="O40" t="n">
         <v>1.38</v>
@@ -8162,49 +8162,49 @@
         <v>1.81</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R40" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S40" t="n">
         <v>4</v>
       </c>
       <c r="T40" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U40" t="n">
         <v>2.02</v>
       </c>
       <c r="V40" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="X40" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Y40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA40" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AC40" t="n">
         <v>7.6</v>
       </c>
       <c r="AD40" t="n">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="AF40" t="n">
         <v>12.5</v>
@@ -8228,10 +8228,10 @@
         <v>40</v>
       </c>
       <c r="AM40" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN40" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AO40" t="n">
         <v>75</v>
@@ -8240,43 +8240,43 @@
         <v>11.5</v>
       </c>
       <c r="AQ40" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR40" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS40" t="n">
         <v>70</v>
       </c>
       <c r="AT40" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU40" t="n">
         <v>7.2</v>
       </c>
       <c r="AV40" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AW40" t="n">
+        <v>46</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA40" t="n">
         <v>48</v>
-      </c>
-      <c r="AX40" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY40" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AZ40" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA40" t="n">
-        <v>50</v>
       </c>
       <c r="BB40" t="n">
         <v>24</v>
       </c>
       <c r="BC40" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD40" t="n">
         <v>36</v>
@@ -8285,14 +8285,14 @@
         <v>85</v>
       </c>
       <c r="BF40" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BG40" t="n">
         <v>50</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -8326,22 +8326,22 @@
         <v>2.14</v>
       </c>
       <c r="G41" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H41" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="I41" t="n">
         <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K41" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L41" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
@@ -8353,10 +8353,10 @@
         <v>1.37</v>
       </c>
       <c r="P41" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R41" t="n">
         <v>1.29</v>
@@ -8374,22 +8374,22 @@
         <v>1.34</v>
       </c>
       <c r="W41" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="X41" t="n">
         <v>13</v>
       </c>
       <c r="Y41" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="Z41" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="AA41" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB41" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC41" t="n">
         <v>8.199999999999999</v>
@@ -8401,7 +8401,7 @@
         <v>55</v>
       </c>
       <c r="AF41" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AG41" t="n">
         <v>11.5</v>
@@ -8410,16 +8410,16 @@
         <v>20</v>
       </c>
       <c r="AI41" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ41" t="n">
         <v>85</v>
       </c>
       <c r="AK41" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AL41" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="AM41" t="n">
         <v>580</v>
@@ -8428,7 +8428,7 @@
         <v>22</v>
       </c>
       <c r="AO41" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP41" t="n">
         <v>10</v>
@@ -8437,31 +8437,31 @@
         <v>10.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AS41" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT41" t="n">
         <v>7.6</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>7.2</v>
       </c>
       <c r="AU41" t="n">
         <v>6.6</v>
       </c>
       <c r="AV41" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW41" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="AX41" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY41" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ41" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA41" t="n">
         <v>8.199999999999999</v>
@@ -8473,20 +8473,20 @@
         <v>21</v>
       </c>
       <c r="BD41" t="n">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="BE41" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF41" t="n">
         <v>17.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>7.6</v>
+        <v>11</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
         <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="M42" t="n">
         <v>1.1</v>
@@ -8619,7 +8619,7 @@
         <v>580</v>
       </c>
       <c r="AN42" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AO42" t="n">
         <v>700</v>
@@ -8634,7 +8634,7 @@
         <v>7.2</v>
       </c>
       <c r="AS42" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AT42" t="n">
         <v>6.2</v>
@@ -8646,7 +8646,7 @@
         <v>18</v>
       </c>
       <c r="AW42" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AX42" t="n">
         <v>8.800000000000001</v>
@@ -8658,7 +8658,7 @@
         <v>19.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB42" t="n">
         <v>18</v>
@@ -8667,7 +8667,7 @@
         <v>19.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE42" t="n">
         <v>36</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -8711,16 +8711,16 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="G43" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="H43" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="J43" t="n">
         <v>3.05</v>
@@ -8729,7 +8729,7 @@
         <v>3.25</v>
       </c>
       <c r="L43" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M43" t="n">
         <v>1.12</v>
@@ -8738,13 +8738,13 @@
         <v>2.84</v>
       </c>
       <c r="O43" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P43" t="n">
         <v>1.59</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="R43" t="n">
         <v>1.21</v>
@@ -8756,7 +8756,7 @@
         <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="V43" t="n">
         <v>1.66</v>
@@ -8765,7 +8765,7 @@
         <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Y43" t="n">
         <v>8.199999999999999</v>
@@ -8816,7 +8816,7 @@
         <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AP43" t="n">
         <v>8</v>
@@ -8858,23 +8858,23 @@
         <v>9.6</v>
       </c>
       <c r="BC43" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BD43" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE43" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF43" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG43" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -8908,16 +8908,16 @@
         <v>3.95</v>
       </c>
       <c r="G44" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H44" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I44" t="n">
         <v>2.42</v>
       </c>
       <c r="J44" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="K44" t="n">
         <v>3.1</v>
@@ -8935,7 +8935,7 @@
         <v>1.44</v>
       </c>
       <c r="P44" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q44" t="n">
         <v>2.36</v>
@@ -8956,40 +8956,40 @@
         <v>1.7</v>
       </c>
       <c r="W44" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X44" t="n">
-        <v>19</v>
+        <v>10.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>980</v>
+        <v>8.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA44" t="n">
         <v>900</v>
       </c>
       <c r="AB44" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="AC44" t="n">
-        <v>11.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD44" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="AE44" t="n">
         <v>110</v>
       </c>
       <c r="AF44" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="AG44" t="n">
-        <v>980</v>
+        <v>34</v>
       </c>
       <c r="AH44" t="n">
-        <v>980</v>
+        <v>36</v>
       </c>
       <c r="AI44" t="n">
         <v>980</v>
@@ -9010,19 +9010,19 @@
         <v>500</v>
       </c>
       <c r="AO44" t="n">
-        <v>980</v>
+        <v>70</v>
       </c>
       <c r="AP44" t="n">
         <v>7.4</v>
       </c>
       <c r="AQ44" t="n">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="AR44" t="n">
         <v>11</v>
       </c>
       <c r="AS44" t="n">
-        <v>8.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="AT44" t="n">
         <v>6.4</v>
@@ -9031,10 +9031,10 @@
         <v>6</v>
       </c>
       <c r="AV44" t="n">
-        <v>7</v>
+        <v>9.6</v>
       </c>
       <c r="AW44" t="n">
-        <v>8.4</v>
+        <v>21</v>
       </c>
       <c r="AX44" t="n">
         <v>10.5</v>
@@ -9046,29 +9046,29 @@
         <v>9</v>
       </c>
       <c r="BA44" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB44" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="BC44" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BD44" t="n">
-        <v>4.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE44" t="n">
-        <v>6.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF44" t="n">
         <v>8.4</v>
       </c>
       <c r="BG44" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -9108,13 +9108,13 @@
         <v>7.2</v>
       </c>
       <c r="I45" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J45" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K45" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L45" t="n">
         <v>1.41</v>
@@ -9210,7 +9210,7 @@
         <v>13</v>
       </c>
       <c r="AQ45" t="n">
-        <v>15.5</v>
+        <v>19</v>
       </c>
       <c r="AR45" t="n">
         <v>30</v>
@@ -9225,7 +9225,7 @@
         <v>9</v>
       </c>
       <c r="AV45" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AW45" t="n">
         <v>40</v>
@@ -9246,7 +9246,7 @@
         <v>11.5</v>
       </c>
       <c r="BC45" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD45" t="n">
         <v>26</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G46" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="H46" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="J46" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L46" t="n">
         <v>1.38</v>
@@ -9317,146 +9317,146 @@
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O46" t="n">
         <v>1.29</v>
       </c>
       <c r="P46" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R46" t="n">
         <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T46" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="U46" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="V46" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W46" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="X46" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="Y46" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="Z46" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AA46" t="n">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="AB46" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD46" t="n">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="AE46" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AF46" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG46" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH46" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI46" t="n">
-        <v>520</v>
+        <v>160</v>
       </c>
       <c r="AJ46" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK46" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="AL46" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM46" t="n">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="AN46" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AO46" t="n">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="AP46" t="n">
         <v>14</v>
       </c>
       <c r="AQ46" t="n">
-        <v>12.5</v>
+        <v>24</v>
       </c>
       <c r="AR46" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AS46" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY46" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AT46" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>7</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AZ46" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA46" t="n">
-        <v>8.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="BB46" t="n">
         <v>10.5</v>
       </c>
       <c r="BC46" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="BD46" t="n">
-        <v>19.5</v>
+        <v>30</v>
       </c>
       <c r="BE46" t="n">
         <v>34</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.9</v>
+        <v>5.1</v>
       </c>
       <c r="BG46" t="n">
         <v>15</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="G47" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H47" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I47" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J47" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N47" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="P47" t="n">
         <v>1.73</v>
       </c>
-      <c r="G47" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="H47" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="I47" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K47" t="n">
+      <c r="Q47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S47" t="n">
         <v>4.1</v>
       </c>
-      <c r="L47" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="M47" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S47" t="n">
-        <v>4</v>
-      </c>
       <c r="T47" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="U47" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V47" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="W47" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="X47" t="n">
         <v>90</v>
@@ -9553,7 +9553,7 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="AC47" t="n">
         <v>16</v>
@@ -9589,68 +9589,68 @@
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>29</v>
+        <v>85</v>
       </c>
       <c r="AO47" t="n">
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
       <c r="AQ47" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AR47" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AS47" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AT47" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AU47" t="n">
         <v>4.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>3.95</v>
+        <v>2.64</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="AX47" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="AY47" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AZ47" t="n">
-        <v>3.95</v>
+        <v>2.5</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="BB47" t="n">
-        <v>3.95</v>
+        <v>2.62</v>
       </c>
       <c r="BC47" t="n">
-        <v>3.65</v>
+        <v>2.42</v>
       </c>
       <c r="BD47" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.54</v>
+        <v>2.4</v>
       </c>
       <c r="BF47" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="BG47" t="n">
-        <v>4.5</v>
+        <v>2.68</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -9681,19 +9681,19 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G48" t="n">
         <v>3.4</v>
       </c>
       <c r="H48" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="I48" t="n">
         <v>2.64</v>
       </c>
       <c r="J48" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K48" t="n">
         <v>3.3</v>
@@ -9714,13 +9714,13 @@
         <v>1.61</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="T48" t="n">
         <v>1.98</v>
@@ -9729,7 +9729,7 @@
         <v>1.86</v>
       </c>
       <c r="V48" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W48" t="n">
         <v>1.42</v>
@@ -9738,7 +9738,7 @@
         <v>10</v>
       </c>
       <c r="Y48" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Z48" t="n">
         <v>15.5</v>
@@ -9750,10 +9750,10 @@
         <v>10.5</v>
       </c>
       <c r="AC48" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD48" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AE48" t="n">
         <v>40</v>
@@ -9798,7 +9798,7 @@
         <v>13</v>
       </c>
       <c r="AS48" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AT48" t="n">
         <v>8.800000000000001</v>
@@ -9810,10 +9810,10 @@
         <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX48" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AY48" t="n">
         <v>12</v>
@@ -9822,29 +9822,29 @@
         <v>18</v>
       </c>
       <c r="BA48" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="BB48" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BC48" t="n">
-        <v>6.6</v>
+        <v>38</v>
       </c>
       <c r="BD48" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE48" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BF48" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BG48" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -9878,13 +9878,13 @@
         <v>1.72</v>
       </c>
       <c r="G49" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H49" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I49" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J49" t="n">
         <v>3.7</v>
@@ -9899,13 +9899,13 @@
         <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>1.38</v>
       </c>
       <c r="P49" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="Q49" t="n">
         <v>2.18</v>
@@ -9917,16 +9917,16 @@
         <v>4.1</v>
       </c>
       <c r="T49" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U49" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V49" t="n">
         <v>1.19</v>
       </c>
       <c r="W49" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X49" t="n">
         <v>14.5</v>
@@ -9983,28 +9983,28 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AQ49" t="n">
         <v>3.7</v>
       </c>
       <c r="AR49" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS49" t="n">
         <v>4.3</v>
       </c>
       <c r="AT49" t="n">
-        <v>6.2</v>
+        <v>3.15</v>
       </c>
       <c r="AU49" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="AV49" t="n">
         <v>3.85</v>
       </c>
       <c r="AW49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX49" t="n">
         <v>3.4</v>
@@ -10013,13 +10013,13 @@
         <v>3.35</v>
       </c>
       <c r="AZ49" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BA49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB49" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="BC49" t="n">
         <v>3.75</v>
@@ -10028,17 +10028,17 @@
         <v>4</v>
       </c>
       <c r="BE49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF49" t="n">
         <v>9.6</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -10099,7 +10099,7 @@
         <v>1.48</v>
       </c>
       <c r="P50" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q50" t="n">
         <v>2.5</v>
@@ -10114,7 +10114,7 @@
         <v>2</v>
       </c>
       <c r="U50" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V50" t="n">
         <v>1.62</v>
@@ -10129,34 +10129,34 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z50" t="n">
-        <v>17.5</v>
+        <v>15</v>
       </c>
       <c r="AA50" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AB50" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC50" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AD50" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AE50" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF50" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AG50" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AH50" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AI50" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ50" t="n">
         <v>85</v>
@@ -10174,7 +10174,7 @@
         <v>80</v>
       </c>
       <c r="AO50" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AP50" t="n">
         <v>8.4</v>
@@ -10183,10 +10183,10 @@
         <v>7.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="AS50" t="n">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="AT50" t="n">
         <v>8.800000000000001</v>
@@ -10198,7 +10198,7 @@
         <v>10</v>
       </c>
       <c r="AW50" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AX50" t="n">
         <v>20</v>
@@ -10210,29 +10210,29 @@
         <v>18</v>
       </c>
       <c r="BA50" t="n">
-        <v>4.9</v>
+        <v>6.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BC50" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BD50" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="BE50" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="BF50" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BG50" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G51" t="n">
         <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K51" t="n">
         <v>3.15</v>
-      </c>
-      <c r="J51" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3.2</v>
       </c>
       <c r="L51" t="n">
         <v>1.58</v>
@@ -10290,19 +10290,19 @@
         <v>2.72</v>
       </c>
       <c r="O51" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="P51" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="R51" t="n">
         <v>1.2</v>
       </c>
       <c r="S51" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="T51" t="n">
         <v>1.91</v>
@@ -10311,7 +10311,7 @@
         <v>1.68</v>
       </c>
       <c r="V51" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W51" t="n">
         <v>1.5</v>
@@ -10320,22 +10320,22 @@
         <v>10.5</v>
       </c>
       <c r="Y51" t="n">
-        <v>10.5</v>
+        <v>980</v>
       </c>
       <c r="Z51" t="n">
         <v>23</v>
       </c>
       <c r="AA51" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AB51" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC51" t="n">
-        <v>8</v>
+        <v>980</v>
       </c>
       <c r="AD51" t="n">
-        <v>16.5</v>
+        <v>980</v>
       </c>
       <c r="AE51" t="n">
         <v>980</v>
@@ -10344,13 +10344,13 @@
         <v>22</v>
       </c>
       <c r="AG51" t="n">
-        <v>16</v>
+        <v>980</v>
       </c>
       <c r="AH51" t="n">
         <v>27</v>
       </c>
       <c r="AI51" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AJ51" t="n">
         <v>65</v>
@@ -10362,71 +10362,71 @@
         <v>70</v>
       </c>
       <c r="AM51" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN51" t="n">
         <v>65</v>
       </c>
       <c r="AO51" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AP51" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ51" t="n">
         <v>7.2</v>
       </c>
       <c r="AR51" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="AS51" t="n">
-        <v>5.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT51" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU51" t="n">
         <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="AW51" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX51" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="AY51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ51" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
       <c r="BA51" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BB51" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BC51" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="BD51" t="n">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="BE51" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BF51" t="n">
-        <v>5.3</v>
+        <v>7.4</v>
       </c>
       <c r="BG51" t="n">
-        <v>5.3</v>
+        <v>38</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-09 02:33:46</t>
+          <t>2026-03-09 04:43:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="G2" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="H2" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I2" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.04</v>
       </c>
       <c r="N2" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P2" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="S2" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T2" t="n">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="X2" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y2" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,104 +823,104 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>14.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AL2" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.7</v>
+        <v>17.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4.2</v>
+        <v>24</v>
       </c>
       <c r="AR2" t="n">
-        <v>4.2</v>
+        <v>27</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>4.4</v>
+        <v>7.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>4.2</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>4.1</v>
+        <v>7.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.9</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2.9</v>
+        <v>21</v>
       </c>
       <c r="BA2" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="BB2" t="n">
-        <v>5.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BD2" t="n">
-        <v>2.9</v>
+        <v>25</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.1</v>
+        <v>110</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.95</v>
+        <v>5.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="G3" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="H3" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="M3" t="n">
         <v>1.09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.05</v>
+        <v>2.86</v>
       </c>
       <c r="O3" t="n">
         <v>1.41</v>
       </c>
       <c r="P3" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="S3" t="n">
         <v>4.3</v>
       </c>
       <c r="T3" t="n">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="U3" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.18</v>
+        <v>1.94</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z3" t="n">
         <v>150</v>
@@ -1017,104 +1017,104 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AC3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX3" t="n">
         <v>9</v>
       </c>
-      <c r="AD3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ3" t="n">
+      <c r="AY3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB3" t="n">
         <v>19</v>
       </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV3" t="n">
+      <c r="BC3" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BD3" t="n">
         <v>20</v>
       </c>
-      <c r="AW3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>15</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BE3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BF3" t="n">
-        <v>5.5</v>
+        <v>16</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1145,58 +1145,58 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="H4" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
         <v>3.05</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="O4" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="T4" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="X4" t="n">
         <v>9.199999999999999</v>
@@ -1208,7 +1208,7 @@
         <v>18</v>
       </c>
       <c r="AA4" t="n">
-        <v>200</v>
+        <v>170</v>
       </c>
       <c r="AB4" t="n">
         <v>9.800000000000001</v>
@@ -1220,7 +1220,7 @@
         <v>14.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
@@ -1232,7 +1232,7 @@
         <v>24</v>
       </c>
       <c r="AI4" t="n">
-        <v>260</v>
+        <v>200</v>
       </c>
       <c r="AJ4" t="n">
         <v>65</v>
@@ -1241,7 +1241,7 @@
         <v>500</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>240</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1262,7 +1262,7 @@
         <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="n">
         <v>7.6</v>
@@ -1271,10 +1271,10 @@
         <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
@@ -1286,29 +1286,29 @@
         <v>18</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>38</v>
       </c>
       <c r="BB4" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BD4" t="n">
         <v>50</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BF4" t="n">
         <v>7.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1339,22 +1339,22 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="H5" t="n">
-        <v>2.24</v>
+        <v>2.34</v>
       </c>
       <c r="I5" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="J5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K5" t="n">
         <v>3.25</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.3</v>
       </c>
       <c r="L5" t="n">
         <v>1.54</v>
@@ -1363,70 +1363,70 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.98</v>
+        <v>2.94</v>
       </c>
       <c r="O5" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
         <v>1.89</v>
       </c>
       <c r="V5" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="X5" t="n">
         <v>9.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AA5" t="n">
         <v>32</v>
       </c>
       <c r="AB5" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AE5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
         <v>26</v>
       </c>
       <c r="AG5" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH5" t="n">
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
         <v>85</v>
@@ -1435,31 +1435,31 @@
         <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AM5" t="n">
-        <v>180</v>
+        <v>500</v>
       </c>
       <c r="AN5" t="n">
         <v>80</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AT5" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU5" t="n">
         <v>6.8</v>
@@ -1468,41 +1468,41 @@
         <v>10.5</v>
       </c>
       <c r="AW5" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AX5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
         <v>46</v>
       </c>
       <c r="BB5" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="BC5" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="BD5" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BE5" t="n">
-        <v>38</v>
+        <v>130</v>
       </c>
       <c r="BF5" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="BG5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1533,55 +1533,55 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="H6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="I6" t="n">
         <v>1.2</v>
       </c>
-      <c r="I6" t="n">
-        <v>1.21</v>
-      </c>
       <c r="J6" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="S6" t="n">
-        <v>2.74</v>
+        <v>2.52</v>
       </c>
       <c r="T6" t="n">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="U6" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="V6" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
         <v>1.04</v>
@@ -1590,10 +1590,10 @@
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>980</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AA6" t="n">
         <v>1000</v>
@@ -1605,7 +1605,7 @@
         <v>1000</v>
       </c>
       <c r="AD6" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
         <v>1000</v>
@@ -1638,49 +1638,49 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="AP6" t="n">
         <v>22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="AR6" t="n">
-        <v>4.9</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AT6" t="n">
         <v>18.5</v>
       </c>
       <c r="AU6" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV6" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY6" t="n">
         <v>14</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>26</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>9</v>
+        <v>4.2</v>
       </c>
       <c r="BD6" t="n">
         <v>4.2</v>
@@ -1692,11 +1692,11 @@
         <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1727,82 +1727,82 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="I7" t="n">
-        <v>1.99</v>
+        <v>1.89</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O7" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="P7" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="R7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U7" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="V7" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="W7" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
         <v>10.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="AB7" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AC7" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>20</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="AF7" t="n">
         <v>500</v>
@@ -1811,10 +1811,10 @@
         <v>48</v>
       </c>
       <c r="AH7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
         <v>1000</v>
@@ -1832,65 +1832,65 @@
         <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU7" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.8</v>
+        <v>17.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>10.5</v>
+        <v>20</v>
       </c>
       <c r="AZ7" t="n">
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD7" t="n">
         <v>9.4</v>
       </c>
-      <c r="BC7" t="n">
-        <v>65</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BE7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -1921,46 +1921,46 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="I8" t="n">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T8" t="n">
         <v>2.1</v>
@@ -1969,22 +1969,22 @@
         <v>1.76</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X8" t="n">
         <v>9.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z8" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB8" t="n">
         <v>7.4</v>
@@ -1993,10 +1993,10 @@
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AF8" t="n">
         <v>12.5</v>
@@ -2008,10 +2008,10 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AK8" t="n">
         <v>30</v>
@@ -2023,7 +2023,7 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
@@ -2032,59 +2032,59 @@
         <v>8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>5.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR8" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT8" t="n">
         <v>6</v>
       </c>
       <c r="AU8" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AX8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BE8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF8" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BG8" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2121,58 +2121,58 @@
         <v>1.48</v>
       </c>
       <c r="H9" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="I9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J9" t="n">
         <v>4.4</v>
       </c>
       <c r="K9" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.31</v>
       </c>
       <c r="S9" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="U9" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W9" t="n">
         <v>3.05</v>
       </c>
       <c r="X9" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="Y9" t="n">
-        <v>80</v>
+        <v>980</v>
       </c>
       <c r="Z9" t="n">
         <v>480</v>
@@ -2181,10 +2181,10 @@
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AC9" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AD9" t="n">
         <v>980</v>
@@ -2199,19 +2199,19 @@
         <v>19.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>980</v>
+        <v>180</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AK9" t="n">
         <v>65</v>
       </c>
       <c r="AL9" t="n">
-        <v>980</v>
+        <v>380</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
@@ -2223,28 +2223,28 @@
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AT9" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="AU9" t="n">
         <v>6.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>19.5</v>
+        <v>29</v>
       </c>
       <c r="AX9" t="n">
         <v>6.2</v>
@@ -2253,32 +2253,32 @@
         <v>7.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>9</v>
+        <v>19.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="BB9" t="n">
         <v>6.2</v>
       </c>
       <c r="BC9" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BD9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BE9" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BG9" t="n">
         <v>10</v>
       </c>
-      <c r="BF9" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G10" t="n">
         <v>2.82</v>
@@ -2351,7 +2351,7 @@
         <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
         <v>2.14</v>
@@ -2420,19 +2420,19 @@
         <v>12.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
         <v>17</v>
       </c>
       <c r="AS10" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV10" t="n">
         <v>11</v>
@@ -2441,7 +2441,7 @@
         <v>18</v>
       </c>
       <c r="AX10" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY10" t="n">
         <v>10</v>
@@ -2450,29 +2450,29 @@
         <v>14</v>
       </c>
       <c r="BA10" t="n">
-        <v>9.800000000000001</v>
+        <v>23</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>13</v>
+        <v>17.5</v>
       </c>
       <c r="BD10" t="n">
-        <v>9.800000000000001</v>
+        <v>18.5</v>
       </c>
       <c r="BE10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BF10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>8.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="H11" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K11" t="n">
         <v>3.4</v>
@@ -2527,25 +2527,25 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="O11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="P11" t="n">
         <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="T11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="U11" t="n">
         <v>1.67</v>
@@ -2563,40 +2563,40 @@
         <v>6.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB11" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AC11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD11" t="n">
         <v>23</v>
       </c>
       <c r="AE11" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AF11" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG11" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AH11" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI11" t="n">
         <v>500</v>
       </c>
-      <c r="AI11" t="n">
-        <v>1000</v>
-      </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2614,7 +2614,7 @@
         <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="AR11" t="n">
         <v>6.6</v>
@@ -2629,7 +2629,7 @@
         <v>6.8</v>
       </c>
       <c r="AV11" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AW11" t="n">
         <v>22</v>
@@ -2638,35 +2638,35 @@
         <v>13.5</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AZ11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA11" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB11" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BD11" t="n">
         <v>7.8</v>
       </c>
-      <c r="BC11" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BE11" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF11" t="n">
-        <v>8</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2697,40 +2697,40 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="G12" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="M12" t="n">
         <v>1.11</v>
       </c>
       <c r="N12" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="O12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P12" t="n">
         <v>1.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R12" t="n">
         <v>1.2</v>
@@ -2739,7 +2739,7 @@
         <v>5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="U12" t="n">
         <v>1.62</v>
@@ -2748,7 +2748,7 @@
         <v>1.14</v>
       </c>
       <c r="W12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="X12" t="n">
         <v>9.800000000000001</v>
@@ -2808,10 +2808,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ12" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>8.6</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>9.800000000000001</v>
@@ -2820,22 +2820,22 @@
         <v>5.1</v>
       </c>
       <c r="AU12" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV12" t="n">
         <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>9.800000000000001</v>
+        <v>36</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA12" t="n">
         <v>9.4</v>
@@ -2844,10 +2844,10 @@
         <v>14.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD12" t="n">
-        <v>8.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
         <v>9.6</v>
@@ -2856,11 +2856,11 @@
         <v>13.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -2894,82 +2894,82 @@
         <v>1.39</v>
       </c>
       <c r="G13" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H13" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J13" t="n">
         <v>4.9</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="M13" t="n">
         <v>1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O13" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
         <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U13" t="n">
         <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="X13" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Y13" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="Z13" t="n">
-        <v>110</v>
+        <v>140</v>
       </c>
       <c r="AA13" t="n">
-        <v>640</v>
+        <v>510</v>
       </c>
       <c r="AB13" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD13" t="n">
         <v>42</v>
       </c>
       <c r="AE13" t="n">
-        <v>380</v>
+        <v>230</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
@@ -2993,22 +2993,22 @@
         <v>280</v>
       </c>
       <c r="AN13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO13" t="n">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="AP13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AR13" t="n">
         <v>16.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
@@ -3017,44 +3017,44 @@
         <v>10</v>
       </c>
       <c r="AV13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AW13" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA13" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="BB13" t="n">
         <v>10</v>
       </c>
       <c r="BC13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD13" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="BE13" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="BF13" t="n">
         <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3085,22 +3085,22 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="G14" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L14" t="n">
         <v>1.54</v>
@@ -3109,91 +3109,91 @@
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="O14" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="P14" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="R14" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S14" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T14" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U14" t="n">
         <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="X14" t="n">
-        <v>17.5</v>
+        <v>13.5</v>
       </c>
       <c r="Y14" t="n">
         <v>22</v>
       </c>
       <c r="Z14" t="n">
-        <v>980</v>
+        <v>70</v>
       </c>
       <c r="AA14" t="n">
         <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AE14" t="n">
-        <v>980</v>
+        <v>250</v>
       </c>
       <c r="AF14" t="n">
         <v>30</v>
       </c>
       <c r="AG14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AI14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>500</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>980</v>
       </c>
       <c r="AK14" t="n">
         <v>110</v>
       </c>
       <c r="AL14" t="n">
-        <v>980</v>
+        <v>150</v>
       </c>
       <c r="AM14" t="n">
         <v>580</v>
       </c>
       <c r="AN14" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AO14" t="n">
         <v>600</v>
       </c>
       <c r="AP14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AQ14" t="n">
         <v>8.4</v>
@@ -3208,7 +3208,7 @@
         <v>7.4</v>
       </c>
       <c r="AU14" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV14" t="n">
         <v>11.5</v>
@@ -3223,19 +3223,19 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>13.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA14" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BB14" t="n">
         <v>16</v>
       </c>
       <c r="BC14" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="BE14" t="n">
         <v>29</v>
@@ -3244,11 +3244,11 @@
         <v>11</v>
       </c>
       <c r="BG14" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3279,13 +3279,13 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="G15" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="H15" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I15" t="n">
         <v>3.3</v>
@@ -3297,7 +3297,7 @@
         <v>3.25</v>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
@@ -3309,10 +3309,10 @@
         <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
@@ -3327,31 +3327,31 @@
         <v>1.78</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
         <v>1.53</v>
       </c>
       <c r="X15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z15" t="n">
         <v>90</v>
       </c>
-      <c r="Y15" t="n">
-        <v>25</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AE15" t="n">
         <v>440</v>
@@ -3360,16 +3360,16 @@
         <v>1000</v>
       </c>
       <c r="AG15" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AI15" t="n">
         <v>1000</v>
       </c>
       <c r="AJ15" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AK15" t="n">
         <v>1000</v>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AR15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AV15" t="n">
         <v>10.5</v>
       </c>
-      <c r="AS15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>7.6</v>
-      </c>
       <c r="AW15" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="AX15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY15" t="n">
         <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="BA15" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BB15" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC15" t="n">
-        <v>8.6</v>
+        <v>16</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="BF15" t="n">
         <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.36</v>
+        <v>3.4</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="J16" t="n">
         <v>3.75</v>
@@ -3497,34 +3497,34 @@
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="O16" t="n">
         <v>1.24</v>
       </c>
       <c r="P16" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
         <v>1.73</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
         <v>2.82</v>
       </c>
       <c r="T16" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U16" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X16" t="n">
         <v>23</v>
@@ -3536,7 +3536,7 @@
         <v>19</v>
       </c>
       <c r="AA16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AB16" t="n">
         <v>18</v>
@@ -3563,7 +3563,7 @@
         <v>36</v>
       </c>
       <c r="AJ16" t="n">
-        <v>900</v>
+        <v>55</v>
       </c>
       <c r="AK16" t="n">
         <v>42</v>
@@ -3617,7 +3617,7 @@
         <v>14.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BC16" t="n">
         <v>29</v>
@@ -3626,7 +3626,7 @@
         <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BF16" t="n">
         <v>19.5</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3670,10 +3670,10 @@
         <v>2.14</v>
       </c>
       <c r="G17" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I17" t="n">
         <v>3.8</v>
@@ -3691,22 +3691,22 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O17" t="n">
         <v>1.29</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="R17" t="n">
         <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T17" t="n">
         <v>1.72</v>
@@ -3718,10 +3718,10 @@
         <v>1.36</v>
       </c>
       <c r="W17" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="X17" t="n">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="Y17" t="n">
         <v>18</v>
@@ -3742,7 +3742,7 @@
         <v>18</v>
       </c>
       <c r="AE17" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF17" t="n">
         <v>16.5</v>
@@ -3760,10 +3760,10 @@
         <v>32</v>
       </c>
       <c r="AK17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM17" t="n">
         <v>200</v>
@@ -3805,7 +3805,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ17" t="n">
-        <v>15</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA17" t="n">
         <v>23</v>
@@ -3820,7 +3820,7 @@
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BF17" t="n">
         <v>13.5</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -3861,64 +3861,64 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="G18" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I18" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K18" t="n">
         <v>3.8</v>
       </c>
       <c r="L18" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="M18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.06</v>
+        <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>3.1</v>
+        <v>3.45</v>
       </c>
       <c r="T18" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="W18" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="Z18" t="n">
         <v>25</v>
@@ -3927,104 +3927,104 @@
         <v>60</v>
       </c>
       <c r="AB18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>42</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AG18" t="n">
         <v>12.5</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>12</v>
       </c>
       <c r="AH18" t="n">
         <v>20</v>
       </c>
       <c r="AI18" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AJ18" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AK18" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="AM18" t="n">
         <v>200</v>
       </c>
       <c r="AN18" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AP18" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AQ18" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AR18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS18" t="n">
         <v>42</v>
       </c>
       <c r="AT18" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY18" t="n">
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA18" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
-        <v>14.5</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD18" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BF18" t="n">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>21</v>
+        <v>7.8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4055,13 +4055,13 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="G19" t="n">
         <v>4.2</v>
       </c>
       <c r="H19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="I19" t="n">
         <v>2.28</v>
@@ -4079,25 +4079,25 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="O19" t="n">
         <v>1.45</v>
       </c>
       <c r="P19" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="Q19" t="n">
         <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S19" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="T19" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="U19" t="n">
         <v>1.9</v>
@@ -4109,7 +4109,7 @@
         <v>1.31</v>
       </c>
       <c r="X19" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="Y19" t="n">
         <v>9</v>
@@ -4142,13 +4142,13 @@
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="AJ19" t="n">
         <v>110</v>
       </c>
       <c r="AK19" t="n">
-        <v>370</v>
+        <v>160</v>
       </c>
       <c r="AL19" t="n">
         <v>95</v>
@@ -4199,16 +4199,16 @@
         <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
       </c>
       <c r="BD19" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BE19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF19" t="n">
         <v>12.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
@@ -4258,7 +4258,7 @@
         <v>4.6</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.55</v>
@@ -4267,7 +4267,7 @@
         <v>3.6</v>
       </c>
       <c r="L20" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -4276,10 +4276,10 @@
         <v>3.6</v>
       </c>
       <c r="O20" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P20" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
         <v>2.12</v>
@@ -4288,16 +4288,16 @@
         <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="U20" t="n">
         <v>2.04</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
@@ -4321,40 +4321,40 @@
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>32</v>
+        <v>18.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF20" t="n">
         <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AH20" t="n">
         <v>20</v>
       </c>
       <c r="AI20" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ20" t="n">
         <v>23</v>
       </c>
       <c r="AK20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL20" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>580</v>
+        <v>500</v>
       </c>
       <c r="AN20" t="n">
         <v>16.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>270</v>
+        <v>120</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
@@ -4363,10 +4363,10 @@
         <v>14</v>
       </c>
       <c r="AR20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS20" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AT20" t="n">
         <v>7.8</v>
@@ -4375,7 +4375,7 @@
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AW20" t="n">
         <v>44</v>
@@ -4384,16 +4384,16 @@
         <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA20" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="BB20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC20" t="n">
         <v>20</v>
@@ -4402,17 +4402,17 @@
         <v>34</v>
       </c>
       <c r="BE20" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="BF20" t="n">
         <v>14.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4443,13 +4443,13 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
         <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I21" t="n">
         <v>2.1</v>
@@ -4467,7 +4467,7 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
@@ -4476,31 +4476,31 @@
         <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S21" t="n">
         <v>3.2</v>
       </c>
       <c r="T21" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="U21" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V21" t="n">
         <v>1.9</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X21" t="n">
         <v>16.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Z21" t="n">
         <v>14</v>
@@ -4509,31 +4509,31 @@
         <v>25</v>
       </c>
       <c r="AB21" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AG21" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH21" t="n">
         <v>17</v>
       </c>
       <c r="AI21" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ21" t="n">
-        <v>190</v>
+        <v>80</v>
       </c>
       <c r="AK21" t="n">
         <v>44</v>
@@ -4545,7 +4545,7 @@
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>44</v>
+        <v>600</v>
       </c>
       <c r="AO21" t="n">
         <v>13.5</v>
@@ -4566,7 +4566,7 @@
         <v>14.5</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
@@ -4581,32 +4581,32 @@
         <v>14</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BB21" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="BC21" t="n">
         <v>38</v>
       </c>
       <c r="BD21" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BF21" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BG21" t="n">
         <v>12</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4637,7 +4637,7 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="G22" t="n">
         <v>2.18</v>
@@ -4649,52 +4649,52 @@
         <v>4.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L22" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M22" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O22" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P22" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="R22" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S22" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="U22" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="W22" t="n">
         <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="Y22" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z22" t="n">
         <v>80</v>
@@ -4703,7 +4703,7 @@
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC22" t="n">
         <v>9.4</v>
@@ -4712,7 +4712,7 @@
         <v>500</v>
       </c>
       <c r="AE22" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AF22" t="n">
         <v>500</v>
@@ -4724,7 +4724,7 @@
         <v>60</v>
       </c>
       <c r="AI22" t="n">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ22" t="n">
         <v>80</v>
@@ -4733,7 +4733,7 @@
         <v>30</v>
       </c>
       <c r="AL22" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>1000</v>
@@ -4745,62 +4745,62 @@
         <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ22" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR22" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
       </c>
       <c r="AV22" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW22" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="AX22" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY22" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>5.3</v>
+        <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
       </c>
       <c r="BC22" t="n">
-        <v>5.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE22" t="n">
-        <v>6.2</v>
+        <v>28</v>
       </c>
       <c r="BF22" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="BG22" t="n">
-        <v>6.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -4831,61 +4831,61 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="G23" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H23" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="I23" t="n">
         <v>2.72</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K23" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L23" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="M23" t="n">
         <v>1.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P23" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="R23" t="n">
         <v>1.29</v>
       </c>
       <c r="S23" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="T23" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U23" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V23" t="n">
         <v>1.58</v>
       </c>
       <c r="W23" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="X23" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="Y23" t="n">
         <v>10.5</v>
@@ -4927,7 +4927,7 @@
         <v>500</v>
       </c>
       <c r="AL23" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
         <v>1000</v>
@@ -4939,16 +4939,16 @@
         <v>600</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AQ23" t="n">
         <v>5.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>8.4</v>
+        <v>18.5</v>
       </c>
       <c r="AT23" t="n">
         <v>9.4</v>
@@ -4975,7 +4975,7 @@
         <v>23</v>
       </c>
       <c r="BB23" t="n">
-        <v>8.800000000000001</v>
+        <v>20</v>
       </c>
       <c r="BC23" t="n">
         <v>18.5</v>
@@ -4984,7 +4984,7 @@
         <v>8.6</v>
       </c>
       <c r="BE23" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BF23" t="n">
         <v>7.8</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G24" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H24" t="n">
         <v>4.4</v>
@@ -5049,34 +5049,34 @@
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
         <v>1.46</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="R24" t="n">
         <v>1.24</v>
       </c>
       <c r="S24" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T24" t="n">
         <v>2.04</v>
       </c>
       <c r="U24" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V24" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="X24" t="n">
         <v>10.5</v>
@@ -5127,7 +5127,7 @@
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="AO24" t="n">
         <v>600</v>
@@ -5136,10 +5136,10 @@
         <v>7.8</v>
       </c>
       <c r="AQ24" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AR24" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AS24" t="n">
         <v>10</v>
@@ -5151,13 +5151,13 @@
         <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW24" t="n">
         <v>23</v>
       </c>
       <c r="AX24" t="n">
-        <v>5.9</v>
+        <v>10</v>
       </c>
       <c r="AY24" t="n">
         <v>6.2</v>
@@ -5166,29 +5166,29 @@
         <v>15</v>
       </c>
       <c r="BA24" t="n">
-        <v>70</v>
+        <v>46</v>
       </c>
       <c r="BB24" t="n">
         <v>20</v>
       </c>
       <c r="BC24" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD24" t="n">
         <v>27</v>
       </c>
       <c r="BE24" t="n">
+        <v>28</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BG24" t="n">
         <v>10.5</v>
       </c>
-      <c r="BF24" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BG24" t="n">
-        <v>12</v>
-      </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="G25" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H25" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I25" t="n">
         <v>3.1</v>
       </c>
-      <c r="I25" t="n">
-        <v>3.15</v>
-      </c>
       <c r="J25" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K25" t="n">
         <v>3.3</v>
@@ -5240,46 +5240,46 @@
         <v>1.49</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O25" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="P25" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="T25" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U25" t="n">
         <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W25" t="n">
         <v>1.58</v>
       </c>
       <c r="X25" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AA25" t="n">
         <v>60</v>
@@ -5297,7 +5297,7 @@
         <v>55</v>
       </c>
       <c r="AF25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG25" t="n">
         <v>12</v>
@@ -5306,7 +5306,7 @@
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AJ25" t="n">
         <v>40</v>
@@ -5315,16 +5315,16 @@
         <v>32</v>
       </c>
       <c r="AL25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM25" t="n">
         <v>500</v>
       </c>
       <c r="AN25" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO25" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
@@ -5333,56 +5333,56 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS25" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="AT25" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AU25" t="n">
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AW25" t="n">
         <v>34</v>
       </c>
       <c r="AX25" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BA25" t="n">
         <v>23</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="BC25" t="n">
+        <v>27</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE25" t="n">
         <v>28</v>
       </c>
-      <c r="BD25" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BF25" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BG25" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="G26" t="n">
         <v>2.28</v>
       </c>
       <c r="H26" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I26" t="n">
         <v>3.4</v>
@@ -5428,7 +5428,7 @@
         <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L26" t="n">
         <v>1.26</v>
@@ -5437,34 +5437,34 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P26" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R26" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="S26" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
         <v>1.46</v>
       </c>
       <c r="U26" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="V26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="W26" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X26" t="n">
         <v>80</v>
@@ -5479,7 +5479,7 @@
         <v>300</v>
       </c>
       <c r="AB26" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC26" t="n">
         <v>10.5</v>
@@ -5515,10 +5515,10 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
-        <v>600</v>
+        <v>19</v>
       </c>
       <c r="AP26" t="n">
         <v>16.5</v>
@@ -5530,13 +5530,13 @@
         <v>14.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>10.5</v>
+        <v>25</v>
       </c>
       <c r="AT26" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AU26" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV26" t="n">
         <v>12.5</v>
@@ -5569,14 +5569,14 @@
         <v>27</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG26" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -5607,16 +5607,16 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G27" t="n">
         <v>10</v>
       </c>
       <c r="H27" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="I27" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J27" t="n">
         <v>3.9</v>
@@ -5631,28 +5631,28 @@
         <v>1.11</v>
       </c>
       <c r="N27" t="n">
-        <v>2.88</v>
+        <v>2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P27" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="U27" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
         <v>2.72</v>
@@ -5664,7 +5664,7 @@
         <v>9.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="Z27" t="n">
         <v>7.6</v>
@@ -5673,7 +5673,7 @@
         <v>13.5</v>
       </c>
       <c r="AB27" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="AC27" t="n">
         <v>9.6</v>
@@ -5700,7 +5700,7 @@
         <v>440</v>
       </c>
       <c r="AK27" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="AL27" t="n">
         <v>280</v>
@@ -5709,13 +5709,13 @@
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AO27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ27" t="n">
         <v>5.3</v>
@@ -5724,10 +5724,10 @@
         <v>6.6</v>
       </c>
       <c r="AS27" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
         <v>8.6</v>
@@ -5736,41 +5736,41 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AY27" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AZ27" t="n">
-        <v>30</v>
+        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="BB27" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BC27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BD27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BE27" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF27" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BG27" t="n">
-        <v>12</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -5804,16 +5804,16 @@
         <v>4.3</v>
       </c>
       <c r="G28" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I28" t="n">
         <v>2.16</v>
       </c>
       <c r="J28" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="K28" t="n">
         <v>3.4</v>
@@ -5825,7 +5825,7 @@
         <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="O28" t="n">
         <v>1.47</v>
@@ -5834,13 +5834,13 @@
         <v>1.64</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
       <c r="R28" t="n">
         <v>1.23</v>
       </c>
       <c r="S28" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="T28" t="n">
         <v>2.04</v>
@@ -5852,7 +5852,7 @@
         <v>1.86</v>
       </c>
       <c r="W28" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="X28" t="n">
         <v>18.5</v>
@@ -5879,7 +5879,7 @@
         <v>65</v>
       </c>
       <c r="AF28" t="n">
-        <v>980</v>
+        <v>90</v>
       </c>
       <c r="AG28" t="n">
         <v>34</v>
@@ -5909,7 +5909,7 @@
         <v>600</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
@@ -5918,13 +5918,13 @@
         <v>10</v>
       </c>
       <c r="AS28" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
       </c>
       <c r="AU28" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV28" t="n">
         <v>6.6</v>
@@ -5933,7 +5933,7 @@
         <v>22</v>
       </c>
       <c r="AX28" t="n">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AY28" t="n">
         <v>13.5</v>
@@ -5942,10 +5942,10 @@
         <v>11.5</v>
       </c>
       <c r="BA28" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB28" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="BC28" t="n">
         <v>10.5</v>
@@ -5954,7 +5954,7 @@
         <v>10.5</v>
       </c>
       <c r="BE28" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF28" t="n">
         <v>12.5</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="G29" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H29" t="n">
         <v>4.4</v>
@@ -6007,25 +6007,25 @@
         <v>5.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K29" t="n">
         <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="M29" t="n">
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.82</v>
+        <v>2.56</v>
       </c>
       <c r="O29" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="P29" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Q29" t="n">
         <v>2.6</v>
@@ -6043,10 +6043,10 @@
         <v>1.73</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="W29" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="X29" t="n">
         <v>10.5</v>
@@ -6097,7 +6097,7 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>980</v>
       </c>
       <c r="AO29" t="n">
         <v>700</v>
@@ -6109,7 +6109,7 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AS29" t="n">
         <v>9.199999999999999</v>
@@ -6136,29 +6136,29 @@
         <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB29" t="n">
         <v>7.2</v>
       </c>
       <c r="BC29" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF29" t="n">
         <v>22</v>
       </c>
       <c r="BG29" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="G30" t="n">
         <v>2</v>
@@ -6198,22 +6198,22 @@
         <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="J30" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K30" t="n">
         <v>3.6</v>
       </c>
       <c r="L30" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M30" t="n">
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O30" t="n">
         <v>1.48</v>
@@ -6222,7 +6222,7 @@
         <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="R30" t="n">
         <v>1.22</v>
@@ -6297,16 +6297,16 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="AQ30" t="n">
         <v>11.5</v>
       </c>
       <c r="AR30" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT30" t="n">
         <v>6</v>
@@ -6315,10 +6315,10 @@
         <v>6</v>
       </c>
       <c r="AV30" t="n">
-        <v>6.2</v>
+        <v>10</v>
       </c>
       <c r="AW30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AX30" t="n">
         <v>5.6</v>
@@ -6330,10 +6330,10 @@
         <v>13</v>
       </c>
       <c r="BA30" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>7</v>
+        <v>10.5</v>
       </c>
       <c r="BC30" t="n">
         <v>13</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -6383,22 +6383,22 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="G31" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H31" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="I31" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L31" t="n">
         <v>1.45</v>
@@ -6407,37 +6407,37 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="O31" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
         <v>2.12</v>
       </c>
       <c r="R31" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T31" t="n">
         <v>2.08</v>
       </c>
       <c r="U31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V31" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="X31" t="n">
-        <v>90</v>
+        <v>26</v>
       </c>
       <c r="Y31" t="n">
         <v>1000</v>
@@ -6452,7 +6452,7 @@
         <v>13</v>
       </c>
       <c r="AC31" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="AD31" t="n">
         <v>1000</v>
@@ -6491,28 +6491,28 @@
         <v>1000</v>
       </c>
       <c r="AP31" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AQ31" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AR31" t="n">
         <v>11</v>
       </c>
       <c r="AS31" t="n">
-        <v>8.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
         <v>4.9</v>
       </c>
       <c r="AU31" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AV31" t="n">
         <v>13</v>
       </c>
       <c r="AW31" t="n">
-        <v>36</v>
+        <v>12.5</v>
       </c>
       <c r="AX31" t="n">
         <v>5.8</v>
@@ -6524,29 +6524,29 @@
         <v>14.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>4.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB31" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BC31" t="n">
         <v>10.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>2.98</v>
+        <v>10.5</v>
       </c>
       <c r="BE31" t="n">
         <v>12.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -6589,49 +6589,49 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="L32" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M32" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N32" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="O32" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P32" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S32" t="n">
         <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="V32" t="n">
         <v>1.12</v>
       </c>
       <c r="W32" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="X32" t="n">
-        <v>14.5</v>
+        <v>90</v>
       </c>
       <c r="Y32" t="n">
         <v>25</v>
@@ -6685,62 +6685,62 @@
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AQ32" t="n">
-        <v>17.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR32" t="n">
-        <v>4.3</v>
+        <v>7</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AT32" t="n">
         <v>5.5</v>
       </c>
       <c r="AU32" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AV32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AW32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX32" t="n">
         <v>6.8</v>
       </c>
       <c r="AY32" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="AZ32" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BA32" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD32" t="n">
         <v>6.8</v>
       </c>
-      <c r="BB32" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>6.2</v>
-      </c>
       <c r="BE32" t="n">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="BF32" t="n">
         <v>9.6</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -6777,34 +6777,34 @@
         <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="I33" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>3.1</v>
       </c>
       <c r="K33" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L33" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="M33" t="n">
         <v>1.12</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O33" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P33" t="n">
         <v>1.59</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.52</v>
+        <v>2.44</v>
       </c>
       <c r="R33" t="n">
         <v>1.21</v>
@@ -6813,49 +6813,49 @@
         <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U33" t="n">
         <v>1.83</v>
       </c>
       <c r="V33" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="W33" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X33" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="Y33" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="Z33" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>900</v>
+        <v>38</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC33" t="n">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="AD33" t="n">
         <v>12</v>
       </c>
       <c r="AE33" t="n">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="AF33" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="AG33" t="n">
-        <v>18.5</v>
+        <v>42</v>
       </c>
       <c r="AH33" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="AI33" t="n">
         <v>1000</v>
@@ -6864,7 +6864,7 @@
         <v>900</v>
       </c>
       <c r="AK33" t="n">
-        <v>480</v>
+        <v>1000</v>
       </c>
       <c r="AL33" t="n">
         <v>1000</v>
@@ -6876,65 +6876,65 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AS33" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AT33" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU33" t="n">
         <v>6.6</v>
       </c>
       <c r="AV33" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AW33" t="n">
-        <v>13</v>
+        <v>19.5</v>
       </c>
       <c r="AX33" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG33" t="n">
         <v>13.5</v>
       </c>
-      <c r="AY33" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>23</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>7</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -6965,46 +6965,46 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="G34" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="H34" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I34" t="n">
         <v>4.1</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K34" t="n">
         <v>3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="O34" t="n">
         <v>1.31</v>
       </c>
       <c r="P34" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T34" t="n">
         <v>1.74</v>
@@ -7013,16 +7013,16 @@
         <v>2.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W34" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X34" t="n">
         <v>90</v>
       </c>
       <c r="Y34" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="Z34" t="n">
         <v>500</v>
@@ -7079,7 +7079,7 @@
         <v>11.5</v>
       </c>
       <c r="AR34" t="n">
-        <v>7.8</v>
+        <v>11.5</v>
       </c>
       <c r="AS34" t="n">
         <v>9</v>
@@ -7094,7 +7094,7 @@
         <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>32</v>
+        <v>8.4</v>
       </c>
       <c r="AX34" t="n">
         <v>7</v>
@@ -7103,19 +7103,19 @@
         <v>6.2</v>
       </c>
       <c r="AZ34" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC34" t="n">
         <v>10.5</v>
       </c>
-      <c r="BA34" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BD34" t="n">
-        <v>8.4</v>
+        <v>15</v>
       </c>
       <c r="BE34" t="n">
         <v>9.199999999999999</v>
@@ -7124,11 +7124,11 @@
         <v>6.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -7159,64 +7159,64 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G35" t="n">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="H35" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I35" t="n">
         <v>6.8</v>
-      </c>
-      <c r="I35" t="n">
-        <v>7.2</v>
       </c>
       <c r="J35" t="n">
         <v>4.6</v>
       </c>
       <c r="K35" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L35" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M35" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P35" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="R35" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="S35" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="T35" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="U35" t="n">
         <v>2.16</v>
       </c>
       <c r="V35" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="X35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y35" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="Z35" t="n">
         <v>60</v>
@@ -7225,7 +7225,7 @@
         <v>190</v>
       </c>
       <c r="AB35" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC35" t="n">
         <v>10.5</v>
@@ -7240,61 +7240,61 @@
         <v>10</v>
       </c>
       <c r="AG35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AH35" t="n">
         <v>21</v>
       </c>
       <c r="AI35" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ35" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AK35" t="n">
         <v>15</v>
       </c>
       <c r="AL35" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM35" t="n">
         <v>100</v>
       </c>
       <c r="AN35" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AO35" t="n">
-        <v>95</v>
+        <v>130</v>
       </c>
       <c r="AP35" t="n">
         <v>20</v>
       </c>
       <c r="AQ35" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AR35" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="AS35" t="n">
-        <v>19.5</v>
+        <v>36</v>
       </c>
       <c r="AT35" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AU35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AV35" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW35" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="AX35" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AY35" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ35" t="n">
         <v>18.5</v>
@@ -7309,20 +7309,20 @@
         <v>14</v>
       </c>
       <c r="BD35" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE35" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="BF35" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG35" t="n">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -7353,22 +7353,22 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="G36" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="H36" t="n">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="I36" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="J36" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K36" t="n">
         <v>3.45</v>
-      </c>
-      <c r="K36" t="n">
-        <v>3.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.45</v>
@@ -7377,37 +7377,37 @@
         <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P36" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="R36" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="S36" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="T36" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U36" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V36" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="W36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="X36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y36" t="n">
         <v>9.6</v>
@@ -7419,104 +7419,104 @@
         <v>32</v>
       </c>
       <c r="AB36" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC36" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AF36" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AG36" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH36" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI36" t="n">
         <v>44</v>
       </c>
       <c r="AJ36" t="n">
-        <v>440</v>
+        <v>70</v>
       </c>
       <c r="AK36" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AL36" t="n">
         <v>60</v>
       </c>
       <c r="AM36" t="n">
-        <v>580</v>
+        <v>110</v>
       </c>
       <c r="AN36" t="n">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="AO36" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP36" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AR36" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AS36" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AT36" t="n">
         <v>11</v>
       </c>
       <c r="AU36" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW36" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX36" t="n">
         <v>21</v>
       </c>
       <c r="AY36" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ36" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="BB36" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="BC36" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD36" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="BE36" t="n">
         <v>48</v>
       </c>
       <c r="BF36" t="n">
-        <v>8.4</v>
+        <v>12</v>
       </c>
       <c r="BG36" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="G37" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H37" t="n">
         <v>2.88</v>
       </c>
-      <c r="H37" t="n">
-        <v>2.9</v>
-      </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J37" t="n">
         <v>3.2</v>
@@ -7571,16 +7571,16 @@
         <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="O37" t="n">
         <v>1.48</v>
       </c>
       <c r="P37" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R37" t="n">
         <v>1.24</v>
@@ -7589,22 +7589,22 @@
         <v>4.8</v>
       </c>
       <c r="T37" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="U37" t="n">
         <v>1.9</v>
       </c>
       <c r="V37" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W37" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="X37" t="n">
         <v>10.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z37" t="n">
         <v>17.5</v>
@@ -7634,7 +7634,7 @@
         <v>22</v>
       </c>
       <c r="AI37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ37" t="n">
         <v>46</v>
@@ -7649,13 +7649,13 @@
         <v>140</v>
       </c>
       <c r="AN37" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AO37" t="n">
         <v>46</v>
       </c>
       <c r="AP37" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ37" t="n">
         <v>8.800000000000001</v>
@@ -7664,10 +7664,10 @@
         <v>15.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="AT37" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU37" t="n">
         <v>6.6</v>
@@ -7685,10 +7685,10 @@
         <v>12</v>
       </c>
       <c r="AZ37" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BB37" t="n">
         <v>40</v>
@@ -7697,20 +7697,20 @@
         <v>32</v>
       </c>
       <c r="BD37" t="n">
+        <v>27</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>21</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>32</v>
+      </c>
+      <c r="BG37" t="n">
         <v>36</v>
       </c>
-      <c r="BE37" t="n">
-        <v>16</v>
-      </c>
-      <c r="BF37" t="n">
-        <v>34</v>
-      </c>
-      <c r="BG37" t="n">
-        <v>38</v>
-      </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -7741,16 +7741,16 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="G38" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H38" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="I38" t="n">
         <v>3.6</v>
-      </c>
-      <c r="I38" t="n">
-        <v>3.65</v>
       </c>
       <c r="J38" t="n">
         <v>3.25</v>
@@ -7765,13 +7765,13 @@
         <v>1.1</v>
       </c>
       <c r="N38" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O38" t="n">
         <v>1.43</v>
       </c>
       <c r="P38" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="Q38" t="n">
         <v>2.3</v>
@@ -7783,25 +7783,25 @@
         <v>4.5</v>
       </c>
       <c r="T38" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U38" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="V38" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W38" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X38" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y38" t="n">
         <v>11.5</v>
       </c>
       <c r="Z38" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA38" t="n">
         <v>70</v>
@@ -7810,10 +7810,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AC38" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD38" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE38" t="n">
         <v>48</v>
@@ -7825,16 +7825,16 @@
         <v>11.5</v>
       </c>
       <c r="AH38" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI38" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AJ38" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK38" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL38" t="n">
         <v>48</v>
@@ -7843,7 +7843,7 @@
         <v>130</v>
       </c>
       <c r="AN38" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO38" t="n">
         <v>60</v>
@@ -7855,13 +7855,13 @@
         <v>10.5</v>
       </c>
       <c r="AR38" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS38" t="n">
         <v>60</v>
       </c>
       <c r="AT38" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
@@ -7879,13 +7879,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ38" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA38" t="n">
         <v>50</v>
       </c>
       <c r="BB38" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="BC38" t="n">
         <v>25</v>
@@ -7897,14 +7897,14 @@
         <v>100</v>
       </c>
       <c r="BF38" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BG38" t="n">
         <v>50</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -7935,10 +7935,10 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G39" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H39" t="n">
         <v>4.8</v>
@@ -7974,13 +7974,13 @@
         <v>1.28</v>
       </c>
       <c r="S39" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="T39" t="n">
         <v>2.04</v>
       </c>
       <c r="U39" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V39" t="n">
         <v>1.25</v>
@@ -8040,7 +8040,7 @@
         <v>17</v>
       </c>
       <c r="AO39" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AP39" t="n">
         <v>10</v>
@@ -8061,7 +8061,7 @@
         <v>7.4</v>
       </c>
       <c r="AV39" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW39" t="n">
         <v>60</v>
@@ -8070,13 +8070,13 @@
         <v>10</v>
       </c>
       <c r="AY39" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AZ39" t="n">
         <v>20</v>
       </c>
       <c r="BA39" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="BB39" t="n">
         <v>20</v>
@@ -8088,17 +8088,17 @@
         <v>40</v>
       </c>
       <c r="BE39" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="BF39" t="n">
         <v>15.5</v>
       </c>
       <c r="BG39" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="G40" t="n">
         <v>2.16</v>
       </c>
       <c r="H40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J40" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K40" t="n">
         <v>3.5</v>
-      </c>
-      <c r="K40" t="n">
-        <v>3.55</v>
       </c>
       <c r="L40" t="n">
         <v>1.47</v>
@@ -8153,49 +8153,49 @@
         <v>1.09</v>
       </c>
       <c r="N40" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="O40" t="n">
         <v>1.38</v>
       </c>
       <c r="P40" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="R40" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="T40" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U40" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W40" t="n">
         <v>1.86</v>
       </c>
       <c r="X40" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y40" t="n">
         <v>13</v>
       </c>
       <c r="Z40" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA40" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AB40" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC40" t="n">
         <v>7.6</v>
@@ -8204,7 +8204,7 @@
         <v>16.5</v>
       </c>
       <c r="AE40" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF40" t="n">
         <v>12.5</v>
@@ -8216,7 +8216,7 @@
         <v>19.5</v>
       </c>
       <c r="AI40" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ40" t="n">
         <v>27</v>
@@ -8228,7 +8228,7 @@
         <v>40</v>
       </c>
       <c r="AM40" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN40" t="n">
         <v>19</v>
@@ -8237,7 +8237,7 @@
         <v>75</v>
       </c>
       <c r="AP40" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ40" t="n">
         <v>12</v>
@@ -8249,7 +8249,7 @@
         <v>70</v>
       </c>
       <c r="AT40" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU40" t="n">
         <v>7.2</v>
@@ -8258,7 +8258,7 @@
         <v>15</v>
       </c>
       <c r="AW40" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AX40" t="n">
         <v>11.5</v>
@@ -8267,7 +8267,7 @@
         <v>10</v>
       </c>
       <c r="AZ40" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA40" t="n">
         <v>48</v>
@@ -8282,17 +8282,17 @@
         <v>36</v>
       </c>
       <c r="BE40" t="n">
-        <v>85</v>
+        <v>29</v>
       </c>
       <c r="BF40" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BG40" t="n">
         <v>50</v>
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -8326,55 +8326,55 @@
         <v>2.14</v>
       </c>
       <c r="G41" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="H41" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="I41" t="n">
         <v>4</v>
       </c>
       <c r="J41" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K41" t="n">
         <v>3.7</v>
       </c>
       <c r="L41" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="M41" t="n">
         <v>1.08</v>
       </c>
       <c r="N41" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="R41" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S41" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="T41" t="n">
         <v>1.83</v>
       </c>
       <c r="U41" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V41" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="W41" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X41" t="n">
         <v>13</v>
@@ -8428,7 +8428,7 @@
         <v>22</v>
       </c>
       <c r="AO41" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP41" t="n">
         <v>10</v>
@@ -8437,13 +8437,13 @@
         <v>10.5</v>
       </c>
       <c r="AR41" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AS41" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT41" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="AU41" t="n">
         <v>6.6</v>
@@ -8464,7 +8464,7 @@
         <v>15.5</v>
       </c>
       <c r="BA41" t="n">
-        <v>8.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="BB41" t="n">
         <v>11.5</v>
@@ -8476,17 +8476,17 @@
         <v>32</v>
       </c>
       <c r="BE41" t="n">
-        <v>8.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BF41" t="n">
         <v>17.5</v>
       </c>
       <c r="BG41" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G42" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="H42" t="n">
         <v>5.1</v>
@@ -8529,46 +8529,46 @@
         <v>5.7</v>
       </c>
       <c r="J42" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K42" t="n">
         <v>3.7</v>
       </c>
       <c r="L42" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
         <v>1.1</v>
       </c>
       <c r="N42" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
         <v>1.43</v>
       </c>
       <c r="P42" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="R42" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="S42" t="n">
         <v>4.4</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="U42" t="n">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="V42" t="n">
         <v>1.21</v>
       </c>
       <c r="W42" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="X42" t="n">
         <v>13.5</v>
@@ -8631,22 +8631,22 @@
         <v>13</v>
       </c>
       <c r="AR42" t="n">
-        <v>7.2</v>
+        <v>16</v>
       </c>
       <c r="AS42" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AT42" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AU42" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AV42" t="n">
         <v>18</v>
       </c>
       <c r="AW42" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="AX42" t="n">
         <v>8.800000000000001</v>
@@ -8658,7 +8658,7 @@
         <v>19.5</v>
       </c>
       <c r="BA42" t="n">
-        <v>8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB42" t="n">
         <v>18</v>
@@ -8667,10 +8667,10 @@
         <v>19.5</v>
       </c>
       <c r="BD42" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="BF42" t="n">
         <v>12.5</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -8711,64 +8711,64 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="G43" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H43" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I43" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="J43" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K43" t="n">
         <v>3.05</v>
       </c>
-      <c r="K43" t="n">
-        <v>3.25</v>
-      </c>
       <c r="L43" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="M43" t="n">
         <v>1.12</v>
       </c>
       <c r="N43" t="n">
-        <v>2.84</v>
+        <v>2.64</v>
       </c>
       <c r="O43" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="P43" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="R43" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S43" t="n">
         <v>5.1</v>
       </c>
       <c r="T43" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="U43" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="V43" t="n">
-        <v>1.66</v>
+        <v>1.61</v>
       </c>
       <c r="W43" t="n">
         <v>1.36</v>
       </c>
       <c r="X43" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="Y43" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="Z43" t="n">
         <v>28</v>
@@ -8777,7 +8777,7 @@
         <v>900</v>
       </c>
       <c r="AB43" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC43" t="n">
         <v>7.4</v>
@@ -8786,10 +8786,10 @@
         <v>12.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG43" t="n">
         <v>34</v>
@@ -8798,13 +8798,13 @@
         <v>60</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ43" t="n">
         <v>1000</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="AL43" t="n">
         <v>1000</v>
@@ -8816,10 +8816,10 @@
         <v>1000</v>
       </c>
       <c r="AO43" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AP43" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ43" t="n">
         <v>6.8</v>
@@ -8852,29 +8852,29 @@
         <v>18.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BB43" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BD43" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BE43" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BF43" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="G44" t="n">
         <v>4.1</v>
@@ -8917,10 +8917,10 @@
         <v>2.42</v>
       </c>
       <c r="J44" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="K44" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="L44" t="n">
         <v>1.51</v>
@@ -8935,10 +8935,10 @@
         <v>1.44</v>
       </c>
       <c r="P44" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="R44" t="n">
         <v>1.25</v>
@@ -8947,10 +8947,10 @@
         <v>4.4</v>
       </c>
       <c r="T44" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V44" t="n">
         <v>1.7</v>
@@ -8965,34 +8965,34 @@
         <v>8.6</v>
       </c>
       <c r="Z44" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="AA44" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AB44" t="n">
         <v>13</v>
       </c>
       <c r="AC44" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AD44" t="n">
         <v>12</v>
       </c>
       <c r="AE44" t="n">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="AF44" t="n">
-        <v>75</v>
+        <v>27</v>
       </c>
       <c r="AG44" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="AH44" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="AI44" t="n">
-        <v>980</v>
+        <v>500</v>
       </c>
       <c r="AJ44" t="n">
         <v>900</v>
@@ -9010,65 +9010,65 @@
         <v>500</v>
       </c>
       <c r="AO44" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="AP44" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ44" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR44" t="n">
         <v>11</v>
       </c>
       <c r="AS44" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AT44" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AU44" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV44" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AW44" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX44" t="n">
-        <v>10.5</v>
+        <v>17</v>
       </c>
       <c r="AY44" t="n">
-        <v>8.4</v>
+        <v>14.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="BA44" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BB44" t="n">
-        <v>8.4</v>
+        <v>34</v>
       </c>
       <c r="BC44" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BD44" t="n">
-        <v>8.199999999999999</v>
+        <v>34</v>
       </c>
       <c r="BE44" t="n">
-        <v>8.800000000000001</v>
+        <v>48</v>
       </c>
       <c r="BF44" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="BG44" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9105,7 @@
         <v>1.56</v>
       </c>
       <c r="H45" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I45" t="n">
         <v>8</v>
@@ -9117,7 +9117,7 @@
         <v>4.7</v>
       </c>
       <c r="L45" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M45" t="n">
         <v>1.06</v>
@@ -9132,13 +9132,13 @@
         <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="R45" t="n">
         <v>1.37</v>
       </c>
       <c r="S45" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="T45" t="n">
         <v>2.06</v>
@@ -9150,7 +9150,7 @@
         <v>1.14</v>
       </c>
       <c r="W45" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="X45" t="n">
         <v>18.5</v>
@@ -9213,13 +9213,13 @@
         <v>19</v>
       </c>
       <c r="AR45" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AS45" t="n">
         <v>48</v>
       </c>
       <c r="AT45" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU45" t="n">
         <v>9</v>
@@ -9231,10 +9231,10 @@
         <v>40</v>
       </c>
       <c r="AX45" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="AY45" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ45" t="n">
         <v>18</v>
@@ -9249,7 +9249,7 @@
         <v>14</v>
       </c>
       <c r="BD45" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="BE45" t="n">
         <v>70</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -9293,13 +9293,13 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G46" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I46" t="n">
         <v>10.5</v>
@@ -9308,16 +9308,16 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L46" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M46" t="n">
         <v>1.06</v>
       </c>
       <c r="N46" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O46" t="n">
         <v>1.29</v>
@@ -9326,25 +9326,25 @@
         <v>2.06</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R46" t="n">
         <v>1.4</v>
       </c>
       <c r="S46" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T46" t="n">
         <v>2.18</v>
       </c>
       <c r="U46" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="V46" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W46" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="X46" t="n">
         <v>17</v>
@@ -9356,13 +9356,13 @@
         <v>90</v>
       </c>
       <c r="AA46" t="n">
-        <v>410</v>
+        <v>1000</v>
       </c>
       <c r="AB46" t="n">
         <v>7.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AD46" t="n">
         <v>38</v>
@@ -9392,25 +9392,25 @@
         <v>42</v>
       </c>
       <c r="AM46" t="n">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AN46" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO46" t="n">
         <v>250</v>
       </c>
       <c r="AP46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ46" t="n">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AR46" t="n">
         <v>13</v>
       </c>
       <c r="AS46" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT46" t="n">
         <v>6.8</v>
@@ -9422,7 +9422,7 @@
         <v>26</v>
       </c>
       <c r="AW46" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX46" t="n">
         <v>7.2</v>
@@ -9443,20 +9443,20 @@
         <v>12</v>
       </c>
       <c r="BD46" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="BE46" t="n">
         <v>34</v>
       </c>
       <c r="BF46" t="n">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="BG46" t="n">
         <v>15</v>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -9487,58 +9487,58 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="G47" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="I47" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="J47" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K47" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L47" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M47" t="n">
         <v>1.09</v>
       </c>
       <c r="N47" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="O47" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P47" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R47" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S47" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="T47" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="U47" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="V47" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="W47" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="X47" t="n">
         <v>90</v>
@@ -9553,10 +9553,10 @@
         <v>1000</v>
       </c>
       <c r="AB47" t="n">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC47" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AD47" t="n">
         <v>1000</v>
@@ -9577,7 +9577,7 @@
         <v>1000</v>
       </c>
       <c r="AJ47" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK47" t="n">
         <v>1000</v>
@@ -9595,62 +9595,62 @@
         <v>1000</v>
       </c>
       <c r="AP47" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT47" t="n">
         <v>4.4</v>
       </c>
-      <c r="AQ47" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AS47" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AT47" t="n">
-        <v>4.2</v>
-      </c>
       <c r="AU47" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AV47" t="n">
-        <v>2.64</v>
+        <v>2</v>
       </c>
       <c r="AW47" t="n">
-        <v>2.34</v>
+        <v>1.9</v>
       </c>
       <c r="AX47" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="AY47" t="n">
-        <v>3.5</v>
+        <v>1.9</v>
       </c>
       <c r="AZ47" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="BA47" t="n">
-        <v>2.34</v>
+        <v>1.86</v>
       </c>
       <c r="BB47" t="n">
-        <v>2.62</v>
+        <v>6.8</v>
       </c>
       <c r="BC47" t="n">
-        <v>2.42</v>
+        <v>1.96</v>
       </c>
       <c r="BD47" t="n">
-        <v>2.38</v>
+        <v>1.99</v>
       </c>
       <c r="BE47" t="n">
-        <v>2.4</v>
+        <v>2.04</v>
       </c>
       <c r="BF47" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="BG47" t="n">
-        <v>2.68</v>
+        <v>2.04</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -9684,7 +9684,7 @@
         <v>3.25</v>
       </c>
       <c r="G48" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="H48" t="n">
         <v>2.5</v>
@@ -9693,10 +9693,10 @@
         <v>2.64</v>
       </c>
       <c r="J48" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K48" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L48" t="n">
         <v>1.55</v>
@@ -9705,22 +9705,22 @@
         <v>1.11</v>
       </c>
       <c r="N48" t="n">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="O48" t="n">
         <v>1.49</v>
       </c>
       <c r="P48" t="n">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="R48" t="n">
         <v>1.22</v>
       </c>
       <c r="S48" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="T48" t="n">
         <v>1.98</v>
@@ -9729,13 +9729,13 @@
         <v>1.86</v>
       </c>
       <c r="V48" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="W48" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="X48" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y48" t="n">
         <v>8.6</v>
@@ -9810,7 +9810,7 @@
         <v>10.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="AX48" t="n">
         <v>19</v>
@@ -9819,32 +9819,32 @@
         <v>12</v>
       </c>
       <c r="AZ48" t="n">
-        <v>18</v>
+        <v>6.4</v>
       </c>
       <c r="BA48" t="n">
         <v>8</v>
       </c>
       <c r="BB48" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC48" t="n">
         <v>38</v>
       </c>
       <c r="BD48" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE48" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF48" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG48" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -9875,61 +9875,61 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="G49" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="H49" t="n">
         <v>5.7</v>
       </c>
       <c r="I49" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J49" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="K49" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L49" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="M49" t="n">
         <v>1.08</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O49" t="n">
         <v>1.38</v>
       </c>
       <c r="P49" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R49" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="S49" t="n">
+        <v>4</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U49" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q49" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R49" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S49" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T49" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.83</v>
-      </c>
       <c r="V49" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W49" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X49" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
         <v>1000</v>
@@ -9941,7 +9941,7 @@
         <v>1000</v>
       </c>
       <c r="AB49" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC49" t="n">
         <v>10.5</v>
@@ -9983,62 +9983,62 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AQ49" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AR49" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AS49" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD49" t="n">
         <v>4.3</v>
       </c>
-      <c r="AT49" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX49" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AY49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AZ49" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BA49" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BB49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC49" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BD49" t="n">
-        <v>4</v>
-      </c>
       <c r="BE49" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BF49" t="n">
         <v>9.6</v>
       </c>
       <c r="BG49" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -10078,16 +10078,16 @@
         <v>2.44</v>
       </c>
       <c r="I50" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="J50" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K50" t="n">
         <v>3.3</v>
       </c>
       <c r="L50" t="n">
-        <v>1.54</v>
+        <v>1.44</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
@@ -10102,13 +10102,13 @@
         <v>1.62</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R50" t="n">
         <v>1.22</v>
       </c>
       <c r="S50" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T50" t="n">
         <v>2</v>
@@ -10117,7 +10117,7 @@
         <v>1.87</v>
       </c>
       <c r="V50" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="W50" t="n">
         <v>1.39</v>
@@ -10174,7 +10174,7 @@
         <v>80</v>
       </c>
       <c r="AO50" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP50" t="n">
         <v>8.4</v>
@@ -10183,7 +10183,7 @@
         <v>7.2</v>
       </c>
       <c r="AR50" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS50" t="n">
         <v>30</v>
@@ -10198,7 +10198,7 @@
         <v>10</v>
       </c>
       <c r="AW50" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX50" t="n">
         <v>20</v>
@@ -10213,26 +10213,26 @@
         <v>6.8</v>
       </c>
       <c r="BB50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC50" t="n">
         <v>6.8</v>
       </c>
       <c r="BD50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BE50" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BF50" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BG50" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>
@@ -10266,25 +10266,25 @@
         <v>2.82</v>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H51" t="n">
         <v>2.94</v>
       </c>
       <c r="I51" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J51" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="K51" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L51" t="n">
         <v>1.58</v>
       </c>
       <c r="M51" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N51" t="n">
         <v>2.72</v>
@@ -10296,19 +10296,19 @@
         <v>1.57</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="R51" t="n">
         <v>1.2</v>
       </c>
       <c r="S51" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="T51" t="n">
         <v>1.91</v>
       </c>
       <c r="U51" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="V51" t="n">
         <v>1.47</v>
@@ -10326,7 +10326,7 @@
         <v>23</v>
       </c>
       <c r="AA51" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AB51" t="n">
         <v>8.800000000000001</v>
@@ -10365,7 +10365,7 @@
         <v>200</v>
       </c>
       <c r="AN51" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AO51" t="n">
         <v>60</v>
@@ -10389,7 +10389,7 @@
         <v>6.2</v>
       </c>
       <c r="AV51" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="AW51" t="n">
         <v>7.2</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-09 04:43:26</t>
+          <t>2026-03-09 06:53:17</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-09.xlsx
@@ -757,64 +757,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="G2" t="n">
-        <v>1.37</v>
+        <v>1.03</v>
       </c>
       <c r="H2" t="n">
-        <v>9.6</v>
+        <v>100</v>
       </c>
       <c r="I2" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>5.6</v>
+        <v>34</v>
       </c>
       <c r="K2" t="n">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L2" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.04</v>
       </c>
-      <c r="N2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="P2" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.86</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>3.65</v>
+        <v>34</v>
       </c>
       <c r="X2" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -823,104 +823,104 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AD2" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
         <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>9.199999999999999</v>
+        <v>5.3</v>
       </c>
       <c r="AG2" t="n">
-        <v>11</v>
+        <v>800</v>
       </c>
       <c r="AH2" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>13</v>
+        <v>800</v>
       </c>
       <c r="AK2" t="n">
-        <v>17</v>
+        <v>990</v>
       </c>
       <c r="AL2" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>17.5</v>
+        <v>1.55</v>
       </c>
       <c r="AQ2" t="n">
-        <v>24</v>
+        <v>1.41</v>
       </c>
       <c r="AR2" t="n">
-        <v>27</v>
+        <v>1.41</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.4</v>
+        <v>1.41</v>
       </c>
       <c r="AT2" t="n">
-        <v>7.4</v>
+        <v>1.41</v>
       </c>
       <c r="AU2" t="n">
-        <v>10.5</v>
+        <v>1.55</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>1.41</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.2</v>
+        <v>1.41</v>
       </c>
       <c r="AX2" t="n">
-        <v>7.2</v>
+        <v>1.11</v>
       </c>
       <c r="AY2" t="n">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="AZ2" t="n">
-        <v>21</v>
+        <v>1.55</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.2</v>
+        <v>2.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.6</v>
+        <v>1.41</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>1.41</v>
       </c>
       <c r="BD2" t="n">
-        <v>25</v>
+        <v>2.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>110</v>
+        <v>1.55</v>
       </c>
       <c r="BF2" t="n">
-        <v>5.4</v>
+        <v>1.24</v>
       </c>
       <c r="BG2" t="n">
-        <v>8</v>
+        <v>1.41</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -951,64 +951,64 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="G3" t="n">
-        <v>2.06</v>
+        <v>1.78</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>2.86</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="P3" t="n">
-        <v>1.62</v>
+        <v>1.98</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="R3" t="n">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="S3" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="T3" t="n">
-        <v>1.97</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
-        <v>1.8</v>
+        <v>1.99</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W3" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="X3" t="n">
-        <v>11.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="Z3" t="n">
         <v>150</v>
@@ -1017,13 +1017,13 @@
         <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
         <v>1000</v>
@@ -1032,89 +1032,89 @@
         <v>11</v>
       </c>
       <c r="AG3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AI3" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ3" t="n">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AK3" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AL3" t="n">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="AM3" t="n">
         <v>1000</v>
       </c>
       <c r="AN3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD3" t="n">
         <v>21</v>
       </c>
-      <c r="AO3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP3" t="n">
+      <c r="BE3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BF3" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>15</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>8</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>16</v>
-      </c>
       <c r="BG3" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="G4" t="n">
-        <v>3.45</v>
+        <v>2.56</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.05</v>
       </c>
-      <c r="J4" t="n">
-        <v>2.8</v>
-      </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M4" t="n">
         <v>1.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.5</v>
+        <v>1.96</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
-        <v>5.3</v>
+        <v>1.05</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V4" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="W4" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="X4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
         <v>18</v>
       </c>
-      <c r="AA4" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14.5</v>
-      </c>
       <c r="AE4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AF4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>15.5</v>
+        <v>13</v>
       </c>
       <c r="AH4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AI4" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AK4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL4" t="n">
         <v>500</v>
       </c>
-      <c r="AL4" t="n">
-        <v>240</v>
-      </c>
       <c r="AM4" t="n">
         <v>1000</v>
       </c>
       <c r="AN4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="AQ4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW4" t="n">
         <v>7</v>
       </c>
-      <c r="AR4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>22</v>
-      </c>
       <c r="AX4" t="n">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="AZ4" t="n">
-        <v>18</v>
+        <v>5.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>38</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="BC4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="BE4" t="n">
-        <v>8</v>
+        <v>140</v>
       </c>
       <c r="BF4" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1339,61 +1339,61 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="P5" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
         <v>1.23</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="V5" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="W5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="Y5" t="n">
         <v>8</v>
@@ -1402,107 +1402,107 @@
         <v>13</v>
       </c>
       <c r="AA5" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AB5" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AF5" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AG5" t="n">
         <v>16.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI5" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="AJ5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK5" t="n">
         <v>60</v>
       </c>
       <c r="AL5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AM5" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AO5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ5" t="n">
         <v>7.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS5" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AT5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>10</v>
       </c>
-      <c r="AU5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AW5" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="AX5" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AY5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA5" t="n">
         <v>46</v>
       </c>
       <c r="BB5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BD5" t="n">
         <v>60</v>
       </c>
-      <c r="BC5" t="n">
-        <v>46</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>55</v>
-      </c>
       <c r="BE5" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="BF5" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="BG5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1533,85 +1533,85 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H6" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="I6" t="n">
         <v>1.2</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="K6" t="n">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
       <c r="L6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N6" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="P6" t="n">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="T6" t="n">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="V6" t="n">
         <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
         <v>1000</v>
       </c>
       <c r="Y6" t="n">
-        <v>980</v>
+        <v>9.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA6" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
         <v>1000</v>
       </c>
       <c r="AC6" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD6" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="AG6" t="n">
         <v>1000</v>
@@ -1638,13 +1638,13 @@
         <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="AP6" t="n">
         <v>22</v>
       </c>
       <c r="AQ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR6" t="n">
         <v>6</v>
@@ -1653,50 +1653,50 @@
         <v>7</v>
       </c>
       <c r="AT6" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="n">
         <v>11.5</v>
       </c>
       <c r="AV6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW6" t="n">
         <v>7.4</v>
       </c>
-      <c r="AW6" t="n">
-        <v>8</v>
-      </c>
       <c r="AX6" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
         <v>21</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>10.5</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>11</v>
       </c>
       <c r="BE6" t="n">
-        <v>28</v>
+        <v>150</v>
       </c>
       <c r="BF6" t="n">
         <v>15</v>
       </c>
       <c r="BG6" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1727,170 +1727,170 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.4</v>
       </c>
-      <c r="K7" t="n">
-        <v>3.65</v>
-      </c>
       <c r="L7" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="M7" t="n">
         <v>1.12</v>
       </c>
       <c r="N7" t="n">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="P7" t="n">
         <v>1.58</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="R7" t="n">
         <v>1.2</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="V7" t="n">
-        <v>2.12</v>
+        <v>1.92</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X7" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Z7" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AA7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS7" t="n">
         <v>21</v>
       </c>
-      <c r="AB7" t="n">
-        <v>15</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>48</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>60</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>55</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS7" t="n">
+      <c r="AT7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV7" t="n">
         <v>10</v>
       </c>
-      <c r="AT7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="AW7" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>28</v>
       </c>
       <c r="AY7" t="n">
         <v>20</v>
       </c>
       <c r="AZ7" t="n">
-        <v>12.5</v>
+        <v>23</v>
       </c>
       <c r="BA7" t="n">
-        <v>8.6</v>
+        <v>44</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.6</v>
+        <v>55</v>
       </c>
       <c r="BC7" t="n">
-        <v>9.199999999999999</v>
+        <v>48</v>
       </c>
       <c r="BD7" t="n">
-        <v>9.4</v>
+        <v>60</v>
       </c>
       <c r="BE7" t="n">
-        <v>9.6</v>
+        <v>150</v>
       </c>
       <c r="BF7" t="n">
-        <v>9.6</v>
+        <v>16</v>
       </c>
       <c r="BG7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -1921,13 +1921,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G8" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I8" t="n">
         <v>4.5</v>
@@ -1936,10 +1936,10 @@
         <v>2.98</v>
       </c>
       <c r="K8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
@@ -1951,7 +1951,7 @@
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q8" t="n">
         <v>2.5</v>
@@ -1972,7 +1972,7 @@
         <v>1.28</v>
       </c>
       <c r="W8" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="X8" t="n">
         <v>9.4</v>
@@ -1984,7 +1984,7 @@
         <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AB8" t="n">
         <v>7.4</v>
@@ -1993,13 +1993,13 @@
         <v>7.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AF8" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2008,13 +2008,13 @@
         <v>24</v>
       </c>
       <c r="AI8" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ8" t="n">
         <v>32</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL8" t="n">
         <v>60</v>
@@ -2023,22 +2023,22 @@
         <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AO8" t="n">
         <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR8" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AS8" t="n">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AT8" t="n">
         <v>6</v>
@@ -2050,41 +2050,41 @@
         <v>15</v>
       </c>
       <c r="AW8" t="n">
-        <v>9.6</v>
+        <v>42</v>
       </c>
       <c r="AX8" t="n">
-        <v>5.8</v>
+        <v>10.5</v>
       </c>
       <c r="AY8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7.6</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="BD8" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG8" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BE8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>10</v>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2115,76 +2115,76 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="G9" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="H9" t="n">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="I9" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="L9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O9" t="n">
         <v>1.38</v>
       </c>
       <c r="P9" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="R9" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.34</v>
+        <v>2.58</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="X9" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="Y9" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="Z9" t="n">
-        <v>480</v>
+        <v>140</v>
       </c>
       <c r="AA9" t="n">
         <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AD9" t="n">
         <v>980</v>
@@ -2193,92 +2193,92 @@
         <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="AG9" t="n">
-        <v>19.5</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>180</v>
+        <v>980</v>
       </c>
       <c r="AI9" t="n">
         <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AK9" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="AL9" t="n">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="AM9" t="n">
         <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>25</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO9" t="n">
         <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AR9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="AU9" t="n">
-        <v>6.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV9" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW9" t="n">
         <v>29</v>
       </c>
       <c r="AX9" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="BB9" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC9" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BD9" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="BE9" t="n">
         <v>28</v>
       </c>
       <c r="BF9" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="BG9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2309,31 +2309,31 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="G10" t="n">
-        <v>2.82</v>
+        <v>3.25</v>
       </c>
       <c r="H10" t="n">
-        <v>2.78</v>
+        <v>2.34</v>
       </c>
       <c r="I10" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N10" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="O10" t="n">
         <v>1.31</v>
@@ -2342,7 +2342,7 @@
         <v>1.92</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="R10" t="n">
         <v>1.36</v>
@@ -2351,52 +2351,52 @@
         <v>3.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="U10" t="n">
         <v>2.14</v>
       </c>
       <c r="V10" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W10" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="X10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="Y10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AA10" t="n">
-        <v>900</v>
+        <v>42</v>
       </c>
       <c r="AB10" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AC10" t="n">
         <v>8.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE10" t="n">
-        <v>95</v>
+        <v>32</v>
       </c>
       <c r="AF10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH10" t="n">
         <v>18</v>
       </c>
-      <c r="AG10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>17.5</v>
-      </c>
       <c r="AI10" t="n">
-        <v>230</v>
+        <v>42</v>
       </c>
       <c r="AJ10" t="n">
         <v>170</v>
@@ -2405,74 +2405,74 @@
         <v>110</v>
       </c>
       <c r="AL10" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AM10" t="n">
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AO10" t="n">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="AP10" t="n">
-        <v>12.5</v>
+        <v>6.6</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10</v>
+        <v>5.1</v>
       </c>
       <c r="AR10" t="n">
-        <v>17</v>
+        <v>6.2</v>
       </c>
       <c r="AS10" t="n">
-        <v>20</v>
+        <v>7.4</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.800000000000001</v>
+        <v>5.5</v>
       </c>
       <c r="AU10" t="n">
-        <v>6.8</v>
+        <v>4.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AW10" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AX10" t="n">
-        <v>15</v>
+        <v>7.8</v>
       </c>
       <c r="AY10" t="n">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="AZ10" t="n">
-        <v>14</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA10" t="n">
-        <v>23</v>
+        <v>7.4</v>
       </c>
       <c r="BB10" t="n">
         <v>14.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>17.5</v>
+        <v>7.4</v>
       </c>
       <c r="BD10" t="n">
-        <v>18.5</v>
+        <v>6.6</v>
       </c>
       <c r="BE10" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="BF10" t="n">
-        <v>19.5</v>
+        <v>6</v>
       </c>
       <c r="BG10" t="n">
-        <v>12</v>
+        <v>5.8</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G11" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="H11" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="I11" t="n">
-        <v>1.99</v>
+        <v>1.94</v>
       </c>
       <c r="J11" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>1.63</v>
@@ -2527,7 +2527,7 @@
         <v>1.13</v>
       </c>
       <c r="N11" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
         <v>1.58</v>
@@ -2536,67 +2536,67 @@
         <v>1.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="R11" t="n">
         <v>1.18</v>
       </c>
       <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="Y11" t="n">
         <v>5.9</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V11" t="n">
-        <v>2</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>6.2</v>
       </c>
       <c r="Z11" t="n">
         <v>15</v>
       </c>
       <c r="AA11" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AB11" t="n">
         <v>26</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AD11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE11" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AF11" t="n">
-        <v>500</v>
+        <v>980</v>
       </c>
       <c r="AG11" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AH11" t="n">
         <v>60</v>
       </c>
       <c r="AI11" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="AJ11" t="n">
         <v>1000</v>
       </c>
       <c r="AK11" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AL11" t="n">
         <v>1000</v>
@@ -2611,62 +2611,62 @@
         <v>1000</v>
       </c>
       <c r="AP11" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV11" t="n">
         <v>7.4</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>7</v>
       </c>
       <c r="AW11" t="n">
         <v>22</v>
       </c>
       <c r="AX11" t="n">
-        <v>13.5</v>
+        <v>25</v>
       </c>
       <c r="AY11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BC11" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE11" t="n">
         <v>15.5</v>
       </c>
-      <c r="BD11" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BF11" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="BG11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2697,170 +2697,170 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>8</v>
+        <v>11.5</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="L12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P12" t="n">
         <v>1.52</v>
       </c>
-      <c r="M12" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.56</v>
-      </c>
       <c r="Q12" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="R12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="U12" t="n">
-        <v>1.62</v>
+        <v>1.47</v>
       </c>
       <c r="V12" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="W12" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="X12" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Z12" t="n">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="AA12" t="n">
         <v>1000</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.2</v>
+        <v>5.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AE12" t="n">
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>8.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AG12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH12" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AI12" t="n">
         <v>1000</v>
       </c>
       <c r="AJ12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AK12" t="n">
         <v>24</v>
       </c>
       <c r="AL12" t="n">
-        <v>65</v>
+        <v>140</v>
       </c>
       <c r="AM12" t="n">
         <v>1000</v>
       </c>
       <c r="AN12" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AO12" t="n">
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
-        <v>14.5</v>
+        <v>17.5</v>
       </c>
       <c r="AR12" t="n">
         <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="AU12" t="n">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AW12" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="AX12" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ12" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB12" t="n">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>7.8</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="BE12" t="n">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF12" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -2894,16 +2894,16 @@
         <v>1.39</v>
       </c>
       <c r="G13" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="H13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I13" t="n">
         <v>11.5</v>
       </c>
       <c r="J13" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="K13" t="n">
         <v>5.3</v>
@@ -2912,16 +2912,16 @@
         <v>1.43</v>
       </c>
       <c r="M13" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N13" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O13" t="n">
         <v>1.34</v>
       </c>
       <c r="P13" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
@@ -2930,46 +2930,46 @@
         <v>1.34</v>
       </c>
       <c r="S13" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="U13" t="n">
         <v>1.68</v>
       </c>
       <c r="V13" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="X13" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Z13" t="n">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="AA13" t="n">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AC13" t="n">
         <v>11.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AE13" t="n">
         <v>230</v>
       </c>
       <c r="AF13" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AG13" t="n">
         <v>10.5</v>
@@ -2981,55 +2981,55 @@
         <v>250</v>
       </c>
       <c r="AJ13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK13" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM13" t="n">
         <v>280</v>
       </c>
       <c r="AN13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AO13" t="n">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="AP13" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AQ13" t="n">
         <v>24</v>
       </c>
       <c r="AR13" t="n">
-        <v>16.5</v>
+        <v>46</v>
       </c>
       <c r="AS13" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT13" t="n">
         <v>6</v>
       </c>
       <c r="AU13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV13" t="n">
         <v>32</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY13" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ13" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA13" t="n">
         <v>18</v>
@@ -3041,20 +3041,20 @@
         <v>15</v>
       </c>
       <c r="BD13" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="BE13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BF13" t="n">
         <v>7.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.48</v>
       </c>
       <c r="G14" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="H14" t="n">
         <v>3.45</v>
       </c>
       <c r="I14" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J14" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K14" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L14" t="n">
         <v>1.54</v>
@@ -3109,22 +3109,22 @@
         <v>1.11</v>
       </c>
       <c r="N14" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="R14" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T14" t="n">
         <v>1.98</v>
@@ -3133,76 +3133,76 @@
         <v>1.94</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X14" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
         <v>22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>70</v>
       </c>
       <c r="AA14" t="n">
         <v>500</v>
       </c>
       <c r="AB14" t="n">
-        <v>14.5</v>
+        <v>8.4</v>
       </c>
       <c r="AC14" t="n">
         <v>7.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>27</v>
+        <v>15.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>250</v>
+        <v>55</v>
       </c>
       <c r="AF14" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="AG14" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="AI14" t="n">
-        <v>160</v>
+        <v>380</v>
       </c>
       <c r="AJ14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>32</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>290</v>
+      </c>
+      <c r="AM14" t="n">
         <v>500</v>
       </c>
-      <c r="AK14" t="n">
-        <v>110</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>150</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>580</v>
-      </c>
       <c r="AN14" t="n">
-        <v>600</v>
+        <v>32</v>
       </c>
       <c r="AO14" t="n">
-        <v>600</v>
+        <v>60</v>
       </c>
       <c r="AP14" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ14" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="AS14" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="n">
         <v>7.4</v>
@@ -3217,38 +3217,38 @@
         <v>20</v>
       </c>
       <c r="AX14" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AZ14" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA14" t="n">
-        <v>15.5</v>
+        <v>21</v>
       </c>
       <c r="BB14" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BC14" t="n">
         <v>15</v>
       </c>
       <c r="BD14" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="BE14" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BG14" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3279,40 +3279,40 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.66</v>
+        <v>2.28</v>
       </c>
       <c r="G15" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="H15" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
-        <v>2.94</v>
+        <v>3.15</v>
       </c>
       <c r="K15" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
         <v>1.12</v>
       </c>
       <c r="N15" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="O15" t="n">
         <v>1.53</v>
       </c>
       <c r="P15" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="R15" t="n">
         <v>1.19</v>
@@ -3321,59 +3321,59 @@
         <v>5.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="U15" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="W15" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="X15" t="n">
         <v>17.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>20</v>
+        <v>10.5</v>
       </c>
       <c r="Z15" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="AA15" t="n">
         <v>1000</v>
       </c>
       <c r="AB15" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
+        <v>17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>270</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>500</v>
+      </c>
+      <c r="AH15" t="n">
         <v>60</v>
       </c>
-      <c r="AE15" t="n">
-        <v>440</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>65</v>
-      </c>
       <c r="AI15" t="n">
-        <v>1000</v>
+        <v>380</v>
       </c>
       <c r="AJ15" t="n">
+        <v>900</v>
+      </c>
+      <c r="AK15" t="n">
         <v>500</v>
       </c>
-      <c r="AK15" t="n">
-        <v>1000</v>
-      </c>
       <c r="AL15" t="n">
         <v>1000</v>
       </c>
@@ -3387,62 +3387,62 @@
         <v>1000</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR15" t="n">
         <v>11.5</v>
       </c>
       <c r="AS15" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="AT15" t="n">
         <v>7</v>
       </c>
       <c r="AU15" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AV15" t="n">
         <v>10.5</v>
       </c>
       <c r="AW15" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA15" t="n">
         <v>6.6</v>
       </c>
-      <c r="AY15" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>9.6</v>
-      </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="BD15" t="n">
         <v>6.2</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF15" t="n">
         <v>6.6</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3473,58 +3473,58 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="H16" t="n">
-        <v>2.24</v>
+        <v>2.36</v>
       </c>
       <c r="I16" t="n">
-        <v>2.34</v>
+        <v>2.48</v>
       </c>
       <c r="J16" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M16" t="n">
         <v>1.05</v>
       </c>
       <c r="N16" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="R16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="S16" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T16" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="V16" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>23</v>
@@ -3533,67 +3533,67 @@
         <v>14.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AA16" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AB16" t="n">
         <v>18</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF16" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="AH16" t="n">
         <v>19.5</v>
       </c>
       <c r="AI16" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL16" t="n">
         <v>36</v>
       </c>
-      <c r="AJ16" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>42</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>44</v>
-      </c>
       <c r="AM16" t="n">
-        <v>90</v>
+        <v>580</v>
       </c>
       <c r="AN16" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AO16" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP16" t="n">
         <v>18</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>16</v>
       </c>
       <c r="AQ16" t="n">
         <v>10.5</v>
       </c>
       <c r="AR16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS16" t="n">
         <v>12</v>
       </c>
-      <c r="AS16" t="n">
-        <v>22</v>
-      </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AU16" t="n">
         <v>7.8</v>
@@ -3605,38 +3605,38 @@
         <v>19</v>
       </c>
       <c r="AX16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BA16" t="n">
         <v>14.5</v>
       </c>
       <c r="BB16" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BC16" t="n">
-        <v>29</v>
+        <v>15.5</v>
       </c>
       <c r="BD16" t="n">
         <v>15</v>
       </c>
       <c r="BE16" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="BF16" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG16" t="n">
         <v>11</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3667,22 +3667,22 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="G17" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="H17" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="I17" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
         <v>3.6</v>
       </c>
       <c r="K17" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L17" t="n">
         <v>1.38</v>
@@ -3691,34 +3691,34 @@
         <v>1.06</v>
       </c>
       <c r="N17" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="Q17" t="n">
         <v>1.83</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="T17" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="V17" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="X17" t="n">
         <v>19.5</v>
@@ -3727,64 +3727,64 @@
         <v>18</v>
       </c>
       <c r="Z17" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AA17" t="n">
         <v>85</v>
       </c>
       <c r="AB17" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF17" t="n">
         <v>16.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI17" t="n">
         <v>60</v>
       </c>
       <c r="AJ17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AL17" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM17" t="n">
-        <v>200</v>
+        <v>110</v>
       </c>
       <c r="AN17" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AO17" t="n">
         <v>46</v>
       </c>
       <c r="AP17" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AR17" t="n">
         <v>13.5</v>
       </c>
       <c r="AS17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT17" t="n">
         <v>9.4</v>
@@ -3793,13 +3793,13 @@
         <v>7.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>8.6</v>
+        <v>13.5</v>
       </c>
       <c r="AW17" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="AY17" t="n">
         <v>9.6</v>
@@ -3811,26 +3811,26 @@
         <v>23</v>
       </c>
       <c r="BB17" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC17" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD17" t="n">
         <v>18</v>
       </c>
       <c r="BE17" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="BF17" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -3867,19 +3867,19 @@
         <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="J18" t="n">
         <v>3.25</v>
       </c>
       <c r="K18" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3888,43 +3888,43 @@
         <v>3.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="P18" t="n">
         <v>1.84</v>
       </c>
       <c r="Q18" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S18" t="n">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="T18" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="U18" t="n">
         <v>2.04</v>
       </c>
       <c r="V18" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W18" t="n">
         <v>1.65</v>
       </c>
       <c r="X18" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y18" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Z18" t="n">
         <v>25</v>
       </c>
       <c r="AA18" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="AB18" t="n">
         <v>10.5</v>
@@ -3936,7 +3936,7 @@
         <v>16</v>
       </c>
       <c r="AE18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AF18" t="n">
         <v>16</v>
@@ -3945,7 +3945,7 @@
         <v>12.5</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI18" t="n">
         <v>55</v>
@@ -3966,10 +3966,10 @@
         <v>23</v>
       </c>
       <c r="AO18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
         <v>10</v>
@@ -3978,10 +3978,10 @@
         <v>18</v>
       </c>
       <c r="AS18" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AT18" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU18" t="n">
         <v>6.8</v>
@@ -3990,7 +3990,7 @@
         <v>12</v>
       </c>
       <c r="AW18" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AX18" t="n">
         <v>12.5</v>
@@ -3999,13 +3999,13 @@
         <v>10</v>
       </c>
       <c r="AZ18" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA18" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC18" t="n">
         <v>18</v>
@@ -4014,17 +4014,17 @@
         <v>34</v>
       </c>
       <c r="BE18" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="BF18" t="n">
         <v>18.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>7.8</v>
+        <v>16.5</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="G19" t="n">
         <v>4.2</v>
@@ -4064,7 +4064,7 @@
         <v>2.18</v>
       </c>
       <c r="I19" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="J19" t="n">
         <v>3.1</v>
@@ -4079,7 +4079,7 @@
         <v>1.11</v>
       </c>
       <c r="N19" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="O19" t="n">
         <v>1.45</v>
@@ -4091,7 +4091,7 @@
         <v>2.34</v>
       </c>
       <c r="R19" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="S19" t="n">
         <v>4.6</v>
@@ -4103,16 +4103,16 @@
         <v>1.9</v>
       </c>
       <c r="V19" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="W19" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="X19" t="n">
         <v>10.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Z19" t="n">
         <v>15.5</v>
@@ -4172,7 +4172,7 @@
         <v>11.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="AT19" t="n">
         <v>10</v>
@@ -4184,7 +4184,7 @@
         <v>9.6</v>
       </c>
       <c r="AW19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX19" t="n">
         <v>13.5</v>
@@ -4199,16 +4199,16 @@
         <v>23</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC19" t="n">
         <v>23</v>
       </c>
       <c r="BD19" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="BE19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BF19" t="n">
         <v>12.5</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4249,25 +4249,25 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="H20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="I20" t="n">
         <v>4.6</v>
       </c>
-      <c r="I20" t="n">
-        <v>4.8</v>
-      </c>
       <c r="J20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K20" t="n">
         <v>3.55</v>
       </c>
-      <c r="K20" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L20" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M20" t="n">
         <v>1.08</v>
@@ -4282,25 +4282,25 @@
         <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="R20" t="n">
         <v>1.32</v>
       </c>
       <c r="S20" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T20" t="n">
         <v>1.89</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V20" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="X20" t="n">
         <v>12.5</v>
@@ -4312,7 +4312,7 @@
         <v>32</v>
       </c>
       <c r="AA20" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB20" t="n">
         <v>8.4</v>
@@ -4321,40 +4321,40 @@
         <v>7.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AE20" t="n">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="AF20" t="n">
         <v>11.5</v>
       </c>
       <c r="AG20" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI20" t="n">
         <v>190</v>
       </c>
       <c r="AJ20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL20" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM20" t="n">
-        <v>500</v>
+        <v>120</v>
       </c>
       <c r="AN20" t="n">
         <v>16.5</v>
       </c>
       <c r="AO20" t="n">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="AP20" t="n">
         <v>11.5</v>
@@ -4363,34 +4363,34 @@
         <v>14</v>
       </c>
       <c r="AR20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU20" t="n">
         <v>7.2</v>
       </c>
       <c r="AV20" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AW20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AX20" t="n">
         <v>10.5</v>
       </c>
       <c r="AY20" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ20" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA20" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="BB20" t="n">
         <v>21</v>
@@ -4399,20 +4399,20 @@
         <v>20</v>
       </c>
       <c r="BD20" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
         <v>60</v>
       </c>
       <c r="BF20" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BG20" t="n">
         <v>30</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H21" t="n">
         <v>2.06</v>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J21" t="n">
         <v>3.65</v>
       </c>
       <c r="K21" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L21" t="n">
         <v>1.38</v>
@@ -4467,67 +4467,67 @@
         <v>1.06</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q21" t="n">
         <v>1.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="U21" t="n">
         <v>2.28</v>
       </c>
       <c r="V21" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="W21" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X21" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y21" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AA21" t="n">
         <v>25</v>
       </c>
       <c r="AB21" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AC21" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG21" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH21" t="n">
         <v>16</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>17</v>
       </c>
       <c r="AI21" t="n">
         <v>32</v>
@@ -4536,37 +4536,37 @@
         <v>80</v>
       </c>
       <c r="AK21" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM21" t="n">
         <v>85</v>
       </c>
       <c r="AN21" t="n">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="AO21" t="n">
         <v>13.5</v>
       </c>
       <c r="AP21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ21" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR21" t="n">
         <v>12</v>
       </c>
       <c r="AS21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT21" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU21" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AV21" t="n">
         <v>9.6</v>
@@ -4575,13 +4575,13 @@
         <v>18.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY21" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA21" t="n">
         <v>28</v>
@@ -4590,23 +4590,23 @@
         <v>50</v>
       </c>
       <c r="BC21" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BD21" t="n">
         <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BF21" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG21" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4640,88 +4640,88 @@
         <v>2.1</v>
       </c>
       <c r="G22" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H22" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="I22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K22" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L22" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="M22" t="n">
         <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P22" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="R22" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="T22" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="U22" t="n">
         <v>1.94</v>
       </c>
       <c r="V22" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W22" t="n">
         <v>1.84</v>
       </c>
       <c r="X22" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z22" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AA22" t="n">
         <v>1000</v>
       </c>
       <c r="AB22" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC22" t="n">
         <v>9.4</v>
       </c>
       <c r="AD22" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE22" t="n">
         <v>500</v>
       </c>
-      <c r="AE22" t="n">
-        <v>1000</v>
-      </c>
       <c r="AF22" t="n">
-        <v>500</v>
+        <v>24</v>
       </c>
       <c r="AG22" t="n">
         <v>20</v>
       </c>
       <c r="AH22" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="AI22" t="n">
         <v>190</v>
@@ -4730,7 +4730,7 @@
         <v>80</v>
       </c>
       <c r="AK22" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="AL22" t="n">
         <v>48</v>
@@ -4739,13 +4739,13 @@
         <v>1000</v>
       </c>
       <c r="AN22" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AO22" t="n">
         <v>600</v>
       </c>
       <c r="AP22" t="n">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="AQ22" t="n">
         <v>7.6</v>
@@ -4754,10 +4754,10 @@
         <v>13</v>
       </c>
       <c r="AS22" t="n">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="AT22" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
         <v>6.6</v>
@@ -4772,13 +4772,13 @@
         <v>6.6</v>
       </c>
       <c r="AY22" t="n">
-        <v>9.4</v>
+        <v>6.4</v>
       </c>
       <c r="AZ22" t="n">
         <v>10.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>7.8</v>
+        <v>28</v>
       </c>
       <c r="BB22" t="n">
         <v>13</v>
@@ -4787,20 +4787,20 @@
         <v>11.5</v>
       </c>
       <c r="BD22" t="n">
-        <v>7.4</v>
+        <v>19.5</v>
       </c>
       <c r="BE22" t="n">
         <v>28</v>
       </c>
       <c r="BF22" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BG22" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -4831,25 +4831,25 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="G23" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="H23" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="I23" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="J23" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K23" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
         <v>1.1</v>
@@ -4858,73 +4858,73 @@
         <v>3.25</v>
       </c>
       <c r="O23" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="P23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="R23" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="S23" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="T23" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="U23" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="V23" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W23" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="X23" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y23" t="n">
         <v>10.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="AA23" t="n">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB23" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AC23" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="AE23" t="n">
         <v>110</v>
       </c>
       <c r="AF23" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG23" t="n">
-        <v>26</v>
+        <v>14.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AI23" t="n">
-        <v>500</v>
+        <v>290</v>
       </c>
       <c r="AJ23" t="n">
-        <v>500</v>
+        <v>150</v>
       </c>
       <c r="AK23" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AL23" t="n">
         <v>1000</v>
@@ -4933,37 +4933,37 @@
         <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO23" t="n">
         <v>600</v>
       </c>
       <c r="AP23" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AQ23" t="n">
-        <v>5.4</v>
+        <v>8.4</v>
       </c>
       <c r="AR23" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>18.5</v>
+        <v>36</v>
       </c>
       <c r="AT23" t="n">
-        <v>9.4</v>
+        <v>5.8</v>
       </c>
       <c r="AU23" t="n">
         <v>6.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW23" t="n">
         <v>14.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY23" t="n">
         <v>11.5</v>
@@ -4972,29 +4972,29 @@
         <v>13</v>
       </c>
       <c r="BA23" t="n">
-        <v>23</v>
+        <v>7.8</v>
       </c>
       <c r="BB23" t="n">
         <v>20</v>
       </c>
       <c r="BC23" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BD23" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="BE23" t="n">
         <v>29</v>
       </c>
       <c r="BF23" t="n">
-        <v>7.8</v>
+        <v>30</v>
       </c>
       <c r="BG23" t="n">
-        <v>22</v>
+        <v>7.2</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5025,16 +5025,16 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="G24" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="H24" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I24" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J24" t="n">
         <v>3.35</v>
@@ -5049,64 +5049,64 @@
         <v>1.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="P24" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S24" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U24" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W24" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X24" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="Y24" t="n">
         <v>14</v>
       </c>
       <c r="Z24" t="n">
-        <v>980</v>
+        <v>55</v>
       </c>
       <c r="AA24" t="n">
         <v>500</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD24" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AE24" t="n">
         <v>370</v>
       </c>
       <c r="AF24" t="n">
-        <v>23</v>
+        <v>12.5</v>
       </c>
       <c r="AG24" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -5115,10 +5115,10 @@
         <v>500</v>
       </c>
       <c r="AJ24" t="n">
-        <v>980</v>
+        <v>75</v>
       </c>
       <c r="AK24" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AL24" t="n">
         <v>290</v>
@@ -5127,13 +5127,13 @@
         <v>580</v>
       </c>
       <c r="AN24" t="n">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="AO24" t="n">
         <v>600</v>
       </c>
       <c r="AP24" t="n">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AQ24" t="n">
         <v>11</v>
@@ -5142,31 +5142,31 @@
         <v>21</v>
       </c>
       <c r="AS24" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT24" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU24" t="n">
         <v>6.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AW24" t="n">
-        <v>23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY24" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AZ24" t="n">
-        <v>15</v>
+        <v>18.5</v>
       </c>
       <c r="BA24" t="n">
-        <v>46</v>
+        <v>8.6</v>
       </c>
       <c r="BB24" t="n">
         <v>20</v>
@@ -5175,20 +5175,20 @@
         <v>12</v>
       </c>
       <c r="BD24" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="BE24" t="n">
         <v>28</v>
       </c>
       <c r="BF24" t="n">
-        <v>8.199999999999999</v>
+        <v>6.6</v>
       </c>
       <c r="BG24" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5219,16 +5219,16 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="G25" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="H25" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I25" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
@@ -5240,52 +5240,52 @@
         <v>1.49</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="N25" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="O25" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P25" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q25" t="n">
         <v>2.22</v>
       </c>
       <c r="R25" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S25" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T25" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="U25" t="n">
         <v>2.04</v>
       </c>
       <c r="V25" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="W25" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X25" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="Z25" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA25" t="n">
         <v>60</v>
       </c>
       <c r="AB25" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AC25" t="n">
         <v>7.4</v>
@@ -5294,7 +5294,7 @@
         <v>13.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>55</v>
+        <v>980</v>
       </c>
       <c r="AF25" t="n">
         <v>17</v>
@@ -5303,13 +5303,13 @@
         <v>12</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI25" t="n">
         <v>60</v>
       </c>
       <c r="AJ25" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK25" t="n">
         <v>32</v>
@@ -5318,25 +5318,25 @@
         <v>48</v>
       </c>
       <c r="AM25" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN25" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO25" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AP25" t="n">
         <v>10</v>
       </c>
       <c r="AQ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AR25" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AS25" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="AT25" t="n">
         <v>8.6</v>
@@ -5345,44 +5345,44 @@
         <v>6.6</v>
       </c>
       <c r="AV25" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AW25" t="n">
-        <v>34</v>
+        <v>18.5</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AY25" t="n">
         <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BA25" t="n">
+        <v>42</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>32</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>26</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>85</v>
+      </c>
+      <c r="BF25" t="n">
         <v>23</v>
       </c>
-      <c r="BB25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>24</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>28</v>
-      </c>
-      <c r="BF25" t="n">
+      <c r="BG25" t="n">
         <v>14</v>
       </c>
-      <c r="BG25" t="n">
-        <v>19</v>
-      </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5413,13 +5413,13 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G26" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I26" t="n">
         <v>3.4</v>
@@ -5428,7 +5428,7 @@
         <v>3.95</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L26" t="n">
         <v>1.26</v>
@@ -5437,28 +5437,28 @@
         <v>1.03</v>
       </c>
       <c r="N26" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O26" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T26" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="U26" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="V26" t="n">
         <v>1.41</v>
@@ -5470,10 +5470,10 @@
         <v>80</v>
       </c>
       <c r="Y26" t="n">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="Z26" t="n">
-        <v>80</v>
+        <v>48</v>
       </c>
       <c r="AA26" t="n">
         <v>300</v>
@@ -5488,22 +5488,22 @@
         <v>15.5</v>
       </c>
       <c r="AE26" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF26" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="AG26" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
         <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AJ26" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AK26" t="n">
         <v>50</v>
@@ -5515,25 +5515,25 @@
         <v>580</v>
       </c>
       <c r="AN26" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AO26" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AP26" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
-        <v>14.5</v>
+        <v>24</v>
       </c>
       <c r="AS26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU26" t="n">
         <v>8.800000000000001</v>
@@ -5545,13 +5545,13 @@
         <v>24</v>
       </c>
       <c r="AX26" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AY26" t="n">
         <v>10</v>
       </c>
       <c r="AZ26" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BA26" t="n">
         <v>23</v>
@@ -5569,14 +5569,14 @@
         <v>27</v>
       </c>
       <c r="BF26" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG26" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5607,76 +5607,76 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="G27" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O27" t="n">
         <v>1.54</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="J27" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N27" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="O27" t="n">
-        <v>1.51</v>
       </c>
       <c r="P27" t="n">
         <v>1.56</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="R27" t="n">
         <v>1.2</v>
       </c>
       <c r="S27" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="V27" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="W27" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X27" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y27" t="n">
         <v>5.6</v>
       </c>
       <c r="Z27" t="n">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AA27" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AB27" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="AC27" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AD27" t="n">
         <v>11.5</v>
@@ -5694,40 +5694,40 @@
         <v>40</v>
       </c>
       <c r="AI27" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AJ27" t="n">
         <v>440</v>
       </c>
       <c r="AK27" t="n">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="AL27" t="n">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="AM27" t="n">
         <v>580</v>
       </c>
       <c r="AN27" t="n">
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="AO27" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AP27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AQ27" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="AR27" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AS27" t="n">
         <v>12.5</v>
       </c>
       <c r="AT27" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AU27" t="n">
         <v>8.6</v>
@@ -5736,41 +5736,41 @@
         <v>10</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AX27" t="n">
         <v>34</v>
       </c>
       <c r="AY27" t="n">
+        <v>34</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>32</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>18.5</v>
       </c>
       <c r="BA27" t="n">
         <v>28</v>
       </c>
       <c r="BB27" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BD27" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BE27" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BF27" t="n">
-        <v>6.4</v>
+        <v>15</v>
       </c>
       <c r="BG27" t="n">
-        <v>8.199999999999999</v>
+        <v>12.5</v>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5801,46 +5801,46 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G28" t="n">
         <v>4.8</v>
       </c>
       <c r="H28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I28" t="n">
         <v>2.06</v>
       </c>
-      <c r="I28" t="n">
-        <v>2.16</v>
-      </c>
       <c r="J28" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K28" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="M28" t="n">
         <v>1.11</v>
       </c>
       <c r="N28" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="P28" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="T28" t="n">
         <v>2.04</v>
@@ -5849,34 +5849,34 @@
         <v>1.89</v>
       </c>
       <c r="V28" t="n">
-        <v>1.86</v>
+        <v>1.94</v>
       </c>
       <c r="W28" t="n">
         <v>1.27</v>
       </c>
       <c r="X28" t="n">
-        <v>18.5</v>
+        <v>11</v>
       </c>
       <c r="Y28" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="Z28" t="n">
-        <v>23</v>
+        <v>11.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>900</v>
+        <v>36</v>
       </c>
       <c r="AB28" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD28" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="AE28" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AF28" t="n">
         <v>90</v>
@@ -5885,10 +5885,10 @@
         <v>34</v>
       </c>
       <c r="AH28" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="AI28" t="n">
-        <v>980</v>
+        <v>120</v>
       </c>
       <c r="AJ28" t="n">
         <v>900</v>
@@ -5906,65 +5906,65 @@
         <v>600</v>
       </c>
       <c r="AO28" t="n">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="AP28" t="n">
-        <v>5.7</v>
+        <v>9</v>
       </c>
       <c r="AQ28" t="n">
         <v>6.4</v>
       </c>
       <c r="AR28" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>16</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB28" t="n">
         <v>10</v>
       </c>
-      <c r="AS28" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>28</v>
-      </c>
       <c r="BC28" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BD28" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BE28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF28" t="n">
-        <v>12.5</v>
+        <v>10</v>
       </c>
       <c r="BG28" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -5995,37 +5995,37 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="G29" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H29" t="n">
         <v>4.4</v>
       </c>
       <c r="I29" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="J29" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="K29" t="n">
         <v>3.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="n">
         <v>1.12</v>
       </c>
       <c r="N29" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>1.52</v>
       </c>
       <c r="P29" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Q29" t="n">
         <v>2.6</v>
@@ -6049,7 +6049,7 @@
         <v>1.87</v>
       </c>
       <c r="X29" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y29" t="n">
         <v>12.5</v>
@@ -6097,7 +6097,7 @@
         <v>580</v>
       </c>
       <c r="AN29" t="n">
-        <v>980</v>
+        <v>600</v>
       </c>
       <c r="AO29" t="n">
         <v>700</v>
@@ -6109,10 +6109,10 @@
         <v>10</v>
       </c>
       <c r="AR29" t="n">
-        <v>8.4</v>
+        <v>16.5</v>
       </c>
       <c r="AS29" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT29" t="n">
         <v>5.7</v>
@@ -6124,7 +6124,7 @@
         <v>18</v>
       </c>
       <c r="AW29" t="n">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AX29" t="n">
         <v>9.4</v>
@@ -6136,29 +6136,29 @@
         <v>22</v>
       </c>
       <c r="BA29" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="BB29" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BC29" t="n">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BD29" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="BG29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -6213,10 +6213,10 @@
         <v>1.11</v>
       </c>
       <c r="N30" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="O30" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P30" t="n">
         <v>1.61</v>
@@ -6246,7 +6246,7 @@
         <v>19</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="Z30" t="n">
         <v>1000</v>
@@ -6306,7 +6306,7 @@
         <v>7.6</v>
       </c>
       <c r="AS30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AT30" t="n">
         <v>6</v>
@@ -6327,7 +6327,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA30" t="n">
         <v>7.6</v>
@@ -6342,17 +6342,17 @@
         <v>7</v>
       </c>
       <c r="BE30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF30" t="n">
         <v>6</v>
       </c>
       <c r="BG30" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -6386,16 +6386,16 @@
         <v>1.63</v>
       </c>
       <c r="G31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="H31" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I31" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K31" t="n">
         <v>4.1</v>
@@ -6407,22 +6407,22 @@
         <v>1.08</v>
       </c>
       <c r="N31" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="O31" t="n">
         <v>1.37</v>
       </c>
       <c r="P31" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R31" t="n">
         <v>1.29</v>
       </c>
       <c r="S31" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T31" t="n">
         <v>2.08</v>
@@ -6434,13 +6434,13 @@
         <v>1.15</v>
       </c>
       <c r="W31" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="X31" t="n">
         <v>26</v>
       </c>
       <c r="Y31" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z31" t="n">
         <v>1000</v>
@@ -6449,13 +6449,13 @@
         <v>1000</v>
       </c>
       <c r="AB31" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AD31" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AE31" t="n">
         <v>1000</v>
@@ -6464,7 +6464,7 @@
         <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH31" t="n">
         <v>1000</v>
@@ -6473,7 +6473,7 @@
         <v>1000</v>
       </c>
       <c r="AJ31" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AK31" t="n">
         <v>1000</v>
@@ -6503,16 +6503,16 @@
         <v>13</v>
       </c>
       <c r="AT31" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AU31" t="n">
         <v>5.6</v>
       </c>
       <c r="AV31" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX31" t="n">
         <v>5.8</v>
@@ -6521,32 +6521,32 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AZ31" t="n">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="BA31" t="n">
-        <v>12.5</v>
+        <v>36</v>
       </c>
       <c r="BB31" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC31" t="n">
         <v>10.5</v>
       </c>
       <c r="BD31" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE31" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF31" t="n">
         <v>6.8</v>
       </c>
       <c r="BG31" t="n">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -6577,64 +6577,64 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="G32" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="H32" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="I32" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="J32" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K32" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L32" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M32" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N32" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="R32" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
         <v>4.2</v>
       </c>
       <c r="T32" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="U32" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="V32" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W32" t="n">
-        <v>2.76</v>
+        <v>3</v>
       </c>
       <c r="X32" t="n">
         <v>90</v>
       </c>
       <c r="Y32" t="n">
-        <v>25</v>
+        <v>980</v>
       </c>
       <c r="Z32" t="n">
         <v>190</v>
@@ -6652,10 +6652,10 @@
         <v>980</v>
       </c>
       <c r="AE32" t="n">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AF32" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AG32" t="n">
         <v>23</v>
@@ -6664,10 +6664,10 @@
         <v>980</v>
       </c>
       <c r="AI32" t="n">
-        <v>200</v>
+        <v>230</v>
       </c>
       <c r="AJ32" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK32" t="n">
         <v>24</v>
@@ -6679,16 +6679,16 @@
         <v>1000</v>
       </c>
       <c r="AN32" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="AO32" t="n">
         <v>1000</v>
       </c>
       <c r="AP32" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="AQ32" t="n">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AR32" t="n">
         <v>7</v>
@@ -6697,50 +6697,50 @@
         <v>4.7</v>
       </c>
       <c r="AT32" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AU32" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AX32" t="n">
         <v>4.8</v>
       </c>
-      <c r="AV32" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>6.8</v>
-      </c>
       <c r="AY32" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ32" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
       <c r="BA32" t="n">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB32" t="n">
-        <v>5.7</v>
+        <v>7.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
       <c r="BD32" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE32" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BF32" t="n">
-        <v>9.6</v>
+        <v>5.1</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.7</v>
+        <v>9.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -6777,64 +6777,64 @@
         <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="J33" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K33" t="n">
         <v>3.35</v>
       </c>
       <c r="L33" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="M33" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N33" t="n">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="O33" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="P33" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="R33" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
       </c>
       <c r="T33" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="V33" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W33" t="n">
         <v>1.33</v>
       </c>
       <c r="X33" t="n">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="Y33" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="Z33" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AA33" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AB33" t="n">
         <v>11</v>
@@ -6846,22 +6846,22 @@
         <v>12</v>
       </c>
       <c r="AE33" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="AF33" t="n">
         <v>100</v>
       </c>
       <c r="AG33" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="AH33" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="AI33" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ33" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="AK33" t="n">
         <v>1000</v>
@@ -6876,25 +6876,25 @@
         <v>1000</v>
       </c>
       <c r="AO33" t="n">
-        <v>600</v>
+        <v>1000</v>
       </c>
       <c r="AP33" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ33" t="n">
         <v>6.8</v>
       </c>
       <c r="AR33" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AS33" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="AT33" t="n">
         <v>9.6</v>
       </c>
       <c r="AU33" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AV33" t="n">
         <v>10</v>
@@ -6906,35 +6906,35 @@
         <v>22</v>
       </c>
       <c r="AY33" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ33" t="n">
         <v>10.5</v>
       </c>
       <c r="BA33" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB33" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD33" t="n">
         <v>11</v>
       </c>
-      <c r="BC33" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD33" t="n">
+      <c r="BE33" t="n">
         <v>11.5</v>
       </c>
-      <c r="BE33" t="n">
-        <v>12</v>
-      </c>
       <c r="BF33" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BG33" t="n">
-        <v>13.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -6968,55 +6968,55 @@
         <v>2.14</v>
       </c>
       <c r="G34" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H34" t="n">
         <v>3.6</v>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="J34" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K34" t="n">
         <v>3.7</v>
       </c>
       <c r="L34" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="M34" t="n">
         <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="O34" t="n">
         <v>1.31</v>
       </c>
       <c r="P34" t="n">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="R34" t="n">
         <v>1.36</v>
       </c>
       <c r="S34" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="T34" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="U34" t="n">
         <v>2.1</v>
       </c>
       <c r="V34" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="X34" t="n">
         <v>90</v>
@@ -7082,10 +7082,10 @@
         <v>11.5</v>
       </c>
       <c r="AS34" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AT34" t="n">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="AU34" t="n">
         <v>6.6</v>
@@ -7094,7 +7094,7 @@
         <v>8.4</v>
       </c>
       <c r="AW34" t="n">
-        <v>8.4</v>
+        <v>32</v>
       </c>
       <c r="AX34" t="n">
         <v>7</v>
@@ -7106,7 +7106,7 @@
         <v>11</v>
       </c>
       <c r="BA34" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB34" t="n">
         <v>12</v>
@@ -7118,17 +7118,17 @@
         <v>15</v>
       </c>
       <c r="BE34" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF34" t="n">
         <v>6.6</v>
       </c>
       <c r="BG34" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -7159,154 +7159,154 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="G35" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="H35" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="I35" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="J35" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K35" t="n">
         <v>4.6</v>
       </c>
-      <c r="K35" t="n">
-        <v>4.8</v>
-      </c>
       <c r="L35" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M35" t="n">
         <v>1.05</v>
       </c>
       <c r="N35" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="O35" t="n">
         <v>1.24</v>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="S35" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="T35" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U35" t="n">
         <v>2.16</v>
       </c>
       <c r="V35" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W35" t="n">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="X35" t="n">
         <v>21</v>
       </c>
       <c r="Y35" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z35" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AA35" t="n">
-        <v>190</v>
+        <v>150</v>
       </c>
       <c r="AB35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AC35" t="n">
         <v>10.5</v>
       </c>
       <c r="AD35" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AE35" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AF35" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG35" t="n">
         <v>9.4</v>
       </c>
       <c r="AH35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI35" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ35" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK35" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AL35" t="n">
         <v>30</v>
       </c>
       <c r="AM35" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AN35" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AO35" t="n">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="AP35" t="n">
         <v>20</v>
       </c>
       <c r="AQ35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR35" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AS35" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="AT35" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU35" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AU35" t="n">
-        <v>9.6</v>
-      </c>
       <c r="AV35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW35" t="n">
         <v>65</v>
       </c>
       <c r="AX35" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY35" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ35" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BA35" t="n">
         <v>60</v>
       </c>
       <c r="BB35" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="BC35" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD35" t="n">
         <v>27</v>
@@ -7315,14 +7315,14 @@
         <v>50</v>
       </c>
       <c r="BF35" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BG35" t="n">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -7353,73 +7353,73 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G36" t="n">
         <v>3.6</v>
       </c>
       <c r="H36" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="I36" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="J36" t="n">
         <v>3.3</v>
       </c>
       <c r="K36" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L36" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M36" t="n">
         <v>1.08</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O36" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P36" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="R36" t="n">
         <v>1.31</v>
       </c>
       <c r="S36" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T36" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U36" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V36" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W36" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="X36" t="n">
         <v>12.5</v>
       </c>
       <c r="Y36" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z36" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AA36" t="n">
         <v>32</v>
       </c>
       <c r="AB36" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AC36" t="n">
         <v>7.6</v>
@@ -7428,10 +7428,10 @@
         <v>11</v>
       </c>
       <c r="AE36" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AF36" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AG36" t="n">
         <v>15</v>
@@ -7461,10 +7461,10 @@
         <v>23</v>
       </c>
       <c r="AP36" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AQ36" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AR36" t="n">
         <v>13</v>
@@ -7473,13 +7473,13 @@
         <v>28</v>
       </c>
       <c r="AT36" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU36" t="n">
         <v>7</v>
       </c>
       <c r="AV36" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AW36" t="n">
         <v>23</v>
@@ -7494,13 +7494,13 @@
         <v>16.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB36" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BC36" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD36" t="n">
         <v>40</v>
@@ -7509,14 +7509,14 @@
         <v>48</v>
       </c>
       <c r="BF36" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="BG36" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-09 06:53:17</t>
+          <t>2026-03-09 09:03:27</t>
         </is>
       </c>
     </row>
@@ -7547,64 +7547,64 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="G37" t="n">
         <v>2.86</v>
       </c>
       <c r="H37" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="I37" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="J37" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K37" t="n">
         <v>3.35</v>
       </c>
       <c r="L37" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="M37" t="n">
         <v>1.11</v>
       </c>
       <c r="N37" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="P37" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="R37" t="n">
         <v>1.24</v>
       </c>
       <c r="S37" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="T37" t="n">
         <v>1.98</v>
       </c>
       <c r="U37" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="V37" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="W37" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X37" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Y37" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="Z37" t="n">
         <v>17.5</v>
@@ -7619,10 +7619,10 @@
         <v>7.2</v>
       </c>
       <c r="AD37" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r